--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Index"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="342">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Dynamically find the order from OrderHistory page using Playwright Script logic</t>
   </si>
   <si>
-    <t>08-Apr</t>
+    <t>15-Apr</t>
   </si>
   <si>
     <t>End to End code discussed in the Section for reference</t>
@@ -85,7 +85,7 @@
     <t>End to end example of validating calendars with assertion in playwright</t>
   </si>
   <si>
-    <t>09-Apr</t>
+    <t>16-Apr</t>
   </si>
   <si>
     <t>code download</t>
@@ -109,7 +109,7 @@
     <t>Parsing API response &amp; passing token to browser local storage with Playwright</t>
   </si>
   <si>
-    <t>10-Apr</t>
+    <t>17-Apr</t>
   </si>
   <si>
     <t>Place order API to create order and bypass the flow in UI with mix of web/API</t>
@@ -127,7 +127,7 @@
     <t>How to save session storage using Playwright and inject into new Browser context</t>
   </si>
   <si>
-    <t>11-Apr</t>
+    <t>18-Apr</t>
   </si>
   <si>
     <t>How to debug the API steps in script using Visual code debugging</t>
@@ -142,7 +142,7 @@
     <t>Understand the playwright route method and its parameters in intercepting - demo</t>
   </si>
   <si>
-    <t>12-Apr</t>
+    <t>19-Apr</t>
   </si>
   <si>
     <t>How to intercept Network request calls with Playwright - Example demo</t>
@@ -166,7 +166,7 @@
     <t>Traversing rows and columns of excel worksheet with excelJS library</t>
   </si>
   <si>
-    <t>13-Apr</t>
+    <t>20-Apr</t>
   </si>
   <si>
     <t>Build Util functions to read and update excel file strategically</t>
@@ -181,7 +181,7 @@
     <t>End to end example for excel edits and upload with assertions using Playwright</t>
   </si>
   <si>
-    <t>14-Apr</t>
+    <t>21-Apr</t>
   </si>
   <si>
     <t>What is page object pattern &amp; Importance of its implementation</t>
@@ -202,7 +202,7 @@
     <t>Implementing Parameterization in running tests with different data sets</t>
   </si>
   <si>
-    <t>15-Apr</t>
+    <t>22-Apr</t>
   </si>
   <si>
     <t>How to pass test data as fixture by extend test annotation behaviour</t>
@@ -229,7 +229,7 @@
     <t>Reason for test failures - Race condition - Fix them</t>
   </si>
   <si>
-    <t>16-Apr</t>
+    <t>23-Apr</t>
   </si>
   <si>
     <t>How to tag tests and control the execution from the command line parameters</t>
@@ -256,7 +256,7 @@
     <t>Create Step Definition files and associate with Cucumber.js config file</t>
   </si>
   <si>
-    <t>17-Apr</t>
+    <t>24-Apr</t>
   </si>
   <si>
     <t>Implement Code login into StepDefinition file and run Cucumber feature files</t>
@@ -274,7 +274,7 @@
     <t>Parameterization with Scenario outline &amp; run tests Parallel in Playwright</t>
   </si>
   <si>
-    <t>18-Apr</t>
+    <t>25-Apr</t>
   </si>
   <si>
     <t>Generate HTML reports for Cucumber Playwright &amp; Rerun failed Scenarios</t>
@@ -286,7 +286,7 @@
     <t>Introduction</t>
   </si>
   <si>
-    <t>19-Apr</t>
+    <t>26-Apr</t>
   </si>
   <si>
     <t>Playwright vs Cypress</t>
@@ -319,7 +319,7 @@
     <t>Logical Operators</t>
   </si>
   <si>
-    <t>20-Apr</t>
+    <t>27-Apr</t>
   </si>
   <si>
     <t>Conditional Statements</t>
@@ -343,7 +343,7 @@
     <t>Test Execution with CLI</t>
   </si>
   <si>
-    <t>21-Apr</t>
+    <t>28-Apr</t>
   </si>
   <si>
     <t>Test Execution with UI</t>
@@ -367,7 +367,7 @@
     <t>User-Facing Locators</t>
   </si>
   <si>
-    <t>22-Apr</t>
+    <t>29-Apr</t>
   </si>
   <si>
     <t>Child Elements</t>
@@ -388,7 +388,7 @@
     <t>Auto-Waiting</t>
   </si>
   <si>
-    <t>23-Apr</t>
+    <t>30-Apr</t>
   </si>
   <si>
     <t>Timeouts</t>
@@ -406,7 +406,7 @@
     <t>Lists and Dropdowns</t>
   </si>
   <si>
-    <t>24-Apr</t>
+    <t>01-May</t>
   </si>
   <si>
     <t>Tooltips</t>
@@ -424,7 +424,7 @@
     <t>Date Picker (Part 1)</t>
   </si>
   <si>
-    <t>25-Apr</t>
+    <t>02-May</t>
   </si>
   <si>
     <t>Date Picker (Part 2)</t>
@@ -442,7 +442,7 @@
     <t>First Page Object</t>
   </si>
   <si>
-    <t>26-Apr</t>
+    <t>03-May</t>
   </si>
   <si>
     <t>Navigation Page Object</t>
@@ -463,7 +463,7 @@
     <t>Page Objects Helper Base</t>
   </si>
   <si>
-    <t>27-Apr</t>
+    <t>04-May</t>
   </si>
   <si>
     <t>What is API</t>
@@ -484,7 +484,7 @@
     <t>Intercept Browser API Response</t>
   </si>
   <si>
-    <t>28-Apr</t>
+    <t>05-May</t>
   </si>
   <si>
     <t>Sharing Authentication State</t>
@@ -505,7 +505,7 @@
     <t>Parallel Execution</t>
   </si>
   <si>
-    <t>29-Apr</t>
+    <t>06-May</t>
   </si>
   <si>
     <t>Screenshots and Videos</t>
@@ -523,9 +523,6 @@
     <t>Project Setup and Teardown</t>
   </si>
   <si>
-    <t>30-Apr</t>
-  </si>
-  <si>
     <t>Global Setup and Teardown</t>
   </si>
   <si>
@@ -544,7 +541,7 @@
     <t>Playwright with Docker Container</t>
   </si>
   <si>
-    <t>01-May</t>
+    <t>07-May</t>
   </si>
   <si>
     <t>Final Words</t>
@@ -556,31 +553,37 @@
     <t>NA</t>
   </si>
   <si>
-    <t>02-May</t>
+    <t>08-May</t>
   </si>
   <si>
     <t>Revision Day 2</t>
   </si>
   <si>
-    <t>03-May</t>
+    <t>09-May</t>
   </si>
   <si>
     <t>Revision Day 3</t>
   </si>
   <si>
-    <t>04-May</t>
+    <t>10-May</t>
   </si>
   <si>
     <t>Revision Day 4</t>
   </si>
   <si>
-    <t>05-May</t>
+    <t>11-May</t>
   </si>
   <si>
     <t>Revision Day 5</t>
   </si>
   <si>
+    <t>12-May</t>
+  </si>
+  <si>
     <t>Revision Day 6</t>
+  </si>
+  <si>
+    <t>13-May</t>
   </si>
   <si>
     <t>Notes</t>
@@ -738,7 +741,7 @@
     <t>#1 - What is TypeScript || Install Typescript || TypeScript vs JavaScript</t>
   </si>
   <si>
-    <t>23-Mar</t>
+    <t>01-Apr</t>
   </si>
   <si>
     <t>#2 - Type, Type Inference, Type Annotations in TypeScript</t>
@@ -753,7 +756,7 @@
     <t>#5 - Enum in TypeScript</t>
   </si>
   <si>
-    <t>24-Mar</t>
+    <t>02-Apr</t>
   </si>
   <si>
     <t>#6 - Union Type in TypeScript</t>
@@ -771,7 +774,7 @@
     <t>#10 - Switch Case In TypeScript || If Else vs Switch Case</t>
   </si>
   <si>
-    <t>25-Mar</t>
+    <t>03-Apr</t>
   </si>
   <si>
     <t>#11 - Loops in TypeScript || For,  For..Of,  For..In,  While,  D0-While Loops</t>
@@ -780,7 +783,7 @@
     <t>#12 - Functions in TypeScript || Anonymous Function</t>
   </si>
   <si>
-    <t>26-Mar</t>
+    <t>04-Apr</t>
   </si>
   <si>
     <t>#13 - Arrow Functions in TypeScript</t>
@@ -798,7 +801,7 @@
     <t>#1 - Playwright with TypeScript - Setup &amp; Installation | First Script</t>
   </si>
   <si>
-    <t>27-Mar</t>
+    <t>05-Apr</t>
   </si>
   <si>
     <t>#2 - Time Travel Debugging - UI Mode Feature In Playwright - Typescript</t>
@@ -810,7 +813,7 @@
     <t>#4 - Login Page Script With Playwright- TypeScript ||How To Launch Chrome, Chromium, Firefox, WebKit</t>
   </si>
   <si>
-    <t>28-Mar</t>
+    <t>06-Apr</t>
   </si>
   <si>
     <t>#5 - BrowserContext in Playwright || Handle Two different user sessions with BrowserContext</t>
@@ -822,7 +825,7 @@
     <t>#7 - Locators (ID, ClassName, Text, CSS Selector, XPath) in Playwright - Typescript</t>
   </si>
   <si>
-    <t>29-Mar</t>
+    <t>07-Apr</t>
   </si>
   <si>
     <t>#8 - Data-Test-Id or Test-Data-ID - Locate by test id in Playwright+Typescript</t>
@@ -834,7 +837,7 @@
     <t>#10 - Open Browser without Incognito Mode (Normal Mode) with Playwright</t>
   </si>
   <si>
-    <t>30-Mar</t>
+    <t>08-Apr</t>
   </si>
   <si>
     <t>#11 - Chaining Locators in Playwright + Typescript</t>
@@ -846,19 +849,13 @@
     <t>In-Progress</t>
   </si>
   <si>
-    <t>31-Mar</t>
-  </si>
-  <si>
-    <t>01-Apr</t>
-  </si>
-  <si>
-    <t>02-Apr</t>
+    <t>09-Apr</t>
   </si>
   <si>
     <t>Introduction to Playwright Features - Part 1</t>
   </si>
   <si>
-    <t>03-Apr</t>
+    <t>10-Apr</t>
   </si>
   <si>
     <t>Introduction to Playwright Features - Part 2</t>
@@ -882,7 +879,7 @@
     <t>Importance of Playwright configuration file and its details to run the tests</t>
   </si>
   <si>
-    <t>04-Apr</t>
+    <t>11-Apr</t>
   </si>
   <si>
     <t>Running Playwright tests in multiple browsers - chrome, Firefox 7 Webkit</t>
@@ -900,7 +897,7 @@
     <t>Understanding how wait mechanism works if list of elements are returned</t>
   </si>
   <si>
-    <t>05-Apr</t>
+    <t>12-Apr</t>
   </si>
   <si>
     <t>Techniques to wait dynamically for new page in Service based applications</t>
@@ -918,7 +915,7 @@
     <t>Handling Child windows &amp; Tabs with Playwright by switching browser context</t>
   </si>
   <si>
-    <t>06-Apr</t>
+    <t>13-Apr</t>
   </si>
   <si>
     <t>What is Playwright Inspector? And how to debug the playwright script</t>
@@ -936,7 +933,7 @@
     <t>Write the Script to dynamically find the product to buy from list of products</t>
   </si>
   <si>
-    <t>07-Apr</t>
+    <t>14-Apr</t>
   </si>
   <si>
     <t>Add assertions for the actions performed and implement necessary Sync steps</t>
@@ -1651,13 +1648,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="F2" s="48" t="s">
         <v>308</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="G2" s="14" t="s">
         <v>309</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>310</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>6</v>
@@ -1671,13 +1668,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F3" s="21">
         <v>1</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H3" s="17"/>
     </row>
@@ -1689,13 +1686,13 @@
         <v>2</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F4" s="21">
         <v>1</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H4" s="17"/>
     </row>
@@ -1707,13 +1704,13 @@
         <v>3</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F5" s="21">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -1731,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H6" s="17"/>
     </row>
@@ -1743,16 +1740,16 @@
         <v>5</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F7" s="21">
         <v>1</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
@@ -1763,13 +1760,13 @@
         <v>6</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F8" s="21">
         <v>2</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H8" s="17"/>
     </row>
@@ -1781,13 +1778,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F9" s="21">
         <v>2</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H9" s="17"/>
     </row>
@@ -1799,13 +1796,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F10" s="21">
         <v>3</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H10" s="17"/>
     </row>
@@ -1817,13 +1814,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F11" s="21">
         <v>3</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H11" s="17"/>
     </row>
@@ -1835,13 +1832,13 @@
         <v>10</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F12" s="21">
         <v>1</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -1853,13 +1850,13 @@
         <v>11</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F13" s="21">
         <v>3</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -1871,13 +1868,13 @@
         <v>12</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F14" s="21">
         <v>2</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H14" s="17"/>
     </row>
@@ -1889,19 +1886,19 @@
         <v>13</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F15" s="21">
         <v>3</v>
       </c>
       <c r="G15" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H15" s="49" t="s">
         <v>327</v>
       </c>
-      <c r="H15" s="49" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="33">
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="33.75">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -1909,19 +1906,19 @@
         <v>14</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F16" s="21">
         <v>1</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H16" s="49" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="33">
+        <v>329</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="33.75">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -1929,19 +1926,19 @@
         <v>15</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F17" s="21">
         <v>3</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H17" s="49" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+        <v>331</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25">
       <c r="A18" s="22"/>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -1949,17 +1946,17 @@
         <v>16</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F18" s="21">
         <v>3</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H18" s="17"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.25">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -1967,13 +1964,13 @@
         <v>17</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F19" s="21">
         <v>1</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H19" s="35"/>
     </row>
@@ -1985,17 +1982,17 @@
         <v>18</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F20" s="21">
         <v>2</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H20" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -2003,17 +2000,17 @@
         <v>19</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F21" s="21">
         <v>1</v>
       </c>
       <c r="G21" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H21" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -2021,17 +2018,17 @@
         <v>20</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F22" s="21">
         <v>1</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H22" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="57">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="47.25">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -2039,19 +2036,19 @@
         <v>21</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F23" s="21">
         <v>1</v>
       </c>
       <c r="G23" s="35" t="s">
+        <v>338</v>
+      </c>
+      <c r="H23" s="35" t="s">
         <v>339</v>
       </c>
-      <c r="H23" s="35" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="40.5">
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -2059,19 +2056,19 @@
         <v>22</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F24" s="21">
         <v>1</v>
       </c>
       <c r="G24" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+        <v>341</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -2116,7 +2113,7 @@
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="21"/>
       <c r="B1" s="35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C1" s="30"/>
       <c r="D1" s="31"/>
@@ -2129,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="31"/>
@@ -2142,7 +2139,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C3" s="30"/>
       <c r="D3" s="31"/>
@@ -2155,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="31"/>
@@ -2174,7 +2171,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="36" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B6" s="37"/>
       <c r="C6" s="38"/>
@@ -2209,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C8" s="29">
         <v>8.03</v>
@@ -2218,7 +2215,7 @@
         <v>45355</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="35"/>
@@ -2228,7 +2225,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C9" s="29">
         <v>20.56</v>
@@ -2237,7 +2234,7 @@
         <v>45355</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="35"/>
@@ -2247,7 +2244,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C10" s="29">
         <v>34.45</v>
@@ -2256,11 +2253,11 @@
         <v>45355</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="33.75">
@@ -2268,7 +2265,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C11" s="29">
         <v>32.53</v>
@@ -2277,7 +2274,7 @@
         <v>45356</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="35"/>
@@ -2287,7 +2284,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C12" s="29">
         <v>28.2</v>
@@ -2296,7 +2293,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="35"/>
@@ -2306,7 +2303,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C13" s="29">
         <v>32.09</v>
@@ -2315,7 +2312,7 @@
         <v>45357</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="35"/>
@@ -2325,7 +2322,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C14" s="29">
         <v>15.04</v>
@@ -2334,7 +2331,7 @@
         <v>45357</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="35"/>
@@ -2344,7 +2341,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C15" s="29">
         <v>29.46</v>
@@ -2353,7 +2350,7 @@
         <v>45358</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="35"/>
@@ -2363,7 +2360,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C16" s="29">
         <v>26.4</v>
@@ -2372,7 +2369,7 @@
         <v>45358</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="35"/>
@@ -2382,7 +2379,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C17" s="29">
         <v>24.52</v>
@@ -2391,7 +2388,7 @@
         <v>45359</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="35"/>
@@ -2401,7 +2398,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C18" s="29">
         <v>7.19</v>
@@ -2410,7 +2407,7 @@
         <v>45359</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="35"/>
@@ -2420,7 +2417,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C19" s="29">
         <v>13.33</v>
@@ -2429,7 +2426,7 @@
         <v>45359</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="35"/>
@@ -2439,7 +2436,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="29">
         <v>19.1</v>
@@ -2448,7 +2445,7 @@
         <v>45359</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="35"/>
@@ -2458,7 +2455,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C21" s="29">
         <v>25.43</v>
@@ -2467,7 +2464,7 @@
         <v>45360</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="35"/>
@@ -2477,7 +2474,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C22" s="29">
         <v>37.1</v>
@@ -2486,7 +2483,7 @@
         <v>45360</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="35"/>
@@ -2496,7 +2493,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C23" s="29">
         <v>19.22</v>
@@ -2505,7 +2502,7 @@
         <v>45361</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="35"/>
@@ -2515,7 +2512,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C24" s="29">
         <v>9.48</v>
@@ -2524,7 +2521,7 @@
         <v>45361</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="35"/>
@@ -2534,7 +2531,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C25" s="29">
         <v>22.52</v>
@@ -2543,10 +2540,10 @@
         <v>45361</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G25" s="35"/>
     </row>
@@ -2555,7 +2552,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C26" s="29">
         <v>10.07</v>
@@ -2564,10 +2561,10 @@
         <v>45361</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G26" s="35"/>
     </row>
@@ -2576,7 +2573,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C27" s="29">
         <v>18.28</v>
@@ -2585,10 +2582,10 @@
         <v>45362</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G27" s="35"/>
     </row>
@@ -2597,7 +2594,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C28" s="29">
         <v>16.07</v>
@@ -2606,10 +2603,10 @@
         <v>45362</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G28" s="35"/>
     </row>
@@ -2618,7 +2615,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C29" s="29">
         <v>12.29</v>
@@ -2627,10 +2624,10 @@
         <v>45362</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G29" s="35"/>
     </row>
@@ -2639,7 +2636,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C30" s="29">
         <v>13.4</v>
@@ -2648,10 +2645,10 @@
         <v>45362</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G30" s="35"/>
     </row>
@@ -2660,7 +2657,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C31" s="29">
         <v>8.25</v>
@@ -2669,10 +2666,10 @@
         <v>45363</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G31" s="35"/>
     </row>
@@ -2681,7 +2678,7 @@
         <v>25</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C32" s="29">
         <v>5.13</v>
@@ -2690,10 +2687,10 @@
         <v>45363</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G32" s="35"/>
     </row>
@@ -2702,7 +2699,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C33" s="29">
         <v>6.04</v>
@@ -2711,10 +2708,10 @@
         <v>45363</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G33" s="35"/>
     </row>
@@ -2723,7 +2720,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C34" s="29">
         <v>6.09</v>
@@ -2732,10 +2729,10 @@
         <v>45363</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G34" s="35"/>
     </row>
@@ -2744,7 +2741,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C35" s="29">
         <v>12.09</v>
@@ -2753,10 +2750,10 @@
         <v>45363</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G35" s="35"/>
     </row>
@@ -2765,7 +2762,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C36" s="29">
         <v>12.09</v>
@@ -2773,9 +2770,11 @@
       <c r="D36" s="18">
         <v>45363</v>
       </c>
-      <c r="E36" s="17"/>
+      <c r="E36" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F36" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G36" s="35"/>
     </row>
@@ -2784,7 +2783,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C37" s="29">
         <v>25.47</v>
@@ -2792,9 +2791,11 @@
       <c r="D37" s="18">
         <v>45364</v>
       </c>
-      <c r="E37" s="17"/>
+      <c r="E37" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F37" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G37" s="35"/>
     </row>
@@ -2803,7 +2804,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C38" s="29">
         <v>10.16</v>
@@ -2811,9 +2812,11 @@
       <c r="D38" s="18">
         <v>45364</v>
       </c>
-      <c r="E38" s="17"/>
+      <c r="E38" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F38" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G38" s="35"/>
     </row>
@@ -2822,7 +2825,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C39" s="29">
         <v>17.23</v>
@@ -2830,9 +2833,11 @@
       <c r="D39" s="18">
         <v>45364</v>
       </c>
-      <c r="E39" s="17"/>
+      <c r="E39" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F39" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G39" s="35"/>
     </row>
@@ -2841,7 +2846,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C40" s="29">
         <v>13.18</v>
@@ -2849,9 +2854,11 @@
       <c r="D40" s="18">
         <v>45364</v>
       </c>
-      <c r="E40" s="17"/>
+      <c r="E40" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F40" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G40" s="35"/>
     </row>
@@ -2860,7 +2867,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C41" s="29">
         <v>10.06</v>
@@ -2868,9 +2875,11 @@
       <c r="D41" s="18">
         <v>45365</v>
       </c>
-      <c r="E41" s="17"/>
+      <c r="E41" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F41" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G41" s="35"/>
     </row>
@@ -2879,7 +2888,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C42" s="29">
         <v>2.3</v>
@@ -2887,9 +2896,11 @@
       <c r="D42" s="18">
         <v>45365</v>
       </c>
-      <c r="E42" s="17"/>
+      <c r="E42" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F42" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G42" s="35"/>
     </row>
@@ -2898,7 +2909,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C43" s="29">
         <v>14.17</v>
@@ -2906,9 +2917,11 @@
       <c r="D43" s="18">
         <v>45365</v>
       </c>
-      <c r="E43" s="17"/>
+      <c r="E43" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F43" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G43" s="35"/>
     </row>
@@ -2917,7 +2930,7 @@
         <v>37</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C44" s="29">
         <v>27.06</v>
@@ -2925,9 +2938,11 @@
       <c r="D44" s="18">
         <v>45365</v>
       </c>
-      <c r="E44" s="17"/>
+      <c r="E44" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F44" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G44" s="35"/>
     </row>
@@ -2942,7 +2957,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A46" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="25"/>
@@ -2977,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C48" s="29">
         <v>17.33</v>
@@ -2987,7 +3002,7 @@
       </c>
       <c r="E48" s="17"/>
       <c r="F48" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G48" s="35"/>
     </row>
@@ -2996,7 +3011,7 @@
         <v>2</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C49" s="29">
         <v>18.21</v>
@@ -3006,7 +3021,7 @@
       </c>
       <c r="E49" s="17"/>
       <c r="F49" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G49" s="35"/>
     </row>
@@ -3015,7 +3030,7 @@
         <v>3</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C50" s="29">
         <v>13.01</v>
@@ -3025,7 +3040,7 @@
       </c>
       <c r="E50" s="17"/>
       <c r="F50" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G50" s="35"/>
     </row>
@@ -3034,7 +3049,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C51" s="29">
         <v>10.17</v>
@@ -3044,7 +3059,7 @@
       </c>
       <c r="E51" s="17"/>
       <c r="F51" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G51" s="35"/>
     </row>
@@ -3053,7 +3068,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C52" s="29">
         <v>16.56</v>
@@ -3063,7 +3078,7 @@
       </c>
       <c r="E52" s="17"/>
       <c r="F52" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G52" s="35"/>
     </row>
@@ -3072,7 +3087,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C53" s="29">
         <v>7.56</v>
@@ -3082,7 +3097,7 @@
       </c>
       <c r="E53" s="17"/>
       <c r="F53" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G53" s="35"/>
     </row>
@@ -3091,7 +3106,7 @@
         <v>7</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C54" s="29">
         <v>12.49</v>
@@ -3101,7 +3116,7 @@
       </c>
       <c r="E54" s="17"/>
       <c r="F54" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G54" s="35"/>
     </row>
@@ -3110,7 +3125,7 @@
         <v>8</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C55" s="29">
         <v>7.13</v>
@@ -3120,7 +3135,7 @@
       </c>
       <c r="E55" s="17"/>
       <c r="F55" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G55" s="35"/>
     </row>
@@ -3129,7 +3144,7 @@
         <v>9</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C56" s="29">
         <v>18.22</v>
@@ -3139,7 +3154,7 @@
       </c>
       <c r="E56" s="17"/>
       <c r="F56" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G56" s="35"/>
     </row>
@@ -3148,7 +3163,7 @@
         <v>10</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C57" s="29">
         <v>23.21</v>
@@ -3158,7 +3173,7 @@
       </c>
       <c r="E57" s="17"/>
       <c r="F57" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G57" s="35"/>
     </row>
@@ -3167,7 +3182,7 @@
         <v>11</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C58" s="29">
         <v>28.28</v>
@@ -3177,7 +3192,7 @@
       </c>
       <c r="E58" s="17"/>
       <c r="F58" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G58" s="35"/>
     </row>
@@ -3186,7 +3201,7 @@
         <v>12</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C59" s="29">
         <v>17.27</v>
@@ -3196,7 +3211,7 @@
       </c>
       <c r="E59" s="17"/>
       <c r="F59" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G59" s="35"/>
     </row>
@@ -3205,7 +3220,7 @@
         <v>13</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C60" s="29">
         <v>11.51</v>
@@ -3215,7 +3230,7 @@
       </c>
       <c r="E60" s="17"/>
       <c r="F60" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G60" s="35"/>
     </row>
@@ -3224,7 +3239,7 @@
         <v>14</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C61" s="29">
         <v>7.15</v>
@@ -3234,7 +3249,7 @@
       </c>
       <c r="E61" s="17"/>
       <c r="F61" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G61" s="35"/>
     </row>
@@ -3243,7 +3258,7 @@
         <v>15</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C62" s="29">
         <v>9.02</v>
@@ -3253,7 +3268,7 @@
       </c>
       <c r="E62" s="17"/>
       <c r="F62" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G62" s="35"/>
     </row>
@@ -3268,7 +3283,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A64" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="25"/>
@@ -3303,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C66" s="29">
         <v>26.05</v>
@@ -3313,7 +3328,7 @@
       </c>
       <c r="E66" s="17"/>
       <c r="F66" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G66" s="35"/>
     </row>
@@ -3322,7 +3337,7 @@
         <v>2</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C67" s="29">
         <v>12.51</v>
@@ -3332,7 +3347,7 @@
       </c>
       <c r="E67" s="17"/>
       <c r="F67" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G67" s="35"/>
     </row>
@@ -3341,7 +3356,7 @@
         <v>3</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C68" s="29">
         <v>13.31</v>
@@ -3351,7 +3366,7 @@
       </c>
       <c r="E68" s="17"/>
       <c r="F68" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G68" s="35"/>
     </row>
@@ -3360,7 +3375,7 @@
         <v>4</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C69" s="29">
         <v>24.56</v>
@@ -3370,7 +3385,7 @@
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G69" s="35"/>
     </row>
@@ -3379,7 +3394,7 @@
         <v>5</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C70" s="29">
         <v>18.08</v>
@@ -3389,7 +3404,7 @@
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G70" s="35"/>
     </row>
@@ -3398,7 +3413,7 @@
         <v>6</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C71" s="29">
         <v>13.55</v>
@@ -3408,7 +3423,7 @@
       </c>
       <c r="E71" s="17"/>
       <c r="F71" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G71" s="35"/>
     </row>
@@ -3417,7 +3432,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C72" s="29">
         <v>29.41</v>
@@ -3427,7 +3442,7 @@
       </c>
       <c r="E72" s="17"/>
       <c r="F72" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G72" s="35"/>
     </row>
@@ -3436,7 +3451,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C73" s="29">
         <v>10.49</v>
@@ -3446,7 +3461,7 @@
       </c>
       <c r="E73" s="17"/>
       <c r="F73" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G73" s="35"/>
     </row>
@@ -3455,7 +3470,7 @@
         <v>9</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C74" s="29">
         <v>16.02</v>
@@ -3465,7 +3480,7 @@
       </c>
       <c r="E74" s="17"/>
       <c r="F74" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G74" s="35"/>
     </row>
@@ -3474,7 +3489,7 @@
         <v>10</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C75" s="29">
         <v>10.48</v>
@@ -3484,7 +3499,7 @@
       </c>
       <c r="E75" s="17"/>
       <c r="F75" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G75" s="35"/>
     </row>
@@ -3493,7 +3508,7 @@
         <v>11</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C76" s="29">
         <v>20.49</v>
@@ -3503,7 +3518,7 @@
       </c>
       <c r="E76" s="17"/>
       <c r="F76" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G76" s="35"/>
     </row>
@@ -3553,19 +3568,19 @@
         <v>1</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C80" s="44">
-        <v>17.11954861111111</v>
+        <v>18.11943287037037</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G80" s="35"/>
     </row>
@@ -3574,17 +3589,17 @@
         <v>2</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C81" s="44">
-        <v>17.11954861111111</v>
+        <v>18.11943287037037</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
       </c>
       <c r="E81" s="19"/>
       <c r="F81" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G81" s="35"/>
     </row>
@@ -3593,10 +3608,10 @@
         <v>3</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C82" s="44">
-        <v>17.11954861111111</v>
+        <v>18.11943287037037</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -3612,17 +3627,17 @@
         <v>4</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C83" s="44">
-        <v>17.11954861111111</v>
+        <v>18.11943287037037</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
       </c>
       <c r="E83" s="19"/>
       <c r="F83" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G83" s="35"/>
     </row>
@@ -3631,7 +3646,7 @@
         <v>5</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C84" s="29">
         <v>10.13</v>
@@ -3641,7 +3656,7 @@
       </c>
       <c r="E84" s="17"/>
       <c r="F84" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G84" s="35"/>
     </row>
@@ -3650,7 +3665,7 @@
         <v>6</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C85" s="29">
         <v>9.05</v>
@@ -3660,7 +3675,7 @@
       </c>
       <c r="E85" s="17"/>
       <c r="F85" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G85" s="35"/>
     </row>
@@ -3669,7 +3684,7 @@
         <v>7</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C86" s="29">
         <v>3.39</v>
@@ -3679,7 +3694,7 @@
       </c>
       <c r="E86" s="17"/>
       <c r="F86" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G86" s="35"/>
     </row>
@@ -3688,7 +3703,7 @@
         <v>8</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C87" s="29">
         <v>8.27</v>
@@ -3698,7 +3713,7 @@
       </c>
       <c r="E87" s="17"/>
       <c r="F87" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G87" s="35"/>
     </row>
@@ -3707,7 +3722,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C88" s="29">
         <v>7.21</v>
@@ -3717,7 +3732,7 @@
       </c>
       <c r="E88" s="17"/>
       <c r="F88" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G88" s="35"/>
     </row>
@@ -3726,7 +3741,7 @@
         <v>10</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C89" s="29">
         <v>9.04</v>
@@ -3736,7 +3751,7 @@
       </c>
       <c r="E89" s="17"/>
       <c r="F89" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G89" s="35"/>
     </row>
@@ -3745,7 +3760,7 @@
         <v>11</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C90" s="29">
         <v>14.14</v>
@@ -3755,7 +3770,7 @@
       </c>
       <c r="E90" s="17"/>
       <c r="F90" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G90" s="35"/>
     </row>
@@ -3764,7 +3779,7 @@
         <v>12</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C91" s="29">
         <v>14.01</v>
@@ -3774,7 +3789,7 @@
       </c>
       <c r="E91" s="17"/>
       <c r="F91" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G91" s="35"/>
     </row>
@@ -3783,7 +3798,7 @@
         <v>13</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C92" s="29">
         <v>11.17</v>
@@ -3793,7 +3808,7 @@
       </c>
       <c r="E92" s="17"/>
       <c r="F92" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G92" s="35"/>
     </row>
@@ -3802,7 +3817,7 @@
         <v>14</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C93" s="15">
         <v>12</v>
@@ -3812,7 +3827,7 @@
       </c>
       <c r="E93" s="17"/>
       <c r="F93" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G93" s="35"/>
     </row>
@@ -3821,7 +3836,7 @@
         <v>15</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C94" s="29">
         <v>12.33</v>
@@ -3831,7 +3846,7 @@
       </c>
       <c r="E94" s="17"/>
       <c r="F94" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G94" s="35"/>
     </row>
@@ -3840,7 +3855,7 @@
         <v>16</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C95" s="29">
         <v>10.57</v>
@@ -3850,7 +3865,7 @@
       </c>
       <c r="E95" s="17"/>
       <c r="F95" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G95" s="35"/>
     </row>
@@ -3859,7 +3874,7 @@
         <v>17</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C96" s="29">
         <v>10.13</v>
@@ -3869,7 +3884,7 @@
       </c>
       <c r="E96" s="18"/>
       <c r="F96" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G96" s="35"/>
     </row>
@@ -3878,7 +3893,7 @@
         <v>18</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C97" s="29">
         <v>17.37</v>
@@ -3888,7 +3903,7 @@
       </c>
       <c r="E97" s="18"/>
       <c r="F97" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G97" s="35"/>
     </row>
@@ -3897,7 +3912,7 @@
         <v>19</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C98" s="29">
         <v>9.28</v>
@@ -3907,7 +3922,7 @@
       </c>
       <c r="E98" s="18"/>
       <c r="F98" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G98" s="35"/>
     </row>
@@ -3916,7 +3931,7 @@
         <v>20</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C99" s="29">
         <v>7.18</v>
@@ -3926,7 +3941,7 @@
       </c>
       <c r="E99" s="18"/>
       <c r="F99" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G99" s="35"/>
     </row>
@@ -3935,7 +3950,7 @@
         <v>21</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C100" s="29">
         <v>7.54</v>
@@ -3945,7 +3960,7 @@
       </c>
       <c r="E100" s="18"/>
       <c r="F100" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G100" s="35"/>
     </row>
@@ -3954,7 +3969,7 @@
         <v>22</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C101" s="29">
         <v>25.46</v>
@@ -3964,7 +3979,7 @@
       </c>
       <c r="E101" s="18"/>
       <c r="F101" s="17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G101" s="35"/>
     </row>
@@ -3973,7 +3988,7 @@
         <v>23</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C102" s="29">
         <v>8.47</v>
@@ -3983,7 +3998,7 @@
       </c>
       <c r="E102" s="18"/>
       <c r="F102" s="17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G102" s="35"/>
     </row>
@@ -3992,7 +4007,7 @@
         <v>24</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C103" s="29">
         <v>5.43</v>
@@ -4002,7 +4017,7 @@
       </c>
       <c r="E103" s="18"/>
       <c r="F103" s="17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G103" s="35"/>
     </row>
@@ -4011,7 +4026,7 @@
         <v>25</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C104" s="29">
         <v>12.35</v>
@@ -4021,7 +4036,7 @@
       </c>
       <c r="E104" s="18"/>
       <c r="F104" s="17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G104" s="35"/>
     </row>
@@ -4030,7 +4045,7 @@
         <v>26</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C105" s="29">
         <v>4.06</v>
@@ -4040,7 +4055,7 @@
       </c>
       <c r="E105" s="18"/>
       <c r="F105" s="17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G105" s="35"/>
     </row>
@@ -4049,7 +4064,7 @@
         <v>27</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C106" s="29">
         <v>14.59</v>
@@ -4059,7 +4074,7 @@
       </c>
       <c r="E106" s="18"/>
       <c r="F106" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G106" s="35"/>
     </row>
@@ -4068,7 +4083,7 @@
         <v>28</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C107" s="29">
         <v>18.2</v>
@@ -4078,7 +4093,7 @@
       </c>
       <c r="E107" s="18"/>
       <c r="F107" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G107" s="35"/>
     </row>
@@ -4087,7 +4102,7 @@
         <v>29</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C108" s="29">
         <v>13.41</v>
@@ -4097,7 +4112,7 @@
       </c>
       <c r="E108" s="18"/>
       <c r="F108" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G108" s="35"/>
     </row>
@@ -4106,7 +4121,7 @@
         <v>30</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C109" s="29">
         <v>11.59</v>
@@ -4116,7 +4131,7 @@
       </c>
       <c r="E109" s="18"/>
       <c r="F109" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G109" s="35"/>
     </row>
@@ -4990,7 +5005,7 @@
     <col min="3" max="3" style="33" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="34" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="24" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="24" width="9.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="24" width="16.433571428571426" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -6525,7 +6540,7 @@
         <v>45395</v>
       </c>
       <c r="E82" s="17"/>
-      <c r="F82" s="17" t="s">
+      <c r="F82" s="19" t="s">
         <v>99</v>
       </c>
       <c r="G82" s="2"/>
@@ -6544,7 +6559,7 @@
         <v>45395</v>
       </c>
       <c r="E83" s="17"/>
-      <c r="F83" s="17" t="s">
+      <c r="F83" s="19" t="s">
         <v>99</v>
       </c>
       <c r="G83" s="2"/>
@@ -6563,7 +6578,7 @@
         <v>45395</v>
       </c>
       <c r="E84" s="17"/>
-      <c r="F84" s="17" t="s">
+      <c r="F84" s="19" t="s">
         <v>99</v>
       </c>
       <c r="G84" s="2"/>
@@ -6582,7 +6597,7 @@
         <v>45395</v>
       </c>
       <c r="E85" s="17"/>
-      <c r="F85" s="17" t="s">
+      <c r="F85" s="19" t="s">
         <v>99</v>
       </c>
       <c r="G85" s="2"/>
@@ -6601,7 +6616,7 @@
         <v>45395</v>
       </c>
       <c r="E86" s="17"/>
-      <c r="F86" s="17" t="s">
+      <c r="F86" s="19" t="s">
         <v>99</v>
       </c>
       <c r="G86" s="2"/>
@@ -6620,7 +6635,7 @@
         <v>45395</v>
       </c>
       <c r="E87" s="17"/>
-      <c r="F87" s="17" t="s">
+      <c r="F87" s="19" t="s">
         <v>99</v>
       </c>
       <c r="G87" s="2"/>
@@ -7628,7 +7643,7 @@
       </c>
       <c r="E140" s="17"/>
       <c r="F140" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G140" s="2"/>
     </row>
@@ -7637,7 +7652,7 @@
         <v>70</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C141" s="29">
         <v>12.49</v>
@@ -7647,7 +7662,7 @@
       </c>
       <c r="E141" s="17"/>
       <c r="F141" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G141" s="2"/>
     </row>
@@ -7656,7 +7671,7 @@
         <v>71</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C142" s="29">
         <v>3.5</v>
@@ -7666,7 +7681,7 @@
       </c>
       <c r="E142" s="17"/>
       <c r="F142" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G142" s="2"/>
     </row>
@@ -7675,7 +7690,7 @@
         <v>72</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C143" s="29">
         <v>7.54</v>
@@ -7685,7 +7700,7 @@
       </c>
       <c r="E143" s="17"/>
       <c r="F143" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G143" s="2"/>
     </row>
@@ -7694,7 +7709,7 @@
         <v>73</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C144" s="29">
         <v>6.43</v>
@@ -7704,7 +7719,7 @@
       </c>
       <c r="E144" s="17"/>
       <c r="F144" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G144" s="2"/>
     </row>
@@ -7713,7 +7728,7 @@
         <v>74</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C145" s="29">
         <v>9.41</v>
@@ -7723,7 +7738,7 @@
       </c>
       <c r="E145" s="17"/>
       <c r="F145" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G145" s="2"/>
     </row>
@@ -7732,7 +7747,7 @@
         <v>75</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C146" s="29">
         <v>19.37</v>
@@ -7742,7 +7757,7 @@
       </c>
       <c r="E146" s="17"/>
       <c r="F146" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G146" s="2"/>
     </row>
@@ -7751,7 +7766,7 @@
         <v>76</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C147" s="29">
         <v>0.56</v>
@@ -7761,7 +7776,7 @@
       </c>
       <c r="E147" s="17"/>
       <c r="F147" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G147" s="2"/>
     </row>
@@ -7770,17 +7785,17 @@
         <v>77</v>
       </c>
       <c r="B148" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C148" s="32" t="s">
         <v>176</v>
-      </c>
-      <c r="C148" s="32" t="s">
-        <v>177</v>
       </c>
       <c r="D148" s="18">
         <v>45407</v>
       </c>
       <c r="E148" s="17"/>
       <c r="F148" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G148" s="2"/>
     </row>
@@ -7789,17 +7804,17 @@
         <v>78</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C149" s="32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D149" s="18">
         <v>45408</v>
       </c>
       <c r="E149" s="17"/>
       <c r="F149" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G149" s="2"/>
     </row>
@@ -7808,17 +7823,17 @@
         <v>79</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C150" s="32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D150" s="18">
         <v>45409</v>
       </c>
       <c r="E150" s="17"/>
       <c r="F150" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G150" s="2"/>
     </row>
@@ -7827,17 +7842,17 @@
         <v>80</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C151" s="32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D151" s="18">
         <v>45410</v>
       </c>
       <c r="E151" s="17"/>
       <c r="F151" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G151" s="2"/>
     </row>
@@ -7846,17 +7861,17 @@
         <v>81</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C152" s="32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D152" s="18">
         <v>45411</v>
       </c>
       <c r="E152" s="17"/>
       <c r="F152" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G152" s="2"/>
     </row>
@@ -7868,14 +7883,14 @@
         <v>186</v>
       </c>
       <c r="C153" s="32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D153" s="18">
         <v>45412</v>
       </c>
       <c r="E153" s="17"/>
       <c r="F153" s="17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G153" s="2"/>
     </row>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Index"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="342">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -3000,7 +3000,9 @@
       <c r="D48" s="18">
         <v>45366</v>
       </c>
-      <c r="E48" s="17"/>
+      <c r="E48" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F48" s="17" t="s">
         <v>239</v>
       </c>
@@ -3019,7 +3021,9 @@
       <c r="D49" s="18">
         <v>45366</v>
       </c>
-      <c r="E49" s="17"/>
+      <c r="E49" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F49" s="17" t="s">
         <v>239</v>
       </c>
@@ -3571,7 +3575,7 @@
         <v>273</v>
       </c>
       <c r="C80" s="44">
-        <v>18.11943287037037</v>
+        <v>19.11931712962963</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -3592,7 +3596,7 @@
         <v>273</v>
       </c>
       <c r="C81" s="44">
-        <v>18.11943287037037</v>
+        <v>19.11931712962963</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -3611,7 +3615,7 @@
         <v>273</v>
       </c>
       <c r="C82" s="44">
-        <v>18.11943287037037</v>
+        <v>19.11931712962963</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -3630,7 +3634,7 @@
         <v>273</v>
       </c>
       <c r="C83" s="44">
-        <v>18.11943287037037</v>
+        <v>19.11931712962963</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
@@ -6469,7 +6473,7 @@
       </c>
       <c r="G78" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="15">
         <v>8</v>
       </c>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="G79" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="15">
         <v>9</v>
       </c>
@@ -6507,7 +6511,7 @@
       </c>
       <c r="G80" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
       <c r="A81" s="15">
         <v>10</v>
       </c>
@@ -6526,7 +6530,7 @@
       </c>
       <c r="G81" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="15">
         <v>11</v>
       </c>
@@ -6545,7 +6549,7 @@
       </c>
       <c r="G82" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
       <c r="A83" s="15">
         <v>12</v>
       </c>
@@ -6564,7 +6568,7 @@
       </c>
       <c r="G83" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
       <c r="A84" s="15">
         <v>13</v>
       </c>
@@ -6583,7 +6587,7 @@
       </c>
       <c r="G84" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
       <c r="A85" s="15">
         <v>14</v>
       </c>
@@ -6602,7 +6606,7 @@
       </c>
       <c r="G85" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
       <c r="A86" s="15">
         <v>15</v>
       </c>
@@ -6621,7 +6625,7 @@
       </c>
       <c r="G86" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="15">
         <v>16</v>
       </c>
@@ -6640,7 +6644,7 @@
       </c>
       <c r="G87" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="15">
         <v>17</v>
       </c>
@@ -6659,7 +6663,7 @@
       </c>
       <c r="G88" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
       <c r="A89" s="15">
         <v>18</v>
       </c>
@@ -6678,7 +6682,7 @@
       </c>
       <c r="G89" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
       <c r="A90" s="15">
         <v>19</v>
       </c>
@@ -6697,7 +6701,7 @@
       </c>
       <c r="G90" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
       <c r="A91" s="15">
         <v>20</v>
       </c>
@@ -6716,7 +6720,7 @@
       </c>
       <c r="G91" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
       <c r="A92" s="15">
         <v>21</v>
       </c>
@@ -6735,7 +6739,7 @@
       </c>
       <c r="G92" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
       <c r="A93" s="15">
         <v>22</v>
       </c>
@@ -6754,7 +6758,7 @@
       </c>
       <c r="G93" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
       <c r="A94" s="15">
         <v>23</v>
       </c>
@@ -6773,7 +6777,7 @@
       </c>
       <c r="G94" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="15">
         <v>24</v>
       </c>
@@ -6792,7 +6796,7 @@
       </c>
       <c r="G95" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
       <c r="A96" s="15">
         <v>25</v>
       </c>
@@ -6811,7 +6815,7 @@
       </c>
       <c r="G96" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
       <c r="A97" s="15">
         <v>26</v>
       </c>
@@ -6830,7 +6834,7 @@
       </c>
       <c r="G97" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="19.5">
       <c r="A98" s="15">
         <v>27</v>
       </c>
@@ -6849,7 +6853,7 @@
       </c>
       <c r="G98" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="19.5">
       <c r="A99" s="15">
         <v>28</v>
       </c>
@@ -6868,7 +6872,7 @@
       </c>
       <c r="G99" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="19.5">
       <c r="A100" s="15">
         <v>29</v>
       </c>
@@ -6887,7 +6891,7 @@
       </c>
       <c r="G100" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="19.5">
       <c r="A101" s="15">
         <v>30</v>
       </c>
@@ -6906,7 +6910,7 @@
       </c>
       <c r="G101" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="19.5">
       <c r="A102" s="15">
         <v>31</v>
       </c>
@@ -6925,7 +6929,7 @@
       </c>
       <c r="G102" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="19.5">
       <c r="A103" s="15">
         <v>32</v>
       </c>
@@ -6944,7 +6948,7 @@
       </c>
       <c r="G103" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="19.5">
       <c r="A104" s="15">
         <v>33</v>
       </c>
@@ -6963,7 +6967,7 @@
       </c>
       <c r="G104" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="19.5">
       <c r="A105" s="15">
         <v>34</v>
       </c>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="343">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -1050,6 +1050,9 @@
   </si>
   <si>
     <t>https://www.udemy.com/course/javascript-and-nodejs-essentials-for-test-automation</t>
+  </si>
+  <si>
+    <t>Learn Chat GPT</t>
   </si>
 </sst>
 </file>
@@ -2072,10 +2075,18 @@
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="35"/>
+      <c r="D25" s="48">
+        <v>23</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="F25" s="21">
+        <v>1</v>
+      </c>
+      <c r="G25" s="35" t="s">
+        <v>314</v>
+      </c>
       <c r="H25" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
@@ -3042,7 +3053,9 @@
       <c r="D50" s="18">
         <v>45366</v>
       </c>
-      <c r="E50" s="17"/>
+      <c r="E50" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F50" s="17" t="s">
         <v>239</v>
       </c>
@@ -3061,13 +3074,15 @@
       <c r="D51" s="18">
         <v>45366</v>
       </c>
-      <c r="E51" s="17"/>
+      <c r="E51" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F51" s="17" t="s">
         <v>239</v>
       </c>
       <c r="G51" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="15">
         <v>5</v>
       </c>
@@ -3080,13 +3095,15 @@
       <c r="D52" s="18">
         <v>45367</v>
       </c>
-      <c r="E52" s="17"/>
+      <c r="E52" s="17" t="s">
+        <v>194</v>
+      </c>
       <c r="F52" s="17" t="s">
         <v>244</v>
       </c>
       <c r="G52" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="15">
         <v>6</v>
       </c>
@@ -3575,7 +3592,7 @@
         <v>273</v>
       </c>
       <c r="C80" s="44">
-        <v>19.11931712962963</v>
+        <v>20.11920138888889</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -3596,7 +3613,7 @@
         <v>273</v>
       </c>
       <c r="C81" s="44">
-        <v>19.11931712962963</v>
+        <v>20.11920138888889</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -3615,7 +3632,7 @@
         <v>273</v>
       </c>
       <c r="C82" s="44">
-        <v>19.11931712962963</v>
+        <v>20.11920138888889</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -3634,7 +3651,7 @@
         <v>273</v>
       </c>
       <c r="C83" s="44">
-        <v>19.11931712962963</v>
+        <v>20.11920138888889</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="359">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>19-May</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>End to End code discussed in the Section for reference</t>
@@ -1163,15 +1160,15 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1223,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="54">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1303,8 +1300,8 @@
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1312,14 +1309,11 @@
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1335,6 +1329,9 @@
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1378,17 +1375,8 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1701,7 +1689,7 @@
     <col min="1" max="1" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="56" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="53" width="6.719285714285714" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="50" width="38.86214285714286" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="23" width="7.719285714285714" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="50" width="23.862142857142857" customWidth="1" bestFit="1"/>
@@ -1726,13 +1714,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>320</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="G2" s="14" t="s">
         <v>321</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>322</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>6</v>
@@ -1746,13 +1734,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F3" s="21">
         <v>1</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H3" s="17"/>
     </row>
@@ -1764,16 +1752,16 @@
         <v>2</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F4" s="21">
         <v>1</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -1784,13 +1772,13 @@
         <v>3</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5" s="21">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -1808,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H6" s="17"/>
     </row>
@@ -1820,16 +1808,16 @@
         <v>5</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F7" s="21">
         <v>1</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
@@ -1840,13 +1828,13 @@
         <v>6</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F8" s="21">
         <v>2</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H8" s="17"/>
     </row>
@@ -1858,13 +1846,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F9" s="21">
         <v>2</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H9" s="17"/>
     </row>
@@ -1876,13 +1864,13 @@
         <v>8</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F10" s="21">
         <v>3</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H10" s="17"/>
     </row>
@@ -1894,13 +1882,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F11" s="21">
         <v>3</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H11" s="17"/>
     </row>
@@ -1912,13 +1900,13 @@
         <v>10</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F12" s="21">
         <v>1</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -1930,13 +1918,13 @@
         <v>11</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F13" s="21">
         <v>3</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -1948,13 +1936,13 @@
         <v>12</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F14" s="21">
         <v>2</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H14" s="17"/>
     </row>
@@ -1966,16 +1954,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F15" s="21">
         <v>3</v>
       </c>
       <c r="G15" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="H15" s="52" t="s">
         <v>340</v>
-      </c>
-      <c r="H15" s="52" t="s">
-        <v>341</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="33.75">
@@ -1986,16 +1974,16 @@
         <v>14</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F16" s="21">
         <v>1</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="33.75">
@@ -2006,16 +1994,16 @@
         <v>15</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="21">
         <v>3</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25">
@@ -2026,13 +2014,13 @@
         <v>16</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="21">
         <v>3</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -2044,13 +2032,13 @@
         <v>17</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F19" s="21">
         <v>1</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H19" s="38"/>
     </row>
@@ -2062,13 +2050,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F20" s="21">
         <v>2</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H20" s="38"/>
     </row>
@@ -2080,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F21" s="21">
         <v>1</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H21" s="38"/>
     </row>
@@ -2098,13 +2086,13 @@
         <v>20</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F22" s="21">
         <v>1</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H22" s="38"/>
     </row>
@@ -2116,16 +2104,16 @@
         <v>21</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F23" s="21">
         <v>1</v>
       </c>
       <c r="G23" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="H23" s="38" t="s">
         <v>352</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>353</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -2136,16 +2124,16 @@
         <v>22</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F24" s="21">
         <v>1</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H24" s="38" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
@@ -2156,13 +2144,13 @@
         <v>23</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F25" s="21">
         <v>1</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H25" s="38"/>
     </row>
@@ -2170,17 +2158,17 @@
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
-      <c r="D26" s="53">
+      <c r="D26" s="51">
         <v>24</v>
       </c>
-      <c r="E26" s="54" t="s">
-        <v>357</v>
-      </c>
-      <c r="F26" s="55">
+      <c r="E26" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="F26" s="21">
         <v>1</v>
       </c>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="22"/>
@@ -2190,37 +2178,37 @@
         <v>25</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F27" s="21">
         <v>1</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="22"/>
@@ -2247,10 +2235,10 @@
   <cols>
     <col min="1" max="1" style="23" width="7.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="50" width="60.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="36" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="37" width="7.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="35" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="36" width="7.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="50" width="12.005" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="50" width="15.43357142857143" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="50" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -2259,12 +2247,12 @@
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="21"/>
       <c r="B1" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+        <v>190</v>
+      </c>
+      <c r="C1" s="32"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
       <c r="G1" s="38"/>
       <c r="H1" s="38"/>
       <c r="I1" s="38"/>
@@ -2274,12 +2262,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+        <v>191</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
@@ -2289,12 +2277,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
+        <v>192</v>
+      </c>
+      <c r="C3" s="32"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
@@ -2304,12 +2292,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+        <v>193</v>
+      </c>
+      <c r="C4" s="32"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
       <c r="G4" s="38"/>
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
@@ -2317,23 +2305,23 @@
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="21"/>
       <c r="B5" s="38"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
       <c r="G5" s="38"/>
       <c r="H5" s="38"/>
       <c r="I5" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="41"/>
       <c r="D6" s="42"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="38"/>
@@ -2351,11 +2339,11 @@
       <c r="D7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>196</v>
+      <c r="F7" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>5</v>
@@ -2370,20 +2358,20 @@
         <v>1</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="30">
+        <v>196</v>
+      </c>
+      <c r="C8" s="31">
         <v>8.03</v>
       </c>
       <c r="D8" s="18">
         <v>45355</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="F8" s="30"/>
+      <c r="G8" s="17" t="s">
         <v>198</v>
-      </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="17" t="s">
-        <v>199</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="38"/>
@@ -2393,20 +2381,20 @@
         <v>2</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C9" s="30">
+        <v>199</v>
+      </c>
+      <c r="C9" s="31">
         <v>20.56</v>
       </c>
       <c r="D9" s="18">
         <v>45355</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="F9" s="30"/>
+      <c r="G9" s="17" t="s">
         <v>198</v>
-      </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="17" t="s">
-        <v>199</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="38"/>
@@ -2416,24 +2404,24 @@
         <v>3</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="30">
+        <v>200</v>
+      </c>
+      <c r="C10" s="31">
         <v>34.45</v>
       </c>
       <c r="D10" s="18">
         <v>45355</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="30"/>
+      <c r="G10" s="17" t="s">
         <v>198</v>
-      </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="17" t="s">
-        <v>199</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="33.75">
@@ -2441,20 +2429,20 @@
         <v>4</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="30">
+        <v>202</v>
+      </c>
+      <c r="C11" s="31">
         <v>32.53</v>
       </c>
       <c r="D11" s="18">
         <v>45356</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="F11" s="22"/>
+      <c r="E11" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="F11" s="30"/>
       <c r="G11" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="38"/>
@@ -2464,20 +2452,20 @@
         <v>5</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="30">
+        <v>204</v>
+      </c>
+      <c r="C12" s="31">
         <v>28.2</v>
       </c>
       <c r="D12" s="18">
         <v>45356</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="F12" s="22"/>
+      <c r="E12" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="30"/>
       <c r="G12" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="38"/>
@@ -2487,20 +2475,20 @@
         <v>6</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="30">
+        <v>205</v>
+      </c>
+      <c r="C13" s="31">
         <v>32.09</v>
       </c>
       <c r="D13" s="18">
         <v>45357</v>
       </c>
-      <c r="E13" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="F13" s="22"/>
+      <c r="E13" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="F13" s="30"/>
       <c r="G13" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="38"/>
@@ -2510,20 +2498,20 @@
         <v>7</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14" s="30">
+        <v>207</v>
+      </c>
+      <c r="C14" s="31">
         <v>15.04</v>
       </c>
       <c r="D14" s="18">
         <v>45357</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="F14" s="22"/>
+      <c r="E14" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="F14" s="30"/>
       <c r="G14" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="38"/>
@@ -2533,20 +2521,20 @@
         <v>8</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" s="30">
+        <v>208</v>
+      </c>
+      <c r="C15" s="31">
         <v>29.46</v>
       </c>
       <c r="D15" s="18">
         <v>45358</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="F15" s="22"/>
+      <c r="E15" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="30"/>
       <c r="G15" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="38"/>
@@ -2556,20 +2544,20 @@
         <v>9</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="C16" s="30">
+        <v>210</v>
+      </c>
+      <c r="C16" s="31">
         <v>26.4</v>
       </c>
       <c r="D16" s="18">
         <v>45358</v>
       </c>
-      <c r="E16" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="F16" s="22"/>
+      <c r="E16" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="F16" s="30"/>
       <c r="G16" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="38"/>
@@ -2579,20 +2567,20 @@
         <v>10</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="C17" s="30">
+        <v>211</v>
+      </c>
+      <c r="C17" s="31">
         <v>24.52</v>
       </c>
       <c r="D17" s="18">
         <v>45359</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="F17" s="22"/>
+      <c r="E17" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="F17" s="30"/>
       <c r="G17" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="38"/>
@@ -2602,20 +2590,20 @@
         <v>11</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="30">
+        <v>213</v>
+      </c>
+      <c r="C18" s="31">
         <v>7.19</v>
       </c>
       <c r="D18" s="18">
         <v>45359</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="F18" s="22"/>
+      <c r="E18" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="F18" s="30"/>
       <c r="G18" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="38"/>
@@ -2625,20 +2613,20 @@
         <v>12</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="C19" s="30">
+        <v>214</v>
+      </c>
+      <c r="C19" s="31">
         <v>13.33</v>
       </c>
       <c r="D19" s="18">
         <v>45359</v>
       </c>
-      <c r="E19" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="F19" s="22"/>
+      <c r="E19" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="F19" s="30"/>
       <c r="G19" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="38"/>
@@ -2648,20 +2636,20 @@
         <v>13</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="C20" s="30">
+        <v>215</v>
+      </c>
+      <c r="C20" s="31">
         <v>19.1</v>
       </c>
       <c r="D20" s="18">
         <v>45359</v>
       </c>
-      <c r="E20" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="F20" s="22"/>
+      <c r="E20" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="F20" s="30"/>
       <c r="G20" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="38"/>
@@ -2671,20 +2659,20 @@
         <v>14</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C21" s="30">
+        <v>216</v>
+      </c>
+      <c r="C21" s="31">
         <v>25.43</v>
       </c>
       <c r="D21" s="18">
         <v>45360</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="F21" s="22"/>
+      <c r="E21" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="F21" s="30"/>
       <c r="G21" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="38"/>
@@ -2694,20 +2682,20 @@
         <v>15</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C22" s="30">
+        <v>218</v>
+      </c>
+      <c r="C22" s="31">
         <v>37.1</v>
       </c>
       <c r="D22" s="18">
         <v>45360</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="F22" s="22"/>
+      <c r="E22" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="F22" s="30"/>
       <c r="G22" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="38"/>
@@ -2717,20 +2705,20 @@
         <v>16</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="C23" s="30">
+        <v>219</v>
+      </c>
+      <c r="C23" s="31">
         <v>19.22</v>
       </c>
       <c r="D23" s="18">
         <v>45361</v>
       </c>
-      <c r="E23" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F23" s="22"/>
+      <c r="E23" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="F23" s="30"/>
       <c r="G23" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H23" s="17"/>
       <c r="I23" s="38"/>
@@ -2740,20 +2728,20 @@
         <v>17</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="C24" s="30">
+        <v>221</v>
+      </c>
+      <c r="C24" s="31">
         <v>9.48</v>
       </c>
       <c r="D24" s="18">
         <v>45361</v>
       </c>
-      <c r="E24" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F24" s="22"/>
+      <c r="E24" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" s="30"/>
       <c r="G24" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H24" s="17"/>
       <c r="I24" s="38"/>
@@ -2763,24 +2751,22 @@
         <v>18</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="C25" s="30">
+        <v>222</v>
+      </c>
+      <c r="C25" s="31">
         <v>22.52</v>
       </c>
       <c r="D25" s="18">
         <v>45361</v>
       </c>
-      <c r="E25" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F25" s="22"/>
+      <c r="E25" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="F25" s="30"/>
       <c r="G25" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H25" s="17"/>
       <c r="I25" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
@@ -2788,24 +2774,22 @@
         <v>19</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="C26" s="30">
+        <v>223</v>
+      </c>
+      <c r="C26" s="31">
         <v>10.07</v>
       </c>
       <c r="D26" s="18">
         <v>45361</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F26" s="22"/>
+      <c r="E26" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="F26" s="30"/>
       <c r="G26" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H26" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H26" s="17"/>
       <c r="I26" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="33.75">
@@ -2813,24 +2797,22 @@
         <v>20</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="C27" s="30">
+        <v>224</v>
+      </c>
+      <c r="C27" s="31">
         <v>18.28</v>
       </c>
       <c r="D27" s="18">
         <v>45362</v>
       </c>
-      <c r="E27" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="F27" s="22"/>
+      <c r="E27" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="F27" s="30"/>
       <c r="G27" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H27" s="17"/>
       <c r="I27" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
@@ -2838,24 +2820,22 @@
         <v>21</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="C28" s="30">
+        <v>226</v>
+      </c>
+      <c r="C28" s="31">
         <v>16.07</v>
       </c>
       <c r="D28" s="18">
         <v>45362</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="F28" s="22"/>
+      <c r="E28" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="F28" s="30"/>
       <c r="G28" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H28" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H28" s="17"/>
       <c r="I28" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
@@ -2863,24 +2843,22 @@
         <v>22</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="C29" s="30">
+        <v>227</v>
+      </c>
+      <c r="C29" s="31">
         <v>12.29</v>
       </c>
       <c r="D29" s="18">
         <v>45362</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="F29" s="22"/>
+      <c r="E29" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="F29" s="30"/>
       <c r="G29" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H29" s="17"/>
       <c r="I29" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
@@ -2888,24 +2866,22 @@
         <v>23</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C30" s="30">
+        <v>228</v>
+      </c>
+      <c r="C30" s="31">
         <v>13.4</v>
       </c>
       <c r="D30" s="18">
         <v>45362</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="F30" s="22"/>
+      <c r="E30" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="F30" s="30"/>
       <c r="G30" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H30" s="17"/>
       <c r="I30" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
@@ -2913,24 +2889,22 @@
         <v>24</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="C31" s="30">
+        <v>229</v>
+      </c>
+      <c r="C31" s="31">
         <v>8.25</v>
       </c>
       <c r="D31" s="18">
         <v>45363</v>
       </c>
-      <c r="E31" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="F31" s="22"/>
+      <c r="E31" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F31" s="30"/>
       <c r="G31" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H31" s="17"/>
       <c r="I31" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -2938,24 +2912,22 @@
         <v>25</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="C32" s="30">
+        <v>231</v>
+      </c>
+      <c r="C32" s="31">
         <v>5.13</v>
       </c>
       <c r="D32" s="18">
         <v>45363</v>
       </c>
-      <c r="E32" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="F32" s="22"/>
+      <c r="E32" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F32" s="30"/>
       <c r="G32" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H32" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H32" s="17"/>
       <c r="I32" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -2963,24 +2935,22 @@
         <v>26</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="C33" s="30">
+        <v>232</v>
+      </c>
+      <c r="C33" s="31">
         <v>6.04</v>
       </c>
       <c r="D33" s="18">
         <v>45363</v>
       </c>
-      <c r="E33" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="F33" s="22"/>
+      <c r="E33" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" s="30"/>
       <c r="G33" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H33" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H33" s="17"/>
       <c r="I33" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -2988,24 +2958,22 @@
         <v>27</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="C34" s="30">
+        <v>233</v>
+      </c>
+      <c r="C34" s="31">
         <v>6.09</v>
       </c>
       <c r="D34" s="18">
         <v>45363</v>
       </c>
-      <c r="E34" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="F34" s="22"/>
+      <c r="E34" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F34" s="30"/>
       <c r="G34" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H34" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H34" s="17"/>
       <c r="I34" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="33.75">
@@ -3013,24 +2981,22 @@
         <v>28</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="C35" s="30">
+        <v>234</v>
+      </c>
+      <c r="C35" s="31">
         <v>12.09</v>
       </c>
       <c r="D35" s="18">
         <v>45363</v>
       </c>
-      <c r="E35" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="F35" s="22"/>
+      <c r="E35" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F35" s="30"/>
       <c r="G35" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H35" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H35" s="17"/>
       <c r="I35" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
@@ -3038,24 +3004,22 @@
         <v>29</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="C36" s="30">
+        <v>235</v>
+      </c>
+      <c r="C36" s="31">
         <v>12.09</v>
       </c>
       <c r="D36" s="18">
         <v>45363</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="F36" s="22"/>
+      <c r="E36" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F36" s="30"/>
       <c r="G36" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H36" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H36" s="17"/>
       <c r="I36" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
@@ -3063,24 +3027,22 @@
         <v>30</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C37" s="30">
+        <v>236</v>
+      </c>
+      <c r="C37" s="31">
         <v>25.47</v>
       </c>
       <c r="D37" s="18">
         <v>45364</v>
       </c>
-      <c r="E37" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="F37" s="22"/>
+      <c r="E37" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F37" s="30"/>
       <c r="G37" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H37" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H37" s="17"/>
       <c r="I37" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
@@ -3088,24 +3050,22 @@
         <v>31</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="C38" s="30">
+        <v>238</v>
+      </c>
+      <c r="C38" s="31">
         <v>10.16</v>
       </c>
       <c r="D38" s="18">
         <v>45364</v>
       </c>
-      <c r="E38" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="F38" s="22"/>
+      <c r="E38" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F38" s="30"/>
       <c r="G38" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H38" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H38" s="17"/>
       <c r="I38" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="33.75">
@@ -3113,24 +3073,22 @@
         <v>32</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="C39" s="30">
+        <v>239</v>
+      </c>
+      <c r="C39" s="31">
         <v>17.23</v>
       </c>
       <c r="D39" s="18">
         <v>45364</v>
       </c>
-      <c r="E39" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="F39" s="22"/>
+      <c r="E39" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F39" s="30"/>
       <c r="G39" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H39" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H39" s="17"/>
       <c r="I39" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
@@ -3138,24 +3096,22 @@
         <v>33</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="C40" s="30">
+        <v>240</v>
+      </c>
+      <c r="C40" s="31">
         <v>13.18</v>
       </c>
       <c r="D40" s="18">
         <v>45364</v>
       </c>
-      <c r="E40" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="F40" s="22"/>
+      <c r="E40" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F40" s="30"/>
       <c r="G40" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H40" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H40" s="17"/>
       <c r="I40" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
@@ -3163,24 +3119,22 @@
         <v>34</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="C41" s="30">
+        <v>241</v>
+      </c>
+      <c r="C41" s="31">
         <v>10.06</v>
       </c>
       <c r="D41" s="18">
         <v>45365</v>
       </c>
-      <c r="E41" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="F41" s="22"/>
+      <c r="E41" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="F41" s="30"/>
       <c r="G41" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H41" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H41" s="17"/>
       <c r="I41" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
@@ -3188,24 +3142,22 @@
         <v>35</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="C42" s="30">
+        <v>243</v>
+      </c>
+      <c r="C42" s="31">
         <v>2.3</v>
       </c>
       <c r="D42" s="18">
         <v>45365</v>
       </c>
-      <c r="E42" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="F42" s="22"/>
+      <c r="E42" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="F42" s="30"/>
       <c r="G42" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H42" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H42" s="17"/>
       <c r="I42" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
@@ -3213,24 +3165,22 @@
         <v>36</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="C43" s="30">
+        <v>244</v>
+      </c>
+      <c r="C43" s="31">
         <v>14.17</v>
       </c>
       <c r="D43" s="18">
         <v>45365</v>
       </c>
-      <c r="E43" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="F43" s="22"/>
+      <c r="E43" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="F43" s="30"/>
       <c r="G43" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H43" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H43" s="17"/>
       <c r="I43" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20.25">
@@ -3238,40 +3188,38 @@
         <v>37</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="C44" s="30">
+        <v>245</v>
+      </c>
+      <c r="C44" s="31">
         <v>27.06</v>
       </c>
       <c r="D44" s="18">
         <v>45365</v>
       </c>
-      <c r="E44" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="F44" s="22"/>
+      <c r="E44" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="F44" s="30"/>
       <c r="G44" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H44" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H44" s="17"/>
       <c r="I44" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="21"/>
       <c r="B45" s="38"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
       <c r="I45" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A46" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="25"/>
@@ -3295,11 +3243,11 @@
       <c r="D47" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E47" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="22" t="s">
-        <v>196</v>
+      <c r="F47" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>5</v>
@@ -3314,24 +3262,22 @@
         <v>1</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="C48" s="30">
+        <v>247</v>
+      </c>
+      <c r="C48" s="31">
         <v>17.33</v>
       </c>
       <c r="D48" s="18">
         <v>45366</v>
       </c>
-      <c r="E48" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="F48" s="22"/>
+      <c r="E48" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="F48" s="30"/>
       <c r="G48" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H48" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H48" s="17"/>
       <c r="I48" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
@@ -3339,24 +3285,22 @@
         <v>2</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="C49" s="30">
+        <v>249</v>
+      </c>
+      <c r="C49" s="31">
         <v>18.21</v>
       </c>
       <c r="D49" s="18">
         <v>45366</v>
       </c>
-      <c r="E49" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="F49" s="22"/>
+      <c r="E49" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="F49" s="30"/>
       <c r="G49" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H49" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H49" s="17"/>
       <c r="I49" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
@@ -3364,24 +3308,22 @@
         <v>3</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="C50" s="30">
+        <v>250</v>
+      </c>
+      <c r="C50" s="31">
         <v>13.01</v>
       </c>
       <c r="D50" s="18">
         <v>45366</v>
       </c>
-      <c r="E50" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="F50" s="22"/>
+      <c r="E50" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="F50" s="30"/>
       <c r="G50" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H50" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H50" s="17"/>
       <c r="I50" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
@@ -3389,24 +3331,22 @@
         <v>4</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C51" s="30">
+        <v>251</v>
+      </c>
+      <c r="C51" s="31">
         <v>10.17</v>
       </c>
       <c r="D51" s="18">
         <v>45366</v>
       </c>
-      <c r="E51" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="F51" s="22"/>
+      <c r="E51" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="F51" s="30"/>
       <c r="G51" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H51" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H51" s="17"/>
       <c r="I51" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
@@ -3414,24 +3354,22 @@
         <v>5</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="C52" s="30">
+        <v>252</v>
+      </c>
+      <c r="C52" s="31">
         <v>16.56</v>
       </c>
       <c r="D52" s="18">
         <v>45367</v>
       </c>
-      <c r="E52" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F52" s="22"/>
+      <c r="E52" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="F52" s="30"/>
       <c r="G52" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H52" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H52" s="17"/>
       <c r="I52" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
@@ -3439,24 +3377,22 @@
         <v>6</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="C53" s="30">
+        <v>254</v>
+      </c>
+      <c r="C53" s="31">
         <v>7.56</v>
       </c>
       <c r="D53" s="18">
         <v>45367</v>
       </c>
-      <c r="E53" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F53" s="22"/>
+      <c r="E53" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="F53" s="30"/>
       <c r="G53" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H53" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H53" s="17"/>
       <c r="I53" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
@@ -3464,24 +3400,22 @@
         <v>7</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="C54" s="30">
+        <v>255</v>
+      </c>
+      <c r="C54" s="31">
         <v>12.49</v>
       </c>
       <c r="D54" s="18">
         <v>45367</v>
       </c>
-      <c r="E54" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F54" s="22"/>
+      <c r="E54" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="F54" s="30"/>
       <c r="G54" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H54" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H54" s="17"/>
       <c r="I54" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
@@ -3489,24 +3423,22 @@
         <v>8</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="C55" s="30">
+        <v>256</v>
+      </c>
+      <c r="C55" s="31">
         <v>7.13</v>
       </c>
       <c r="D55" s="18">
         <v>45367</v>
       </c>
-      <c r="E55" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F55" s="22"/>
+      <c r="E55" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="F55" s="30"/>
       <c r="G55" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H55" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H55" s="17"/>
       <c r="I55" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
@@ -3514,24 +3446,22 @@
         <v>9</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="C56" s="30">
+        <v>257</v>
+      </c>
+      <c r="C56" s="31">
         <v>18.22</v>
       </c>
       <c r="D56" s="18">
         <v>45367</v>
       </c>
-      <c r="E56" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="F56" s="22"/>
+      <c r="E56" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="F56" s="30"/>
       <c r="G56" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="H56" s="32" t="s">
-        <v>16</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H56" s="17"/>
       <c r="I56" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
@@ -3539,22 +3469,22 @@
         <v>10</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="C57" s="30">
+        <v>258</v>
+      </c>
+      <c r="C57" s="31">
         <v>23.21</v>
       </c>
       <c r="D57" s="18">
         <v>45368</v>
       </c>
-      <c r="E57" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="F57" s="22"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="E57" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="F57" s="30"/>
+      <c r="G57" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" s="17"/>
       <c r="I57" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="33.75">
@@ -3562,22 +3492,22 @@
         <v>11</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="C58" s="30">
+        <v>260</v>
+      </c>
+      <c r="C58" s="31">
         <v>28.28</v>
       </c>
       <c r="D58" s="18">
         <v>45368</v>
       </c>
-      <c r="E58" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="F58" s="22"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="E58" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58" s="30"/>
+      <c r="G58" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H58" s="17"/>
       <c r="I58" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
@@ -3585,22 +3515,20 @@
         <v>12</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="C59" s="30">
+        <v>261</v>
+      </c>
+      <c r="C59" s="31">
         <v>17.27</v>
       </c>
       <c r="D59" s="18">
         <v>45369</v>
       </c>
-      <c r="E59" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="F59" s="22"/>
+      <c r="E59" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="F59" s="30"/>
       <c r="G59" s="17"/>
-      <c r="H59" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H59" s="17"/>
       <c r="I59" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
@@ -3608,22 +3536,20 @@
         <v>13</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="C60" s="30">
+        <v>263</v>
+      </c>
+      <c r="C60" s="31">
         <v>11.51</v>
       </c>
       <c r="D60" s="18">
         <v>45369</v>
       </c>
-      <c r="E60" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="F60" s="22"/>
+      <c r="E60" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="F60" s="30"/>
       <c r="G60" s="17"/>
-      <c r="H60" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H60" s="17"/>
       <c r="I60" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
@@ -3631,22 +3557,20 @@
         <v>14</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="C61" s="30">
+        <v>264</v>
+      </c>
+      <c r="C61" s="31">
         <v>7.15</v>
       </c>
       <c r="D61" s="18">
         <v>45369</v>
       </c>
-      <c r="E61" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="F61" s="22"/>
+      <c r="E61" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="F61" s="30"/>
       <c r="G61" s="17"/>
-      <c r="H61" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H61" s="17"/>
       <c r="I61" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="20.25">
@@ -3654,22 +3578,20 @@
         <v>15</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="C62" s="30">
+        <v>265</v>
+      </c>
+      <c r="C62" s="31">
         <v>9.02</v>
       </c>
       <c r="D62" s="18">
         <v>45369</v>
       </c>
-      <c r="E62" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="F62" s="22"/>
+      <c r="E62" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="F62" s="30"/>
       <c r="G62" s="17"/>
-      <c r="H62" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H62" s="17"/>
       <c r="I62" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5" customFormat="1" s="1">
@@ -3685,7 +3607,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A64" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="25"/>
@@ -3709,11 +3631,11 @@
       <c r="D65" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F65" s="22" t="s">
-        <v>196</v>
+      <c r="F65" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="G65" s="14" t="s">
         <v>5</v>
@@ -3728,22 +3650,20 @@
         <v>1</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="C66" s="30">
+        <v>267</v>
+      </c>
+      <c r="C66" s="31">
         <v>26.05</v>
       </c>
       <c r="D66" s="18">
         <v>45370</v>
       </c>
-      <c r="E66" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="F66" s="22"/>
+      <c r="E66" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="F66" s="30"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H66" s="17"/>
       <c r="I66" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="33.75">
@@ -3751,22 +3671,20 @@
         <v>2</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="C67" s="30">
+        <v>269</v>
+      </c>
+      <c r="C67" s="31">
         <v>12.51</v>
       </c>
       <c r="D67" s="18">
         <v>45370</v>
       </c>
-      <c r="E67" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="F67" s="22"/>
+      <c r="E67" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="F67" s="30"/>
       <c r="G67" s="17"/>
-      <c r="H67" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H67" s="17"/>
       <c r="I67" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="33.75">
@@ -3774,22 +3692,20 @@
         <v>3</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="C68" s="30">
+        <v>270</v>
+      </c>
+      <c r="C68" s="31">
         <v>13.31</v>
       </c>
       <c r="D68" s="18">
         <v>45370</v>
       </c>
-      <c r="E68" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="F68" s="22"/>
+      <c r="E68" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="F68" s="30"/>
       <c r="G68" s="17"/>
-      <c r="H68" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H68" s="17"/>
       <c r="I68" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="33.75">
@@ -3797,22 +3713,20 @@
         <v>4</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="C69" s="30">
+        <v>271</v>
+      </c>
+      <c r="C69" s="31">
         <v>24.56</v>
       </c>
       <c r="D69" s="18">
         <v>45371</v>
       </c>
-      <c r="E69" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="F69" s="22"/>
+      <c r="E69" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="F69" s="30"/>
       <c r="G69" s="17"/>
-      <c r="H69" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H69" s="17"/>
       <c r="I69" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="33.75">
@@ -3820,22 +3734,20 @@
         <v>5</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C70" s="30">
+        <v>273</v>
+      </c>
+      <c r="C70" s="31">
         <v>18.08</v>
       </c>
       <c r="D70" s="18">
         <v>45371</v>
       </c>
-      <c r="E70" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="F70" s="22"/>
+      <c r="E70" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="F70" s="30"/>
       <c r="G70" s="17"/>
-      <c r="H70" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H70" s="17"/>
       <c r="I70" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -3843,22 +3755,20 @@
         <v>6</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="C71" s="30">
+        <v>274</v>
+      </c>
+      <c r="C71" s="31">
         <v>13.55</v>
       </c>
       <c r="D71" s="18">
         <v>45371</v>
       </c>
-      <c r="E71" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="F71" s="22"/>
+      <c r="E71" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="F71" s="30"/>
       <c r="G71" s="17"/>
-      <c r="H71" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H71" s="17"/>
       <c r="I71" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
@@ -3866,22 +3776,20 @@
         <v>7</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="C72" s="30">
+        <v>275</v>
+      </c>
+      <c r="C72" s="31">
         <v>29.41</v>
       </c>
       <c r="D72" s="18">
         <v>45372</v>
       </c>
-      <c r="E72" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="F72" s="22"/>
+      <c r="E72" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="F72" s="30"/>
       <c r="G72" s="17"/>
-      <c r="H72" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H72" s="17"/>
       <c r="I72" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -3889,22 +3797,20 @@
         <v>8</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="C73" s="30">
+        <v>277</v>
+      </c>
+      <c r="C73" s="31">
         <v>10.49</v>
       </c>
       <c r="D73" s="18">
         <v>45372</v>
       </c>
-      <c r="E73" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="F73" s="22"/>
+      <c r="E73" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="F73" s="30"/>
       <c r="G73" s="17"/>
-      <c r="H73" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H73" s="17"/>
       <c r="I73" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -3912,22 +3818,20 @@
         <v>9</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="C74" s="30">
+        <v>278</v>
+      </c>
+      <c r="C74" s="31">
         <v>16.02</v>
       </c>
       <c r="D74" s="18">
         <v>45372</v>
       </c>
-      <c r="E74" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="F74" s="22"/>
+      <c r="E74" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="F74" s="30"/>
       <c r="G74" s="17"/>
-      <c r="H74" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H74" s="17"/>
       <c r="I74" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -3935,22 +3839,20 @@
         <v>10</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="C75" s="30">
+        <v>279</v>
+      </c>
+      <c r="C75" s="31">
         <v>10.48</v>
       </c>
       <c r="D75" s="18">
         <v>45373</v>
       </c>
-      <c r="E75" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="F75" s="22"/>
+      <c r="E75" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="F75" s="30"/>
       <c r="G75" s="17"/>
-      <c r="H75" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H75" s="17"/>
       <c r="I75" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -3958,31 +3860,29 @@
         <v>11</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="C76" s="30">
+        <v>281</v>
+      </c>
+      <c r="C76" s="31">
         <v>20.49</v>
       </c>
       <c r="D76" s="18">
         <v>45373</v>
       </c>
-      <c r="E76" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="F76" s="22"/>
+      <c r="E76" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="F76" s="30"/>
       <c r="G76" s="17"/>
-      <c r="H76" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H76" s="17"/>
       <c r="I76" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="21"/>
       <c r="B77" s="38"/>
-      <c r="C77" s="33"/>
-      <c r="D77" s="34"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="33"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
       <c r="G77" s="38"/>
       <c r="H77" s="38"/>
       <c r="I77" s="38"/>
@@ -4013,11 +3913,11 @@
       <c r="D79" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E79" s="22" t="s">
+      <c r="E79" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F79" s="22" t="s">
-        <v>196</v>
+      <c r="F79" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="G79" s="14" t="s">
         <v>5</v>
@@ -4032,24 +3932,20 @@
         <v>1</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C80" s="47">
-        <v>24.118738425925926</v>
+        <v>25.118622685185183</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
       </c>
-      <c r="E80" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="F80" s="22"/>
-      <c r="G80" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="H80" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="E80" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="F80" s="30"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="19"/>
       <c r="I80" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
@@ -4057,22 +3953,20 @@
         <v>2</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C81" s="47">
-        <v>24.118738425925926</v>
+        <v>25.118622685185183</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
       </c>
-      <c r="E81" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="F81" s="22"/>
+      <c r="E81" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="F81" s="30"/>
       <c r="G81" s="19"/>
-      <c r="H81" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="H81" s="19"/>
       <c r="I81" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
@@ -4080,22 +3974,20 @@
         <v>3</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C82" s="47">
-        <v>24.118738425925926</v>
+        <v>25.118622685185183</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
       </c>
-      <c r="E82" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="F82" s="22"/>
+      <c r="E82" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="F82" s="30"/>
       <c r="G82" s="19"/>
-      <c r="H82" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="H82" s="19"/>
       <c r="I82" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
@@ -4103,22 +3995,20 @@
         <v>4</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C83" s="47">
-        <v>24.118738425925926</v>
+        <v>25.118622685185183</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
       </c>
-      <c r="E83" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="F83" s="22"/>
+      <c r="E83" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="F83" s="30"/>
       <c r="G83" s="19"/>
-      <c r="H83" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="H83" s="19"/>
       <c r="I83" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -4126,22 +4016,20 @@
         <v>5</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="C84" s="30">
+        <v>287</v>
+      </c>
+      <c r="C84" s="31">
         <v>10.13</v>
       </c>
       <c r="D84" s="18">
         <v>45378</v>
       </c>
-      <c r="E84" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F84" s="22"/>
+      <c r="E84" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F84" s="30"/>
       <c r="G84" s="17"/>
-      <c r="H84" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H84" s="17"/>
       <c r="I84" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -4149,22 +4037,20 @@
         <v>6</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="C85" s="30">
+        <v>289</v>
+      </c>
+      <c r="C85" s="31">
         <v>9.05</v>
       </c>
       <c r="D85" s="18">
         <v>45378</v>
       </c>
-      <c r="E85" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F85" s="22"/>
+      <c r="E85" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F85" s="30"/>
       <c r="G85" s="17"/>
-      <c r="H85" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H85" s="17"/>
       <c r="I85" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -4172,22 +4058,20 @@
         <v>7</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="C86" s="30">
+        <v>290</v>
+      </c>
+      <c r="C86" s="31">
         <v>3.39</v>
       </c>
       <c r="D86" s="18">
         <v>45378</v>
       </c>
-      <c r="E86" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F86" s="22"/>
+      <c r="E86" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F86" s="30"/>
       <c r="G86" s="17"/>
-      <c r="H86" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H86" s="17"/>
       <c r="I86" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
@@ -4195,22 +4079,20 @@
         <v>8</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="C87" s="30">
+        <v>291</v>
+      </c>
+      <c r="C87" s="31">
         <v>8.27</v>
       </c>
       <c r="D87" s="18">
         <v>45378</v>
       </c>
-      <c r="E87" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F87" s="22"/>
+      <c r="E87" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F87" s="30"/>
       <c r="G87" s="17"/>
-      <c r="H87" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H87" s="17"/>
       <c r="I87" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
@@ -4218,22 +4100,20 @@
         <v>9</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="C88" s="30">
+        <v>292</v>
+      </c>
+      <c r="C88" s="31">
         <v>7.21</v>
       </c>
       <c r="D88" s="18">
         <v>45378</v>
       </c>
-      <c r="E88" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F88" s="22"/>
+      <c r="E88" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F88" s="30"/>
       <c r="G88" s="17"/>
-      <c r="H88" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H88" s="17"/>
       <c r="I88" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -4241,22 +4121,20 @@
         <v>10</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="C89" s="30">
+        <v>293</v>
+      </c>
+      <c r="C89" s="31">
         <v>9.04</v>
       </c>
       <c r="D89" s="18">
         <v>45378</v>
       </c>
-      <c r="E89" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F89" s="22"/>
+      <c r="E89" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F89" s="30"/>
       <c r="G89" s="17"/>
-      <c r="H89" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H89" s="17"/>
       <c r="I89" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
@@ -4264,22 +4142,20 @@
         <v>11</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="C90" s="30">
+        <v>294</v>
+      </c>
+      <c r="C90" s="31">
         <v>14.14</v>
       </c>
       <c r="D90" s="18">
         <v>45378</v>
       </c>
-      <c r="E90" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="F90" s="22"/>
+      <c r="E90" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F90" s="30"/>
       <c r="G90" s="17"/>
-      <c r="H90" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H90" s="17"/>
       <c r="I90" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -4287,22 +4163,20 @@
         <v>12</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="C91" s="30">
+        <v>295</v>
+      </c>
+      <c r="C91" s="31">
         <v>14.01</v>
       </c>
       <c r="D91" s="18">
         <v>46840</v>
       </c>
-      <c r="E91" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="F91" s="22"/>
+      <c r="E91" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F91" s="30"/>
       <c r="G91" s="17"/>
-      <c r="H91" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H91" s="17"/>
       <c r="I91" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -4310,22 +4184,20 @@
         <v>13</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C92" s="30">
+        <v>297</v>
+      </c>
+      <c r="C92" s="31">
         <v>11.17</v>
       </c>
       <c r="D92" s="18">
         <v>46840</v>
       </c>
-      <c r="E92" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="F92" s="22"/>
+      <c r="E92" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F92" s="30"/>
       <c r="G92" s="17"/>
-      <c r="H92" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H92" s="17"/>
       <c r="I92" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -4333,7 +4205,7 @@
         <v>14</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C93" s="15">
         <v>12</v>
@@ -4341,14 +4213,12 @@
       <c r="D93" s="18">
         <v>46840</v>
       </c>
-      <c r="E93" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="F93" s="22"/>
+      <c r="E93" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F93" s="30"/>
       <c r="G93" s="17"/>
-      <c r="H93" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H93" s="17"/>
       <c r="I93" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
@@ -4356,22 +4226,20 @@
         <v>15</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="C94" s="30">
+        <v>299</v>
+      </c>
+      <c r="C94" s="31">
         <v>12.33</v>
       </c>
       <c r="D94" s="18">
         <v>46840</v>
       </c>
-      <c r="E94" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="F94" s="22"/>
+      <c r="E94" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F94" s="30"/>
       <c r="G94" s="17"/>
-      <c r="H94" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H94" s="17"/>
       <c r="I94" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
@@ -4379,22 +4247,20 @@
         <v>16</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="C95" s="30">
+        <v>300</v>
+      </c>
+      <c r="C95" s="31">
         <v>10.57</v>
       </c>
       <c r="D95" s="18">
         <v>46840</v>
       </c>
-      <c r="E95" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="F95" s="22"/>
+      <c r="E95" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F95" s="30"/>
       <c r="G95" s="17"/>
-      <c r="H95" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H95" s="17"/>
       <c r="I95" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
@@ -4402,22 +4268,20 @@
         <v>17</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="C96" s="30">
+        <v>301</v>
+      </c>
+      <c r="C96" s="31">
         <v>10.13</v>
       </c>
       <c r="D96" s="18">
         <v>45380</v>
       </c>
-      <c r="E96" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="F96" s="22"/>
+      <c r="E96" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="F96" s="30"/>
       <c r="G96" s="18"/>
-      <c r="H96" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H96" s="17"/>
       <c r="I96" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
@@ -4425,22 +4289,20 @@
         <v>18</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="C97" s="30">
+        <v>303</v>
+      </c>
+      <c r="C97" s="31">
         <v>17.37</v>
       </c>
       <c r="D97" s="18">
         <v>45380</v>
       </c>
-      <c r="E97" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="F97" s="22"/>
+      <c r="E97" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="F97" s="30"/>
       <c r="G97" s="18"/>
-      <c r="H97" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H97" s="17"/>
       <c r="I97" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
@@ -4448,22 +4310,20 @@
         <v>19</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="C98" s="30">
+        <v>304</v>
+      </c>
+      <c r="C98" s="31">
         <v>9.28</v>
       </c>
       <c r="D98" s="18">
         <v>45380</v>
       </c>
-      <c r="E98" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="F98" s="22"/>
+      <c r="E98" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="F98" s="30"/>
       <c r="G98" s="18"/>
-      <c r="H98" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H98" s="17"/>
       <c r="I98" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
@@ -4471,22 +4331,20 @@
         <v>20</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="C99" s="30">
+        <v>305</v>
+      </c>
+      <c r="C99" s="31">
         <v>7.18</v>
       </c>
       <c r="D99" s="18">
         <v>45380</v>
       </c>
-      <c r="E99" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="F99" s="22"/>
+      <c r="E99" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="F99" s="30"/>
       <c r="G99" s="18"/>
-      <c r="H99" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H99" s="17"/>
       <c r="I99" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
@@ -4494,22 +4352,20 @@
         <v>21</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="C100" s="30">
+        <v>306</v>
+      </c>
+      <c r="C100" s="31">
         <v>7.54</v>
       </c>
       <c r="D100" s="18">
         <v>45380</v>
       </c>
-      <c r="E100" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="F100" s="22"/>
+      <c r="E100" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="F100" s="30"/>
       <c r="G100" s="18"/>
-      <c r="H100" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H100" s="17"/>
       <c r="I100" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
@@ -4517,22 +4373,20 @@
         <v>22</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="C101" s="30">
+        <v>307</v>
+      </c>
+      <c r="C101" s="31">
         <v>25.46</v>
       </c>
       <c r="D101" s="18">
         <v>45381</v>
       </c>
-      <c r="E101" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="F101" s="22"/>
+      <c r="E101" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="F101" s="30"/>
       <c r="G101" s="18"/>
-      <c r="H101" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H101" s="17"/>
       <c r="I101" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
@@ -4540,22 +4394,20 @@
         <v>23</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="C102" s="30">
+        <v>309</v>
+      </c>
+      <c r="C102" s="31">
         <v>8.47</v>
       </c>
       <c r="D102" s="18">
         <v>45381</v>
       </c>
-      <c r="E102" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="F102" s="22"/>
+      <c r="E102" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="F102" s="30"/>
       <c r="G102" s="18"/>
-      <c r="H102" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H102" s="17"/>
       <c r="I102" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="33">
@@ -4563,22 +4415,20 @@
         <v>24</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="C103" s="30">
+        <v>311</v>
+      </c>
+      <c r="C103" s="31">
         <v>5.43</v>
       </c>
       <c r="D103" s="18">
         <v>45381</v>
       </c>
-      <c r="E103" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="F103" s="22"/>
+      <c r="E103" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="F103" s="30"/>
       <c r="G103" s="18"/>
-      <c r="H103" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H103" s="17"/>
       <c r="I103" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="33.75">
@@ -4586,22 +4436,20 @@
         <v>25</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="C104" s="30">
+        <v>312</v>
+      </c>
+      <c r="C104" s="31">
         <v>12.35</v>
       </c>
       <c r="D104" s="18">
         <v>45381</v>
       </c>
-      <c r="E104" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="F104" s="22"/>
+      <c r="E104" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="F104" s="30"/>
       <c r="G104" s="18"/>
-      <c r="H104" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H104" s="17"/>
       <c r="I104" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="33">
@@ -4609,22 +4457,20 @@
         <v>26</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="C105" s="30">
+        <v>313</v>
+      </c>
+      <c r="C105" s="31">
         <v>4.06</v>
       </c>
       <c r="D105" s="18">
         <v>45381</v>
       </c>
-      <c r="E105" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="F105" s="22"/>
+      <c r="E105" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="F105" s="30"/>
       <c r="G105" s="18"/>
-      <c r="H105" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H105" s="17"/>
       <c r="I105" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
@@ -4632,22 +4478,20 @@
         <v>27</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="C106" s="30">
+        <v>314</v>
+      </c>
+      <c r="C106" s="31">
         <v>14.59</v>
       </c>
       <c r="D106" s="18">
         <v>45382</v>
       </c>
-      <c r="E106" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="F106" s="22"/>
+      <c r="E106" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="F106" s="30"/>
       <c r="G106" s="18"/>
-      <c r="H106" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H106" s="17"/>
       <c r="I106" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
@@ -4655,22 +4499,20 @@
         <v>28</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="C107" s="30">
+        <v>316</v>
+      </c>
+      <c r="C107" s="31">
         <v>18.2</v>
       </c>
       <c r="D107" s="18">
         <v>45382</v>
       </c>
-      <c r="E107" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="F107" s="22"/>
+      <c r="E107" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="F107" s="30"/>
       <c r="G107" s="18"/>
-      <c r="H107" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H107" s="17"/>
       <c r="I107" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="33">
@@ -4678,22 +4520,20 @@
         <v>29</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="C108" s="30">
+        <v>317</v>
+      </c>
+      <c r="C108" s="31">
         <v>13.41</v>
       </c>
       <c r="D108" s="18">
         <v>45382</v>
       </c>
-      <c r="E108" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="F108" s="22"/>
+      <c r="E108" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="F108" s="30"/>
       <c r="G108" s="18"/>
-      <c r="H108" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H108" s="17"/>
       <c r="I108" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
@@ -4701,31 +4541,29 @@
         <v>30</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="C109" s="30">
+        <v>318</v>
+      </c>
+      <c r="C109" s="31">
         <v>11.59</v>
       </c>
       <c r="D109" s="18">
         <v>45382</v>
       </c>
-      <c r="E109" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="F109" s="22"/>
+      <c r="E109" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="F109" s="30"/>
       <c r="G109" s="18"/>
-      <c r="H109" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="H109" s="17"/>
       <c r="I109" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="21"/>
       <c r="B110" s="38"/>
-      <c r="C110" s="33"/>
-      <c r="D110" s="34"/>
-      <c r="E110" s="22"/>
-      <c r="F110" s="22"/>
+      <c r="C110" s="32"/>
+      <c r="D110" s="33"/>
+      <c r="E110" s="30"/>
+      <c r="F110" s="30"/>
       <c r="G110" s="48"/>
       <c r="H110" s="38"/>
       <c r="I110" s="38"/>
@@ -4733,10 +4571,10 @@
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="21"/>
       <c r="B111" s="38"/>
-      <c r="C111" s="33"/>
-      <c r="D111" s="34"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22"/>
+      <c r="C111" s="32"/>
+      <c r="D111" s="33"/>
+      <c r="E111" s="30"/>
+      <c r="F111" s="30"/>
       <c r="G111" s="48"/>
       <c r="H111" s="38"/>
       <c r="I111" s="38"/>
@@ -4744,10 +4582,10 @@
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="21"/>
       <c r="B112" s="38"/>
-      <c r="C112" s="33"/>
-      <c r="D112" s="34"/>
-      <c r="E112" s="22"/>
-      <c r="F112" s="22"/>
+      <c r="C112" s="32"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="30"/>
+      <c r="F112" s="30"/>
       <c r="G112" s="48"/>
       <c r="H112" s="38"/>
       <c r="I112" s="38"/>
@@ -4755,10 +4593,10 @@
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="21"/>
       <c r="B113" s="38"/>
-      <c r="C113" s="33"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="22"/>
-      <c r="F113" s="22"/>
+      <c r="C113" s="32"/>
+      <c r="D113" s="33"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
       <c r="G113" s="48"/>
       <c r="H113" s="38"/>
       <c r="I113" s="38"/>
@@ -4766,10 +4604,10 @@
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="21"/>
       <c r="B114" s="38"/>
-      <c r="C114" s="33"/>
-      <c r="D114" s="34"/>
-      <c r="E114" s="22"/>
-      <c r="F114" s="22"/>
+      <c r="C114" s="32"/>
+      <c r="D114" s="33"/>
+      <c r="E114" s="30"/>
+      <c r="F114" s="30"/>
       <c r="G114" s="48"/>
       <c r="H114" s="38"/>
       <c r="I114" s="38"/>
@@ -4777,10 +4615,10 @@
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="21"/>
       <c r="B115" s="38"/>
-      <c r="C115" s="33"/>
-      <c r="D115" s="34"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
+      <c r="C115" s="32"/>
+      <c r="D115" s="33"/>
+      <c r="E115" s="30"/>
+      <c r="F115" s="30"/>
       <c r="G115" s="48"/>
       <c r="H115" s="38"/>
       <c r="I115" s="38"/>
@@ -4788,10 +4626,10 @@
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="21"/>
       <c r="B116" s="38"/>
-      <c r="C116" s="33"/>
-      <c r="D116" s="34"/>
-      <c r="E116" s="22"/>
-      <c r="F116" s="22"/>
+      <c r="C116" s="32"/>
+      <c r="D116" s="33"/>
+      <c r="E116" s="30"/>
+      <c r="F116" s="30"/>
       <c r="G116" s="48"/>
       <c r="H116" s="38"/>
       <c r="I116" s="38"/>
@@ -4799,10 +4637,10 @@
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="21"/>
       <c r="B117" s="38"/>
-      <c r="C117" s="33"/>
-      <c r="D117" s="34"/>
-      <c r="E117" s="22"/>
-      <c r="F117" s="22"/>
+      <c r="C117" s="32"/>
+      <c r="D117" s="33"/>
+      <c r="E117" s="30"/>
+      <c r="F117" s="30"/>
       <c r="G117" s="48"/>
       <c r="H117" s="38"/>
       <c r="I117" s="38"/>
@@ -4810,10 +4648,10 @@
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="21"/>
       <c r="B118" s="38"/>
-      <c r="C118" s="33"/>
-      <c r="D118" s="34"/>
-      <c r="E118" s="22"/>
-      <c r="F118" s="22"/>
+      <c r="C118" s="32"/>
+      <c r="D118" s="33"/>
+      <c r="E118" s="30"/>
+      <c r="F118" s="30"/>
       <c r="G118" s="48"/>
       <c r="H118" s="38"/>
       <c r="I118" s="38"/>
@@ -4821,10 +4659,10 @@
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="21"/>
       <c r="B119" s="38"/>
-      <c r="C119" s="33"/>
-      <c r="D119" s="34"/>
-      <c r="E119" s="22"/>
-      <c r="F119" s="22"/>
+      <c r="C119" s="32"/>
+      <c r="D119" s="33"/>
+      <c r="E119" s="30"/>
+      <c r="F119" s="30"/>
       <c r="G119" s="48"/>
       <c r="H119" s="38"/>
       <c r="I119" s="38"/>
@@ -4832,10 +4670,10 @@
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="21"/>
       <c r="B120" s="38"/>
-      <c r="C120" s="33"/>
-      <c r="D120" s="34"/>
-      <c r="E120" s="22"/>
-      <c r="F120" s="22"/>
+      <c r="C120" s="32"/>
+      <c r="D120" s="33"/>
+      <c r="E120" s="30"/>
+      <c r="F120" s="30"/>
       <c r="G120" s="48"/>
       <c r="H120" s="38"/>
       <c r="I120" s="38"/>
@@ -4843,10 +4681,10 @@
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="21"/>
       <c r="B121" s="38"/>
-      <c r="C121" s="33"/>
-      <c r="D121" s="34"/>
-      <c r="E121" s="22"/>
-      <c r="F121" s="22"/>
+      <c r="C121" s="32"/>
+      <c r="D121" s="33"/>
+      <c r="E121" s="30"/>
+      <c r="F121" s="30"/>
       <c r="G121" s="48"/>
       <c r="H121" s="38"/>
       <c r="I121" s="38"/>
@@ -4854,10 +4692,10 @@
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="21"/>
       <c r="B122" s="38"/>
-      <c r="C122" s="33"/>
-      <c r="D122" s="34"/>
-      <c r="E122" s="22"/>
-      <c r="F122" s="22"/>
+      <c r="C122" s="32"/>
+      <c r="D122" s="33"/>
+      <c r="E122" s="30"/>
+      <c r="F122" s="30"/>
       <c r="G122" s="48"/>
       <c r="H122" s="38"/>
       <c r="I122" s="38"/>
@@ -4865,10 +4703,10 @@
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="21"/>
       <c r="B123" s="38"/>
-      <c r="C123" s="33"/>
-      <c r="D123" s="34"/>
-      <c r="E123" s="22"/>
-      <c r="F123" s="22"/>
+      <c r="C123" s="32"/>
+      <c r="D123" s="33"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
       <c r="G123" s="48"/>
       <c r="H123" s="38"/>
       <c r="I123" s="38"/>
@@ -4876,10 +4714,10 @@
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="21"/>
       <c r="B124" s="38"/>
-      <c r="C124" s="33"/>
-      <c r="D124" s="34"/>
-      <c r="E124" s="22"/>
-      <c r="F124" s="22"/>
+      <c r="C124" s="32"/>
+      <c r="D124" s="33"/>
+      <c r="E124" s="30"/>
+      <c r="F124" s="30"/>
       <c r="G124" s="48"/>
       <c r="H124" s="38"/>
       <c r="I124" s="38"/>
@@ -4887,10 +4725,10 @@
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="21"/>
       <c r="B125" s="38"/>
-      <c r="C125" s="33"/>
-      <c r="D125" s="34"/>
-      <c r="E125" s="22"/>
-      <c r="F125" s="22"/>
+      <c r="C125" s="32"/>
+      <c r="D125" s="33"/>
+      <c r="E125" s="30"/>
+      <c r="F125" s="30"/>
       <c r="G125" s="48"/>
       <c r="H125" s="38"/>
       <c r="I125" s="38"/>
@@ -4898,10 +4736,10 @@
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="21"/>
       <c r="B126" s="38"/>
-      <c r="C126" s="33"/>
-      <c r="D126" s="34"/>
-      <c r="E126" s="22"/>
-      <c r="F126" s="22"/>
+      <c r="C126" s="32"/>
+      <c r="D126" s="33"/>
+      <c r="E126" s="30"/>
+      <c r="F126" s="30"/>
       <c r="G126" s="48"/>
       <c r="H126" s="38"/>
       <c r="I126" s="38"/>
@@ -4909,10 +4747,10 @@
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="21"/>
       <c r="B127" s="38"/>
-      <c r="C127" s="33"/>
-      <c r="D127" s="34"/>
-      <c r="E127" s="22"/>
-      <c r="F127" s="22"/>
+      <c r="C127" s="32"/>
+      <c r="D127" s="33"/>
+      <c r="E127" s="30"/>
+      <c r="F127" s="30"/>
       <c r="G127" s="48"/>
       <c r="H127" s="38"/>
       <c r="I127" s="38"/>
@@ -4920,10 +4758,10 @@
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="21"/>
       <c r="B128" s="38"/>
-      <c r="C128" s="33"/>
-      <c r="D128" s="34"/>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
+      <c r="C128" s="32"/>
+      <c r="D128" s="33"/>
+      <c r="E128" s="30"/>
+      <c r="F128" s="30"/>
       <c r="G128" s="48"/>
       <c r="H128" s="38"/>
       <c r="I128" s="38"/>
@@ -4931,10 +4769,10 @@
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="21"/>
       <c r="B129" s="38"/>
-      <c r="C129" s="33"/>
-      <c r="D129" s="34"/>
-      <c r="E129" s="22"/>
-      <c r="F129" s="22"/>
+      <c r="C129" s="32"/>
+      <c r="D129" s="33"/>
+      <c r="E129" s="30"/>
+      <c r="F129" s="30"/>
       <c r="G129" s="48"/>
       <c r="H129" s="38"/>
       <c r="I129" s="38"/>
@@ -4942,10 +4780,10 @@
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="21"/>
       <c r="B130" s="38"/>
-      <c r="C130" s="33"/>
-      <c r="D130" s="34"/>
-      <c r="E130" s="22"/>
-      <c r="F130" s="22"/>
+      <c r="C130" s="32"/>
+      <c r="D130" s="33"/>
+      <c r="E130" s="30"/>
+      <c r="F130" s="30"/>
       <c r="G130" s="48"/>
       <c r="H130" s="38"/>
       <c r="I130" s="38"/>
@@ -4953,10 +4791,10 @@
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
       <c r="A131" s="21"/>
       <c r="B131" s="38"/>
-      <c r="C131" s="33"/>
-      <c r="D131" s="34"/>
-      <c r="E131" s="22"/>
-      <c r="F131" s="22"/>
+      <c r="C131" s="32"/>
+      <c r="D131" s="33"/>
+      <c r="E131" s="30"/>
+      <c r="F131" s="30"/>
       <c r="G131" s="48"/>
       <c r="H131" s="38"/>
       <c r="I131" s="38"/>
@@ -4964,10 +4802,10 @@
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
       <c r="A132" s="21"/>
       <c r="B132" s="38"/>
-      <c r="C132" s="33"/>
-      <c r="D132" s="34"/>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
+      <c r="C132" s="32"/>
+      <c r="D132" s="33"/>
+      <c r="E132" s="30"/>
+      <c r="F132" s="30"/>
       <c r="G132" s="48"/>
       <c r="H132" s="38"/>
       <c r="I132" s="38"/>
@@ -4975,10 +4813,10 @@
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
       <c r="A133" s="21"/>
       <c r="B133" s="38"/>
-      <c r="C133" s="33"/>
-      <c r="D133" s="34"/>
-      <c r="E133" s="22"/>
-      <c r="F133" s="22"/>
+      <c r="C133" s="32"/>
+      <c r="D133" s="33"/>
+      <c r="E133" s="30"/>
+      <c r="F133" s="30"/>
       <c r="G133" s="48"/>
       <c r="H133" s="38"/>
       <c r="I133" s="38"/>
@@ -4986,10 +4824,10 @@
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="21"/>
       <c r="B134" s="38"/>
-      <c r="C134" s="33"/>
-      <c r="D134" s="34"/>
-      <c r="E134" s="22"/>
-      <c r="F134" s="22"/>
+      <c r="C134" s="32"/>
+      <c r="D134" s="33"/>
+      <c r="E134" s="30"/>
+      <c r="F134" s="30"/>
       <c r="G134" s="48"/>
       <c r="H134" s="38"/>
       <c r="I134" s="38"/>
@@ -4997,10 +4835,10 @@
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
       <c r="A135" s="21"/>
       <c r="B135" s="38"/>
-      <c r="C135" s="33"/>
-      <c r="D135" s="34"/>
-      <c r="E135" s="22"/>
-      <c r="F135" s="22"/>
+      <c r="C135" s="32"/>
+      <c r="D135" s="33"/>
+      <c r="E135" s="30"/>
+      <c r="F135" s="30"/>
       <c r="G135" s="48"/>
       <c r="H135" s="38"/>
       <c r="I135" s="38"/>
@@ -5008,10 +4846,10 @@
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
       <c r="A136" s="21"/>
       <c r="B136" s="38"/>
-      <c r="C136" s="33"/>
-      <c r="D136" s="34"/>
-      <c r="E136" s="22"/>
-      <c r="F136" s="22"/>
+      <c r="C136" s="32"/>
+      <c r="D136" s="33"/>
+      <c r="E136" s="30"/>
+      <c r="F136" s="30"/>
       <c r="G136" s="48"/>
       <c r="H136" s="38"/>
       <c r="I136" s="38"/>
@@ -5019,10 +4857,10 @@
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
       <c r="A137" s="21"/>
       <c r="B137" s="38"/>
-      <c r="C137" s="33"/>
-      <c r="D137" s="34"/>
-      <c r="E137" s="22"/>
-      <c r="F137" s="22"/>
+      <c r="C137" s="32"/>
+      <c r="D137" s="33"/>
+      <c r="E137" s="30"/>
+      <c r="F137" s="30"/>
       <c r="G137" s="48"/>
       <c r="H137" s="38"/>
       <c r="I137" s="38"/>
@@ -5030,10 +4868,10 @@
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
       <c r="A138" s="21"/>
       <c r="B138" s="38"/>
-      <c r="C138" s="33"/>
-      <c r="D138" s="34"/>
-      <c r="E138" s="22"/>
-      <c r="F138" s="22"/>
+      <c r="C138" s="32"/>
+      <c r="D138" s="33"/>
+      <c r="E138" s="30"/>
+      <c r="F138" s="30"/>
       <c r="G138" s="48"/>
       <c r="H138" s="38"/>
       <c r="I138" s="38"/>
@@ -5041,10 +4879,10 @@
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
       <c r="A139" s="21"/>
       <c r="B139" s="38"/>
-      <c r="C139" s="33"/>
-      <c r="D139" s="34"/>
-      <c r="E139" s="22"/>
-      <c r="F139" s="22"/>
+      <c r="C139" s="32"/>
+      <c r="D139" s="33"/>
+      <c r="E139" s="30"/>
+      <c r="F139" s="30"/>
       <c r="G139" s="48"/>
       <c r="H139" s="38"/>
       <c r="I139" s="38"/>
@@ -5052,10 +4890,10 @@
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
       <c r="A140" s="21"/>
       <c r="B140" s="38"/>
-      <c r="C140" s="33"/>
-      <c r="D140" s="34"/>
-      <c r="E140" s="22"/>
-      <c r="F140" s="22"/>
+      <c r="C140" s="32"/>
+      <c r="D140" s="33"/>
+      <c r="E140" s="30"/>
+      <c r="F140" s="30"/>
       <c r="G140" s="48"/>
       <c r="H140" s="38"/>
       <c r="I140" s="38"/>
@@ -5063,10 +4901,10 @@
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
       <c r="A141" s="21"/>
       <c r="B141" s="38"/>
-      <c r="C141" s="33"/>
-      <c r="D141" s="34"/>
-      <c r="E141" s="22"/>
-      <c r="F141" s="22"/>
+      <c r="C141" s="32"/>
+      <c r="D141" s="33"/>
+      <c r="E141" s="30"/>
+      <c r="F141" s="30"/>
       <c r="G141" s="48"/>
       <c r="H141" s="38"/>
       <c r="I141" s="38"/>
@@ -5074,10 +4912,10 @@
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
       <c r="A142" s="21"/>
       <c r="B142" s="38"/>
-      <c r="C142" s="33"/>
-      <c r="D142" s="34"/>
-      <c r="E142" s="22"/>
-      <c r="F142" s="22"/>
+      <c r="C142" s="32"/>
+      <c r="D142" s="33"/>
+      <c r="E142" s="30"/>
+      <c r="F142" s="30"/>
       <c r="G142" s="48"/>
       <c r="H142" s="38"/>
       <c r="I142" s="38"/>
@@ -5085,10 +4923,10 @@
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
       <c r="A143" s="21"/>
       <c r="B143" s="38"/>
-      <c r="C143" s="33"/>
-      <c r="D143" s="34"/>
-      <c r="E143" s="22"/>
-      <c r="F143" s="22"/>
+      <c r="C143" s="32"/>
+      <c r="D143" s="33"/>
+      <c r="E143" s="30"/>
+      <c r="F143" s="30"/>
       <c r="G143" s="48"/>
       <c r="H143" s="38"/>
       <c r="I143" s="38"/>
@@ -5096,10 +4934,10 @@
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
       <c r="A144" s="21"/>
       <c r="B144" s="38"/>
-      <c r="C144" s="33"/>
-      <c r="D144" s="34"/>
-      <c r="E144" s="22"/>
-      <c r="F144" s="22"/>
+      <c r="C144" s="32"/>
+      <c r="D144" s="33"/>
+      <c r="E144" s="30"/>
+      <c r="F144" s="30"/>
       <c r="G144" s="48"/>
       <c r="H144" s="38"/>
       <c r="I144" s="38"/>
@@ -5107,10 +4945,10 @@
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
       <c r="A145" s="21"/>
       <c r="B145" s="38"/>
-      <c r="C145" s="33"/>
-      <c r="D145" s="34"/>
-      <c r="E145" s="22"/>
-      <c r="F145" s="22"/>
+      <c r="C145" s="32"/>
+      <c r="D145" s="33"/>
+      <c r="E145" s="30"/>
+      <c r="F145" s="30"/>
       <c r="G145" s="48"/>
       <c r="H145" s="38"/>
       <c r="I145" s="38"/>
@@ -5118,10 +4956,10 @@
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
       <c r="A146" s="21"/>
       <c r="B146" s="38"/>
-      <c r="C146" s="33"/>
-      <c r="D146" s="34"/>
-      <c r="E146" s="22"/>
-      <c r="F146" s="22"/>
+      <c r="C146" s="32"/>
+      <c r="D146" s="33"/>
+      <c r="E146" s="30"/>
+      <c r="F146" s="30"/>
       <c r="G146" s="48"/>
       <c r="H146" s="38"/>
       <c r="I146" s="38"/>
@@ -5129,10 +4967,10 @@
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
       <c r="A147" s="21"/>
       <c r="B147" s="38"/>
-      <c r="C147" s="33"/>
-      <c r="D147" s="34"/>
-      <c r="E147" s="22"/>
-      <c r="F147" s="22"/>
+      <c r="C147" s="32"/>
+      <c r="D147" s="33"/>
+      <c r="E147" s="30"/>
+      <c r="F147" s="30"/>
       <c r="G147" s="48"/>
       <c r="H147" s="38"/>
       <c r="I147" s="38"/>
@@ -5140,10 +4978,10 @@
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
       <c r="A148" s="21"/>
       <c r="B148" s="38"/>
-      <c r="C148" s="33"/>
-      <c r="D148" s="34"/>
-      <c r="E148" s="22"/>
-      <c r="F148" s="22"/>
+      <c r="C148" s="32"/>
+      <c r="D148" s="33"/>
+      <c r="E148" s="30"/>
+      <c r="F148" s="30"/>
       <c r="G148" s="48"/>
       <c r="H148" s="38"/>
       <c r="I148" s="38"/>
@@ -5151,10 +4989,10 @@
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
       <c r="A149" s="21"/>
       <c r="B149" s="38"/>
-      <c r="C149" s="33"/>
-      <c r="D149" s="34"/>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
+      <c r="C149" s="32"/>
+      <c r="D149" s="33"/>
+      <c r="E149" s="30"/>
+      <c r="F149" s="30"/>
       <c r="G149" s="48"/>
       <c r="H149" s="38"/>
       <c r="I149" s="38"/>
@@ -5162,10 +5000,10 @@
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
       <c r="A150" s="21"/>
       <c r="B150" s="38"/>
-      <c r="C150" s="33"/>
-      <c r="D150" s="34"/>
-      <c r="E150" s="22"/>
-      <c r="F150" s="22"/>
+      <c r="C150" s="32"/>
+      <c r="D150" s="33"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
       <c r="G150" s="48"/>
       <c r="H150" s="38"/>
       <c r="I150" s="38"/>
@@ -5173,10 +5011,10 @@
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
       <c r="A151" s="21"/>
       <c r="B151" s="38"/>
-      <c r="C151" s="33"/>
-      <c r="D151" s="34"/>
-      <c r="E151" s="22"/>
-      <c r="F151" s="22"/>
+      <c r="C151" s="32"/>
+      <c r="D151" s="33"/>
+      <c r="E151" s="30"/>
+      <c r="F151" s="30"/>
       <c r="G151" s="48"/>
       <c r="H151" s="38"/>
       <c r="I151" s="38"/>
@@ -5184,10 +5022,10 @@
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
       <c r="A152" s="21"/>
       <c r="B152" s="38"/>
-      <c r="C152" s="33"/>
-      <c r="D152" s="34"/>
-      <c r="E152" s="22"/>
-      <c r="F152" s="22"/>
+      <c r="C152" s="32"/>
+      <c r="D152" s="33"/>
+      <c r="E152" s="30"/>
+      <c r="F152" s="30"/>
       <c r="G152" s="48"/>
       <c r="H152" s="38"/>
       <c r="I152" s="38"/>
@@ -5195,10 +5033,10 @@
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
       <c r="A153" s="21"/>
       <c r="B153" s="38"/>
-      <c r="C153" s="33"/>
-      <c r="D153" s="34"/>
-      <c r="E153" s="22"/>
-      <c r="F153" s="22"/>
+      <c r="C153" s="32"/>
+      <c r="D153" s="33"/>
+      <c r="E153" s="30"/>
+      <c r="F153" s="30"/>
       <c r="G153" s="48"/>
       <c r="H153" s="38"/>
       <c r="I153" s="38"/>
@@ -5206,10 +5044,10 @@
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="21"/>
       <c r="B154" s="38"/>
-      <c r="C154" s="33"/>
-      <c r="D154" s="34"/>
-      <c r="E154" s="22"/>
-      <c r="F154" s="22"/>
+      <c r="C154" s="32"/>
+      <c r="D154" s="33"/>
+      <c r="E154" s="30"/>
+      <c r="F154" s="30"/>
       <c r="G154" s="48"/>
       <c r="H154" s="38"/>
       <c r="I154" s="38"/>
@@ -5217,10 +5055,10 @@
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="21"/>
       <c r="B155" s="38"/>
-      <c r="C155" s="33"/>
-      <c r="D155" s="34"/>
-      <c r="E155" s="22"/>
-      <c r="F155" s="22"/>
+      <c r="C155" s="32"/>
+      <c r="D155" s="33"/>
+      <c r="E155" s="30"/>
+      <c r="F155" s="30"/>
       <c r="G155" s="48"/>
       <c r="H155" s="38"/>
       <c r="I155" s="38"/>
@@ -5228,10 +5066,10 @@
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="21"/>
       <c r="B156" s="38"/>
-      <c r="C156" s="33"/>
-      <c r="D156" s="34"/>
-      <c r="E156" s="22"/>
-      <c r="F156" s="22"/>
+      <c r="C156" s="32"/>
+      <c r="D156" s="33"/>
+      <c r="E156" s="30"/>
+      <c r="F156" s="30"/>
       <c r="G156" s="48"/>
       <c r="H156" s="38"/>
       <c r="I156" s="38"/>
@@ -5239,10 +5077,10 @@
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="21"/>
       <c r="B157" s="38"/>
-      <c r="C157" s="33"/>
-      <c r="D157" s="34"/>
-      <c r="E157" s="22"/>
-      <c r="F157" s="22"/>
+      <c r="C157" s="32"/>
+      <c r="D157" s="33"/>
+      <c r="E157" s="30"/>
+      <c r="F157" s="30"/>
       <c r="G157" s="48"/>
       <c r="H157" s="38"/>
       <c r="I157" s="38"/>
@@ -5250,10 +5088,10 @@
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="21"/>
       <c r="B158" s="38"/>
-      <c r="C158" s="33"/>
-      <c r="D158" s="34"/>
-      <c r="E158" s="22"/>
-      <c r="F158" s="22"/>
+      <c r="C158" s="32"/>
+      <c r="D158" s="33"/>
+      <c r="E158" s="30"/>
+      <c r="F158" s="30"/>
       <c r="G158" s="48"/>
       <c r="H158" s="38"/>
       <c r="I158" s="38"/>
@@ -5261,10 +5099,10 @@
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="21"/>
       <c r="B159" s="38"/>
-      <c r="C159" s="33"/>
-      <c r="D159" s="34"/>
-      <c r="E159" s="22"/>
-      <c r="F159" s="22"/>
+      <c r="C159" s="32"/>
+      <c r="D159" s="33"/>
+      <c r="E159" s="30"/>
+      <c r="F159" s="30"/>
       <c r="G159" s="48"/>
       <c r="H159" s="38"/>
       <c r="I159" s="38"/>
@@ -5272,10 +5110,10 @@
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="21"/>
       <c r="B160" s="38"/>
-      <c r="C160" s="33"/>
-      <c r="D160" s="34"/>
-      <c r="E160" s="22"/>
-      <c r="F160" s="22"/>
+      <c r="C160" s="32"/>
+      <c r="D160" s="33"/>
+      <c r="E160" s="30"/>
+      <c r="F160" s="30"/>
       <c r="G160" s="48"/>
       <c r="H160" s="38"/>
       <c r="I160" s="38"/>
@@ -5283,10 +5121,10 @@
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="21"/>
       <c r="B161" s="38"/>
-      <c r="C161" s="33"/>
-      <c r="D161" s="34"/>
-      <c r="E161" s="22"/>
-      <c r="F161" s="22"/>
+      <c r="C161" s="32"/>
+      <c r="D161" s="33"/>
+      <c r="E161" s="30"/>
+      <c r="F161" s="30"/>
       <c r="G161" s="48"/>
       <c r="H161" s="38"/>
       <c r="I161" s="38"/>
@@ -5294,10 +5132,10 @@
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="21"/>
       <c r="B162" s="38"/>
-      <c r="C162" s="33"/>
-      <c r="D162" s="34"/>
-      <c r="E162" s="22"/>
-      <c r="F162" s="22"/>
+      <c r="C162" s="32"/>
+      <c r="D162" s="33"/>
+      <c r="E162" s="30"/>
+      <c r="F162" s="30"/>
       <c r="G162" s="48"/>
       <c r="H162" s="38"/>
       <c r="I162" s="38"/>
@@ -5305,10 +5143,10 @@
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="21"/>
       <c r="B163" s="38"/>
-      <c r="C163" s="33"/>
-      <c r="D163" s="34"/>
-      <c r="E163" s="22"/>
-      <c r="F163" s="22"/>
+      <c r="C163" s="32"/>
+      <c r="D163" s="33"/>
+      <c r="E163" s="30"/>
+      <c r="F163" s="30"/>
       <c r="G163" s="48"/>
       <c r="H163" s="38"/>
       <c r="I163" s="38"/>
@@ -5316,10 +5154,10 @@
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="21"/>
       <c r="B164" s="38"/>
-      <c r="C164" s="33"/>
-      <c r="D164" s="34"/>
-      <c r="E164" s="22"/>
-      <c r="F164" s="22"/>
+      <c r="C164" s="32"/>
+      <c r="D164" s="33"/>
+      <c r="E164" s="30"/>
+      <c r="F164" s="30"/>
       <c r="G164" s="48"/>
       <c r="H164" s="38"/>
       <c r="I164" s="38"/>
@@ -5327,10 +5165,10 @@
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="21"/>
       <c r="B165" s="38"/>
-      <c r="C165" s="33"/>
-      <c r="D165" s="34"/>
-      <c r="E165" s="22"/>
-      <c r="F165" s="22"/>
+      <c r="C165" s="32"/>
+      <c r="D165" s="33"/>
+      <c r="E165" s="30"/>
+      <c r="F165" s="30"/>
       <c r="G165" s="48"/>
       <c r="H165" s="38"/>
       <c r="I165" s="38"/>
@@ -5338,10 +5176,10 @@
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="21"/>
       <c r="B166" s="38"/>
-      <c r="C166" s="33"/>
-      <c r="D166" s="34"/>
-      <c r="E166" s="22"/>
-      <c r="F166" s="22"/>
+      <c r="C166" s="32"/>
+      <c r="D166" s="33"/>
+      <c r="E166" s="30"/>
+      <c r="F166" s="30"/>
       <c r="G166" s="48"/>
       <c r="H166" s="38"/>
       <c r="I166" s="38"/>
@@ -5349,10 +5187,10 @@
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="21"/>
       <c r="B167" s="38"/>
-      <c r="C167" s="33"/>
-      <c r="D167" s="34"/>
-      <c r="E167" s="22"/>
-      <c r="F167" s="22"/>
+      <c r="C167" s="32"/>
+      <c r="D167" s="33"/>
+      <c r="E167" s="30"/>
+      <c r="F167" s="30"/>
       <c r="G167" s="48"/>
       <c r="H167" s="38"/>
       <c r="I167" s="38"/>
@@ -5360,10 +5198,10 @@
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="21"/>
       <c r="B168" s="38"/>
-      <c r="C168" s="33"/>
-      <c r="D168" s="34"/>
-      <c r="E168" s="22"/>
-      <c r="F168" s="22"/>
+      <c r="C168" s="32"/>
+      <c r="D168" s="33"/>
+      <c r="E168" s="30"/>
+      <c r="F168" s="30"/>
       <c r="G168" s="48"/>
       <c r="H168" s="38"/>
       <c r="I168" s="38"/>
@@ -5371,10 +5209,10 @@
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
       <c r="A169" s="21"/>
       <c r="B169" s="38"/>
-      <c r="C169" s="33"/>
-      <c r="D169" s="34"/>
-      <c r="E169" s="22"/>
-      <c r="F169" s="22"/>
+      <c r="C169" s="32"/>
+      <c r="D169" s="33"/>
+      <c r="E169" s="30"/>
+      <c r="F169" s="30"/>
       <c r="G169" s="48"/>
       <c r="H169" s="38"/>
       <c r="I169" s="38"/>
@@ -5382,10 +5220,10 @@
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
       <c r="A170" s="21"/>
       <c r="B170" s="38"/>
-      <c r="C170" s="33"/>
-      <c r="D170" s="34"/>
-      <c r="E170" s="22"/>
-      <c r="F170" s="22"/>
+      <c r="C170" s="32"/>
+      <c r="D170" s="33"/>
+      <c r="E170" s="30"/>
+      <c r="F170" s="30"/>
       <c r="G170" s="48"/>
       <c r="H170" s="38"/>
       <c r="I170" s="38"/>
@@ -5393,10 +5231,10 @@
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
       <c r="A171" s="21"/>
       <c r="B171" s="38"/>
-      <c r="C171" s="33"/>
-      <c r="D171" s="34"/>
-      <c r="E171" s="22"/>
-      <c r="F171" s="22"/>
+      <c r="C171" s="32"/>
+      <c r="D171" s="33"/>
+      <c r="E171" s="30"/>
+      <c r="F171" s="30"/>
       <c r="G171" s="48"/>
       <c r="H171" s="38"/>
       <c r="I171" s="38"/>
@@ -5404,10 +5242,10 @@
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
       <c r="A172" s="21"/>
       <c r="B172" s="38"/>
-      <c r="C172" s="33"/>
-      <c r="D172" s="34"/>
-      <c r="E172" s="22"/>
-      <c r="F172" s="22"/>
+      <c r="C172" s="32"/>
+      <c r="D172" s="33"/>
+      <c r="E172" s="30"/>
+      <c r="F172" s="30"/>
       <c r="G172" s="48"/>
       <c r="H172" s="38"/>
       <c r="I172" s="38"/>
@@ -5415,10 +5253,10 @@
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
       <c r="A173" s="21"/>
       <c r="B173" s="38"/>
-      <c r="C173" s="33"/>
-      <c r="D173" s="34"/>
-      <c r="E173" s="22"/>
-      <c r="F173" s="22"/>
+      <c r="C173" s="32"/>
+      <c r="D173" s="33"/>
+      <c r="E173" s="30"/>
+      <c r="F173" s="30"/>
       <c r="G173" s="48"/>
       <c r="H173" s="38"/>
       <c r="I173" s="38"/>
@@ -5426,10 +5264,10 @@
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
       <c r="A174" s="21"/>
       <c r="B174" s="38"/>
-      <c r="C174" s="33"/>
-      <c r="D174" s="34"/>
-      <c r="E174" s="22"/>
-      <c r="F174" s="22"/>
+      <c r="C174" s="32"/>
+      <c r="D174" s="33"/>
+      <c r="E174" s="30"/>
+      <c r="F174" s="30"/>
       <c r="G174" s="48"/>
       <c r="H174" s="38"/>
       <c r="I174" s="38"/>
@@ -5437,10 +5275,10 @@
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
       <c r="A175" s="21"/>
       <c r="B175" s="38"/>
-      <c r="C175" s="33"/>
-      <c r="D175" s="34"/>
-      <c r="E175" s="22"/>
-      <c r="F175" s="22"/>
+      <c r="C175" s="32"/>
+      <c r="D175" s="33"/>
+      <c r="E175" s="30"/>
+      <c r="F175" s="30"/>
       <c r="G175" s="48"/>
       <c r="H175" s="38"/>
       <c r="I175" s="38"/>
@@ -5449,9 +5287,9 @@
       <c r="A176" s="21"/>
       <c r="B176" s="2"/>
       <c r="C176" s="49"/>
-      <c r="D176" s="34"/>
-      <c r="E176" s="22"/>
-      <c r="F176" s="22"/>
+      <c r="D176" s="33"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="30"/>
       <c r="G176" s="38"/>
       <c r="H176" s="38"/>
       <c r="I176" s="38"/>
@@ -5774,9 +5612,9 @@
   <cols>
     <col min="1" max="1" style="23" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="43.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="36" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="35" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="36" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="24" width="10.862142857142858" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="24" width="16.433571428571426" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -5807,7 +5645,7 @@
       <c r="D2" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="30" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="14" t="s">
@@ -5825,19 +5663,17 @@
       <c r="B3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="31">
         <v>15.45</v>
       </c>
       <c r="D3" s="18">
         <v>45383</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="30" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="19"/>
-      <c r="G3" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G3" s="19"/>
       <c r="H3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -5845,21 +5681,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="30">
+        <v>16</v>
+      </c>
+      <c r="C4" s="31">
         <v>1.08</v>
       </c>
       <c r="D4" s="18">
         <v>45383</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="30" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="19"/>
-      <c r="G4" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G4" s="19"/>
       <c r="H4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -5867,21 +5701,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" s="31">
         <v>13.03</v>
       </c>
       <c r="D5" s="18">
         <v>45383</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="30" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="17"/>
-      <c r="G5" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G5" s="19"/>
       <c r="H5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -5889,21 +5721,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="30">
+        <v>18</v>
+      </c>
+      <c r="C6" s="31">
         <v>19.1</v>
       </c>
       <c r="D6" s="18">
         <v>45383</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="30" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="17"/>
-      <c r="G6" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G6" s="19"/>
       <c r="H6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -5911,21 +5741,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="30">
+        <v>19</v>
+      </c>
+      <c r="C7" s="31">
         <v>0.16</v>
       </c>
       <c r="D7" s="18">
         <v>45383</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="30" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="17"/>
-      <c r="G7" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -5933,21 +5761,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="30">
+        <v>20</v>
+      </c>
+      <c r="C8" s="31">
         <v>14.01</v>
       </c>
       <c r="D8" s="18">
         <v>45383</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="30" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="17"/>
-      <c r="G8" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G8" s="19"/>
       <c r="H8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -5955,21 +5781,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="30">
+        <v>21</v>
+      </c>
+      <c r="C9" s="31">
         <v>8.52</v>
       </c>
       <c r="D9" s="18">
         <v>45384</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>23</v>
+      <c r="E9" s="30" t="s">
+        <v>22</v>
       </c>
       <c r="F9" s="17"/>
-      <c r="G9" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G9" s="17"/>
       <c r="H9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -5977,21 +5801,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="30">
+        <v>23</v>
+      </c>
+      <c r="C10" s="31">
         <v>0.18</v>
       </c>
       <c r="D10" s="18">
         <v>45384</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>23</v>
+      <c r="E10" s="30" t="s">
+        <v>22</v>
       </c>
       <c r="F10" s="17"/>
-      <c r="G10" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G10" s="17"/>
       <c r="H10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -5999,21 +5821,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="30">
+        <v>24</v>
+      </c>
+      <c r="C11" s="31">
         <v>8.35</v>
       </c>
       <c r="D11" s="18">
         <v>45384</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>23</v>
+      <c r="E11" s="30" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="17"/>
-      <c r="G11" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G11" s="17"/>
       <c r="H11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -6021,21 +5841,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="30">
+        <v>25</v>
+      </c>
+      <c r="C12" s="31">
         <v>7.35</v>
       </c>
       <c r="D12" s="18">
         <v>45384</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>23</v>
+      <c r="E12" s="30" t="s">
+        <v>22</v>
       </c>
       <c r="F12" s="17"/>
-      <c r="G12" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G12" s="17"/>
       <c r="H12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -6043,21 +5861,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="30">
+        <v>26</v>
+      </c>
+      <c r="C13" s="31">
         <v>11.4</v>
       </c>
       <c r="D13" s="18">
         <v>45384</v>
       </c>
-      <c r="E13" s="22" t="s">
-        <v>23</v>
+      <c r="E13" s="30" t="s">
+        <v>22</v>
       </c>
       <c r="F13" s="17"/>
-      <c r="G13" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G13" s="17"/>
       <c r="H13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
@@ -6065,21 +5881,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="30">
+        <v>27</v>
+      </c>
+      <c r="C14" s="31">
         <v>11.09</v>
       </c>
       <c r="D14" s="18">
         <v>45384</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>23</v>
+      <c r="E14" s="30" t="s">
+        <v>22</v>
       </c>
       <c r="F14" s="17"/>
-      <c r="G14" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G14" s="17"/>
       <c r="H14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
@@ -6087,21 +5901,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="30">
+        <v>28</v>
+      </c>
+      <c r="C15" s="31">
         <v>15.16</v>
       </c>
       <c r="D15" s="18">
         <v>45384</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>23</v>
+      <c r="E15" s="30" t="s">
+        <v>22</v>
       </c>
       <c r="F15" s="17"/>
-      <c r="G15" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G15" s="17"/>
       <c r="H15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -6109,21 +5921,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="30">
+        <v>29</v>
+      </c>
+      <c r="C16" s="31">
         <v>9.31</v>
       </c>
       <c r="D16" s="18">
         <v>45385</v>
       </c>
-      <c r="E16" s="22" t="s">
-        <v>31</v>
+      <c r="E16" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="F16" s="17"/>
-      <c r="G16" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G16" s="17"/>
       <c r="H16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
@@ -6131,21 +5941,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="30">
+        <v>31</v>
+      </c>
+      <c r="C17" s="31">
         <v>9.16</v>
       </c>
       <c r="D17" s="18">
         <v>45385</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>31</v>
+      <c r="E17" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="F17" s="17"/>
-      <c r="G17" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G17" s="17"/>
       <c r="H17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
@@ -6153,21 +5961,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="30">
+        <v>32</v>
+      </c>
+      <c r="C18" s="31">
         <v>14.09</v>
       </c>
       <c r="D18" s="18">
         <v>45385</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>31</v>
+      <c r="E18" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="F18" s="17"/>
-      <c r="G18" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G18" s="17"/>
       <c r="H18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
@@ -6175,21 +5981,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="30">
+        <v>33</v>
+      </c>
+      <c r="C19" s="31">
         <v>14.54</v>
       </c>
       <c r="D19" s="18">
         <v>45385</v>
       </c>
-      <c r="E19" s="22" t="s">
-        <v>31</v>
+      <c r="E19" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="F19" s="17"/>
-      <c r="G19" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G19" s="17"/>
       <c r="H19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
@@ -6197,21 +6001,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="30">
+        <v>34</v>
+      </c>
+      <c r="C20" s="31">
         <v>8.57</v>
       </c>
       <c r="D20" s="18">
         <v>45385</v>
       </c>
-      <c r="E20" s="22" t="s">
-        <v>31</v>
+      <c r="E20" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="F20" s="17"/>
-      <c r="G20" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G20" s="17"/>
       <c r="H20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
@@ -6219,21 +6021,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="30">
+        <v>35</v>
+      </c>
+      <c r="C21" s="31">
         <v>16.55</v>
       </c>
       <c r="D21" s="18">
         <v>45386</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>37</v>
+      <c r="E21" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="F21" s="17"/>
-      <c r="G21" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G21" s="17"/>
       <c r="H21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
@@ -6241,7 +6041,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="15">
         <v>8</v>
@@ -6249,13 +6049,11 @@
       <c r="D22" s="18">
         <v>45386</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>37</v>
+      <c r="E22" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="F22" s="17"/>
-      <c r="G22" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G22" s="17"/>
       <c r="H22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -6263,21 +6061,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="30">
+        <v>38</v>
+      </c>
+      <c r="C23" s="31">
         <v>4.25</v>
       </c>
       <c r="D23" s="18">
         <v>45386</v>
       </c>
-      <c r="E23" s="22" t="s">
-        <v>37</v>
+      <c r="E23" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="F23" s="17"/>
-      <c r="G23" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G23" s="17"/>
       <c r="H23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
@@ -6285,21 +6081,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="30">
+        <v>39</v>
+      </c>
+      <c r="C24" s="31">
         <v>10.16</v>
       </c>
       <c r="D24" s="18">
         <v>45386</v>
       </c>
-      <c r="E24" s="22" t="s">
-        <v>37</v>
+      <c r="E24" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="F24" s="17"/>
-      <c r="G24" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G24" s="17"/>
       <c r="H24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
@@ -6307,21 +6101,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="30">
+        <v>40</v>
+      </c>
+      <c r="C25" s="31">
         <v>24.08</v>
       </c>
       <c r="D25" s="18">
         <v>45386</v>
       </c>
-      <c r="E25" s="22" t="s">
-        <v>37</v>
+      <c r="E25" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="F25" s="17"/>
-      <c r="G25" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G25" s="17"/>
       <c r="H25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
@@ -6329,21 +6121,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="30">
+        <v>19</v>
+      </c>
+      <c r="C26" s="31">
         <v>0.29</v>
       </c>
       <c r="D26" s="18">
         <v>45387</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>42</v>
+      <c r="E26" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="F26" s="17"/>
-      <c r="G26" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G26" s="17"/>
       <c r="H26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
@@ -6351,21 +6141,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="30">
+        <v>42</v>
+      </c>
+      <c r="C27" s="31">
         <v>24.46</v>
       </c>
       <c r="D27" s="18">
         <v>45387</v>
       </c>
-      <c r="E27" s="22" t="s">
-        <v>42</v>
+      <c r="E27" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="F27" s="17"/>
-      <c r="G27" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G27" s="17"/>
       <c r="H27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
@@ -6373,21 +6161,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="30">
+        <v>19</v>
+      </c>
+      <c r="C28" s="31">
         <v>0.19</v>
       </c>
       <c r="D28" s="18">
         <v>45387</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>42</v>
+      <c r="E28" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="F28" s="17"/>
-      <c r="G28" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G28" s="17"/>
       <c r="H28" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
@@ -6395,21 +6181,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="30">
+        <v>43</v>
+      </c>
+      <c r="C29" s="31">
         <v>15.03</v>
       </c>
       <c r="D29" s="18">
         <v>45387</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>42</v>
+      <c r="E29" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="F29" s="17"/>
-      <c r="G29" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G29" s="17"/>
       <c r="H29" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
@@ -6417,21 +6201,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="30">
+        <v>44</v>
+      </c>
+      <c r="C30" s="31">
         <v>5.51</v>
       </c>
       <c r="D30" s="18">
         <v>45387</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>42</v>
+      <c r="E30" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="F30" s="17"/>
-      <c r="G30" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G30" s="17"/>
       <c r="H30" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -6439,21 +6221,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="30">
+        <v>45</v>
+      </c>
+      <c r="C31" s="31">
         <v>8.45</v>
       </c>
       <c r="D31" s="18">
         <v>45387</v>
       </c>
-      <c r="E31" s="22" t="s">
-        <v>42</v>
+      <c r="E31" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="F31" s="17"/>
-      <c r="G31" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G31" s="17"/>
       <c r="H31" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -6461,21 +6241,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="30">
+        <v>46</v>
+      </c>
+      <c r="C32" s="31">
         <v>0.18</v>
       </c>
       <c r="D32" s="18">
         <v>45387</v>
       </c>
-      <c r="E32" s="22" t="s">
-        <v>42</v>
+      <c r="E32" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="F32" s="17"/>
-      <c r="G32" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G32" s="17"/>
       <c r="H32" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="33">
@@ -6483,21 +6261,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="30">
+        <v>47</v>
+      </c>
+      <c r="C33" s="31">
         <v>8.36</v>
       </c>
       <c r="D33" s="18">
         <v>45387</v>
       </c>
-      <c r="E33" s="22" t="s">
-        <v>42</v>
+      <c r="E33" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="F33" s="17"/>
-      <c r="G33" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G33" s="17"/>
       <c r="H33" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="33">
@@ -6505,21 +6281,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="30">
+        <v>48</v>
+      </c>
+      <c r="C34" s="31">
         <v>16.52</v>
       </c>
       <c r="D34" s="18">
         <v>45388</v>
       </c>
-      <c r="E34" s="22" t="s">
-        <v>50</v>
+      <c r="E34" s="30" t="s">
+        <v>49</v>
       </c>
       <c r="F34" s="17"/>
-      <c r="G34" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G34" s="17"/>
       <c r="H34" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="33">
@@ -6527,21 +6301,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="30">
+        <v>50</v>
+      </c>
+      <c r="C35" s="31">
         <v>13.16</v>
       </c>
       <c r="D35" s="18">
         <v>45388</v>
       </c>
-      <c r="E35" s="22" t="s">
-        <v>50</v>
+      <c r="E35" s="30" t="s">
+        <v>49</v>
       </c>
       <c r="F35" s="17"/>
-      <c r="G35" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G35" s="17"/>
       <c r="H35" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="33">
@@ -6549,21 +6321,19 @@
         <v>34</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="30">
+        <v>51</v>
+      </c>
+      <c r="C36" s="31">
         <v>17.01</v>
       </c>
       <c r="D36" s="18">
         <v>45388</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>50</v>
+      <c r="E36" s="30" t="s">
+        <v>49</v>
       </c>
       <c r="F36" s="17"/>
-      <c r="G36" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G36" s="17"/>
       <c r="H36" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="33">
@@ -6571,21 +6341,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="30">
+        <v>52</v>
+      </c>
+      <c r="C37" s="31">
         <v>15.07</v>
       </c>
       <c r="D37" s="18">
         <v>45388</v>
       </c>
-      <c r="E37" s="22" t="s">
-        <v>50</v>
+      <c r="E37" s="30" t="s">
+        <v>49</v>
       </c>
       <c r="F37" s="17"/>
-      <c r="G37" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G37" s="17"/>
       <c r="H37" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="33">
@@ -6593,21 +6361,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="30">
+        <v>53</v>
+      </c>
+      <c r="C38" s="31">
         <v>10.21</v>
       </c>
       <c r="D38" s="18">
         <v>45389</v>
       </c>
-      <c r="E38" s="22" t="s">
-        <v>55</v>
+      <c r="E38" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="F38" s="17"/>
-      <c r="G38" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G38" s="17"/>
       <c r="H38" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
@@ -6615,21 +6381,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="30">
+        <v>23</v>
+      </c>
+      <c r="C39" s="31">
         <v>0.34</v>
       </c>
       <c r="D39" s="18">
         <v>45389</v>
       </c>
-      <c r="E39" s="22" t="s">
-        <v>55</v>
+      <c r="E39" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="F39" s="17"/>
-      <c r="G39" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G39" s="17"/>
       <c r="H39" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="33">
@@ -6637,21 +6401,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="30">
+        <v>55</v>
+      </c>
+      <c r="C40" s="31">
         <v>14.22</v>
       </c>
       <c r="D40" s="18">
         <v>45389</v>
       </c>
-      <c r="E40" s="22" t="s">
-        <v>55</v>
+      <c r="E40" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="F40" s="17"/>
-      <c r="G40" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G40" s="17"/>
       <c r="H40" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="33">
@@ -6659,21 +6421,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="30">
+        <v>56</v>
+      </c>
+      <c r="C41" s="31">
         <v>10.5</v>
       </c>
       <c r="D41" s="18">
         <v>45389</v>
       </c>
-      <c r="E41" s="22" t="s">
-        <v>55</v>
+      <c r="E41" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="F41" s="17"/>
-      <c r="G41" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G41" s="17"/>
       <c r="H41" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="33">
@@ -6681,21 +6441,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="30">
+        <v>57</v>
+      </c>
+      <c r="C42" s="31">
         <v>7.57</v>
       </c>
       <c r="D42" s="18">
         <v>45389</v>
       </c>
-      <c r="E42" s="22" t="s">
-        <v>55</v>
+      <c r="E42" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="F42" s="17"/>
-      <c r="G42" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G42" s="17"/>
       <c r="H42" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="33">
@@ -6703,21 +6461,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" s="30">
+        <v>58</v>
+      </c>
+      <c r="C43" s="31">
         <v>5.11</v>
       </c>
       <c r="D43" s="18">
         <v>45389</v>
       </c>
-      <c r="E43" s="22" t="s">
-        <v>55</v>
+      <c r="E43" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="F43" s="17"/>
-      <c r="G43" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G43" s="17"/>
       <c r="H43" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="33">
@@ -6725,21 +6481,19 @@
         <v>42</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="30">
+        <v>59</v>
+      </c>
+      <c r="C44" s="31">
         <v>10.07</v>
       </c>
       <c r="D44" s="18">
         <v>45389</v>
       </c>
-      <c r="E44" s="22" t="s">
-        <v>55</v>
+      <c r="E44" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="F44" s="17"/>
-      <c r="G44" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G44" s="17"/>
       <c r="H44" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="33">
@@ -6747,21 +6501,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" s="30">
+        <v>60</v>
+      </c>
+      <c r="C45" s="31">
         <v>7.39</v>
       </c>
       <c r="D45" s="18">
         <v>45390</v>
       </c>
-      <c r="E45" s="22" t="s">
-        <v>62</v>
+      <c r="E45" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F45" s="17"/>
-      <c r="G45" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G45" s="17"/>
       <c r="H45" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="33">
@@ -6769,21 +6521,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="30">
+        <v>62</v>
+      </c>
+      <c r="C46" s="31">
         <v>9.22</v>
       </c>
       <c r="D46" s="18">
         <v>45390</v>
       </c>
-      <c r="E46" s="22" t="s">
-        <v>62</v>
+      <c r="E46" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F46" s="17"/>
-      <c r="G46" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G46" s="17"/>
       <c r="H46" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="33">
@@ -6791,21 +6541,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="30">
+        <v>63</v>
+      </c>
+      <c r="C47" s="31">
         <v>9.29</v>
       </c>
       <c r="D47" s="18">
         <v>45390</v>
       </c>
-      <c r="E47" s="22" t="s">
-        <v>62</v>
+      <c r="E47" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F47" s="17"/>
-      <c r="G47" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G47" s="17"/>
       <c r="H47" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="33">
@@ -6813,21 +6561,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C48" s="30">
+        <v>64</v>
+      </c>
+      <c r="C48" s="31">
         <v>7.16</v>
       </c>
       <c r="D48" s="18">
         <v>45390</v>
       </c>
-      <c r="E48" s="22" t="s">
-        <v>62</v>
+      <c r="E48" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F48" s="17"/>
-      <c r="G48" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G48" s="17"/>
       <c r="H48" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="33">
@@ -6835,21 +6581,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C49" s="30">
+        <v>65</v>
+      </c>
+      <c r="C49" s="31">
         <v>6.1</v>
       </c>
       <c r="D49" s="18">
         <v>45390</v>
       </c>
-      <c r="E49" s="22" t="s">
-        <v>62</v>
+      <c r="E49" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F49" s="17"/>
-      <c r="G49" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G49" s="17"/>
       <c r="H49" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="33">
@@ -6857,21 +6601,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="30">
+        <v>66</v>
+      </c>
+      <c r="C50" s="31">
         <v>6.36</v>
       </c>
       <c r="D50" s="18">
         <v>45390</v>
       </c>
-      <c r="E50" s="22" t="s">
-        <v>62</v>
+      <c r="E50" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F50" s="17"/>
-      <c r="G50" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G50" s="17"/>
       <c r="H50" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="33">
@@ -6879,21 +6621,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C51" s="30">
+        <v>67</v>
+      </c>
+      <c r="C51" s="31">
         <v>7.32</v>
       </c>
       <c r="D51" s="18">
         <v>45390</v>
       </c>
-      <c r="E51" s="22" t="s">
-        <v>62</v>
+      <c r="E51" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F51" s="17"/>
-      <c r="G51" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G51" s="17"/>
       <c r="H51" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="33">
@@ -6901,21 +6641,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C52" s="30">
+        <v>68</v>
+      </c>
+      <c r="C52" s="31">
         <v>6.15</v>
       </c>
       <c r="D52" s="18">
         <v>45390</v>
       </c>
-      <c r="E52" s="22" t="s">
-        <v>62</v>
+      <c r="E52" s="30" t="s">
+        <v>61</v>
       </c>
       <c r="F52" s="17"/>
-      <c r="G52" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G52" s="17"/>
       <c r="H52" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="33">
@@ -6923,21 +6661,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="30">
+        <v>69</v>
+      </c>
+      <c r="C53" s="31">
         <v>6.07</v>
       </c>
       <c r="D53" s="18">
         <v>45391</v>
       </c>
-      <c r="E53" s="22" t="s">
-        <v>71</v>
+      <c r="E53" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="F53" s="17"/>
-      <c r="G53" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G53" s="17"/>
       <c r="H53" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
@@ -6945,21 +6681,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C54" s="30">
+        <v>71</v>
+      </c>
+      <c r="C54" s="31">
         <v>5.04</v>
       </c>
       <c r="D54" s="18">
         <v>45391</v>
       </c>
-      <c r="E54" s="22" t="s">
-        <v>71</v>
+      <c r="E54" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="F54" s="17"/>
-      <c r="G54" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G54" s="17"/>
       <c r="H54" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
@@ -6967,21 +6701,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C55" s="30">
+        <v>72</v>
+      </c>
+      <c r="C55" s="31">
         <v>9.41</v>
       </c>
       <c r="D55" s="18">
         <v>45391</v>
       </c>
-      <c r="E55" s="22" t="s">
-        <v>71</v>
+      <c r="E55" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="F55" s="17"/>
-      <c r="G55" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G55" s="17"/>
       <c r="H55" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -6989,21 +6721,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="30">
+        <v>73</v>
+      </c>
+      <c r="C56" s="31">
         <v>6.12</v>
       </c>
       <c r="D56" s="18">
         <v>45391</v>
       </c>
-      <c r="E56" s="22" t="s">
-        <v>71</v>
+      <c r="E56" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="F56" s="17"/>
-      <c r="G56" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G56" s="17"/>
       <c r="H56" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
@@ -7011,21 +6741,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" s="30">
+        <v>74</v>
+      </c>
+      <c r="C57" s="31">
         <v>4.11</v>
       </c>
       <c r="D57" s="18">
         <v>45391</v>
       </c>
-      <c r="E57" s="22" t="s">
-        <v>71</v>
+      <c r="E57" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="F57" s="17"/>
-      <c r="G57" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G57" s="17"/>
       <c r="H57" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
@@ -7033,21 +6761,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="30">
+        <v>75</v>
+      </c>
+      <c r="C58" s="31">
         <v>9.3</v>
       </c>
       <c r="D58" s="18">
         <v>45391</v>
       </c>
-      <c r="E58" s="22" t="s">
-        <v>71</v>
+      <c r="E58" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="F58" s="17"/>
-      <c r="G58" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G58" s="17"/>
       <c r="H58" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -7055,21 +6781,19 @@
         <v>57</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C59" s="30">
+        <v>76</v>
+      </c>
+      <c r="C59" s="31">
         <v>8.06</v>
       </c>
       <c r="D59" s="18">
         <v>45391</v>
       </c>
-      <c r="E59" s="22" t="s">
-        <v>71</v>
+      <c r="E59" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="F59" s="17"/>
-      <c r="G59" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G59" s="17"/>
       <c r="H59" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
@@ -7077,21 +6801,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C60" s="30">
+        <v>77</v>
+      </c>
+      <c r="C60" s="31">
         <v>10.35</v>
       </c>
       <c r="D60" s="18">
         <v>45391</v>
       </c>
-      <c r="E60" s="22" t="s">
-        <v>71</v>
+      <c r="E60" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="F60" s="17"/>
-      <c r="G60" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G60" s="17"/>
       <c r="H60" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
@@ -7099,21 +6821,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="30">
+        <v>78</v>
+      </c>
+      <c r="C61" s="31">
         <v>9.22</v>
       </c>
       <c r="D61" s="18">
         <v>45392</v>
       </c>
-      <c r="E61" s="22" t="s">
-        <v>80</v>
+      <c r="E61" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="F61" s="17"/>
-      <c r="G61" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G61" s="17"/>
       <c r="H61" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
@@ -7121,21 +6841,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C62" s="30">
+        <v>80</v>
+      </c>
+      <c r="C62" s="31">
         <v>8.05</v>
       </c>
       <c r="D62" s="18">
         <v>45392</v>
       </c>
-      <c r="E62" s="22" t="s">
-        <v>80</v>
+      <c r="E62" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="F62" s="17"/>
-      <c r="G62" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G62" s="17"/>
       <c r="H62" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -7143,21 +6861,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C63" s="30">
+        <v>81</v>
+      </c>
+      <c r="C63" s="31">
         <v>14.14</v>
       </c>
       <c r="D63" s="18">
         <v>45392</v>
       </c>
-      <c r="E63" s="22" t="s">
-        <v>80</v>
+      <c r="E63" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="F63" s="17"/>
-      <c r="G63" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G63" s="17"/>
       <c r="H63" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
@@ -7165,21 +6881,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C64" s="30">
+        <v>82</v>
+      </c>
+      <c r="C64" s="31">
         <v>14.38</v>
       </c>
       <c r="D64" s="18">
         <v>45392</v>
       </c>
-      <c r="E64" s="22" t="s">
-        <v>80</v>
+      <c r="E64" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="F64" s="17"/>
-      <c r="G64" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G64" s="17"/>
       <c r="H64" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -7187,21 +6901,19 @@
         <v>63</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C65" s="30">
+        <v>83</v>
+      </c>
+      <c r="C65" s="31">
         <v>13.16</v>
       </c>
       <c r="D65" s="18">
         <v>45392</v>
       </c>
-      <c r="E65" s="22" t="s">
-        <v>80</v>
+      <c r="E65" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="F65" s="17"/>
-      <c r="G65" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G65" s="17"/>
       <c r="H65" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
@@ -7209,21 +6921,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C66" s="30">
+        <v>84</v>
+      </c>
+      <c r="C66" s="31">
         <v>5.57</v>
       </c>
       <c r="D66" s="18">
         <v>45393</v>
       </c>
-      <c r="E66" s="22" t="s">
-        <v>86</v>
+      <c r="E66" s="30" t="s">
+        <v>85</v>
       </c>
       <c r="F66" s="17"/>
-      <c r="G66" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G66" s="17"/>
       <c r="H66" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -7231,21 +6941,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" s="30">
+        <v>86</v>
+      </c>
+      <c r="C67" s="31">
         <v>12.55</v>
       </c>
       <c r="D67" s="18">
         <v>45393</v>
       </c>
-      <c r="E67" s="22" t="s">
-        <v>86</v>
+      <c r="E67" s="30" t="s">
+        <v>85</v>
       </c>
       <c r="F67" s="17"/>
-      <c r="G67" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G67" s="17"/>
       <c r="H67" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -7253,29 +6961,27 @@
         <v>66</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" s="30">
+        <v>87</v>
+      </c>
+      <c r="C68" s="31">
         <v>0.15</v>
       </c>
       <c r="D68" s="18">
         <v>45393</v>
       </c>
-      <c r="E68" s="22" t="s">
-        <v>86</v>
+      <c r="E68" s="30" t="s">
+        <v>85</v>
       </c>
       <c r="F68" s="17"/>
-      <c r="G68" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G68" s="17"/>
       <c r="H68" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="21"/>
       <c r="B69" s="22"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="22"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="30"/>
       <c r="F69" s="22"/>
       <c r="G69" s="22"/>
       <c r="H69" s="2"/>
@@ -7305,7 +7011,7 @@
       <c r="D71" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="30" t="s">
         <v>13</v>
       </c>
       <c r="F71" s="14" t="s">
@@ -7321,21 +7027,19 @@
         <v>1</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C72" s="30">
+        <v>88</v>
+      </c>
+      <c r="C72" s="31">
         <v>4.13</v>
       </c>
       <c r="D72" s="18">
         <v>45394</v>
       </c>
-      <c r="E72" s="22" t="s">
-        <v>90</v>
+      <c r="E72" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F72" s="19"/>
-      <c r="G72" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G72" s="19"/>
       <c r="H72" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -7343,21 +7047,19 @@
         <v>2</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C73" s="30">
+        <v>90</v>
+      </c>
+      <c r="C73" s="31">
         <v>6.33</v>
       </c>
       <c r="D73" s="18">
         <v>45394</v>
       </c>
-      <c r="E73" s="22" t="s">
-        <v>90</v>
+      <c r="E73" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F73" s="17"/>
-      <c r="G73" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G73" s="19"/>
       <c r="H73" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -7365,21 +7067,19 @@
         <v>3</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C74" s="30">
+        <v>91</v>
+      </c>
+      <c r="C74" s="31">
         <v>7.05</v>
       </c>
       <c r="D74" s="18">
         <v>45394</v>
       </c>
-      <c r="E74" s="22" t="s">
-        <v>90</v>
+      <c r="E74" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F74" s="17"/>
-      <c r="G74" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G74" s="19"/>
       <c r="H74" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -7387,21 +7087,19 @@
         <v>4</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C75" s="30">
+        <v>92</v>
+      </c>
+      <c r="C75" s="31">
         <v>5.05</v>
       </c>
       <c r="D75" s="18">
         <v>45394</v>
       </c>
-      <c r="E75" s="22" t="s">
-        <v>90</v>
+      <c r="E75" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F75" s="17"/>
-      <c r="G75" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G75" s="19"/>
       <c r="H75" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -7409,21 +7107,19 @@
         <v>5</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C76" s="30">
+        <v>93</v>
+      </c>
+      <c r="C76" s="31">
         <v>2.29</v>
       </c>
       <c r="D76" s="18">
         <v>45394</v>
       </c>
-      <c r="E76" s="22" t="s">
-        <v>90</v>
+      <c r="E76" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F76" s="17"/>
-      <c r="G76" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G76" s="19"/>
       <c r="H76" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -7431,21 +7127,19 @@
         <v>6</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C77" s="30">
+        <v>94</v>
+      </c>
+      <c r="C77" s="31">
         <v>4.42</v>
       </c>
       <c r="D77" s="18">
         <v>45394</v>
       </c>
-      <c r="E77" s="22" t="s">
-        <v>90</v>
+      <c r="E77" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F77" s="17"/>
-      <c r="G77" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G77" s="19"/>
       <c r="H77" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -7453,21 +7147,19 @@
         <v>7</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C78" s="30">
+        <v>95</v>
+      </c>
+      <c r="C78" s="31">
         <v>11.17</v>
       </c>
       <c r="D78" s="18">
         <v>45394</v>
       </c>
-      <c r="E78" s="22" t="s">
-        <v>90</v>
+      <c r="E78" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F78" s="17"/>
-      <c r="G78" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G78" s="19"/>
       <c r="H78" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
@@ -7475,21 +7167,19 @@
         <v>8</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C79" s="30">
+        <v>96</v>
+      </c>
+      <c r="C79" s="31">
         <v>6.17</v>
       </c>
       <c r="D79" s="18">
         <v>45394</v>
       </c>
-      <c r="E79" s="22" t="s">
-        <v>90</v>
+      <c r="E79" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F79" s="17"/>
-      <c r="G79" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G79" s="19"/>
       <c r="H79" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
@@ -7497,21 +7187,19 @@
         <v>9</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C80" s="30">
+        <v>97</v>
+      </c>
+      <c r="C80" s="31">
         <v>9.02</v>
       </c>
       <c r="D80" s="18">
         <v>45394</v>
       </c>
-      <c r="E80" s="22" t="s">
-        <v>90</v>
+      <c r="E80" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F80" s="17"/>
-      <c r="G80" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G80" s="19"/>
       <c r="H80" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
@@ -7519,21 +7207,19 @@
         <v>10</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C81" s="30">
+        <v>98</v>
+      </c>
+      <c r="C81" s="31">
         <v>8.02</v>
       </c>
       <c r="D81" s="18">
         <v>45394</v>
       </c>
-      <c r="E81" s="22" t="s">
-        <v>90</v>
+      <c r="E81" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="F81" s="17"/>
-      <c r="G81" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G81" s="19"/>
       <c r="H81" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
@@ -7541,21 +7227,19 @@
         <v>11</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C82" s="30">
+        <v>99</v>
+      </c>
+      <c r="C82" s="31">
         <v>9.4</v>
       </c>
       <c r="D82" s="18">
         <v>45395</v>
       </c>
-      <c r="E82" s="22" t="s">
-        <v>101</v>
+      <c r="E82" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="F82" s="17"/>
-      <c r="G82" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G82" s="19"/>
       <c r="H82" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
@@ -7563,21 +7247,19 @@
         <v>12</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C83" s="30">
+        <v>101</v>
+      </c>
+      <c r="C83" s="31">
         <v>8.21</v>
       </c>
       <c r="D83" s="18">
         <v>45395</v>
       </c>
-      <c r="E83" s="22" t="s">
-        <v>101</v>
+      <c r="E83" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="F83" s="17"/>
-      <c r="G83" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G83" s="19"/>
       <c r="H83" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
@@ -7585,21 +7267,19 @@
         <v>13</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C84" s="30">
+        <v>102</v>
+      </c>
+      <c r="C84" s="31">
         <v>9.29</v>
       </c>
       <c r="D84" s="18">
         <v>45395</v>
       </c>
-      <c r="E84" s="22" t="s">
-        <v>101</v>
+      <c r="E84" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="F84" s="17"/>
-      <c r="G84" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G84" s="19"/>
       <c r="H84" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
@@ -7607,21 +7287,19 @@
         <v>14</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C85" s="30">
+        <v>103</v>
+      </c>
+      <c r="C85" s="31">
         <v>15.19</v>
       </c>
       <c r="D85" s="18">
         <v>45395</v>
       </c>
-      <c r="E85" s="22" t="s">
-        <v>101</v>
+      <c r="E85" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="F85" s="17"/>
-      <c r="G85" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G85" s="19"/>
       <c r="H85" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
@@ -7629,21 +7307,19 @@
         <v>15</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C86" s="30">
+        <v>104</v>
+      </c>
+      <c r="C86" s="31">
         <v>6.57</v>
       </c>
       <c r="D86" s="18">
         <v>45395</v>
       </c>
-      <c r="E86" s="22" t="s">
-        <v>101</v>
+      <c r="E86" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="F86" s="17"/>
-      <c r="G86" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G86" s="19"/>
       <c r="H86" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
@@ -7651,21 +7327,19 @@
         <v>16</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C87" s="30">
+        <v>105</v>
+      </c>
+      <c r="C87" s="31">
         <v>6.18</v>
       </c>
       <c r="D87" s="18">
         <v>45395</v>
       </c>
-      <c r="E87" s="22" t="s">
-        <v>101</v>
+      <c r="E87" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="F87" s="17"/>
-      <c r="G87" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="G87" s="19"/>
       <c r="H87" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
@@ -7673,21 +7347,19 @@
         <v>17</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="C88" s="30">
+        <v>106</v>
+      </c>
+      <c r="C88" s="31">
         <v>5.48</v>
       </c>
       <c r="D88" s="18">
         <v>45395</v>
       </c>
-      <c r="E88" s="22" t="s">
-        <v>101</v>
+      <c r="E88" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="F88" s="17"/>
-      <c r="G88" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G88" s="17"/>
       <c r="H88" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
@@ -7695,21 +7367,19 @@
         <v>18</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C89" s="30">
+        <v>107</v>
+      </c>
+      <c r="C89" s="31">
         <v>7.1</v>
       </c>
       <c r="D89" s="18">
         <v>45396</v>
       </c>
-      <c r="E89" s="22" t="s">
-        <v>109</v>
+      <c r="E89" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="F89" s="17"/>
-      <c r="G89" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G89" s="17"/>
       <c r="H89" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
@@ -7717,21 +7387,19 @@
         <v>19</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C90" s="30">
+        <v>109</v>
+      </c>
+      <c r="C90" s="31">
         <v>6.34</v>
       </c>
       <c r="D90" s="18">
         <v>45396</v>
       </c>
-      <c r="E90" s="22" t="s">
-        <v>109</v>
+      <c r="E90" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="F90" s="17"/>
-      <c r="G90" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G90" s="17"/>
       <c r="H90" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
@@ -7739,21 +7407,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="C91" s="30">
+        <v>110</v>
+      </c>
+      <c r="C91" s="31">
         <v>7.14</v>
       </c>
       <c r="D91" s="18">
         <v>45396</v>
       </c>
-      <c r="E91" s="22" t="s">
-        <v>109</v>
+      <c r="E91" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="F91" s="17"/>
-      <c r="G91" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G91" s="17"/>
       <c r="H91" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
@@ -7761,21 +7427,19 @@
         <v>21</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C92" s="30">
+        <v>111</v>
+      </c>
+      <c r="C92" s="31">
         <v>9.45</v>
       </c>
       <c r="D92" s="18">
         <v>45396</v>
       </c>
-      <c r="E92" s="22" t="s">
-        <v>109</v>
+      <c r="E92" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="F92" s="17"/>
-      <c r="G92" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G92" s="17"/>
       <c r="H92" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
@@ -7783,21 +7447,19 @@
         <v>22</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C93" s="30">
+        <v>112</v>
+      </c>
+      <c r="C93" s="31">
         <v>7.12</v>
       </c>
       <c r="D93" s="18">
         <v>45396</v>
       </c>
-      <c r="E93" s="22" t="s">
-        <v>109</v>
+      <c r="E93" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="F93" s="17"/>
-      <c r="G93" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G93" s="17"/>
       <c r="H93" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
@@ -7805,21 +7467,19 @@
         <v>23</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="C94" s="30">
+        <v>113</v>
+      </c>
+      <c r="C94" s="31">
         <v>5.46</v>
       </c>
       <c r="D94" s="18">
         <v>45396</v>
       </c>
-      <c r="E94" s="22" t="s">
-        <v>109</v>
+      <c r="E94" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="F94" s="17"/>
-      <c r="G94" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G94" s="17"/>
       <c r="H94" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
@@ -7827,21 +7487,19 @@
         <v>24</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C95" s="30">
+        <v>114</v>
+      </c>
+      <c r="C95" s="31">
         <v>13.51</v>
       </c>
       <c r="D95" s="18">
         <v>45396</v>
       </c>
-      <c r="E95" s="22" t="s">
-        <v>109</v>
+      <c r="E95" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="F95" s="17"/>
-      <c r="G95" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G95" s="17"/>
       <c r="H95" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
@@ -7849,21 +7507,19 @@
         <v>25</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="C96" s="30">
+        <v>115</v>
+      </c>
+      <c r="C96" s="31">
         <v>12.21</v>
       </c>
       <c r="D96" s="18">
         <v>45397</v>
       </c>
-      <c r="E96" s="22" t="s">
-        <v>117</v>
+      <c r="E96" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="F96" s="17"/>
-      <c r="G96" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G96" s="17"/>
       <c r="H96" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
@@ -7871,21 +7527,19 @@
         <v>26</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C97" s="30">
+        <v>117</v>
+      </c>
+      <c r="C97" s="31">
         <v>8.45</v>
       </c>
       <c r="D97" s="18">
         <v>45397</v>
       </c>
-      <c r="E97" s="22" t="s">
-        <v>117</v>
+      <c r="E97" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="F97" s="17"/>
-      <c r="G97" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G97" s="17"/>
       <c r="H97" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="19.5">
@@ -7893,21 +7547,19 @@
         <v>27</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C98" s="30">
+        <v>118</v>
+      </c>
+      <c r="C98" s="31">
         <v>12.35</v>
       </c>
       <c r="D98" s="18">
         <v>45397</v>
       </c>
-      <c r="E98" s="22" t="s">
-        <v>117</v>
+      <c r="E98" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="F98" s="17"/>
-      <c r="G98" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G98" s="17"/>
       <c r="H98" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="19.5">
@@ -7915,21 +7567,19 @@
         <v>28</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="C99" s="30">
+        <v>119</v>
+      </c>
+      <c r="C99" s="31">
         <v>5.39</v>
       </c>
       <c r="D99" s="18">
         <v>45397</v>
       </c>
-      <c r="E99" s="22" t="s">
-        <v>117</v>
+      <c r="E99" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="F99" s="17"/>
-      <c r="G99" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G99" s="17"/>
       <c r="H99" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="19.5">
@@ -7937,21 +7587,19 @@
         <v>29</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C100" s="30">
+        <v>120</v>
+      </c>
+      <c r="C100" s="31">
         <v>9.59</v>
       </c>
       <c r="D100" s="18">
         <v>45397</v>
       </c>
-      <c r="E100" s="22" t="s">
-        <v>117</v>
+      <c r="E100" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="F100" s="17"/>
-      <c r="G100" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G100" s="17"/>
       <c r="H100" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="19.5">
@@ -7959,21 +7607,19 @@
         <v>30</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C101" s="30">
+        <v>121</v>
+      </c>
+      <c r="C101" s="31">
         <v>9.57</v>
       </c>
       <c r="D101" s="18">
         <v>45397</v>
       </c>
-      <c r="E101" s="22" t="s">
-        <v>117</v>
+      <c r="E101" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="F101" s="17"/>
-      <c r="G101" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G101" s="17"/>
       <c r="H101" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="19.5">
@@ -7981,21 +7627,19 @@
         <v>31</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="C102" s="30">
+        <v>122</v>
+      </c>
+      <c r="C102" s="31">
         <v>17.55</v>
       </c>
       <c r="D102" s="18">
         <v>45398</v>
       </c>
-      <c r="E102" s="22" t="s">
-        <v>124</v>
+      <c r="E102" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="F102" s="17"/>
-      <c r="G102" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G102" s="17"/>
       <c r="H102" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="19.5">
@@ -8003,21 +7647,19 @@
         <v>32</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C103" s="30">
+        <v>124</v>
+      </c>
+      <c r="C103" s="31">
         <v>12.14</v>
       </c>
       <c r="D103" s="18">
         <v>45398</v>
       </c>
-      <c r="E103" s="22" t="s">
-        <v>124</v>
+      <c r="E103" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="F103" s="17"/>
-      <c r="G103" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G103" s="17"/>
       <c r="H103" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="19.5">
@@ -8025,21 +7667,19 @@
         <v>33</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C104" s="30">
+        <v>125</v>
+      </c>
+      <c r="C104" s="31">
         <v>8.33</v>
       </c>
       <c r="D104" s="18">
         <v>45398</v>
       </c>
-      <c r="E104" s="22" t="s">
-        <v>124</v>
+      <c r="E104" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="F104" s="17"/>
-      <c r="G104" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G104" s="17"/>
       <c r="H104" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="19.5">
@@ -8047,21 +7687,19 @@
         <v>34</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="C105" s="30">
+        <v>126</v>
+      </c>
+      <c r="C105" s="31">
         <v>7.41</v>
       </c>
       <c r="D105" s="18">
         <v>45398</v>
       </c>
-      <c r="E105" s="22" t="s">
-        <v>124</v>
+      <c r="E105" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="F105" s="17"/>
-      <c r="G105" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G105" s="17"/>
       <c r="H105" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
@@ -8069,21 +7707,19 @@
         <v>35</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C106" s="30">
+        <v>127</v>
+      </c>
+      <c r="C106" s="31">
         <v>8.54</v>
       </c>
       <c r="D106" s="18">
         <v>45398</v>
       </c>
-      <c r="E106" s="22" t="s">
-        <v>124</v>
+      <c r="E106" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="F106" s="17"/>
-      <c r="G106" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G106" s="17"/>
       <c r="H106" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
@@ -8091,21 +7727,19 @@
         <v>36</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C107" s="30">
+        <v>128</v>
+      </c>
+      <c r="C107" s="31">
         <v>16.08</v>
       </c>
       <c r="D107" s="18">
         <v>45399</v>
       </c>
-      <c r="E107" s="22" t="s">
-        <v>130</v>
+      <c r="E107" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="F107" s="17"/>
-      <c r="G107" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G107" s="17"/>
       <c r="H107" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
@@ -8113,21 +7747,19 @@
         <v>37</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C108" s="30">
+        <v>130</v>
+      </c>
+      <c r="C108" s="31">
         <v>7.01</v>
       </c>
       <c r="D108" s="18">
         <v>45399</v>
       </c>
-      <c r="E108" s="22" t="s">
-        <v>130</v>
+      <c r="E108" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="F108" s="17"/>
-      <c r="G108" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G108" s="17"/>
       <c r="H108" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
@@ -8135,21 +7767,19 @@
         <v>38</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="C109" s="30">
+        <v>131</v>
+      </c>
+      <c r="C109" s="31">
         <v>7.29</v>
       </c>
       <c r="D109" s="18">
         <v>45399</v>
       </c>
-      <c r="E109" s="22" t="s">
-        <v>130</v>
+      <c r="E109" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="F109" s="17"/>
-      <c r="G109" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G109" s="17"/>
       <c r="H109" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
@@ -8157,21 +7787,19 @@
         <v>39</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="C110" s="30">
+        <v>132</v>
+      </c>
+      <c r="C110" s="31">
         <v>16.33</v>
       </c>
       <c r="D110" s="18">
         <v>45399</v>
       </c>
-      <c r="E110" s="22" t="s">
-        <v>130</v>
+      <c r="E110" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="F110" s="17"/>
-      <c r="G110" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G110" s="17"/>
       <c r="H110" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
@@ -8179,21 +7807,19 @@
         <v>40</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C111" s="30">
+        <v>133</v>
+      </c>
+      <c r="C111" s="31">
         <v>10.58</v>
       </c>
       <c r="D111" s="18">
         <v>45399</v>
       </c>
-      <c r="E111" s="22" t="s">
-        <v>130</v>
+      <c r="E111" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="F111" s="17"/>
-      <c r="G111" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G111" s="17"/>
       <c r="H111" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
@@ -8201,21 +7827,19 @@
         <v>41</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C112" s="30">
+        <v>134</v>
+      </c>
+      <c r="C112" s="31">
         <v>7.33</v>
       </c>
       <c r="D112" s="18">
         <v>45400</v>
       </c>
-      <c r="E112" s="22" t="s">
-        <v>136</v>
+      <c r="E112" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="F112" s="17"/>
-      <c r="G112" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G112" s="17"/>
       <c r="H112" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
@@ -8223,21 +7847,19 @@
         <v>42</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="C113" s="30">
+        <v>136</v>
+      </c>
+      <c r="C113" s="31">
         <v>17.3</v>
       </c>
       <c r="D113" s="18">
         <v>45400</v>
       </c>
-      <c r="E113" s="22" t="s">
-        <v>136</v>
+      <c r="E113" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="F113" s="17"/>
-      <c r="G113" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G113" s="17"/>
       <c r="H113" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
@@ -8245,21 +7867,19 @@
         <v>43</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="C114" s="30">
+        <v>137</v>
+      </c>
+      <c r="C114" s="31">
         <v>16.01</v>
       </c>
       <c r="D114" s="18">
         <v>45400</v>
       </c>
-      <c r="E114" s="22" t="s">
-        <v>136</v>
+      <c r="E114" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="F114" s="17"/>
-      <c r="G114" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G114" s="17"/>
       <c r="H114" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
@@ -8267,21 +7887,19 @@
         <v>44</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="C115" s="30">
+        <v>138</v>
+      </c>
+      <c r="C115" s="31">
         <v>10.06</v>
       </c>
       <c r="D115" s="18">
         <v>45400</v>
       </c>
-      <c r="E115" s="22" t="s">
-        <v>136</v>
+      <c r="E115" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="F115" s="17"/>
-      <c r="G115" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G115" s="17"/>
       <c r="H115" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
@@ -8289,21 +7907,19 @@
         <v>45</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C116" s="30">
+        <v>139</v>
+      </c>
+      <c r="C116" s="31">
         <v>7.13</v>
       </c>
       <c r="D116" s="18">
         <v>45400</v>
       </c>
-      <c r="E116" s="22" t="s">
-        <v>136</v>
+      <c r="E116" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="F116" s="17"/>
-      <c r="G116" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G116" s="17"/>
       <c r="H116" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
@@ -8311,21 +7927,19 @@
         <v>46</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C117" s="30">
+        <v>140</v>
+      </c>
+      <c r="C117" s="31">
         <v>9.06</v>
       </c>
       <c r="D117" s="18">
         <v>45401</v>
       </c>
-      <c r="E117" s="22" t="s">
-        <v>142</v>
+      <c r="E117" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="F117" s="17"/>
-      <c r="G117" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G117" s="17"/>
       <c r="H117" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
@@ -8333,21 +7947,19 @@
         <v>47</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="C118" s="30">
+        <v>142</v>
+      </c>
+      <c r="C118" s="31">
         <v>10.49</v>
       </c>
       <c r="D118" s="18">
         <v>45401</v>
       </c>
-      <c r="E118" s="22" t="s">
-        <v>142</v>
+      <c r="E118" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="F118" s="17"/>
-      <c r="G118" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G118" s="17"/>
       <c r="H118" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
@@ -8355,21 +7967,19 @@
         <v>48</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="C119" s="30">
+        <v>143</v>
+      </c>
+      <c r="C119" s="31">
         <v>8.08</v>
       </c>
       <c r="D119" s="18">
         <v>45401</v>
       </c>
-      <c r="E119" s="22" t="s">
-        <v>142</v>
+      <c r="E119" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="F119" s="17"/>
-      <c r="G119" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G119" s="17"/>
       <c r="H119" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
@@ -8377,21 +7987,19 @@
         <v>49</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C120" s="30">
+        <v>144</v>
+      </c>
+      <c r="C120" s="31">
         <v>13.4</v>
       </c>
       <c r="D120" s="18">
         <v>45401</v>
       </c>
-      <c r="E120" s="22" t="s">
-        <v>142</v>
+      <c r="E120" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="F120" s="17"/>
-      <c r="G120" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G120" s="17"/>
       <c r="H120" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
@@ -8399,21 +8007,19 @@
         <v>50</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C121" s="30">
+        <v>145</v>
+      </c>
+      <c r="C121" s="31">
         <v>12.54</v>
       </c>
       <c r="D121" s="18">
         <v>45401</v>
       </c>
-      <c r="E121" s="22" t="s">
-        <v>142</v>
+      <c r="E121" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="F121" s="17"/>
-      <c r="G121" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G121" s="17"/>
       <c r="H121" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
@@ -8421,21 +8027,19 @@
         <v>51</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="C122" s="30">
+        <v>146</v>
+      </c>
+      <c r="C122" s="31">
         <v>9.57</v>
       </c>
       <c r="D122" s="18">
         <v>45401</v>
       </c>
-      <c r="E122" s="22" t="s">
-        <v>142</v>
+      <c r="E122" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="F122" s="17"/>
-      <c r="G122" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G122" s="17"/>
       <c r="H122" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
@@ -8443,21 +8047,19 @@
         <v>52</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="C123" s="30">
+        <v>147</v>
+      </c>
+      <c r="C123" s="31">
         <v>7.29</v>
       </c>
       <c r="D123" s="18">
         <v>45402</v>
       </c>
-      <c r="E123" s="22" t="s">
-        <v>149</v>
+      <c r="E123" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="F123" s="17"/>
-      <c r="G123" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G123" s="17"/>
       <c r="H123" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
@@ -8465,21 +8067,19 @@
         <v>53</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C124" s="30">
+        <v>149</v>
+      </c>
+      <c r="C124" s="31">
         <v>10.29</v>
       </c>
       <c r="D124" s="18">
         <v>45402</v>
       </c>
-      <c r="E124" s="22" t="s">
-        <v>149</v>
+      <c r="E124" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="F124" s="17"/>
-      <c r="G124" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G124" s="17"/>
       <c r="H124" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
@@ -8487,21 +8087,19 @@
         <v>54</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="C125" s="30">
+        <v>150</v>
+      </c>
+      <c r="C125" s="31">
         <v>9.01</v>
       </c>
       <c r="D125" s="18">
         <v>45402</v>
       </c>
-      <c r="E125" s="22" t="s">
-        <v>149</v>
+      <c r="E125" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="F125" s="17"/>
-      <c r="G125" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G125" s="17"/>
       <c r="H125" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
@@ -8509,21 +8107,19 @@
         <v>55</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C126" s="30">
+        <v>151</v>
+      </c>
+      <c r="C126" s="31">
         <v>7.38</v>
       </c>
       <c r="D126" s="18">
         <v>45402</v>
       </c>
-      <c r="E126" s="22" t="s">
-        <v>149</v>
+      <c r="E126" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="F126" s="17"/>
-      <c r="G126" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G126" s="17"/>
       <c r="H126" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
@@ -8531,21 +8127,19 @@
         <v>56</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="C127" s="30">
+        <v>152</v>
+      </c>
+      <c r="C127" s="31">
         <v>9.29</v>
       </c>
       <c r="D127" s="18">
         <v>45402</v>
       </c>
-      <c r="E127" s="22" t="s">
-        <v>149</v>
+      <c r="E127" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="F127" s="17"/>
-      <c r="G127" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G127" s="17"/>
       <c r="H127" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
@@ -8553,21 +8147,19 @@
         <v>57</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C128" s="30">
+        <v>153</v>
+      </c>
+      <c r="C128" s="31">
         <v>23.01</v>
       </c>
       <c r="D128" s="18">
         <v>45402</v>
       </c>
-      <c r="E128" s="22" t="s">
-        <v>149</v>
+      <c r="E128" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="F128" s="17"/>
-      <c r="G128" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G128" s="17"/>
       <c r="H128" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
@@ -8575,21 +8167,19 @@
         <v>58</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="C129" s="30">
+        <v>154</v>
+      </c>
+      <c r="C129" s="31">
         <v>15.51</v>
       </c>
       <c r="D129" s="18">
         <v>45403</v>
       </c>
-      <c r="E129" s="22" t="s">
-        <v>156</v>
+      <c r="E129" s="30" t="s">
+        <v>155</v>
       </c>
       <c r="F129" s="17"/>
-      <c r="G129" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G129" s="17"/>
       <c r="H129" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
@@ -8597,21 +8187,19 @@
         <v>59</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="C130" s="30">
+        <v>156</v>
+      </c>
+      <c r="C130" s="31">
         <v>9.19</v>
       </c>
       <c r="D130" s="18">
         <v>45403</v>
       </c>
-      <c r="E130" s="22" t="s">
-        <v>156</v>
+      <c r="E130" s="30" t="s">
+        <v>155</v>
       </c>
       <c r="F130" s="17"/>
-      <c r="G130" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G130" s="17"/>
       <c r="H130" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
@@ -8619,21 +8207,19 @@
         <v>60</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="C131" s="30">
+        <v>157</v>
+      </c>
+      <c r="C131" s="31">
         <v>9.27</v>
       </c>
       <c r="D131" s="18">
         <v>45403</v>
       </c>
-      <c r="E131" s="22" t="s">
-        <v>156</v>
+      <c r="E131" s="30" t="s">
+        <v>155</v>
       </c>
       <c r="F131" s="17"/>
-      <c r="G131" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G131" s="17"/>
       <c r="H131" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
@@ -8641,21 +8227,19 @@
         <v>61</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="C132" s="30">
+        <v>158</v>
+      </c>
+      <c r="C132" s="31">
         <v>5.56</v>
       </c>
       <c r="D132" s="18">
         <v>45403</v>
       </c>
-      <c r="E132" s="22" t="s">
-        <v>156</v>
+      <c r="E132" s="30" t="s">
+        <v>155</v>
       </c>
       <c r="F132" s="17"/>
-      <c r="G132" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G132" s="17"/>
       <c r="H132" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
@@ -8663,21 +8247,19 @@
         <v>62</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="C133" s="30">
+        <v>159</v>
+      </c>
+      <c r="C133" s="31">
         <v>8.48</v>
       </c>
       <c r="D133" s="18">
         <v>45403</v>
       </c>
-      <c r="E133" s="22" t="s">
-        <v>156</v>
+      <c r="E133" s="30" t="s">
+        <v>155</v>
       </c>
       <c r="F133" s="17"/>
-      <c r="G133" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G133" s="17"/>
       <c r="H133" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
@@ -8685,21 +8267,19 @@
         <v>63</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="C134" s="30">
+        <v>160</v>
+      </c>
+      <c r="C134" s="31">
         <v>8.42</v>
       </c>
       <c r="D134" s="18">
         <v>45403</v>
       </c>
-      <c r="E134" s="22" t="s">
-        <v>156</v>
+      <c r="E134" s="30" t="s">
+        <v>155</v>
       </c>
       <c r="F134" s="17"/>
-      <c r="G134" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G134" s="17"/>
       <c r="H134" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
@@ -8707,21 +8287,19 @@
         <v>64</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="C135" s="30">
+        <v>161</v>
+      </c>
+      <c r="C135" s="31">
         <v>10.04</v>
       </c>
       <c r="D135" s="18">
         <v>45404</v>
       </c>
-      <c r="E135" s="22" t="s">
-        <v>163</v>
+      <c r="E135" s="30" t="s">
+        <v>162</v>
       </c>
       <c r="F135" s="17"/>
-      <c r="G135" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G135" s="17"/>
       <c r="H135" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
@@ -8729,21 +8307,19 @@
         <v>65</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C136" s="30">
+        <v>163</v>
+      </c>
+      <c r="C136" s="31">
         <v>8.35</v>
       </c>
       <c r="D136" s="18">
         <v>45404</v>
       </c>
-      <c r="E136" s="22" t="s">
-        <v>163</v>
+      <c r="E136" s="30" t="s">
+        <v>162</v>
       </c>
       <c r="F136" s="17"/>
-      <c r="G136" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G136" s="17"/>
       <c r="H136" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
@@ -8751,21 +8327,19 @@
         <v>66</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="C137" s="30">
+        <v>164</v>
+      </c>
+      <c r="C137" s="31">
         <v>19.21</v>
       </c>
       <c r="D137" s="18">
         <v>45404</v>
       </c>
-      <c r="E137" s="22" t="s">
-        <v>163</v>
+      <c r="E137" s="30" t="s">
+        <v>162</v>
       </c>
       <c r="F137" s="17"/>
-      <c r="G137" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G137" s="17"/>
       <c r="H137" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
@@ -8773,21 +8347,19 @@
         <v>67</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C138" s="30">
+        <v>165</v>
+      </c>
+      <c r="C138" s="31">
         <v>12.06</v>
       </c>
       <c r="D138" s="18">
         <v>45404</v>
       </c>
-      <c r="E138" s="22" t="s">
-        <v>163</v>
+      <c r="E138" s="30" t="s">
+        <v>162</v>
       </c>
       <c r="F138" s="17"/>
-      <c r="G138" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G138" s="17"/>
       <c r="H138" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
@@ -8795,21 +8367,19 @@
         <v>68</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C139" s="30">
+        <v>166</v>
+      </c>
+      <c r="C139" s="31">
         <v>12.52</v>
       </c>
       <c r="D139" s="18">
         <v>45404</v>
       </c>
-      <c r="E139" s="22" t="s">
-        <v>163</v>
+      <c r="E139" s="30" t="s">
+        <v>162</v>
       </c>
       <c r="F139" s="17"/>
-      <c r="G139" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G139" s="17"/>
       <c r="H139" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
@@ -8817,21 +8387,19 @@
         <v>69</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="C140" s="30">
+        <v>167</v>
+      </c>
+      <c r="C140" s="31">
         <v>14.16</v>
       </c>
       <c r="D140" s="18">
         <v>45405</v>
       </c>
-      <c r="E140" s="22" t="s">
-        <v>169</v>
+      <c r="E140" s="30" t="s">
+        <v>168</v>
       </c>
       <c r="F140" s="17"/>
-      <c r="G140" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G140" s="17"/>
       <c r="H140" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
@@ -8839,21 +8407,19 @@
         <v>70</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="C141" s="30">
+        <v>169</v>
+      </c>
+      <c r="C141" s="31">
         <v>12.49</v>
       </c>
       <c r="D141" s="18">
         <v>45405</v>
       </c>
-      <c r="E141" s="22" t="s">
-        <v>169</v>
+      <c r="E141" s="30" t="s">
+        <v>168</v>
       </c>
       <c r="F141" s="17"/>
-      <c r="G141" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G141" s="17"/>
       <c r="H141" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
@@ -8861,21 +8427,19 @@
         <v>71</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="C142" s="30">
+        <v>170</v>
+      </c>
+      <c r="C142" s="31">
         <v>3.5</v>
       </c>
       <c r="D142" s="18">
         <v>45405</v>
       </c>
-      <c r="E142" s="22" t="s">
-        <v>169</v>
+      <c r="E142" s="30" t="s">
+        <v>168</v>
       </c>
       <c r="F142" s="17"/>
-      <c r="G142" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G142" s="17"/>
       <c r="H142" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
@@ -8883,21 +8447,19 @@
         <v>72</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C143" s="30">
+        <v>171</v>
+      </c>
+      <c r="C143" s="31">
         <v>7.54</v>
       </c>
       <c r="D143" s="18">
         <v>45405</v>
       </c>
-      <c r="E143" s="22" t="s">
-        <v>169</v>
+      <c r="E143" s="30" t="s">
+        <v>168</v>
       </c>
       <c r="F143" s="17"/>
-      <c r="G143" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G143" s="17"/>
       <c r="H143" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
@@ -8905,21 +8467,19 @@
         <v>73</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="C144" s="30">
+        <v>172</v>
+      </c>
+      <c r="C144" s="31">
         <v>6.43</v>
       </c>
       <c r="D144" s="18">
         <v>45405</v>
       </c>
-      <c r="E144" s="22" t="s">
-        <v>169</v>
+      <c r="E144" s="30" t="s">
+        <v>168</v>
       </c>
       <c r="F144" s="17"/>
-      <c r="G144" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G144" s="17"/>
       <c r="H144" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
@@ -8927,21 +8487,19 @@
         <v>74</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="C145" s="30">
+        <v>173</v>
+      </c>
+      <c r="C145" s="31">
         <v>9.41</v>
       </c>
       <c r="D145" s="18">
         <v>45405</v>
       </c>
-      <c r="E145" s="22" t="s">
-        <v>169</v>
+      <c r="E145" s="30" t="s">
+        <v>168</v>
       </c>
       <c r="F145" s="17"/>
-      <c r="G145" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G145" s="17"/>
       <c r="H145" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
@@ -8949,21 +8507,19 @@
         <v>75</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="C146" s="30">
+        <v>174</v>
+      </c>
+      <c r="C146" s="31">
         <v>19.37</v>
       </c>
       <c r="D146" s="18">
         <v>45406</v>
       </c>
-      <c r="E146" s="22" t="s">
-        <v>176</v>
+      <c r="E146" s="30" t="s">
+        <v>175</v>
       </c>
       <c r="F146" s="17"/>
-      <c r="G146" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G146" s="17"/>
       <c r="H146" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
@@ -8971,21 +8527,19 @@
         <v>76</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C147" s="30">
+        <v>176</v>
+      </c>
+      <c r="C147" s="31">
         <v>0.56</v>
       </c>
       <c r="D147" s="18">
         <v>45406</v>
       </c>
-      <c r="E147" s="22" t="s">
-        <v>176</v>
+      <c r="E147" s="30" t="s">
+        <v>175</v>
       </c>
       <c r="F147" s="17"/>
-      <c r="G147" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G147" s="17"/>
       <c r="H147" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
@@ -8993,21 +8547,19 @@
         <v>77</v>
       </c>
       <c r="B148" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C148" s="34" t="s">
         <v>178</v>
-      </c>
-      <c r="C148" s="35" t="s">
-        <v>179</v>
       </c>
       <c r="D148" s="18">
         <v>45407</v>
       </c>
-      <c r="E148" s="22" t="s">
-        <v>180</v>
+      <c r="E148" s="30" t="s">
+        <v>179</v>
       </c>
       <c r="F148" s="17"/>
-      <c r="G148" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G148" s="17"/>
       <c r="H148" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
@@ -9015,21 +8567,19 @@
         <v>78</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="C149" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
+      </c>
+      <c r="C149" s="34" t="s">
+        <v>178</v>
       </c>
       <c r="D149" s="18">
         <v>45408</v>
       </c>
-      <c r="E149" s="22" t="s">
-        <v>182</v>
+      <c r="E149" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="F149" s="17"/>
-      <c r="G149" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G149" s="17"/>
       <c r="H149" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
@@ -9037,21 +8587,19 @@
         <v>79</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C150" s="35" t="s">
-        <v>179</v>
+        <v>182</v>
+      </c>
+      <c r="C150" s="34" t="s">
+        <v>178</v>
       </c>
       <c r="D150" s="18">
         <v>45409</v>
       </c>
-      <c r="E150" s="22" t="s">
-        <v>184</v>
+      <c r="E150" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="F150" s="17"/>
-      <c r="G150" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G150" s="17"/>
       <c r="H150" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
@@ -9059,21 +8607,19 @@
         <v>80</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="C151" s="35" t="s">
-        <v>179</v>
+        <v>184</v>
+      </c>
+      <c r="C151" s="34" t="s">
+        <v>178</v>
       </c>
       <c r="D151" s="18">
         <v>45410</v>
       </c>
-      <c r="E151" s="22" t="s">
-        <v>186</v>
+      <c r="E151" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="F151" s="17"/>
-      <c r="G151" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G151" s="17"/>
       <c r="H151" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
@@ -9081,21 +8627,19 @@
         <v>81</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="C152" s="35" t="s">
-        <v>179</v>
+        <v>186</v>
+      </c>
+      <c r="C152" s="34" t="s">
+        <v>178</v>
       </c>
       <c r="D152" s="18">
         <v>45411</v>
       </c>
-      <c r="E152" s="22" t="s">
-        <v>188</v>
+      <c r="E152" s="30" t="s">
+        <v>187</v>
       </c>
       <c r="F152" s="17"/>
-      <c r="G152" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G152" s="17"/>
       <c r="H152" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
@@ -9103,29 +8647,27 @@
         <v>82</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="C153" s="35" t="s">
-        <v>179</v>
+        <v>188</v>
+      </c>
+      <c r="C153" s="34" t="s">
+        <v>178</v>
       </c>
       <c r="D153" s="18">
         <v>45412</v>
       </c>
-      <c r="E153" s="22" t="s">
-        <v>190</v>
+      <c r="E153" s="30" t="s">
+        <v>189</v>
       </c>
       <c r="F153" s="17"/>
-      <c r="G153" s="32" t="s">
-        <v>16</v>
-      </c>
+      <c r="G153" s="17"/>
       <c r="H153" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="21"/>
       <c r="B154" s="22"/>
-      <c r="C154" s="33"/>
-      <c r="D154" s="34"/>
-      <c r="E154" s="22"/>
+      <c r="C154" s="32"/>
+      <c r="D154" s="33"/>
+      <c r="E154" s="30"/>
       <c r="F154" s="22"/>
       <c r="G154" s="22"/>
       <c r="H154" s="2"/>
@@ -9133,9 +8675,9 @@
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="21"/>
       <c r="B155" s="22"/>
-      <c r="C155" s="33"/>
-      <c r="D155" s="34"/>
-      <c r="E155" s="22"/>
+      <c r="C155" s="32"/>
+      <c r="D155" s="33"/>
+      <c r="E155" s="30"/>
       <c r="F155" s="22"/>
       <c r="G155" s="22"/>
       <c r="H155" s="2"/>
@@ -9143,9 +8685,9 @@
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="21"/>
       <c r="B156" s="22"/>
-      <c r="C156" s="33"/>
-      <c r="D156" s="34"/>
-      <c r="E156" s="22"/>
+      <c r="C156" s="32"/>
+      <c r="D156" s="33"/>
+      <c r="E156" s="30"/>
       <c r="F156" s="22"/>
       <c r="G156" s="22"/>
       <c r="H156" s="2"/>
@@ -9153,9 +8695,9 @@
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="21"/>
       <c r="B157" s="22"/>
-      <c r="C157" s="33"/>
-      <c r="D157" s="34"/>
-      <c r="E157" s="22"/>
+      <c r="C157" s="32"/>
+      <c r="D157" s="33"/>
+      <c r="E157" s="30"/>
       <c r="F157" s="22"/>
       <c r="G157" s="22"/>
       <c r="H157" s="2"/>
@@ -9163,9 +8705,9 @@
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="21"/>
       <c r="B158" s="22"/>
-      <c r="C158" s="33"/>
-      <c r="D158" s="34"/>
-      <c r="E158" s="22"/>
+      <c r="C158" s="32"/>
+      <c r="D158" s="33"/>
+      <c r="E158" s="30"/>
       <c r="F158" s="22"/>
       <c r="G158" s="22"/>
       <c r="H158" s="2"/>
@@ -9173,9 +8715,9 @@
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="21"/>
       <c r="B159" s="22"/>
-      <c r="C159" s="33"/>
-      <c r="D159" s="34"/>
-      <c r="E159" s="22"/>
+      <c r="C159" s="32"/>
+      <c r="D159" s="33"/>
+      <c r="E159" s="30"/>
       <c r="F159" s="22"/>
       <c r="G159" s="22"/>
       <c r="H159" s="2"/>
@@ -9183,9 +8725,9 @@
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="21"/>
       <c r="B160" s="22"/>
-      <c r="C160" s="33"/>
-      <c r="D160" s="34"/>
-      <c r="E160" s="22"/>
+      <c r="C160" s="32"/>
+      <c r="D160" s="33"/>
+      <c r="E160" s="30"/>
       <c r="F160" s="22"/>
       <c r="G160" s="22"/>
       <c r="H160" s="2"/>
@@ -9193,9 +8735,9 @@
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="21"/>
       <c r="B161" s="22"/>
-      <c r="C161" s="33"/>
-      <c r="D161" s="34"/>
-      <c r="E161" s="22"/>
+      <c r="C161" s="32"/>
+      <c r="D161" s="33"/>
+      <c r="E161" s="30"/>
       <c r="F161" s="22"/>
       <c r="G161" s="22"/>
       <c r="H161" s="2"/>
@@ -9203,9 +8745,9 @@
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="21"/>
       <c r="B162" s="22"/>
-      <c r="C162" s="33"/>
-      <c r="D162" s="34"/>
-      <c r="E162" s="22"/>
+      <c r="C162" s="32"/>
+      <c r="D162" s="33"/>
+      <c r="E162" s="30"/>
       <c r="F162" s="22"/>
       <c r="G162" s="22"/>
       <c r="H162" s="2"/>
@@ -9213,9 +8755,9 @@
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="21"/>
       <c r="B163" s="22"/>
-      <c r="C163" s="33"/>
-      <c r="D163" s="34"/>
-      <c r="E163" s="22"/>
+      <c r="C163" s="32"/>
+      <c r="D163" s="33"/>
+      <c r="E163" s="30"/>
       <c r="F163" s="22"/>
       <c r="G163" s="22"/>
       <c r="H163" s="2"/>
@@ -9223,9 +8765,9 @@
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="21"/>
       <c r="B164" s="22"/>
-      <c r="C164" s="33"/>
-      <c r="D164" s="34"/>
-      <c r="E164" s="22"/>
+      <c r="C164" s="32"/>
+      <c r="D164" s="33"/>
+      <c r="E164" s="30"/>
       <c r="F164" s="22"/>
       <c r="G164" s="22"/>
       <c r="H164" s="2"/>
@@ -9233,9 +8775,9 @@
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="21"/>
       <c r="B165" s="22"/>
-      <c r="C165" s="33"/>
-      <c r="D165" s="34"/>
-      <c r="E165" s="22"/>
+      <c r="C165" s="32"/>
+      <c r="D165" s="33"/>
+      <c r="E165" s="30"/>
       <c r="F165" s="22"/>
       <c r="G165" s="22"/>
       <c r="H165" s="2"/>
@@ -9243,9 +8785,9 @@
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="21"/>
       <c r="B166" s="22"/>
-      <c r="C166" s="33"/>
-      <c r="D166" s="34"/>
-      <c r="E166" s="22"/>
+      <c r="C166" s="32"/>
+      <c r="D166" s="33"/>
+      <c r="E166" s="30"/>
       <c r="F166" s="22"/>
       <c r="G166" s="22"/>
       <c r="H166" s="2"/>
@@ -9253,9 +8795,9 @@
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="21"/>
       <c r="B167" s="22"/>
-      <c r="C167" s="33"/>
-      <c r="D167" s="34"/>
-      <c r="E167" s="22"/>
+      <c r="C167" s="32"/>
+      <c r="D167" s="33"/>
+      <c r="E167" s="30"/>
       <c r="F167" s="22"/>
       <c r="G167" s="22"/>
       <c r="H167" s="2"/>
@@ -9263,9 +8805,9 @@
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="21"/>
       <c r="B168" s="22"/>
-      <c r="C168" s="33"/>
-      <c r="D168" s="34"/>
-      <c r="E168" s="22"/>
+      <c r="C168" s="32"/>
+      <c r="D168" s="33"/>
+      <c r="E168" s="30"/>
       <c r="F168" s="22"/>
       <c r="G168" s="22"/>
       <c r="H168" s="2"/>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="363">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -1101,6 +1101,18 @@
   </si>
   <si>
     <t>https://www.udemy.com/course/build-a-cucumber-playwright-typescript-automation-framework/</t>
+  </si>
+  <si>
+    <t>How to Become Genius in XPath in Selenium - Session -18</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3uktjWgKrtI</t>
+  </si>
+  <si>
+    <t>How to become genius in CSS Selector in Selenium || Create Custom Dynamic CSS Selectors</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VYIDZ57mMy4</t>
   </si>
 </sst>
 </file>
@@ -1160,15 +1172,15 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1300,17 +1312,11 @@
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1329,9 +1335,6 @@
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1375,8 +1378,17 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1683,17 +1695,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="53" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="50" width="38.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="47" width="38.86214285714286" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="23" width="7.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="50" width="23.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="50" width="41.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="47" width="23.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="47" width="41.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -1701,10 +1713,10 @@
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
       <c r="D1" s="21"/>
-      <c r="E1" s="38"/>
+      <c r="E1" s="35"/>
       <c r="F1" s="21"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="22"/>
@@ -1716,7 +1728,7 @@
       <c r="E2" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="48" t="s">
         <v>320</v>
       </c>
       <c r="G2" s="14" t="s">
@@ -1816,7 +1828,7 @@
       <c r="G7" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="49" t="s">
         <v>329</v>
       </c>
     </row>
@@ -1962,7 +1974,7 @@
       <c r="G15" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="49" t="s">
         <v>340</v>
       </c>
     </row>
@@ -1982,7 +1994,7 @@
       <c r="G16" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="49" t="s">
         <v>342</v>
       </c>
     </row>
@@ -2002,7 +2014,7 @@
       <c r="G17" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="49" t="s">
         <v>344</v>
       </c>
     </row>
@@ -2037,82 +2049,82 @@
       <c r="F19" s="21">
         <v>1</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="H19" s="38"/>
+      <c r="H19" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="51">
+      <c r="D20" s="48">
         <v>18</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="35" t="s">
         <v>347</v>
       </c>
       <c r="F20" s="21">
         <v>2</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="H20" s="38"/>
+      <c r="H20" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="51">
+      <c r="D21" s="48">
         <v>19</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="35" t="s">
         <v>348</v>
       </c>
       <c r="F21" s="21">
         <v>1</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G21" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="H21" s="38"/>
+      <c r="H21" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="51">
+      <c r="D22" s="48">
         <v>20</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="35" t="s">
         <v>349</v>
       </c>
       <c r="F22" s="21">
         <v>1</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="G22" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="H22" s="38"/>
+      <c r="H22" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="47.25">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
-      <c r="D23" s="51">
+      <c r="D23" s="48">
         <v>21</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="35" t="s">
         <v>350</v>
       </c>
       <c r="F23" s="21">
         <v>1</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="G23" s="35" t="s">
         <v>351</v>
       </c>
-      <c r="H23" s="38" t="s">
+      <c r="H23" s="35" t="s">
         <v>352</v>
       </c>
     </row>
@@ -2120,19 +2132,19 @@
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="51">
+      <c r="D24" s="48">
         <v>22</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="35" t="s">
         <v>353</v>
       </c>
       <c r="F24" s="21">
         <v>1</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="H24" s="38" t="s">
+      <c r="H24" s="35" t="s">
         <v>354</v>
       </c>
     </row>
@@ -2140,35 +2152,35 @@
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
-      <c r="D25" s="51">
+      <c r="D25" s="48">
         <v>23</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="35" t="s">
         <v>355</v>
       </c>
       <c r="F25" s="21">
         <v>1</v>
       </c>
-      <c r="G25" s="38" t="s">
+      <c r="G25" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="H25" s="38"/>
+      <c r="H25" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
-      <c r="D26" s="51">
+      <c r="D26" s="48">
         <v>24</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="35" t="s">
         <v>356</v>
       </c>
       <c r="F26" s="21">
         <v>1</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="22"/>
@@ -2183,7 +2195,7 @@
       <c r="F27" s="21">
         <v>1</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="35" t="s">
         <v>331</v>
       </c>
       <c r="H27" s="17" t="s">
@@ -2194,31 +2206,111 @@
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
+      <c r="D28" s="48">
+        <v>26</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="F28" s="21">
+        <v>1</v>
+      </c>
+      <c r="G28" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="H28" s="35" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
+      <c r="D29" s="48">
+        <v>27</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>361</v>
+      </c>
+      <c r="F29" s="21">
+        <v>1</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="17"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2234,97 +2326,97 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="23" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="50" width="60.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="35" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="36" width="7.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="50" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="50" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="50" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="47" width="60.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="33" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="34" width="7.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="47" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="47" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="21"/>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="47.25">
       <c r="A2" s="21">
         <v>1</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="21">
         <v>2</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="21">
         <v>3</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="21"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="38"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="13" t="s">
@@ -2333,16 +2425,16 @@
       <c r="B7" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="2" t="s">
         <v>195</v>
       </c>
       <c r="G7" s="14" t="s">
@@ -2351,7 +2443,7 @@
       <c r="H7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="38"/>
+      <c r="I7" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="33.75">
       <c r="A8" s="15">
@@ -2360,21 +2452,21 @@
       <c r="B8" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="29">
         <v>8.03</v>
       </c>
       <c r="D8" s="18">
         <v>45355</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F8" s="30"/>
+      <c r="F8" s="2"/>
       <c r="G8" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H8" s="17"/>
-      <c r="I8" s="38"/>
+      <c r="I8" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="15">
@@ -2383,21 +2475,21 @@
       <c r="B9" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="29">
         <v>20.56</v>
       </c>
       <c r="D9" s="18">
         <v>45355</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F9" s="30"/>
+      <c r="F9" s="2"/>
       <c r="G9" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H9" s="17"/>
-      <c r="I9" s="38"/>
+      <c r="I9" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="15">
@@ -2406,21 +2498,21 @@
       <c r="B10" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="29">
         <v>34.45</v>
       </c>
       <c r="D10" s="18">
         <v>45355</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="30"/>
+      <c r="F10" s="2"/>
       <c r="G10" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H10" s="17"/>
-      <c r="I10" s="43" t="s">
+      <c r="I10" s="40" t="s">
         <v>201</v>
       </c>
     </row>
@@ -2431,21 +2523,21 @@
       <c r="B11" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="29">
         <v>32.53</v>
       </c>
       <c r="D11" s="18">
         <v>45356</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F11" s="30"/>
+      <c r="F11" s="2"/>
       <c r="G11" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H11" s="17"/>
-      <c r="I11" s="38"/>
+      <c r="I11" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="15">
@@ -2454,21 +2546,21 @@
       <c r="B12" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="29">
         <v>28.2</v>
       </c>
       <c r="D12" s="18">
         <v>45356</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F12" s="30"/>
+      <c r="F12" s="2"/>
       <c r="G12" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H12" s="17"/>
-      <c r="I12" s="38"/>
+      <c r="I12" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="15">
@@ -2477,21 +2569,21 @@
       <c r="B13" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="29">
         <v>32.09</v>
       </c>
       <c r="D13" s="18">
         <v>45357</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F13" s="30"/>
+      <c r="F13" s="2"/>
       <c r="G13" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H13" s="17"/>
-      <c r="I13" s="38"/>
+      <c r="I13" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="15">
@@ -2500,21 +2592,21 @@
       <c r="B14" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="29">
         <v>15.04</v>
       </c>
       <c r="D14" s="18">
         <v>45357</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F14" s="30"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H14" s="17"/>
-      <c r="I14" s="38"/>
+      <c r="I14" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="15">
@@ -2523,21 +2615,21 @@
       <c r="B15" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="29">
         <v>29.46</v>
       </c>
       <c r="D15" s="18">
         <v>45358</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="30"/>
+      <c r="F15" s="2"/>
       <c r="G15" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H15" s="17"/>
-      <c r="I15" s="38"/>
+      <c r="I15" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="15">
@@ -2546,21 +2638,21 @@
       <c r="B16" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="29">
         <v>26.4</v>
       </c>
       <c r="D16" s="18">
         <v>45358</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="30"/>
+      <c r="F16" s="2"/>
       <c r="G16" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H16" s="17"/>
-      <c r="I16" s="38"/>
+      <c r="I16" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="15">
@@ -2569,21 +2661,21 @@
       <c r="B17" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="29">
         <v>24.52</v>
       </c>
       <c r="D17" s="18">
         <v>45359</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F17" s="30"/>
+      <c r="F17" s="2"/>
       <c r="G17" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H17" s="17"/>
-      <c r="I17" s="38"/>
+      <c r="I17" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="15">
@@ -2592,21 +2684,21 @@
       <c r="B18" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="29">
         <v>7.19</v>
       </c>
       <c r="D18" s="18">
         <v>45359</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F18" s="30"/>
+      <c r="F18" s="2"/>
       <c r="G18" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H18" s="17"/>
-      <c r="I18" s="38"/>
+      <c r="I18" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="15">
@@ -2615,21 +2707,21 @@
       <c r="B19" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="29">
         <v>13.33</v>
       </c>
       <c r="D19" s="18">
         <v>45359</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F19" s="30"/>
+      <c r="F19" s="2"/>
       <c r="G19" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H19" s="17"/>
-      <c r="I19" s="38"/>
+      <c r="I19" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="33.75">
       <c r="A20" s="15">
@@ -2638,21 +2730,21 @@
       <c r="B20" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="29">
         <v>19.1</v>
       </c>
       <c r="D20" s="18">
         <v>45359</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F20" s="30"/>
+      <c r="F20" s="2"/>
       <c r="G20" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H20" s="17"/>
-      <c r="I20" s="38"/>
+      <c r="I20" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="15">
@@ -2661,21 +2753,21 @@
       <c r="B21" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="29">
         <v>25.43</v>
       </c>
       <c r="D21" s="18">
         <v>45360</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F21" s="30"/>
+      <c r="F21" s="2"/>
       <c r="G21" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H21" s="17"/>
-      <c r="I21" s="38"/>
+      <c r="I21" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="15">
@@ -2684,21 +2776,21 @@
       <c r="B22" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="29">
         <v>37.1</v>
       </c>
       <c r="D22" s="18">
         <v>45360</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F22" s="30"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H22" s="17"/>
-      <c r="I22" s="38"/>
+      <c r="I22" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="15">
@@ -2707,21 +2799,21 @@
       <c r="B23" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="29">
         <v>19.22</v>
       </c>
       <c r="D23" s="18">
         <v>45361</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F23" s="30"/>
+      <c r="F23" s="2"/>
       <c r="G23" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H23" s="17"/>
-      <c r="I23" s="38"/>
+      <c r="I23" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="15">
@@ -2730,21 +2822,21 @@
       <c r="B24" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="29">
         <v>9.48</v>
       </c>
       <c r="D24" s="18">
         <v>45361</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F24" s="30"/>
+      <c r="F24" s="2"/>
       <c r="G24" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H24" s="17"/>
-      <c r="I24" s="38"/>
+      <c r="I24" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="15">
@@ -2753,21 +2845,21 @@
       <c r="B25" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="29">
         <v>22.52</v>
       </c>
       <c r="D25" s="18">
         <v>45361</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="E25" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F25" s="30"/>
+      <c r="F25" s="2"/>
       <c r="G25" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H25" s="17"/>
-      <c r="I25" s="38"/>
+      <c r="I25" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="15">
@@ -2776,21 +2868,21 @@
       <c r="B26" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="29">
         <v>10.07</v>
       </c>
       <c r="D26" s="18">
         <v>45361</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F26" s="30"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H26" s="17"/>
-      <c r="I26" s="38"/>
+      <c r="I26" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="33.75">
       <c r="A27" s="15">
@@ -2799,21 +2891,21 @@
       <c r="B27" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="29">
         <v>18.28</v>
       </c>
       <c r="D27" s="18">
         <v>45362</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F27" s="30"/>
+      <c r="F27" s="2"/>
       <c r="G27" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H27" s="17"/>
-      <c r="I27" s="38"/>
+      <c r="I27" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="15">
@@ -2822,21 +2914,21 @@
       <c r="B28" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="29">
         <v>16.07</v>
       </c>
       <c r="D28" s="18">
         <v>45362</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F28" s="30"/>
+      <c r="F28" s="2"/>
       <c r="G28" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H28" s="17"/>
-      <c r="I28" s="38"/>
+      <c r="I28" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="15">
@@ -2845,21 +2937,21 @@
       <c r="B29" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="29">
         <v>12.29</v>
       </c>
       <c r="D29" s="18">
         <v>45362</v>
       </c>
-      <c r="E29" s="30" t="s">
+      <c r="E29" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F29" s="30"/>
+      <c r="F29" s="2"/>
       <c r="G29" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H29" s="17"/>
-      <c r="I29" s="38"/>
+      <c r="I29" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="15">
@@ -2868,21 +2960,21 @@
       <c r="B30" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="29">
         <v>13.4</v>
       </c>
       <c r="D30" s="18">
         <v>45362</v>
       </c>
-      <c r="E30" s="30" t="s">
+      <c r="E30" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F30" s="30"/>
+      <c r="F30" s="2"/>
       <c r="G30" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H30" s="17"/>
-      <c r="I30" s="38"/>
+      <c r="I30" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="15">
@@ -2891,21 +2983,21 @@
       <c r="B31" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="29">
         <v>8.25</v>
       </c>
       <c r="D31" s="18">
         <v>45363</v>
       </c>
-      <c r="E31" s="30" t="s">
+      <c r="E31" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F31" s="30"/>
+      <c r="F31" s="2"/>
       <c r="G31" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H31" s="17"/>
-      <c r="I31" s="38"/>
+      <c r="I31" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="15">
@@ -2914,21 +3006,21 @@
       <c r="B32" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="29">
         <v>5.13</v>
       </c>
       <c r="D32" s="18">
         <v>45363</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E32" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F32" s="30"/>
+      <c r="F32" s="2"/>
       <c r="G32" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H32" s="17"/>
-      <c r="I32" s="38"/>
+      <c r="I32" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="15">
@@ -2937,21 +3029,21 @@
       <c r="B33" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="29">
         <v>6.04</v>
       </c>
       <c r="D33" s="18">
         <v>45363</v>
       </c>
-      <c r="E33" s="30" t="s">
+      <c r="E33" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F33" s="30"/>
+      <c r="F33" s="2"/>
       <c r="G33" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H33" s="17"/>
-      <c r="I33" s="38"/>
+      <c r="I33" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="15">
@@ -2960,21 +3052,21 @@
       <c r="B34" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="29">
         <v>6.09</v>
       </c>
       <c r="D34" s="18">
         <v>45363</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F34" s="30"/>
+      <c r="F34" s="2"/>
       <c r="G34" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H34" s="17"/>
-      <c r="I34" s="38"/>
+      <c r="I34" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="33.75">
       <c r="A35" s="15">
@@ -2983,21 +3075,21 @@
       <c r="B35" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="29">
         <v>12.09</v>
       </c>
       <c r="D35" s="18">
         <v>45363</v>
       </c>
-      <c r="E35" s="30" t="s">
+      <c r="E35" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F35" s="30"/>
+      <c r="F35" s="2"/>
       <c r="G35" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H35" s="17"/>
-      <c r="I35" s="38"/>
+      <c r="I35" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="15">
@@ -3006,21 +3098,21 @@
       <c r="B36" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="29">
         <v>12.09</v>
       </c>
       <c r="D36" s="18">
         <v>45363</v>
       </c>
-      <c r="E36" s="30" t="s">
+      <c r="E36" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F36" s="30"/>
+      <c r="F36" s="2"/>
       <c r="G36" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H36" s="17"/>
-      <c r="I36" s="38"/>
+      <c r="I36" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="15">
@@ -3029,21 +3121,21 @@
       <c r="B37" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="29">
         <v>25.47</v>
       </c>
       <c r="D37" s="18">
         <v>45364</v>
       </c>
-      <c r="E37" s="30" t="s">
+      <c r="E37" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F37" s="30"/>
+      <c r="F37" s="2"/>
       <c r="G37" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H37" s="17"/>
-      <c r="I37" s="38"/>
+      <c r="I37" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="15">
@@ -3052,21 +3144,21 @@
       <c r="B38" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="29">
         <v>10.16</v>
       </c>
       <c r="D38" s="18">
         <v>45364</v>
       </c>
-      <c r="E38" s="30" t="s">
+      <c r="E38" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F38" s="30"/>
+      <c r="F38" s="2"/>
       <c r="G38" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H38" s="17"/>
-      <c r="I38" s="38"/>
+      <c r="I38" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="33.75">
       <c r="A39" s="15">
@@ -3075,21 +3167,21 @@
       <c r="B39" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="29">
         <v>17.23</v>
       </c>
       <c r="D39" s="18">
         <v>45364</v>
       </c>
-      <c r="E39" s="30" t="s">
+      <c r="E39" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F39" s="30"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H39" s="17"/>
-      <c r="I39" s="38"/>
+      <c r="I39" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="15">
@@ -3098,21 +3190,21 @@
       <c r="B40" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="29">
         <v>13.18</v>
       </c>
       <c r="D40" s="18">
         <v>45364</v>
       </c>
-      <c r="E40" s="30" t="s">
+      <c r="E40" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F40" s="30"/>
+      <c r="F40" s="2"/>
       <c r="G40" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H40" s="17"/>
-      <c r="I40" s="38"/>
+      <c r="I40" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="15">
@@ -3121,21 +3213,21 @@
       <c r="B41" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="29">
         <v>10.06</v>
       </c>
       <c r="D41" s="18">
         <v>45365</v>
       </c>
-      <c r="E41" s="30" t="s">
+      <c r="E41" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F41" s="30"/>
+      <c r="F41" s="2"/>
       <c r="G41" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H41" s="17"/>
-      <c r="I41" s="38"/>
+      <c r="I41" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="15">
@@ -3144,21 +3236,21 @@
       <c r="B42" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="29">
         <v>2.3</v>
       </c>
       <c r="D42" s="18">
         <v>45365</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F42" s="30"/>
+      <c r="F42" s="2"/>
       <c r="G42" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H42" s="17"/>
-      <c r="I42" s="38"/>
+      <c r="I42" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="15">
@@ -3167,21 +3259,21 @@
       <c r="B43" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="29">
         <v>14.17</v>
       </c>
       <c r="D43" s="18">
         <v>45365</v>
       </c>
-      <c r="E43" s="30" t="s">
+      <c r="E43" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F43" s="30"/>
+      <c r="F43" s="2"/>
       <c r="G43" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H43" s="17"/>
-      <c r="I43" s="38"/>
+      <c r="I43" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20.25">
       <c r="A44" s="15">
@@ -3190,32 +3282,32 @@
       <c r="B44" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="29">
         <v>27.06</v>
       </c>
       <c r="D44" s="18">
         <v>45365</v>
       </c>
-      <c r="E44" s="30" t="s">
+      <c r="E44" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F44" s="30"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H44" s="17"/>
-      <c r="I44" s="38"/>
+      <c r="I44" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="21"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A46" s="11" t="s">
@@ -3224,8 +3316,8 @@
       <c r="B46" s="12"/>
       <c r="C46" s="25"/>
       <c r="D46" s="26"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="2"/>
@@ -3237,16 +3329,16 @@
       <c r="B47" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D47" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="30" t="s">
+      <c r="E47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="30" t="s">
+      <c r="F47" s="2" t="s">
         <v>195</v>
       </c>
       <c r="G47" s="14" t="s">
@@ -3255,7 +3347,7 @@
       <c r="H47" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I47" s="38"/>
+      <c r="I47" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="33.75">
       <c r="A48" s="15">
@@ -3264,21 +3356,21 @@
       <c r="B48" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="29">
         <v>17.33</v>
       </c>
       <c r="D48" s="18">
         <v>45366</v>
       </c>
-      <c r="E48" s="30" t="s">
+      <c r="E48" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F48" s="30"/>
+      <c r="F48" s="2"/>
       <c r="G48" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H48" s="17"/>
-      <c r="I48" s="38"/>
+      <c r="I48" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="15">
@@ -3287,21 +3379,21 @@
       <c r="B49" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="29">
         <v>18.21</v>
       </c>
       <c r="D49" s="18">
         <v>45366</v>
       </c>
-      <c r="E49" s="30" t="s">
+      <c r="E49" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F49" s="30"/>
+      <c r="F49" s="2"/>
       <c r="G49" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H49" s="17"/>
-      <c r="I49" s="38"/>
+      <c r="I49" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="15">
@@ -3310,21 +3402,21 @@
       <c r="B50" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="29">
         <v>13.01</v>
       </c>
       <c r="D50" s="18">
         <v>45366</v>
       </c>
-      <c r="E50" s="30" t="s">
+      <c r="E50" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F50" s="30"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H50" s="17"/>
-      <c r="I50" s="38"/>
+      <c r="I50" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
       <c r="A51" s="15">
@@ -3333,21 +3425,21 @@
       <c r="B51" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="29">
         <v>10.17</v>
       </c>
       <c r="D51" s="18">
         <v>45366</v>
       </c>
-      <c r="E51" s="30" t="s">
+      <c r="E51" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F51" s="30"/>
+      <c r="F51" s="2"/>
       <c r="G51" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H51" s="17"/>
-      <c r="I51" s="38"/>
+      <c r="I51" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="15">
@@ -3356,21 +3448,21 @@
       <c r="B52" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="29">
         <v>16.56</v>
       </c>
       <c r="D52" s="18">
         <v>45367</v>
       </c>
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F52" s="30"/>
+      <c r="F52" s="2"/>
       <c r="G52" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H52" s="17"/>
-      <c r="I52" s="38"/>
+      <c r="I52" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="15">
@@ -3379,21 +3471,21 @@
       <c r="B53" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="29">
         <v>7.56</v>
       </c>
       <c r="D53" s="18">
         <v>45367</v>
       </c>
-      <c r="E53" s="30" t="s">
+      <c r="E53" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F53" s="30"/>
+      <c r="F53" s="2"/>
       <c r="G53" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H53" s="17"/>
-      <c r="I53" s="38"/>
+      <c r="I53" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="15">
@@ -3402,21 +3494,21 @@
       <c r="B54" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="29">
         <v>12.49</v>
       </c>
       <c r="D54" s="18">
         <v>45367</v>
       </c>
-      <c r="E54" s="30" t="s">
+      <c r="E54" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F54" s="30"/>
+      <c r="F54" s="2"/>
       <c r="G54" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H54" s="17"/>
-      <c r="I54" s="38"/>
+      <c r="I54" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
       <c r="A55" s="15">
@@ -3425,21 +3517,21 @@
       <c r="B55" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="29">
         <v>7.13</v>
       </c>
       <c r="D55" s="18">
         <v>45367</v>
       </c>
-      <c r="E55" s="30" t="s">
+      <c r="E55" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F55" s="30"/>
+      <c r="F55" s="2"/>
       <c r="G55" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H55" s="17"/>
-      <c r="I55" s="38"/>
+      <c r="I55" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
       <c r="A56" s="15">
@@ -3448,21 +3540,21 @@
       <c r="B56" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="29">
         <v>18.22</v>
       </c>
       <c r="D56" s="18">
         <v>45367</v>
       </c>
-      <c r="E56" s="30" t="s">
+      <c r="E56" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F56" s="30"/>
+      <c r="F56" s="2"/>
       <c r="G56" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H56" s="17"/>
-      <c r="I56" s="38"/>
+      <c r="I56" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="15">
@@ -3471,21 +3563,21 @@
       <c r="B57" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="29">
         <v>23.21</v>
       </c>
       <c r="D57" s="18">
         <v>45368</v>
       </c>
-      <c r="E57" s="30" t="s">
+      <c r="E57" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F57" s="30"/>
+      <c r="F57" s="2"/>
       <c r="G57" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H57" s="17"/>
-      <c r="I57" s="38"/>
+      <c r="I57" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="33.75">
       <c r="A58" s="15">
@@ -3494,21 +3586,21 @@
       <c r="B58" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="29">
         <v>28.28</v>
       </c>
       <c r="D58" s="18">
         <v>45368</v>
       </c>
-      <c r="E58" s="30" t="s">
+      <c r="E58" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F58" s="30"/>
+      <c r="F58" s="2"/>
       <c r="G58" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H58" s="17"/>
-      <c r="I58" s="38"/>
+      <c r="I58" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
       <c r="A59" s="15">
@@ -3517,19 +3609,21 @@
       <c r="B59" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="29">
         <v>17.27</v>
       </c>
       <c r="D59" s="18">
         <v>45369</v>
       </c>
-      <c r="E59" s="30" t="s">
+      <c r="E59" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F59" s="30"/>
-      <c r="G59" s="17"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H59" s="17"/>
-      <c r="I59" s="38"/>
+      <c r="I59" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="15">
@@ -3538,19 +3632,21 @@
       <c r="B60" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="29">
         <v>11.51</v>
       </c>
       <c r="D60" s="18">
         <v>45369</v>
       </c>
-      <c r="E60" s="30" t="s">
+      <c r="E60" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F60" s="30"/>
-      <c r="G60" s="17"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H60" s="17"/>
-      <c r="I60" s="38"/>
+      <c r="I60" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="15">
@@ -3559,19 +3655,21 @@
       <c r="B61" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="29">
         <v>7.15</v>
       </c>
       <c r="D61" s="18">
         <v>45369</v>
       </c>
-      <c r="E61" s="30" t="s">
+      <c r="E61" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F61" s="30"/>
-      <c r="G61" s="17"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H61" s="17"/>
-      <c r="I61" s="38"/>
+      <c r="I61" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="20.25">
       <c r="A62" s="15">
@@ -3580,27 +3678,29 @@
       <c r="B62" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="29">
         <v>9.02</v>
       </c>
       <c r="D62" s="18">
         <v>45369</v>
       </c>
-      <c r="E62" s="30" t="s">
+      <c r="E62" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F62" s="30"/>
-      <c r="G62" s="17"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H62" s="17"/>
-      <c r="I62" s="38"/>
+      <c r="I62" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A63" s="44"/>
+      <c r="A63" s="41"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -3612,8 +3712,8 @@
       <c r="B64" s="12"/>
       <c r="C64" s="25"/>
       <c r="D64" s="26"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12"/>
       <c r="I64" s="2"/>
@@ -3625,16 +3725,16 @@
       <c r="B65" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="C65" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D65" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="30" t="s">
+      <c r="E65" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F65" s="30" t="s">
+      <c r="F65" s="2" t="s">
         <v>195</v>
       </c>
       <c r="G65" s="14" t="s">
@@ -3643,7 +3743,7 @@
       <c r="H65" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I65" s="38"/>
+      <c r="I65" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="15">
@@ -3652,19 +3752,21 @@
       <c r="B66" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="29">
         <v>26.05</v>
       </c>
       <c r="D66" s="18">
         <v>45370</v>
       </c>
-      <c r="E66" s="30" t="s">
+      <c r="E66" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F66" s="30"/>
-      <c r="G66" s="17"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H66" s="17"/>
-      <c r="I66" s="38"/>
+      <c r="I66" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="33.75">
       <c r="A67" s="15">
@@ -3673,19 +3775,21 @@
       <c r="B67" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="29">
         <v>12.51</v>
       </c>
       <c r="D67" s="18">
         <v>45370</v>
       </c>
-      <c r="E67" s="30" t="s">
+      <c r="E67" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F67" s="30"/>
-      <c r="G67" s="17"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H67" s="17"/>
-      <c r="I67" s="38"/>
+      <c r="I67" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="33.75">
       <c r="A68" s="15">
@@ -3694,19 +3798,21 @@
       <c r="B68" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="29">
         <v>13.31</v>
       </c>
       <c r="D68" s="18">
         <v>45370</v>
       </c>
-      <c r="E68" s="30" t="s">
+      <c r="E68" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F68" s="30"/>
-      <c r="G68" s="17"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H68" s="17"/>
-      <c r="I68" s="38"/>
+      <c r="I68" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="33.75">
       <c r="A69" s="15">
@@ -3715,19 +3821,21 @@
       <c r="B69" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="29">
         <v>24.56</v>
       </c>
       <c r="D69" s="18">
         <v>45371</v>
       </c>
-      <c r="E69" s="30" t="s">
+      <c r="E69" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F69" s="30"/>
-      <c r="G69" s="17"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H69" s="17"/>
-      <c r="I69" s="38"/>
+      <c r="I69" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="33.75">
       <c r="A70" s="15">
@@ -3736,187 +3844,195 @@
       <c r="B70" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="29">
         <v>18.08</v>
       </c>
       <c r="D70" s="18">
         <v>45371</v>
       </c>
-      <c r="E70" s="30" t="s">
+      <c r="E70" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F70" s="30"/>
-      <c r="G70" s="17"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H70" s="17"/>
-      <c r="I70" s="38"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+      <c r="I70" s="35"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="33.75">
       <c r="A71" s="15">
         <v>6</v>
       </c>
       <c r="B71" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="29">
         <v>13.55</v>
       </c>
       <c r="D71" s="18">
         <v>45371</v>
       </c>
-      <c r="E71" s="30" t="s">
+      <c r="E71" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F71" s="30"/>
-      <c r="G71" s="17"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H71" s="17"/>
-      <c r="I71" s="38"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+      <c r="I71" s="35"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="33.75">
       <c r="A72" s="15">
         <v>7</v>
       </c>
       <c r="B72" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="29">
         <v>29.41</v>
       </c>
       <c r="D72" s="18">
         <v>45372</v>
       </c>
-      <c r="E72" s="30" t="s">
+      <c r="E72" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F72" s="30"/>
-      <c r="G72" s="17"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H72" s="17"/>
-      <c r="I72" s="38"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+      <c r="I72" s="35"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="33.75">
       <c r="A73" s="15">
         <v>8</v>
       </c>
       <c r="B73" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C73" s="31">
+      <c r="C73" s="29">
         <v>10.49</v>
       </c>
       <c r="D73" s="18">
         <v>45372</v>
       </c>
-      <c r="E73" s="30" t="s">
+      <c r="E73" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F73" s="30"/>
-      <c r="G73" s="17"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H73" s="17"/>
-      <c r="I73" s="38"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+      <c r="I73" s="35"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="33.75">
       <c r="A74" s="15">
         <v>9</v>
       </c>
       <c r="B74" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="C74" s="31">
+      <c r="C74" s="29">
         <v>16.02</v>
       </c>
       <c r="D74" s="18">
         <v>45372</v>
       </c>
-      <c r="E74" s="30" t="s">
+      <c r="E74" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F74" s="30"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="17"/>
       <c r="H74" s="17"/>
-      <c r="I74" s="38"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+      <c r="I74" s="35"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="33.75">
       <c r="A75" s="15">
         <v>10</v>
       </c>
       <c r="B75" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="29">
         <v>10.48</v>
       </c>
       <c r="D75" s="18">
         <v>45373</v>
       </c>
-      <c r="E75" s="30" t="s">
+      <c r="E75" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F75" s="30"/>
+      <c r="F75" s="2"/>
       <c r="G75" s="17"/>
       <c r="H75" s="17"/>
-      <c r="I75" s="38"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+      <c r="I75" s="35"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="20.25">
       <c r="A76" s="15">
         <v>11</v>
       </c>
       <c r="B76" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="C76" s="31">
+      <c r="C76" s="29">
         <v>20.49</v>
       </c>
       <c r="D76" s="18">
         <v>45373</v>
       </c>
-      <c r="E76" s="30" t="s">
+      <c r="E76" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F76" s="30"/>
+      <c r="F76" s="2"/>
       <c r="G76" s="17"/>
       <c r="H76" s="17"/>
-      <c r="I76" s="38"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+      <c r="I76" s="35"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="21"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="33"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="B77" s="35"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="31"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="35"/>
+      <c r="I77" s="35"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A78" s="11" t="s">
         <v>12</v>
       </c>
       <c r="B78" s="12"/>
       <c r="C78" s="25"/>
       <c r="D78" s="26"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12"/>
       <c r="I78" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="28" t="s">
+      <c r="C79" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D79" s="29" t="s">
+      <c r="D79" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E79" s="30" t="s">
+      <c r="E79" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F79" s="30" t="s">
+      <c r="F79" s="2" t="s">
         <v>195</v>
       </c>
       <c r="G79" s="14" t="s">
@@ -3925,7 +4041,7 @@
       <c r="H79" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I79" s="38"/>
+      <c r="I79" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="15">
@@ -3934,19 +4050,19 @@
       <c r="B80" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C80" s="47">
-        <v>25.118622685185183</v>
+      <c r="C80" s="44">
+        <v>28.118275462962963</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
       </c>
-      <c r="E80" s="30" t="s">
+      <c r="E80" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F80" s="30"/>
+      <c r="F80" s="2"/>
       <c r="G80" s="19"/>
       <c r="H80" s="19"/>
-      <c r="I80" s="38"/>
+      <c r="I80" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="15">
@@ -3955,19 +4071,19 @@
       <c r="B81" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C81" s="47">
-        <v>25.118622685185183</v>
+      <c r="C81" s="44">
+        <v>28.118275462962963</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
       </c>
-      <c r="E81" s="30" t="s">
+      <c r="E81" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F81" s="30"/>
+      <c r="F81" s="2"/>
       <c r="G81" s="19"/>
       <c r="H81" s="19"/>
-      <c r="I81" s="38"/>
+      <c r="I81" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="15">
@@ -3976,19 +4092,19 @@
       <c r="B82" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C82" s="47">
-        <v>25.118622685185183</v>
+      <c r="C82" s="44">
+        <v>28.118275462962963</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
       </c>
-      <c r="E82" s="30" t="s">
+      <c r="E82" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="F82" s="30"/>
+      <c r="F82" s="2"/>
       <c r="G82" s="19"/>
       <c r="H82" s="19"/>
-      <c r="I82" s="38"/>
+      <c r="I82" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="15">
@@ -3997,19 +4113,19 @@
       <c r="B83" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C83" s="47">
-        <v>25.118622685185183</v>
+      <c r="C83" s="44">
+        <v>28.118275462962963</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
       </c>
-      <c r="E83" s="30" t="s">
+      <c r="E83" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F83" s="30"/>
+      <c r="F83" s="2"/>
       <c r="G83" s="19"/>
       <c r="H83" s="19"/>
-      <c r="I83" s="38"/>
+      <c r="I83" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="15">
@@ -4018,19 +4134,19 @@
       <c r="B84" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C84" s="29">
         <v>10.13</v>
       </c>
       <c r="D84" s="18">
         <v>45378</v>
       </c>
-      <c r="E84" s="30" t="s">
+      <c r="E84" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F84" s="30"/>
+      <c r="F84" s="2"/>
       <c r="G84" s="17"/>
       <c r="H84" s="17"/>
-      <c r="I84" s="38"/>
+      <c r="I84" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="15">
@@ -4039,19 +4155,19 @@
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="C85" s="31">
+      <c r="C85" s="29">
         <v>9.05</v>
       </c>
       <c r="D85" s="18">
         <v>45378</v>
       </c>
-      <c r="E85" s="30" t="s">
+      <c r="E85" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F85" s="30"/>
+      <c r="F85" s="2"/>
       <c r="G85" s="17"/>
       <c r="H85" s="17"/>
-      <c r="I85" s="38"/>
+      <c r="I85" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="15">
@@ -4060,19 +4176,19 @@
       <c r="B86" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="C86" s="31">
+      <c r="C86" s="29">
         <v>3.39</v>
       </c>
       <c r="D86" s="18">
         <v>45378</v>
       </c>
-      <c r="E86" s="30" t="s">
+      <c r="E86" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F86" s="30"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="17"/>
       <c r="H86" s="17"/>
-      <c r="I86" s="38"/>
+      <c r="I86" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="15">
@@ -4081,19 +4197,19 @@
       <c r="B87" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="C87" s="31">
+      <c r="C87" s="29">
         <v>8.27</v>
       </c>
       <c r="D87" s="18">
         <v>45378</v>
       </c>
-      <c r="E87" s="30" t="s">
+      <c r="E87" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F87" s="30"/>
+      <c r="F87" s="2"/>
       <c r="G87" s="17"/>
       <c r="H87" s="17"/>
-      <c r="I87" s="38"/>
+      <c r="I87" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="15">
@@ -4102,19 +4218,19 @@
       <c r="B88" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C88" s="29">
         <v>7.21</v>
       </c>
       <c r="D88" s="18">
         <v>45378</v>
       </c>
-      <c r="E88" s="30" t="s">
+      <c r="E88" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F88" s="30"/>
+      <c r="F88" s="2"/>
       <c r="G88" s="17"/>
       <c r="H88" s="17"/>
-      <c r="I88" s="38"/>
+      <c r="I88" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="15">
@@ -4123,19 +4239,19 @@
       <c r="B89" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="C89" s="31">
+      <c r="C89" s="29">
         <v>9.04</v>
       </c>
       <c r="D89" s="18">
         <v>45378</v>
       </c>
-      <c r="E89" s="30" t="s">
+      <c r="E89" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F89" s="30"/>
+      <c r="F89" s="2"/>
       <c r="G89" s="17"/>
       <c r="H89" s="17"/>
-      <c r="I89" s="38"/>
+      <c r="I89" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="15">
@@ -4144,19 +4260,19 @@
       <c r="B90" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C90" s="31">
+      <c r="C90" s="29">
         <v>14.14</v>
       </c>
       <c r="D90" s="18">
         <v>45378</v>
       </c>
-      <c r="E90" s="30" t="s">
+      <c r="E90" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F90" s="30"/>
+      <c r="F90" s="2"/>
       <c r="G90" s="17"/>
       <c r="H90" s="17"/>
-      <c r="I90" s="38"/>
+      <c r="I90" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="15">
@@ -4165,19 +4281,19 @@
       <c r="B91" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="C91" s="31">
+      <c r="C91" s="29">
         <v>14.01</v>
       </c>
       <c r="D91" s="18">
         <v>46840</v>
       </c>
-      <c r="E91" s="30" t="s">
+      <c r="E91" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F91" s="30"/>
+      <c r="F91" s="2"/>
       <c r="G91" s="17"/>
       <c r="H91" s="17"/>
-      <c r="I91" s="38"/>
+      <c r="I91" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="15">
@@ -4186,19 +4302,19 @@
       <c r="B92" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="C92" s="31">
+      <c r="C92" s="29">
         <v>11.17</v>
       </c>
       <c r="D92" s="18">
         <v>46840</v>
       </c>
-      <c r="E92" s="30" t="s">
+      <c r="E92" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F92" s="30"/>
+      <c r="F92" s="2"/>
       <c r="G92" s="17"/>
       <c r="H92" s="17"/>
-      <c r="I92" s="38"/>
+      <c r="I92" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="15">
@@ -4213,13 +4329,13 @@
       <c r="D93" s="18">
         <v>46840</v>
       </c>
-      <c r="E93" s="30" t="s">
+      <c r="E93" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F93" s="30"/>
+      <c r="F93" s="2"/>
       <c r="G93" s="17"/>
       <c r="H93" s="17"/>
-      <c r="I93" s="38"/>
+      <c r="I93" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="15">
@@ -4228,19 +4344,19 @@
       <c r="B94" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="C94" s="31">
+      <c r="C94" s="29">
         <v>12.33</v>
       </c>
       <c r="D94" s="18">
         <v>46840</v>
       </c>
-      <c r="E94" s="30" t="s">
+      <c r="E94" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F94" s="30"/>
+      <c r="F94" s="2"/>
       <c r="G94" s="17"/>
       <c r="H94" s="17"/>
-      <c r="I94" s="38"/>
+      <c r="I94" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="15">
@@ -4249,19 +4365,19 @@
       <c r="B95" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="C95" s="31">
+      <c r="C95" s="29">
         <v>10.57</v>
       </c>
       <c r="D95" s="18">
         <v>46840</v>
       </c>
-      <c r="E95" s="30" t="s">
+      <c r="E95" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F95" s="30"/>
+      <c r="F95" s="2"/>
       <c r="G95" s="17"/>
       <c r="H95" s="17"/>
-      <c r="I95" s="38"/>
+      <c r="I95" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="15">
@@ -4270,19 +4386,19 @@
       <c r="B96" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="C96" s="31">
+      <c r="C96" s="29">
         <v>10.13</v>
       </c>
       <c r="D96" s="18">
         <v>45380</v>
       </c>
-      <c r="E96" s="30" t="s">
+      <c r="E96" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F96" s="30"/>
+      <c r="F96" s="2"/>
       <c r="G96" s="18"/>
       <c r="H96" s="17"/>
-      <c r="I96" s="38"/>
+      <c r="I96" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="15">
@@ -4291,19 +4407,19 @@
       <c r="B97" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="C97" s="31">
+      <c r="C97" s="29">
         <v>17.37</v>
       </c>
       <c r="D97" s="18">
         <v>45380</v>
       </c>
-      <c r="E97" s="30" t="s">
+      <c r="E97" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F97" s="30"/>
+      <c r="F97" s="2"/>
       <c r="G97" s="18"/>
       <c r="H97" s="17"/>
-      <c r="I97" s="38"/>
+      <c r="I97" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="15">
@@ -4312,19 +4428,19 @@
       <c r="B98" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="C98" s="31">
+      <c r="C98" s="29">
         <v>9.28</v>
       </c>
       <c r="D98" s="18">
         <v>45380</v>
       </c>
-      <c r="E98" s="30" t="s">
+      <c r="E98" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F98" s="30"/>
+      <c r="F98" s="2"/>
       <c r="G98" s="18"/>
       <c r="H98" s="17"/>
-      <c r="I98" s="38"/>
+      <c r="I98" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="15">
@@ -4333,19 +4449,19 @@
       <c r="B99" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="C99" s="31">
+      <c r="C99" s="29">
         <v>7.18</v>
       </c>
       <c r="D99" s="18">
         <v>45380</v>
       </c>
-      <c r="E99" s="30" t="s">
+      <c r="E99" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F99" s="30"/>
+      <c r="F99" s="2"/>
       <c r="G99" s="18"/>
       <c r="H99" s="17"/>
-      <c r="I99" s="38"/>
+      <c r="I99" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="15">
@@ -4354,19 +4470,19 @@
       <c r="B100" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="C100" s="31">
+      <c r="C100" s="29">
         <v>7.54</v>
       </c>
       <c r="D100" s="18">
         <v>45380</v>
       </c>
-      <c r="E100" s="30" t="s">
+      <c r="E100" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F100" s="30"/>
+      <c r="F100" s="2"/>
       <c r="G100" s="18"/>
       <c r="H100" s="17"/>
-      <c r="I100" s="38"/>
+      <c r="I100" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="15">
@@ -4375,19 +4491,19 @@
       <c r="B101" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="C101" s="31">
+      <c r="C101" s="29">
         <v>25.46</v>
       </c>
       <c r="D101" s="18">
         <v>45381</v>
       </c>
-      <c r="E101" s="30" t="s">
+      <c r="E101" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F101" s="30"/>
+      <c r="F101" s="2"/>
       <c r="G101" s="18"/>
       <c r="H101" s="17"/>
-      <c r="I101" s="38"/>
+      <c r="I101" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="15">
@@ -4396,19 +4512,19 @@
       <c r="B102" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="C102" s="31">
+      <c r="C102" s="29">
         <v>8.47</v>
       </c>
       <c r="D102" s="18">
         <v>45381</v>
       </c>
-      <c r="E102" s="30" t="s">
+      <c r="E102" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F102" s="30"/>
+      <c r="F102" s="2"/>
       <c r="G102" s="18"/>
       <c r="H102" s="17"/>
-      <c r="I102" s="38"/>
+      <c r="I102" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="33">
       <c r="A103" s="15">
@@ -4417,19 +4533,19 @@
       <c r="B103" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="C103" s="31">
+      <c r="C103" s="29">
         <v>5.43</v>
       </c>
       <c r="D103" s="18">
         <v>45381</v>
       </c>
-      <c r="E103" s="30" t="s">
+      <c r="E103" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F103" s="30"/>
+      <c r="F103" s="2"/>
       <c r="G103" s="18"/>
       <c r="H103" s="17"/>
-      <c r="I103" s="38"/>
+      <c r="I103" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="33.75">
       <c r="A104" s="15">
@@ -4438,19 +4554,19 @@
       <c r="B104" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="C104" s="31">
+      <c r="C104" s="29">
         <v>12.35</v>
       </c>
       <c r="D104" s="18">
         <v>45381</v>
       </c>
-      <c r="E104" s="30" t="s">
+      <c r="E104" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F104" s="30"/>
+      <c r="F104" s="2"/>
       <c r="G104" s="18"/>
       <c r="H104" s="17"/>
-      <c r="I104" s="38"/>
+      <c r="I104" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="33">
       <c r="A105" s="15">
@@ -4459,19 +4575,19 @@
       <c r="B105" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="C105" s="31">
+      <c r="C105" s="29">
         <v>4.06</v>
       </c>
       <c r="D105" s="18">
         <v>45381</v>
       </c>
-      <c r="E105" s="30" t="s">
+      <c r="E105" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F105" s="30"/>
+      <c r="F105" s="2"/>
       <c r="G105" s="18"/>
       <c r="H105" s="17"/>
-      <c r="I105" s="38"/>
+      <c r="I105" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="15">
@@ -4480,19 +4596,19 @@
       <c r="B106" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="C106" s="31">
+      <c r="C106" s="29">
         <v>14.59</v>
       </c>
       <c r="D106" s="18">
         <v>45382</v>
       </c>
-      <c r="E106" s="30" t="s">
+      <c r="E106" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F106" s="30"/>
+      <c r="F106" s="2"/>
       <c r="G106" s="18"/>
       <c r="H106" s="17"/>
-      <c r="I106" s="38"/>
+      <c r="I106" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="15">
@@ -4501,19 +4617,19 @@
       <c r="B107" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="C107" s="31">
+      <c r="C107" s="29">
         <v>18.2</v>
       </c>
       <c r="D107" s="18">
         <v>45382</v>
       </c>
-      <c r="E107" s="30" t="s">
+      <c r="E107" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F107" s="30"/>
+      <c r="F107" s="2"/>
       <c r="G107" s="18"/>
       <c r="H107" s="17"/>
-      <c r="I107" s="38"/>
+      <c r="I107" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="33">
       <c r="A108" s="15">
@@ -4522,19 +4638,19 @@
       <c r="B108" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="C108" s="31">
+      <c r="C108" s="29">
         <v>13.41</v>
       </c>
       <c r="D108" s="18">
         <v>45382</v>
       </c>
-      <c r="E108" s="30" t="s">
+      <c r="E108" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F108" s="30"/>
+      <c r="F108" s="2"/>
       <c r="G108" s="18"/>
       <c r="H108" s="17"/>
-      <c r="I108" s="38"/>
+      <c r="I108" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="15">
@@ -4543,1050 +4659,1050 @@
       <c r="B109" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="C109" s="31">
+      <c r="C109" s="29">
         <v>11.59</v>
       </c>
       <c r="D109" s="18">
         <v>45382</v>
       </c>
-      <c r="E109" s="30" t="s">
+      <c r="E109" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F109" s="30"/>
+      <c r="F109" s="2"/>
       <c r="G109" s="18"/>
       <c r="H109" s="17"/>
-      <c r="I109" s="38"/>
+      <c r="I109" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="21"/>
-      <c r="B110" s="38"/>
-      <c r="C110" s="32"/>
-      <c r="D110" s="33"/>
-      <c r="E110" s="30"/>
-      <c r="F110" s="30"/>
-      <c r="G110" s="48"/>
-      <c r="H110" s="38"/>
-      <c r="I110" s="38"/>
+      <c r="B110" s="35"/>
+      <c r="C110" s="30"/>
+      <c r="D110" s="31"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="45"/>
+      <c r="H110" s="35"/>
+      <c r="I110" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="21"/>
-      <c r="B111" s="38"/>
-      <c r="C111" s="32"/>
-      <c r="D111" s="33"/>
-      <c r="E111" s="30"/>
-      <c r="F111" s="30"/>
-      <c r="G111" s="48"/>
-      <c r="H111" s="38"/>
-      <c r="I111" s="38"/>
+      <c r="B111" s="35"/>
+      <c r="C111" s="30"/>
+      <c r="D111" s="31"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="45"/>
+      <c r="H111" s="35"/>
+      <c r="I111" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="21"/>
-      <c r="B112" s="38"/>
-      <c r="C112" s="32"/>
-      <c r="D112" s="33"/>
-      <c r="E112" s="30"/>
-      <c r="F112" s="30"/>
-      <c r="G112" s="48"/>
-      <c r="H112" s="38"/>
-      <c r="I112" s="38"/>
+      <c r="B112" s="35"/>
+      <c r="C112" s="30"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="45"/>
+      <c r="H112" s="35"/>
+      <c r="I112" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="21"/>
-      <c r="B113" s="38"/>
-      <c r="C113" s="32"/>
-      <c r="D113" s="33"/>
-      <c r="E113" s="30"/>
-      <c r="F113" s="30"/>
-      <c r="G113" s="48"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="31"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="45"/>
+      <c r="H113" s="35"/>
+      <c r="I113" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="21"/>
-      <c r="B114" s="38"/>
-      <c r="C114" s="32"/>
-      <c r="D114" s="33"/>
-      <c r="E114" s="30"/>
-      <c r="F114" s="30"/>
-      <c r="G114" s="48"/>
-      <c r="H114" s="38"/>
-      <c r="I114" s="38"/>
+      <c r="B114" s="35"/>
+      <c r="C114" s="30"/>
+      <c r="D114" s="31"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="45"/>
+      <c r="H114" s="35"/>
+      <c r="I114" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="21"/>
-      <c r="B115" s="38"/>
-      <c r="C115" s="32"/>
-      <c r="D115" s="33"/>
-      <c r="E115" s="30"/>
-      <c r="F115" s="30"/>
-      <c r="G115" s="48"/>
-      <c r="H115" s="38"/>
-      <c r="I115" s="38"/>
+      <c r="B115" s="35"/>
+      <c r="C115" s="30"/>
+      <c r="D115" s="31"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="45"/>
+      <c r="H115" s="35"/>
+      <c r="I115" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="21"/>
-      <c r="B116" s="38"/>
-      <c r="C116" s="32"/>
-      <c r="D116" s="33"/>
-      <c r="E116" s="30"/>
-      <c r="F116" s="30"/>
-      <c r="G116" s="48"/>
-      <c r="H116" s="38"/>
-      <c r="I116" s="38"/>
+      <c r="B116" s="35"/>
+      <c r="C116" s="30"/>
+      <c r="D116" s="31"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="45"/>
+      <c r="H116" s="35"/>
+      <c r="I116" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="21"/>
-      <c r="B117" s="38"/>
-      <c r="C117" s="32"/>
-      <c r="D117" s="33"/>
-      <c r="E117" s="30"/>
-      <c r="F117" s="30"/>
-      <c r="G117" s="48"/>
-      <c r="H117" s="38"/>
-      <c r="I117" s="38"/>
+      <c r="B117" s="35"/>
+      <c r="C117" s="30"/>
+      <c r="D117" s="31"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="45"/>
+      <c r="H117" s="35"/>
+      <c r="I117" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="21"/>
-      <c r="B118" s="38"/>
-      <c r="C118" s="32"/>
-      <c r="D118" s="33"/>
-      <c r="E118" s="30"/>
-      <c r="F118" s="30"/>
-      <c r="G118" s="48"/>
-      <c r="H118" s="38"/>
-      <c r="I118" s="38"/>
+      <c r="B118" s="35"/>
+      <c r="C118" s="30"/>
+      <c r="D118" s="31"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="45"/>
+      <c r="H118" s="35"/>
+      <c r="I118" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="21"/>
-      <c r="B119" s="38"/>
-      <c r="C119" s="32"/>
-      <c r="D119" s="33"/>
-      <c r="E119" s="30"/>
-      <c r="F119" s="30"/>
-      <c r="G119" s="48"/>
-      <c r="H119" s="38"/>
-      <c r="I119" s="38"/>
+      <c r="B119" s="35"/>
+      <c r="C119" s="30"/>
+      <c r="D119" s="31"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="45"/>
+      <c r="H119" s="35"/>
+      <c r="I119" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="21"/>
-      <c r="B120" s="38"/>
-      <c r="C120" s="32"/>
-      <c r="D120" s="33"/>
-      <c r="E120" s="30"/>
-      <c r="F120" s="30"/>
-      <c r="G120" s="48"/>
-      <c r="H120" s="38"/>
-      <c r="I120" s="38"/>
+      <c r="B120" s="35"/>
+      <c r="C120" s="30"/>
+      <c r="D120" s="31"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="45"/>
+      <c r="H120" s="35"/>
+      <c r="I120" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="21"/>
-      <c r="B121" s="38"/>
-      <c r="C121" s="32"/>
-      <c r="D121" s="33"/>
-      <c r="E121" s="30"/>
-      <c r="F121" s="30"/>
-      <c r="G121" s="48"/>
-      <c r="H121" s="38"/>
-      <c r="I121" s="38"/>
+      <c r="B121" s="35"/>
+      <c r="C121" s="30"/>
+      <c r="D121" s="31"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="45"/>
+      <c r="H121" s="35"/>
+      <c r="I121" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="21"/>
-      <c r="B122" s="38"/>
-      <c r="C122" s="32"/>
-      <c r="D122" s="33"/>
-      <c r="E122" s="30"/>
-      <c r="F122" s="30"/>
-      <c r="G122" s="48"/>
-      <c r="H122" s="38"/>
-      <c r="I122" s="38"/>
+      <c r="B122" s="35"/>
+      <c r="C122" s="30"/>
+      <c r="D122" s="31"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="45"/>
+      <c r="H122" s="35"/>
+      <c r="I122" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="21"/>
-      <c r="B123" s="38"/>
-      <c r="C123" s="32"/>
-      <c r="D123" s="33"/>
-      <c r="E123" s="30"/>
-      <c r="F123" s="30"/>
-      <c r="G123" s="48"/>
-      <c r="H123" s="38"/>
-      <c r="I123" s="38"/>
+      <c r="B123" s="35"/>
+      <c r="C123" s="30"/>
+      <c r="D123" s="31"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="45"/>
+      <c r="H123" s="35"/>
+      <c r="I123" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="21"/>
-      <c r="B124" s="38"/>
-      <c r="C124" s="32"/>
-      <c r="D124" s="33"/>
-      <c r="E124" s="30"/>
-      <c r="F124" s="30"/>
-      <c r="G124" s="48"/>
-      <c r="H124" s="38"/>
-      <c r="I124" s="38"/>
+      <c r="B124" s="35"/>
+      <c r="C124" s="30"/>
+      <c r="D124" s="31"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="45"/>
+      <c r="H124" s="35"/>
+      <c r="I124" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="21"/>
-      <c r="B125" s="38"/>
-      <c r="C125" s="32"/>
-      <c r="D125" s="33"/>
-      <c r="E125" s="30"/>
-      <c r="F125" s="30"/>
-      <c r="G125" s="48"/>
-      <c r="H125" s="38"/>
-      <c r="I125" s="38"/>
+      <c r="B125" s="35"/>
+      <c r="C125" s="30"/>
+      <c r="D125" s="31"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="45"/>
+      <c r="H125" s="35"/>
+      <c r="I125" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="21"/>
-      <c r="B126" s="38"/>
-      <c r="C126" s="32"/>
-      <c r="D126" s="33"/>
-      <c r="E126" s="30"/>
-      <c r="F126" s="30"/>
-      <c r="G126" s="48"/>
-      <c r="H126" s="38"/>
-      <c r="I126" s="38"/>
+      <c r="B126" s="35"/>
+      <c r="C126" s="30"/>
+      <c r="D126" s="31"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="45"/>
+      <c r="H126" s="35"/>
+      <c r="I126" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="21"/>
-      <c r="B127" s="38"/>
-      <c r="C127" s="32"/>
-      <c r="D127" s="33"/>
-      <c r="E127" s="30"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="48"/>
-      <c r="H127" s="38"/>
-      <c r="I127" s="38"/>
+      <c r="B127" s="35"/>
+      <c r="C127" s="30"/>
+      <c r="D127" s="31"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="45"/>
+      <c r="H127" s="35"/>
+      <c r="I127" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="21"/>
-      <c r="B128" s="38"/>
-      <c r="C128" s="32"/>
-      <c r="D128" s="33"/>
-      <c r="E128" s="30"/>
-      <c r="F128" s="30"/>
-      <c r="G128" s="48"/>
-      <c r="H128" s="38"/>
-      <c r="I128" s="38"/>
+      <c r="B128" s="35"/>
+      <c r="C128" s="30"/>
+      <c r="D128" s="31"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="45"/>
+      <c r="H128" s="35"/>
+      <c r="I128" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="21"/>
-      <c r="B129" s="38"/>
-      <c r="C129" s="32"/>
-      <c r="D129" s="33"/>
-      <c r="E129" s="30"/>
-      <c r="F129" s="30"/>
-      <c r="G129" s="48"/>
-      <c r="H129" s="38"/>
-      <c r="I129" s="38"/>
+      <c r="B129" s="35"/>
+      <c r="C129" s="30"/>
+      <c r="D129" s="31"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="45"/>
+      <c r="H129" s="35"/>
+      <c r="I129" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="21"/>
-      <c r="B130" s="38"/>
-      <c r="C130" s="32"/>
-      <c r="D130" s="33"/>
-      <c r="E130" s="30"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="48"/>
-      <c r="H130" s="38"/>
-      <c r="I130" s="38"/>
+      <c r="B130" s="35"/>
+      <c r="C130" s="30"/>
+      <c r="D130" s="31"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="45"/>
+      <c r="H130" s="35"/>
+      <c r="I130" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
       <c r="A131" s="21"/>
-      <c r="B131" s="38"/>
-      <c r="C131" s="32"/>
-      <c r="D131" s="33"/>
-      <c r="E131" s="30"/>
-      <c r="F131" s="30"/>
-      <c r="G131" s="48"/>
-      <c r="H131" s="38"/>
-      <c r="I131" s="38"/>
+      <c r="B131" s="35"/>
+      <c r="C131" s="30"/>
+      <c r="D131" s="31"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="45"/>
+      <c r="H131" s="35"/>
+      <c r="I131" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
       <c r="A132" s="21"/>
-      <c r="B132" s="38"/>
-      <c r="C132" s="32"/>
-      <c r="D132" s="33"/>
-      <c r="E132" s="30"/>
-      <c r="F132" s="30"/>
-      <c r="G132" s="48"/>
-      <c r="H132" s="38"/>
-      <c r="I132" s="38"/>
+      <c r="B132" s="35"/>
+      <c r="C132" s="30"/>
+      <c r="D132" s="31"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="45"/>
+      <c r="H132" s="35"/>
+      <c r="I132" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
       <c r="A133" s="21"/>
-      <c r="B133" s="38"/>
-      <c r="C133" s="32"/>
-      <c r="D133" s="33"/>
-      <c r="E133" s="30"/>
-      <c r="F133" s="30"/>
-      <c r="G133" s="48"/>
-      <c r="H133" s="38"/>
-      <c r="I133" s="38"/>
+      <c r="B133" s="35"/>
+      <c r="C133" s="30"/>
+      <c r="D133" s="31"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="45"/>
+      <c r="H133" s="35"/>
+      <c r="I133" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="21"/>
-      <c r="B134" s="38"/>
-      <c r="C134" s="32"/>
-      <c r="D134" s="33"/>
-      <c r="E134" s="30"/>
-      <c r="F134" s="30"/>
-      <c r="G134" s="48"/>
-      <c r="H134" s="38"/>
-      <c r="I134" s="38"/>
+      <c r="B134" s="35"/>
+      <c r="C134" s="30"/>
+      <c r="D134" s="31"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="45"/>
+      <c r="H134" s="35"/>
+      <c r="I134" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
       <c r="A135" s="21"/>
-      <c r="B135" s="38"/>
-      <c r="C135" s="32"/>
-      <c r="D135" s="33"/>
-      <c r="E135" s="30"/>
-      <c r="F135" s="30"/>
-      <c r="G135" s="48"/>
-      <c r="H135" s="38"/>
-      <c r="I135" s="38"/>
+      <c r="B135" s="35"/>
+      <c r="C135" s="30"/>
+      <c r="D135" s="31"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="45"/>
+      <c r="H135" s="35"/>
+      <c r="I135" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
       <c r="A136" s="21"/>
-      <c r="B136" s="38"/>
-      <c r="C136" s="32"/>
-      <c r="D136" s="33"/>
-      <c r="E136" s="30"/>
-      <c r="F136" s="30"/>
-      <c r="G136" s="48"/>
-      <c r="H136" s="38"/>
-      <c r="I136" s="38"/>
+      <c r="B136" s="35"/>
+      <c r="C136" s="30"/>
+      <c r="D136" s="31"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="45"/>
+      <c r="H136" s="35"/>
+      <c r="I136" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
       <c r="A137" s="21"/>
-      <c r="B137" s="38"/>
-      <c r="C137" s="32"/>
-      <c r="D137" s="33"/>
-      <c r="E137" s="30"/>
-      <c r="F137" s="30"/>
-      <c r="G137" s="48"/>
-      <c r="H137" s="38"/>
-      <c r="I137" s="38"/>
+      <c r="B137" s="35"/>
+      <c r="C137" s="30"/>
+      <c r="D137" s="31"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="45"/>
+      <c r="H137" s="35"/>
+      <c r="I137" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
       <c r="A138" s="21"/>
-      <c r="B138" s="38"/>
-      <c r="C138" s="32"/>
-      <c r="D138" s="33"/>
-      <c r="E138" s="30"/>
-      <c r="F138" s="30"/>
-      <c r="G138" s="48"/>
-      <c r="H138" s="38"/>
-      <c r="I138" s="38"/>
+      <c r="B138" s="35"/>
+      <c r="C138" s="30"/>
+      <c r="D138" s="31"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="45"/>
+      <c r="H138" s="35"/>
+      <c r="I138" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
       <c r="A139" s="21"/>
-      <c r="B139" s="38"/>
-      <c r="C139" s="32"/>
-      <c r="D139" s="33"/>
-      <c r="E139" s="30"/>
-      <c r="F139" s="30"/>
-      <c r="G139" s="48"/>
-      <c r="H139" s="38"/>
-      <c r="I139" s="38"/>
+      <c r="B139" s="35"/>
+      <c r="C139" s="30"/>
+      <c r="D139" s="31"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="45"/>
+      <c r="H139" s="35"/>
+      <c r="I139" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
       <c r="A140" s="21"/>
-      <c r="B140" s="38"/>
-      <c r="C140" s="32"/>
-      <c r="D140" s="33"/>
-      <c r="E140" s="30"/>
-      <c r="F140" s="30"/>
-      <c r="G140" s="48"/>
-      <c r="H140" s="38"/>
-      <c r="I140" s="38"/>
+      <c r="B140" s="35"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="31"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="45"/>
+      <c r="H140" s="35"/>
+      <c r="I140" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
       <c r="A141" s="21"/>
-      <c r="B141" s="38"/>
-      <c r="C141" s="32"/>
-      <c r="D141" s="33"/>
-      <c r="E141" s="30"/>
-      <c r="F141" s="30"/>
-      <c r="G141" s="48"/>
-      <c r="H141" s="38"/>
-      <c r="I141" s="38"/>
+      <c r="B141" s="35"/>
+      <c r="C141" s="30"/>
+      <c r="D141" s="31"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="45"/>
+      <c r="H141" s="35"/>
+      <c r="I141" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
       <c r="A142" s="21"/>
-      <c r="B142" s="38"/>
-      <c r="C142" s="32"/>
-      <c r="D142" s="33"/>
-      <c r="E142" s="30"/>
-      <c r="F142" s="30"/>
-      <c r="G142" s="48"/>
-      <c r="H142" s="38"/>
-      <c r="I142" s="38"/>
+      <c r="B142" s="35"/>
+      <c r="C142" s="30"/>
+      <c r="D142" s="31"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="45"/>
+      <c r="H142" s="35"/>
+      <c r="I142" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
       <c r="A143" s="21"/>
-      <c r="B143" s="38"/>
-      <c r="C143" s="32"/>
-      <c r="D143" s="33"/>
-      <c r="E143" s="30"/>
-      <c r="F143" s="30"/>
-      <c r="G143" s="48"/>
-      <c r="H143" s="38"/>
-      <c r="I143" s="38"/>
+      <c r="B143" s="35"/>
+      <c r="C143" s="30"/>
+      <c r="D143" s="31"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="45"/>
+      <c r="H143" s="35"/>
+      <c r="I143" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
       <c r="A144" s="21"/>
-      <c r="B144" s="38"/>
-      <c r="C144" s="32"/>
-      <c r="D144" s="33"/>
-      <c r="E144" s="30"/>
-      <c r="F144" s="30"/>
-      <c r="G144" s="48"/>
-      <c r="H144" s="38"/>
-      <c r="I144" s="38"/>
+      <c r="B144" s="35"/>
+      <c r="C144" s="30"/>
+      <c r="D144" s="31"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="45"/>
+      <c r="H144" s="35"/>
+      <c r="I144" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
       <c r="A145" s="21"/>
-      <c r="B145" s="38"/>
-      <c r="C145" s="32"/>
-      <c r="D145" s="33"/>
-      <c r="E145" s="30"/>
-      <c r="F145" s="30"/>
-      <c r="G145" s="48"/>
-      <c r="H145" s="38"/>
-      <c r="I145" s="38"/>
+      <c r="B145" s="35"/>
+      <c r="C145" s="30"/>
+      <c r="D145" s="31"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="45"/>
+      <c r="H145" s="35"/>
+      <c r="I145" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
       <c r="A146" s="21"/>
-      <c r="B146" s="38"/>
-      <c r="C146" s="32"/>
-      <c r="D146" s="33"/>
-      <c r="E146" s="30"/>
-      <c r="F146" s="30"/>
-      <c r="G146" s="48"/>
-      <c r="H146" s="38"/>
-      <c r="I146" s="38"/>
+      <c r="B146" s="35"/>
+      <c r="C146" s="30"/>
+      <c r="D146" s="31"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="45"/>
+      <c r="H146" s="35"/>
+      <c r="I146" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
       <c r="A147" s="21"/>
-      <c r="B147" s="38"/>
-      <c r="C147" s="32"/>
-      <c r="D147" s="33"/>
-      <c r="E147" s="30"/>
-      <c r="F147" s="30"/>
-      <c r="G147" s="48"/>
-      <c r="H147" s="38"/>
-      <c r="I147" s="38"/>
+      <c r="B147" s="35"/>
+      <c r="C147" s="30"/>
+      <c r="D147" s="31"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="45"/>
+      <c r="H147" s="35"/>
+      <c r="I147" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
       <c r="A148" s="21"/>
-      <c r="B148" s="38"/>
-      <c r="C148" s="32"/>
-      <c r="D148" s="33"/>
-      <c r="E148" s="30"/>
-      <c r="F148" s="30"/>
-      <c r="G148" s="48"/>
-      <c r="H148" s="38"/>
-      <c r="I148" s="38"/>
+      <c r="B148" s="35"/>
+      <c r="C148" s="30"/>
+      <c r="D148" s="31"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="45"/>
+      <c r="H148" s="35"/>
+      <c r="I148" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
       <c r="A149" s="21"/>
-      <c r="B149" s="38"/>
-      <c r="C149" s="32"/>
-      <c r="D149" s="33"/>
-      <c r="E149" s="30"/>
-      <c r="F149" s="30"/>
-      <c r="G149" s="48"/>
-      <c r="H149" s="38"/>
-      <c r="I149" s="38"/>
+      <c r="B149" s="35"/>
+      <c r="C149" s="30"/>
+      <c r="D149" s="31"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="45"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
       <c r="A150" s="21"/>
-      <c r="B150" s="38"/>
-      <c r="C150" s="32"/>
-      <c r="D150" s="33"/>
-      <c r="E150" s="30"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="48"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38"/>
+      <c r="B150" s="35"/>
+      <c r="C150" s="30"/>
+      <c r="D150" s="31"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="45"/>
+      <c r="H150" s="35"/>
+      <c r="I150" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
       <c r="A151" s="21"/>
-      <c r="B151" s="38"/>
-      <c r="C151" s="32"/>
-      <c r="D151" s="33"/>
-      <c r="E151" s="30"/>
-      <c r="F151" s="30"/>
-      <c r="G151" s="48"/>
-      <c r="H151" s="38"/>
-      <c r="I151" s="38"/>
+      <c r="B151" s="35"/>
+      <c r="C151" s="30"/>
+      <c r="D151" s="31"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="45"/>
+      <c r="H151" s="35"/>
+      <c r="I151" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
       <c r="A152" s="21"/>
-      <c r="B152" s="38"/>
-      <c r="C152" s="32"/>
-      <c r="D152" s="33"/>
-      <c r="E152" s="30"/>
-      <c r="F152" s="30"/>
-      <c r="G152" s="48"/>
-      <c r="H152" s="38"/>
-      <c r="I152" s="38"/>
+      <c r="B152" s="35"/>
+      <c r="C152" s="30"/>
+      <c r="D152" s="31"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="45"/>
+      <c r="H152" s="35"/>
+      <c r="I152" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
       <c r="A153" s="21"/>
-      <c r="B153" s="38"/>
-      <c r="C153" s="32"/>
-      <c r="D153" s="33"/>
-      <c r="E153" s="30"/>
-      <c r="F153" s="30"/>
-      <c r="G153" s="48"/>
-      <c r="H153" s="38"/>
-      <c r="I153" s="38"/>
+      <c r="B153" s="35"/>
+      <c r="C153" s="30"/>
+      <c r="D153" s="31"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="45"/>
+      <c r="H153" s="35"/>
+      <c r="I153" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="21"/>
-      <c r="B154" s="38"/>
-      <c r="C154" s="32"/>
-      <c r="D154" s="33"/>
-      <c r="E154" s="30"/>
-      <c r="F154" s="30"/>
-      <c r="G154" s="48"/>
-      <c r="H154" s="38"/>
-      <c r="I154" s="38"/>
+      <c r="B154" s="35"/>
+      <c r="C154" s="30"/>
+      <c r="D154" s="31"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="45"/>
+      <c r="H154" s="35"/>
+      <c r="I154" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="21"/>
-      <c r="B155" s="38"/>
-      <c r="C155" s="32"/>
-      <c r="D155" s="33"/>
-      <c r="E155" s="30"/>
-      <c r="F155" s="30"/>
-      <c r="G155" s="48"/>
-      <c r="H155" s="38"/>
-      <c r="I155" s="38"/>
+      <c r="B155" s="35"/>
+      <c r="C155" s="30"/>
+      <c r="D155" s="31"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="45"/>
+      <c r="H155" s="35"/>
+      <c r="I155" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="21"/>
-      <c r="B156" s="38"/>
-      <c r="C156" s="32"/>
-      <c r="D156" s="33"/>
-      <c r="E156" s="30"/>
-      <c r="F156" s="30"/>
-      <c r="G156" s="48"/>
-      <c r="H156" s="38"/>
-      <c r="I156" s="38"/>
+      <c r="B156" s="35"/>
+      <c r="C156" s="30"/>
+      <c r="D156" s="31"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="45"/>
+      <c r="H156" s="35"/>
+      <c r="I156" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="21"/>
-      <c r="B157" s="38"/>
-      <c r="C157" s="32"/>
-      <c r="D157" s="33"/>
-      <c r="E157" s="30"/>
-      <c r="F157" s="30"/>
-      <c r="G157" s="48"/>
-      <c r="H157" s="38"/>
-      <c r="I157" s="38"/>
+      <c r="B157" s="35"/>
+      <c r="C157" s="30"/>
+      <c r="D157" s="31"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="45"/>
+      <c r="H157" s="35"/>
+      <c r="I157" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="21"/>
-      <c r="B158" s="38"/>
-      <c r="C158" s="32"/>
-      <c r="D158" s="33"/>
-      <c r="E158" s="30"/>
-      <c r="F158" s="30"/>
-      <c r="G158" s="48"/>
-      <c r="H158" s="38"/>
-      <c r="I158" s="38"/>
+      <c r="B158" s="35"/>
+      <c r="C158" s="30"/>
+      <c r="D158" s="31"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="45"/>
+      <c r="H158" s="35"/>
+      <c r="I158" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="21"/>
-      <c r="B159" s="38"/>
-      <c r="C159" s="32"/>
-      <c r="D159" s="33"/>
-      <c r="E159" s="30"/>
-      <c r="F159" s="30"/>
-      <c r="G159" s="48"/>
-      <c r="H159" s="38"/>
-      <c r="I159" s="38"/>
+      <c r="B159" s="35"/>
+      <c r="C159" s="30"/>
+      <c r="D159" s="31"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="45"/>
+      <c r="H159" s="35"/>
+      <c r="I159" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="21"/>
-      <c r="B160" s="38"/>
-      <c r="C160" s="32"/>
-      <c r="D160" s="33"/>
-      <c r="E160" s="30"/>
-      <c r="F160" s="30"/>
-      <c r="G160" s="48"/>
-      <c r="H160" s="38"/>
-      <c r="I160" s="38"/>
+      <c r="B160" s="35"/>
+      <c r="C160" s="30"/>
+      <c r="D160" s="31"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="45"/>
+      <c r="H160" s="35"/>
+      <c r="I160" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="21"/>
-      <c r="B161" s="38"/>
-      <c r="C161" s="32"/>
-      <c r="D161" s="33"/>
-      <c r="E161" s="30"/>
-      <c r="F161" s="30"/>
-      <c r="G161" s="48"/>
-      <c r="H161" s="38"/>
-      <c r="I161" s="38"/>
+      <c r="B161" s="35"/>
+      <c r="C161" s="30"/>
+      <c r="D161" s="31"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="45"/>
+      <c r="H161" s="35"/>
+      <c r="I161" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="21"/>
-      <c r="B162" s="38"/>
-      <c r="C162" s="32"/>
-      <c r="D162" s="33"/>
-      <c r="E162" s="30"/>
-      <c r="F162" s="30"/>
-      <c r="G162" s="48"/>
-      <c r="H162" s="38"/>
-      <c r="I162" s="38"/>
+      <c r="B162" s="35"/>
+      <c r="C162" s="30"/>
+      <c r="D162" s="31"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="45"/>
+      <c r="H162" s="35"/>
+      <c r="I162" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="21"/>
-      <c r="B163" s="38"/>
-      <c r="C163" s="32"/>
-      <c r="D163" s="33"/>
-      <c r="E163" s="30"/>
-      <c r="F163" s="30"/>
-      <c r="G163" s="48"/>
-      <c r="H163" s="38"/>
-      <c r="I163" s="38"/>
+      <c r="B163" s="35"/>
+      <c r="C163" s="30"/>
+      <c r="D163" s="31"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="45"/>
+      <c r="H163" s="35"/>
+      <c r="I163" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="21"/>
-      <c r="B164" s="38"/>
-      <c r="C164" s="32"/>
-      <c r="D164" s="33"/>
-      <c r="E164" s="30"/>
-      <c r="F164" s="30"/>
-      <c r="G164" s="48"/>
-      <c r="H164" s="38"/>
-      <c r="I164" s="38"/>
+      <c r="B164" s="35"/>
+      <c r="C164" s="30"/>
+      <c r="D164" s="31"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="45"/>
+      <c r="H164" s="35"/>
+      <c r="I164" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="21"/>
-      <c r="B165" s="38"/>
-      <c r="C165" s="32"/>
-      <c r="D165" s="33"/>
-      <c r="E165" s="30"/>
-      <c r="F165" s="30"/>
-      <c r="G165" s="48"/>
-      <c r="H165" s="38"/>
-      <c r="I165" s="38"/>
+      <c r="B165" s="35"/>
+      <c r="C165" s="30"/>
+      <c r="D165" s="31"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="45"/>
+      <c r="H165" s="35"/>
+      <c r="I165" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="21"/>
-      <c r="B166" s="38"/>
-      <c r="C166" s="32"/>
-      <c r="D166" s="33"/>
-      <c r="E166" s="30"/>
-      <c r="F166" s="30"/>
-      <c r="G166" s="48"/>
-      <c r="H166" s="38"/>
-      <c r="I166" s="38"/>
+      <c r="B166" s="35"/>
+      <c r="C166" s="30"/>
+      <c r="D166" s="31"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="45"/>
+      <c r="H166" s="35"/>
+      <c r="I166" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="21"/>
-      <c r="B167" s="38"/>
-      <c r="C167" s="32"/>
-      <c r="D167" s="33"/>
-      <c r="E167" s="30"/>
-      <c r="F167" s="30"/>
-      <c r="G167" s="48"/>
-      <c r="H167" s="38"/>
-      <c r="I167" s="38"/>
+      <c r="B167" s="35"/>
+      <c r="C167" s="30"/>
+      <c r="D167" s="31"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="45"/>
+      <c r="H167" s="35"/>
+      <c r="I167" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="21"/>
-      <c r="B168" s="38"/>
-      <c r="C168" s="32"/>
-      <c r="D168" s="33"/>
-      <c r="E168" s="30"/>
-      <c r="F168" s="30"/>
-      <c r="G168" s="48"/>
-      <c r="H168" s="38"/>
-      <c r="I168" s="38"/>
+      <c r="B168" s="35"/>
+      <c r="C168" s="30"/>
+      <c r="D168" s="31"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="45"/>
+      <c r="H168" s="35"/>
+      <c r="I168" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
       <c r="A169" s="21"/>
-      <c r="B169" s="38"/>
-      <c r="C169" s="32"/>
-      <c r="D169" s="33"/>
-      <c r="E169" s="30"/>
-      <c r="F169" s="30"/>
-      <c r="G169" s="48"/>
-      <c r="H169" s="38"/>
-      <c r="I169" s="38"/>
+      <c r="B169" s="35"/>
+      <c r="C169" s="30"/>
+      <c r="D169" s="31"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="45"/>
+      <c r="H169" s="35"/>
+      <c r="I169" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
       <c r="A170" s="21"/>
-      <c r="B170" s="38"/>
-      <c r="C170" s="32"/>
-      <c r="D170" s="33"/>
-      <c r="E170" s="30"/>
-      <c r="F170" s="30"/>
-      <c r="G170" s="48"/>
-      <c r="H170" s="38"/>
-      <c r="I170" s="38"/>
+      <c r="B170" s="35"/>
+      <c r="C170" s="30"/>
+      <c r="D170" s="31"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="45"/>
+      <c r="H170" s="35"/>
+      <c r="I170" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
       <c r="A171" s="21"/>
-      <c r="B171" s="38"/>
-      <c r="C171" s="32"/>
-      <c r="D171" s="33"/>
-      <c r="E171" s="30"/>
-      <c r="F171" s="30"/>
-      <c r="G171" s="48"/>
-      <c r="H171" s="38"/>
-      <c r="I171" s="38"/>
+      <c r="B171" s="35"/>
+      <c r="C171" s="30"/>
+      <c r="D171" s="31"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="45"/>
+      <c r="H171" s="35"/>
+      <c r="I171" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
       <c r="A172" s="21"/>
-      <c r="B172" s="38"/>
-      <c r="C172" s="32"/>
-      <c r="D172" s="33"/>
-      <c r="E172" s="30"/>
-      <c r="F172" s="30"/>
-      <c r="G172" s="48"/>
-      <c r="H172" s="38"/>
-      <c r="I172" s="38"/>
+      <c r="B172" s="35"/>
+      <c r="C172" s="30"/>
+      <c r="D172" s="31"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="45"/>
+      <c r="H172" s="35"/>
+      <c r="I172" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
       <c r="A173" s="21"/>
-      <c r="B173" s="38"/>
-      <c r="C173" s="32"/>
-      <c r="D173" s="33"/>
-      <c r="E173" s="30"/>
-      <c r="F173" s="30"/>
-      <c r="G173" s="48"/>
-      <c r="H173" s="38"/>
-      <c r="I173" s="38"/>
+      <c r="B173" s="35"/>
+      <c r="C173" s="30"/>
+      <c r="D173" s="31"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="45"/>
+      <c r="H173" s="35"/>
+      <c r="I173" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
       <c r="A174" s="21"/>
-      <c r="B174" s="38"/>
-      <c r="C174" s="32"/>
-      <c r="D174" s="33"/>
-      <c r="E174" s="30"/>
-      <c r="F174" s="30"/>
-      <c r="G174" s="48"/>
-      <c r="H174" s="38"/>
-      <c r="I174" s="38"/>
+      <c r="B174" s="35"/>
+      <c r="C174" s="30"/>
+      <c r="D174" s="31"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="45"/>
+      <c r="H174" s="35"/>
+      <c r="I174" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
       <c r="A175" s="21"/>
-      <c r="B175" s="38"/>
-      <c r="C175" s="32"/>
-      <c r="D175" s="33"/>
-      <c r="E175" s="30"/>
-      <c r="F175" s="30"/>
-      <c r="G175" s="48"/>
-      <c r="H175" s="38"/>
-      <c r="I175" s="38"/>
+      <c r="B175" s="35"/>
+      <c r="C175" s="30"/>
+      <c r="D175" s="31"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="45"/>
+      <c r="H175" s="35"/>
+      <c r="I175" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
       <c r="A176" s="21"/>
       <c r="B176" s="2"/>
-      <c r="C176" s="49"/>
-      <c r="D176" s="33"/>
-      <c r="E176" s="30"/>
-      <c r="F176" s="30"/>
-      <c r="G176" s="38"/>
-      <c r="H176" s="38"/>
-      <c r="I176" s="38"/>
+      <c r="C176" s="46"/>
+      <c r="D176" s="31"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="35"/>
+      <c r="H176" s="35"/>
+      <c r="I176" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A177" s="44"/>
+      <c r="A177" s="41"/>
       <c r="B177" s="2"/>
-      <c r="C177" s="45"/>
-      <c r="D177" s="46"/>
-      <c r="E177" s="27"/>
-      <c r="F177" s="27"/>
+      <c r="C177" s="42"/>
+      <c r="D177" s="43"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A178" s="44"/>
+      <c r="A178" s="41"/>
       <c r="B178" s="2"/>
-      <c r="C178" s="45"/>
-      <c r="D178" s="46"/>
-      <c r="E178" s="27"/>
-      <c r="F178" s="27"/>
+      <c r="C178" s="42"/>
+      <c r="D178" s="43"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A179" s="44"/>
+      <c r="A179" s="41"/>
       <c r="B179" s="2"/>
-      <c r="C179" s="45"/>
-      <c r="D179" s="46"/>
-      <c r="E179" s="27"/>
-      <c r="F179" s="27"/>
+      <c r="C179" s="42"/>
+      <c r="D179" s="43"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A180" s="44"/>
+      <c r="A180" s="41"/>
       <c r="B180" s="2"/>
-      <c r="C180" s="45"/>
-      <c r="D180" s="46"/>
-      <c r="E180" s="27"/>
-      <c r="F180" s="27"/>
+      <c r="C180" s="42"/>
+      <c r="D180" s="43"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A181" s="44"/>
+      <c r="A181" s="41"/>
       <c r="B181" s="2"/>
-      <c r="C181" s="45"/>
-      <c r="D181" s="46"/>
-      <c r="E181" s="27"/>
-      <c r="F181" s="27"/>
+      <c r="C181" s="42"/>
+      <c r="D181" s="43"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A182" s="44"/>
+      <c r="A182" s="41"/>
       <c r="B182" s="2"/>
-      <c r="C182" s="45"/>
-      <c r="D182" s="46"/>
-      <c r="E182" s="27"/>
-      <c r="F182" s="27"/>
+      <c r="C182" s="42"/>
+      <c r="D182" s="43"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A183" s="44"/>
+      <c r="A183" s="41"/>
       <c r="B183" s="2"/>
-      <c r="C183" s="45"/>
-      <c r="D183" s="46"/>
-      <c r="E183" s="27"/>
-      <c r="F183" s="27"/>
+      <c r="C183" s="42"/>
+      <c r="D183" s="43"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A184" s="44"/>
+      <c r="A184" s="41"/>
       <c r="B184" s="2"/>
-      <c r="C184" s="45"/>
-      <c r="D184" s="46"/>
-      <c r="E184" s="27"/>
-      <c r="F184" s="27"/>
+      <c r="C184" s="42"/>
+      <c r="D184" s="43"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A185" s="44"/>
+      <c r="A185" s="41"/>
       <c r="B185" s="2"/>
-      <c r="C185" s="45"/>
-      <c r="D185" s="46"/>
-      <c r="E185" s="27"/>
-      <c r="F185" s="27"/>
+      <c r="C185" s="42"/>
+      <c r="D185" s="43"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A186" s="44"/>
+      <c r="A186" s="41"/>
       <c r="B186" s="2"/>
-      <c r="C186" s="45"/>
-      <c r="D186" s="46"/>
-      <c r="E186" s="27"/>
-      <c r="F186" s="27"/>
+      <c r="C186" s="42"/>
+      <c r="D186" s="43"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A187" s="44"/>
+      <c r="A187" s="41"/>
       <c r="B187" s="2"/>
-      <c r="C187" s="45"/>
-      <c r="D187" s="46"/>
-      <c r="E187" s="27"/>
-      <c r="F187" s="27"/>
+      <c r="C187" s="42"/>
+      <c r="D187" s="43"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A188" s="44"/>
+      <c r="A188" s="41"/>
       <c r="B188" s="2"/>
-      <c r="C188" s="45"/>
-      <c r="D188" s="46"/>
-      <c r="E188" s="27"/>
-      <c r="F188" s="27"/>
+      <c r="C188" s="42"/>
+      <c r="D188" s="43"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A189" s="44"/>
+      <c r="A189" s="41"/>
       <c r="B189" s="2"/>
-      <c r="C189" s="45"/>
-      <c r="D189" s="46"/>
-      <c r="E189" s="27"/>
-      <c r="F189" s="27"/>
+      <c r="C189" s="42"/>
+      <c r="D189" s="43"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A190" s="44"/>
+      <c r="A190" s="41"/>
       <c r="B190" s="2"/>
-      <c r="C190" s="45"/>
-      <c r="D190" s="46"/>
-      <c r="E190" s="27"/>
-      <c r="F190" s="27"/>
+      <c r="C190" s="42"/>
+      <c r="D190" s="43"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A191" s="44"/>
+      <c r="A191" s="41"/>
       <c r="B191" s="2"/>
-      <c r="C191" s="45"/>
-      <c r="D191" s="46"/>
-      <c r="E191" s="27"/>
-      <c r="F191" s="27"/>
+      <c r="C191" s="42"/>
+      <c r="D191" s="43"/>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A192" s="44"/>
+      <c r="A192" s="41"/>
       <c r="B192" s="2"/>
-      <c r="C192" s="45"/>
-      <c r="D192" s="46"/>
-      <c r="E192" s="27"/>
-      <c r="F192" s="27"/>
+      <c r="C192" s="42"/>
+      <c r="D192" s="43"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A193" s="44"/>
+      <c r="A193" s="41"/>
       <c r="B193" s="2"/>
-      <c r="C193" s="45"/>
-      <c r="D193" s="46"/>
-      <c r="E193" s="27"/>
-      <c r="F193" s="27"/>
+      <c r="C193" s="42"/>
+      <c r="D193" s="43"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A194" s="44"/>
+      <c r="A194" s="41"/>
       <c r="B194" s="2"/>
-      <c r="C194" s="45"/>
-      <c r="D194" s="46"/>
-      <c r="E194" s="27"/>
-      <c r="F194" s="27"/>
+      <c r="C194" s="42"/>
+      <c r="D194" s="43"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A195" s="44"/>
+      <c r="A195" s="41"/>
       <c r="B195" s="2"/>
-      <c r="C195" s="45"/>
-      <c r="D195" s="46"/>
-      <c r="E195" s="27"/>
-      <c r="F195" s="27"/>
+      <c r="C195" s="42"/>
+      <c r="D195" s="43"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A196" s="44"/>
+      <c r="A196" s="41"/>
       <c r="B196" s="2"/>
-      <c r="C196" s="45"/>
-      <c r="D196" s="46"/>
-      <c r="E196" s="27"/>
-      <c r="F196" s="27"/>
+      <c r="C196" s="42"/>
+      <c r="D196" s="43"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A197" s="44"/>
+      <c r="A197" s="41"/>
       <c r="B197" s="2"/>
-      <c r="C197" s="45"/>
-      <c r="D197" s="46"/>
-      <c r="E197" s="27"/>
-      <c r="F197" s="27"/>
+      <c r="C197" s="42"/>
+      <c r="D197" s="43"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A198" s="44"/>
+      <c r="A198" s="41"/>
       <c r="B198" s="2"/>
-      <c r="C198" s="45"/>
-      <c r="D198" s="46"/>
-      <c r="E198" s="27"/>
-      <c r="F198" s="27"/>
+      <c r="C198" s="42"/>
+      <c r="D198" s="43"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A199" s="44"/>
+      <c r="A199" s="41"/>
       <c r="B199" s="2"/>
-      <c r="C199" s="45"/>
-      <c r="D199" s="46"/>
-      <c r="E199" s="27"/>
-      <c r="F199" s="27"/>
+      <c r="C199" s="42"/>
+      <c r="D199" s="43"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A200" s="44"/>
+      <c r="A200" s="41"/>
       <c r="B200" s="2"/>
-      <c r="C200" s="45"/>
-      <c r="D200" s="46"/>
-      <c r="E200" s="27"/>
-      <c r="F200" s="27"/>
+      <c r="C200" s="42"/>
+      <c r="D200" s="43"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A201" s="44"/>
+      <c r="A201" s="41"/>
       <c r="B201" s="2"/>
-      <c r="C201" s="45"/>
-      <c r="D201" s="46"/>
-      <c r="E201" s="27"/>
-      <c r="F201" s="27"/>
+      <c r="C201" s="42"/>
+      <c r="D201" s="43"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A202" s="44"/>
+      <c r="A202" s="41"/>
       <c r="B202" s="2"/>
-      <c r="C202" s="45"/>
-      <c r="D202" s="46"/>
-      <c r="E202" s="27"/>
-      <c r="F202" s="27"/>
+      <c r="C202" s="42"/>
+      <c r="D202" s="43"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A203" s="44"/>
+      <c r="A203" s="41"/>
       <c r="B203" s="2"/>
-      <c r="C203" s="45"/>
-      <c r="D203" s="46"/>
-      <c r="E203" s="27"/>
-      <c r="F203" s="27"/>
+      <c r="C203" s="42"/>
+      <c r="D203" s="43"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
@@ -5612,9 +5728,9 @@
   <cols>
     <col min="1" max="1" style="23" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="43.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="35" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="36" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="37" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="33" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="34" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="24" width="10.862142857142858" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="24" width="16.433571428571426" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -5627,7 +5743,7 @@
       <c r="B1" s="12"/>
       <c r="C1" s="25"/>
       <c r="D1" s="26"/>
-      <c r="E1" s="27"/>
+      <c r="E1" s="2"/>
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
       <c r="H1" s="2"/>
@@ -5639,13 +5755,13 @@
       <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="14" t="s">
@@ -5663,13 +5779,13 @@
       <c r="B3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="29">
         <v>15.45</v>
       </c>
       <c r="D3" s="18">
         <v>45383</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="19"/>
@@ -5683,13 +5799,13 @@
       <c r="B4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="29">
         <v>1.08</v>
       </c>
       <c r="D4" s="18">
         <v>45383</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="19"/>
@@ -5703,13 +5819,13 @@
       <c r="B5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="29">
         <v>13.03</v>
       </c>
       <c r="D5" s="18">
         <v>45383</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="17"/>
@@ -5723,13 +5839,13 @@
       <c r="B6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="29">
         <v>19.1</v>
       </c>
       <c r="D6" s="18">
         <v>45383</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="17"/>
@@ -5743,13 +5859,13 @@
       <c r="B7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="29">
         <v>0.16</v>
       </c>
       <c r="D7" s="18">
         <v>45383</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="17"/>
@@ -5763,13 +5879,13 @@
       <c r="B8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="29">
         <v>14.01</v>
       </c>
       <c r="D8" s="18">
         <v>45383</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="17"/>
@@ -5783,13 +5899,13 @@
       <c r="B9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="29">
         <v>8.52</v>
       </c>
       <c r="D9" s="18">
         <v>45384</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="17"/>
@@ -5803,13 +5919,13 @@
       <c r="B10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="29">
         <v>0.18</v>
       </c>
       <c r="D10" s="18">
         <v>45384</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="17"/>
@@ -5823,13 +5939,13 @@
       <c r="B11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="29">
         <v>8.35</v>
       </c>
       <c r="D11" s="18">
         <v>45384</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="17"/>
@@ -5843,13 +5959,13 @@
       <c r="B12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="29">
         <v>7.35</v>
       </c>
       <c r="D12" s="18">
         <v>45384</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="17"/>
@@ -5863,13 +5979,13 @@
       <c r="B13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="29">
         <v>11.4</v>
       </c>
       <c r="D13" s="18">
         <v>45384</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="17"/>
@@ -5883,13 +5999,13 @@
       <c r="B14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="29">
         <v>11.09</v>
       </c>
       <c r="D14" s="18">
         <v>45384</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="17"/>
@@ -5903,13 +6019,13 @@
       <c r="B15" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="29">
         <v>15.16</v>
       </c>
       <c r="D15" s="18">
         <v>45384</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="17"/>
@@ -5923,13 +6039,13 @@
       <c r="B16" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="29">
         <v>9.31</v>
       </c>
       <c r="D16" s="18">
         <v>45385</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="17"/>
@@ -5943,13 +6059,13 @@
       <c r="B17" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="29">
         <v>9.16</v>
       </c>
       <c r="D17" s="18">
         <v>45385</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F17" s="17"/>
@@ -5963,13 +6079,13 @@
       <c r="B18" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="29">
         <v>14.09</v>
       </c>
       <c r="D18" s="18">
         <v>45385</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F18" s="17"/>
@@ -5983,13 +6099,13 @@
       <c r="B19" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="29">
         <v>14.54</v>
       </c>
       <c r="D19" s="18">
         <v>45385</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="17"/>
@@ -6003,13 +6119,13 @@
       <c r="B20" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="29">
         <v>8.57</v>
       </c>
       <c r="D20" s="18">
         <v>45385</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F20" s="17"/>
@@ -6023,13 +6139,13 @@
       <c r="B21" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="29">
         <v>16.55</v>
       </c>
       <c r="D21" s="18">
         <v>45386</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F21" s="17"/>
@@ -6049,7 +6165,7 @@
       <c r="D22" s="18">
         <v>45386</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="17"/>
@@ -6063,13 +6179,13 @@
       <c r="B23" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="29">
         <v>4.25</v>
       </c>
       <c r="D23" s="18">
         <v>45386</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F23" s="17"/>
@@ -6083,13 +6199,13 @@
       <c r="B24" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="29">
         <v>10.16</v>
       </c>
       <c r="D24" s="18">
         <v>45386</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F24" s="17"/>
@@ -6103,13 +6219,13 @@
       <c r="B25" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="29">
         <v>24.08</v>
       </c>
       <c r="D25" s="18">
         <v>45386</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="E25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F25" s="17"/>
@@ -6123,13 +6239,13 @@
       <c r="B26" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="29">
         <v>0.29</v>
       </c>
       <c r="D26" s="18">
         <v>45387</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F26" s="17"/>
@@ -6143,13 +6259,13 @@
       <c r="B27" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="29">
         <v>24.46</v>
       </c>
       <c r="D27" s="18">
         <v>45387</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F27" s="17"/>
@@ -6163,13 +6279,13 @@
       <c r="B28" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="29">
         <v>0.19</v>
       </c>
       <c r="D28" s="18">
         <v>45387</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F28" s="17"/>
@@ -6183,13 +6299,13 @@
       <c r="B29" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="29">
         <v>15.03</v>
       </c>
       <c r="D29" s="18">
         <v>45387</v>
       </c>
-      <c r="E29" s="30" t="s">
+      <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F29" s="17"/>
@@ -6203,13 +6319,13 @@
       <c r="B30" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="29">
         <v>5.51</v>
       </c>
       <c r="D30" s="18">
         <v>45387</v>
       </c>
-      <c r="E30" s="30" t="s">
+      <c r="E30" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F30" s="17"/>
@@ -6223,13 +6339,13 @@
       <c r="B31" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="29">
         <v>8.45</v>
       </c>
       <c r="D31" s="18">
         <v>45387</v>
       </c>
-      <c r="E31" s="30" t="s">
+      <c r="E31" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F31" s="17"/>
@@ -6243,13 +6359,13 @@
       <c r="B32" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="29">
         <v>0.18</v>
       </c>
       <c r="D32" s="18">
         <v>45387</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E32" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F32" s="17"/>
@@ -6263,13 +6379,13 @@
       <c r="B33" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="29">
         <v>8.36</v>
       </c>
       <c r="D33" s="18">
         <v>45387</v>
       </c>
-      <c r="E33" s="30" t="s">
+      <c r="E33" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F33" s="17"/>
@@ -6283,13 +6399,13 @@
       <c r="B34" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="29">
         <v>16.52</v>
       </c>
       <c r="D34" s="18">
         <v>45388</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F34" s="17"/>
@@ -6303,13 +6419,13 @@
       <c r="B35" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="29">
         <v>13.16</v>
       </c>
       <c r="D35" s="18">
         <v>45388</v>
       </c>
-      <c r="E35" s="30" t="s">
+      <c r="E35" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F35" s="17"/>
@@ -6323,13 +6439,13 @@
       <c r="B36" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="29">
         <v>17.01</v>
       </c>
       <c r="D36" s="18">
         <v>45388</v>
       </c>
-      <c r="E36" s="30" t="s">
+      <c r="E36" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F36" s="17"/>
@@ -6343,13 +6459,13 @@
       <c r="B37" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="29">
         <v>15.07</v>
       </c>
       <c r="D37" s="18">
         <v>45388</v>
       </c>
-      <c r="E37" s="30" t="s">
+      <c r="E37" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F37" s="17"/>
@@ -6363,13 +6479,13 @@
       <c r="B38" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="29">
         <v>10.21</v>
       </c>
       <c r="D38" s="18">
         <v>45389</v>
       </c>
-      <c r="E38" s="30" t="s">
+      <c r="E38" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F38" s="17"/>
@@ -6383,13 +6499,13 @@
       <c r="B39" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="29">
         <v>0.34</v>
       </c>
       <c r="D39" s="18">
         <v>45389</v>
       </c>
-      <c r="E39" s="30" t="s">
+      <c r="E39" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F39" s="17"/>
@@ -6403,13 +6519,13 @@
       <c r="B40" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="29">
         <v>14.22</v>
       </c>
       <c r="D40" s="18">
         <v>45389</v>
       </c>
-      <c r="E40" s="30" t="s">
+      <c r="E40" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F40" s="17"/>
@@ -6423,13 +6539,13 @@
       <c r="B41" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="29">
         <v>10.5</v>
       </c>
       <c r="D41" s="18">
         <v>45389</v>
       </c>
-      <c r="E41" s="30" t="s">
+      <c r="E41" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F41" s="17"/>
@@ -6443,13 +6559,13 @@
       <c r="B42" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="29">
         <v>7.57</v>
       </c>
       <c r="D42" s="18">
         <v>45389</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F42" s="17"/>
@@ -6463,13 +6579,13 @@
       <c r="B43" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="29">
         <v>5.11</v>
       </c>
       <c r="D43" s="18">
         <v>45389</v>
       </c>
-      <c r="E43" s="30" t="s">
+      <c r="E43" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F43" s="17"/>
@@ -6483,13 +6599,13 @@
       <c r="B44" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="29">
         <v>10.07</v>
       </c>
       <c r="D44" s="18">
         <v>45389</v>
       </c>
-      <c r="E44" s="30" t="s">
+      <c r="E44" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F44" s="17"/>
@@ -6503,13 +6619,13 @@
       <c r="B45" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="29">
         <v>7.39</v>
       </c>
       <c r="D45" s="18">
         <v>45390</v>
       </c>
-      <c r="E45" s="30" t="s">
+      <c r="E45" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F45" s="17"/>
@@ -6523,13 +6639,13 @@
       <c r="B46" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="29">
         <v>9.22</v>
       </c>
       <c r="D46" s="18">
         <v>45390</v>
       </c>
-      <c r="E46" s="30" t="s">
+      <c r="E46" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F46" s="17"/>
@@ -6543,13 +6659,13 @@
       <c r="B47" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="29">
         <v>9.29</v>
       </c>
       <c r="D47" s="18">
         <v>45390</v>
       </c>
-      <c r="E47" s="30" t="s">
+      <c r="E47" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F47" s="17"/>
@@ -6563,13 +6679,13 @@
       <c r="B48" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="29">
         <v>7.16</v>
       </c>
       <c r="D48" s="18">
         <v>45390</v>
       </c>
-      <c r="E48" s="30" t="s">
+      <c r="E48" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F48" s="17"/>
@@ -6583,13 +6699,13 @@
       <c r="B49" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="29">
         <v>6.1</v>
       </c>
       <c r="D49" s="18">
         <v>45390</v>
       </c>
-      <c r="E49" s="30" t="s">
+      <c r="E49" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F49" s="17"/>
@@ -6603,13 +6719,13 @@
       <c r="B50" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="29">
         <v>6.36</v>
       </c>
       <c r="D50" s="18">
         <v>45390</v>
       </c>
-      <c r="E50" s="30" t="s">
+      <c r="E50" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F50" s="17"/>
@@ -6623,13 +6739,13 @@
       <c r="B51" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="29">
         <v>7.32</v>
       </c>
       <c r="D51" s="18">
         <v>45390</v>
       </c>
-      <c r="E51" s="30" t="s">
+      <c r="E51" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F51" s="17"/>
@@ -6643,13 +6759,13 @@
       <c r="B52" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="29">
         <v>6.15</v>
       </c>
       <c r="D52" s="18">
         <v>45390</v>
       </c>
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F52" s="17"/>
@@ -6663,13 +6779,13 @@
       <c r="B53" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="29">
         <v>6.07</v>
       </c>
       <c r="D53" s="18">
         <v>45391</v>
       </c>
-      <c r="E53" s="30" t="s">
+      <c r="E53" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F53" s="17"/>
@@ -6683,13 +6799,13 @@
       <c r="B54" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="29">
         <v>5.04</v>
       </c>
       <c r="D54" s="18">
         <v>45391</v>
       </c>
-      <c r="E54" s="30" t="s">
+      <c r="E54" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F54" s="17"/>
@@ -6703,13 +6819,13 @@
       <c r="B55" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="29">
         <v>9.41</v>
       </c>
       <c r="D55" s="18">
         <v>45391</v>
       </c>
-      <c r="E55" s="30" t="s">
+      <c r="E55" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F55" s="17"/>
@@ -6723,13 +6839,13 @@
       <c r="B56" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="29">
         <v>6.12</v>
       </c>
       <c r="D56" s="18">
         <v>45391</v>
       </c>
-      <c r="E56" s="30" t="s">
+      <c r="E56" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F56" s="17"/>
@@ -6743,13 +6859,13 @@
       <c r="B57" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="29">
         <v>4.11</v>
       </c>
       <c r="D57" s="18">
         <v>45391</v>
       </c>
-      <c r="E57" s="30" t="s">
+      <c r="E57" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F57" s="17"/>
@@ -6763,13 +6879,13 @@
       <c r="B58" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="29">
         <v>9.3</v>
       </c>
       <c r="D58" s="18">
         <v>45391</v>
       </c>
-      <c r="E58" s="30" t="s">
+      <c r="E58" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F58" s="17"/>
@@ -6783,13 +6899,13 @@
       <c r="B59" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="29">
         <v>8.06</v>
       </c>
       <c r="D59" s="18">
         <v>45391</v>
       </c>
-      <c r="E59" s="30" t="s">
+      <c r="E59" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F59" s="17"/>
@@ -6803,13 +6919,13 @@
       <c r="B60" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="29">
         <v>10.35</v>
       </c>
       <c r="D60" s="18">
         <v>45391</v>
       </c>
-      <c r="E60" s="30" t="s">
+      <c r="E60" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F60" s="17"/>
@@ -6823,13 +6939,13 @@
       <c r="B61" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="29">
         <v>9.22</v>
       </c>
       <c r="D61" s="18">
         <v>45392</v>
       </c>
-      <c r="E61" s="30" t="s">
+      <c r="E61" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F61" s="17"/>
@@ -6843,13 +6959,13 @@
       <c r="B62" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="29">
         <v>8.05</v>
       </c>
       <c r="D62" s="18">
         <v>45392</v>
       </c>
-      <c r="E62" s="30" t="s">
+      <c r="E62" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F62" s="17"/>
@@ -6863,13 +6979,13 @@
       <c r="B63" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="29">
         <v>14.14</v>
       </c>
       <c r="D63" s="18">
         <v>45392</v>
       </c>
-      <c r="E63" s="30" t="s">
+      <c r="E63" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F63" s="17"/>
@@ -6883,13 +6999,13 @@
       <c r="B64" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="29">
         <v>14.38</v>
       </c>
       <c r="D64" s="18">
         <v>45392</v>
       </c>
-      <c r="E64" s="30" t="s">
+      <c r="E64" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F64" s="17"/>
@@ -6903,13 +7019,13 @@
       <c r="B65" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="29">
         <v>13.16</v>
       </c>
       <c r="D65" s="18">
         <v>45392</v>
       </c>
-      <c r="E65" s="30" t="s">
+      <c r="E65" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F65" s="17"/>
@@ -6923,13 +7039,13 @@
       <c r="B66" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="29">
         <v>5.57</v>
       </c>
       <c r="D66" s="18">
         <v>45393</v>
       </c>
-      <c r="E66" s="30" t="s">
+      <c r="E66" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F66" s="17"/>
@@ -6943,13 +7059,13 @@
       <c r="B67" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="29">
         <v>12.55</v>
       </c>
       <c r="D67" s="18">
         <v>45393</v>
       </c>
-      <c r="E67" s="30" t="s">
+      <c r="E67" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F67" s="17"/>
@@ -6963,13 +7079,13 @@
       <c r="B68" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="29">
         <v>0.15</v>
       </c>
       <c r="D68" s="18">
         <v>45393</v>
       </c>
-      <c r="E68" s="30" t="s">
+      <c r="E68" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F68" s="17"/>
@@ -6979,9 +7095,9 @@
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="21"/>
       <c r="B69" s="22"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="2"/>
       <c r="F69" s="22"/>
       <c r="G69" s="22"/>
       <c r="H69" s="2"/>
@@ -6993,7 +7109,7 @@
       <c r="B70" s="12"/>
       <c r="C70" s="25"/>
       <c r="D70" s="26"/>
-      <c r="E70" s="27"/>
+      <c r="E70" s="2"/>
       <c r="F70" s="12"/>
       <c r="G70" s="12"/>
       <c r="H70" s="2"/>
@@ -7005,13 +7121,13 @@
       <c r="B71" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C71" s="28" t="s">
+      <c r="C71" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D71" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E71" s="30" t="s">
+      <c r="E71" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F71" s="14" t="s">
@@ -7029,13 +7145,13 @@
       <c r="B72" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="29">
         <v>4.13</v>
       </c>
       <c r="D72" s="18">
         <v>45394</v>
       </c>
-      <c r="E72" s="30" t="s">
+      <c r="E72" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F72" s="19"/>
@@ -7049,13 +7165,13 @@
       <c r="B73" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C73" s="31">
+      <c r="C73" s="29">
         <v>6.33</v>
       </c>
       <c r="D73" s="18">
         <v>45394</v>
       </c>
-      <c r="E73" s="30" t="s">
+      <c r="E73" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F73" s="17"/>
@@ -7069,13 +7185,13 @@
       <c r="B74" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C74" s="31">
+      <c r="C74" s="29">
         <v>7.05</v>
       </c>
       <c r="D74" s="18">
         <v>45394</v>
       </c>
-      <c r="E74" s="30" t="s">
+      <c r="E74" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F74" s="17"/>
@@ -7089,13 +7205,13 @@
       <c r="B75" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="29">
         <v>5.05</v>
       </c>
       <c r="D75" s="18">
         <v>45394</v>
       </c>
-      <c r="E75" s="30" t="s">
+      <c r="E75" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F75" s="17"/>
@@ -7109,13 +7225,13 @@
       <c r="B76" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C76" s="31">
+      <c r="C76" s="29">
         <v>2.29</v>
       </c>
       <c r="D76" s="18">
         <v>45394</v>
       </c>
-      <c r="E76" s="30" t="s">
+      <c r="E76" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F76" s="17"/>
@@ -7129,13 +7245,13 @@
       <c r="B77" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C77" s="31">
+      <c r="C77" s="29">
         <v>4.42</v>
       </c>
       <c r="D77" s="18">
         <v>45394</v>
       </c>
-      <c r="E77" s="30" t="s">
+      <c r="E77" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F77" s="17"/>
@@ -7149,13 +7265,13 @@
       <c r="B78" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C78" s="31">
+      <c r="C78" s="29">
         <v>11.17</v>
       </c>
       <c r="D78" s="18">
         <v>45394</v>
       </c>
-      <c r="E78" s="30" t="s">
+      <c r="E78" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F78" s="17"/>
@@ -7169,13 +7285,13 @@
       <c r="B79" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C79" s="31">
+      <c r="C79" s="29">
         <v>6.17</v>
       </c>
       <c r="D79" s="18">
         <v>45394</v>
       </c>
-      <c r="E79" s="30" t="s">
+      <c r="E79" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F79" s="17"/>
@@ -7189,13 +7305,13 @@
       <c r="B80" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C80" s="31">
+      <c r="C80" s="29">
         <v>9.02</v>
       </c>
       <c r="D80" s="18">
         <v>45394</v>
       </c>
-      <c r="E80" s="30" t="s">
+      <c r="E80" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F80" s="17"/>
@@ -7209,13 +7325,13 @@
       <c r="B81" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C81" s="31">
+      <c r="C81" s="29">
         <v>8.02</v>
       </c>
       <c r="D81" s="18">
         <v>45394</v>
       </c>
-      <c r="E81" s="30" t="s">
+      <c r="E81" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F81" s="17"/>
@@ -7229,13 +7345,13 @@
       <c r="B82" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C82" s="31">
+      <c r="C82" s="29">
         <v>9.4</v>
       </c>
       <c r="D82" s="18">
         <v>45395</v>
       </c>
-      <c r="E82" s="30" t="s">
+      <c r="E82" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F82" s="17"/>
@@ -7249,13 +7365,13 @@
       <c r="B83" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C83" s="31">
+      <c r="C83" s="29">
         <v>8.21</v>
       </c>
       <c r="D83" s="18">
         <v>45395</v>
       </c>
-      <c r="E83" s="30" t="s">
+      <c r="E83" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F83" s="17"/>
@@ -7269,13 +7385,13 @@
       <c r="B84" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C84" s="29">
         <v>9.29</v>
       </c>
       <c r="D84" s="18">
         <v>45395</v>
       </c>
-      <c r="E84" s="30" t="s">
+      <c r="E84" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F84" s="17"/>
@@ -7289,13 +7405,13 @@
       <c r="B85" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C85" s="31">
+      <c r="C85" s="29">
         <v>15.19</v>
       </c>
       <c r="D85" s="18">
         <v>45395</v>
       </c>
-      <c r="E85" s="30" t="s">
+      <c r="E85" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F85" s="17"/>
@@ -7309,13 +7425,13 @@
       <c r="B86" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C86" s="31">
+      <c r="C86" s="29">
         <v>6.57</v>
       </c>
       <c r="D86" s="18">
         <v>45395</v>
       </c>
-      <c r="E86" s="30" t="s">
+      <c r="E86" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F86" s="17"/>
@@ -7329,13 +7445,13 @@
       <c r="B87" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C87" s="31">
+      <c r="C87" s="29">
         <v>6.18</v>
       </c>
       <c r="D87" s="18">
         <v>45395</v>
       </c>
-      <c r="E87" s="30" t="s">
+      <c r="E87" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F87" s="17"/>
@@ -7349,13 +7465,13 @@
       <c r="B88" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C88" s="29">
         <v>5.48</v>
       </c>
       <c r="D88" s="18">
         <v>45395</v>
       </c>
-      <c r="E88" s="30" t="s">
+      <c r="E88" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F88" s="17"/>
@@ -7369,13 +7485,13 @@
       <c r="B89" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C89" s="31">
+      <c r="C89" s="29">
         <v>7.1</v>
       </c>
       <c r="D89" s="18">
         <v>45396</v>
       </c>
-      <c r="E89" s="30" t="s">
+      <c r="E89" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F89" s="17"/>
@@ -7389,13 +7505,13 @@
       <c r="B90" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C90" s="31">
+      <c r="C90" s="29">
         <v>6.34</v>
       </c>
       <c r="D90" s="18">
         <v>45396</v>
       </c>
-      <c r="E90" s="30" t="s">
+      <c r="E90" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F90" s="17"/>
@@ -7409,13 +7525,13 @@
       <c r="B91" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C91" s="31">
+      <c r="C91" s="29">
         <v>7.14</v>
       </c>
       <c r="D91" s="18">
         <v>45396</v>
       </c>
-      <c r="E91" s="30" t="s">
+      <c r="E91" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F91" s="17"/>
@@ -7429,13 +7545,13 @@
       <c r="B92" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C92" s="31">
+      <c r="C92" s="29">
         <v>9.45</v>
       </c>
       <c r="D92" s="18">
         <v>45396</v>
       </c>
-      <c r="E92" s="30" t="s">
+      <c r="E92" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F92" s="17"/>
@@ -7449,13 +7565,13 @@
       <c r="B93" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C93" s="31">
+      <c r="C93" s="29">
         <v>7.12</v>
       </c>
       <c r="D93" s="18">
         <v>45396</v>
       </c>
-      <c r="E93" s="30" t="s">
+      <c r="E93" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F93" s="17"/>
@@ -7469,13 +7585,13 @@
       <c r="B94" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C94" s="31">
+      <c r="C94" s="29">
         <v>5.46</v>
       </c>
       <c r="D94" s="18">
         <v>45396</v>
       </c>
-      <c r="E94" s="30" t="s">
+      <c r="E94" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F94" s="17"/>
@@ -7489,13 +7605,13 @@
       <c r="B95" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C95" s="31">
+      <c r="C95" s="29">
         <v>13.51</v>
       </c>
       <c r="D95" s="18">
         <v>45396</v>
       </c>
-      <c r="E95" s="30" t="s">
+      <c r="E95" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F95" s="17"/>
@@ -7509,13 +7625,13 @@
       <c r="B96" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C96" s="31">
+      <c r="C96" s="29">
         <v>12.21</v>
       </c>
       <c r="D96" s="18">
         <v>45397</v>
       </c>
-      <c r="E96" s="30" t="s">
+      <c r="E96" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F96" s="17"/>
@@ -7529,13 +7645,13 @@
       <c r="B97" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C97" s="31">
+      <c r="C97" s="29">
         <v>8.45</v>
       </c>
       <c r="D97" s="18">
         <v>45397</v>
       </c>
-      <c r="E97" s="30" t="s">
+      <c r="E97" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F97" s="17"/>
@@ -7549,13 +7665,13 @@
       <c r="B98" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C98" s="31">
+      <c r="C98" s="29">
         <v>12.35</v>
       </c>
       <c r="D98" s="18">
         <v>45397</v>
       </c>
-      <c r="E98" s="30" t="s">
+      <c r="E98" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F98" s="17"/>
@@ -7569,13 +7685,13 @@
       <c r="B99" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C99" s="31">
+      <c r="C99" s="29">
         <v>5.39</v>
       </c>
       <c r="D99" s="18">
         <v>45397</v>
       </c>
-      <c r="E99" s="30" t="s">
+      <c r="E99" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F99" s="17"/>
@@ -7589,13 +7705,13 @@
       <c r="B100" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C100" s="31">
+      <c r="C100" s="29">
         <v>9.59</v>
       </c>
       <c r="D100" s="18">
         <v>45397</v>
       </c>
-      <c r="E100" s="30" t="s">
+      <c r="E100" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F100" s="17"/>
@@ -7609,13 +7725,13 @@
       <c r="B101" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C101" s="31">
+      <c r="C101" s="29">
         <v>9.57</v>
       </c>
       <c r="D101" s="18">
         <v>45397</v>
       </c>
-      <c r="E101" s="30" t="s">
+      <c r="E101" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F101" s="17"/>
@@ -7629,13 +7745,13 @@
       <c r="B102" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C102" s="31">
+      <c r="C102" s="29">
         <v>17.55</v>
       </c>
       <c r="D102" s="18">
         <v>45398</v>
       </c>
-      <c r="E102" s="30" t="s">
+      <c r="E102" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F102" s="17"/>
@@ -7649,13 +7765,13 @@
       <c r="B103" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C103" s="31">
+      <c r="C103" s="29">
         <v>12.14</v>
       </c>
       <c r="D103" s="18">
         <v>45398</v>
       </c>
-      <c r="E103" s="30" t="s">
+      <c r="E103" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F103" s="17"/>
@@ -7669,13 +7785,13 @@
       <c r="B104" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C104" s="31">
+      <c r="C104" s="29">
         <v>8.33</v>
       </c>
       <c r="D104" s="18">
         <v>45398</v>
       </c>
-      <c r="E104" s="30" t="s">
+      <c r="E104" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F104" s="17"/>
@@ -7689,13 +7805,13 @@
       <c r="B105" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="C105" s="31">
+      <c r="C105" s="29">
         <v>7.41</v>
       </c>
       <c r="D105" s="18">
         <v>45398</v>
       </c>
-      <c r="E105" s="30" t="s">
+      <c r="E105" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F105" s="17"/>
@@ -7709,13 +7825,13 @@
       <c r="B106" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C106" s="31">
+      <c r="C106" s="29">
         <v>8.54</v>
       </c>
       <c r="D106" s="18">
         <v>45398</v>
       </c>
-      <c r="E106" s="30" t="s">
+      <c r="E106" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F106" s="17"/>
@@ -7729,13 +7845,13 @@
       <c r="B107" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C107" s="31">
+      <c r="C107" s="29">
         <v>16.08</v>
       </c>
       <c r="D107" s="18">
         <v>45399</v>
       </c>
-      <c r="E107" s="30" t="s">
+      <c r="E107" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F107" s="17"/>
@@ -7749,13 +7865,13 @@
       <c r="B108" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C108" s="31">
+      <c r="C108" s="29">
         <v>7.01</v>
       </c>
       <c r="D108" s="18">
         <v>45399</v>
       </c>
-      <c r="E108" s="30" t="s">
+      <c r="E108" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F108" s="17"/>
@@ -7769,13 +7885,13 @@
       <c r="B109" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C109" s="31">
+      <c r="C109" s="29">
         <v>7.29</v>
       </c>
       <c r="D109" s="18">
         <v>45399</v>
       </c>
-      <c r="E109" s="30" t="s">
+      <c r="E109" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F109" s="17"/>
@@ -7789,13 +7905,13 @@
       <c r="B110" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="C110" s="31">
+      <c r="C110" s="29">
         <v>16.33</v>
       </c>
       <c r="D110" s="18">
         <v>45399</v>
       </c>
-      <c r="E110" s="30" t="s">
+      <c r="E110" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F110" s="17"/>
@@ -7809,13 +7925,13 @@
       <c r="B111" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C111" s="31">
+      <c r="C111" s="29">
         <v>10.58</v>
       </c>
       <c r="D111" s="18">
         <v>45399</v>
       </c>
-      <c r="E111" s="30" t="s">
+      <c r="E111" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F111" s="17"/>
@@ -7829,13 +7945,13 @@
       <c r="B112" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C112" s="31">
+      <c r="C112" s="29">
         <v>7.33</v>
       </c>
       <c r="D112" s="18">
         <v>45400</v>
       </c>
-      <c r="E112" s="30" t="s">
+      <c r="E112" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F112" s="17"/>
@@ -7849,13 +7965,13 @@
       <c r="B113" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="C113" s="31">
+      <c r="C113" s="29">
         <v>17.3</v>
       </c>
       <c r="D113" s="18">
         <v>45400</v>
       </c>
-      <c r="E113" s="30" t="s">
+      <c r="E113" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F113" s="17"/>
@@ -7869,13 +7985,13 @@
       <c r="B114" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C114" s="31">
+      <c r="C114" s="29">
         <v>16.01</v>
       </c>
       <c r="D114" s="18">
         <v>45400</v>
       </c>
-      <c r="E114" s="30" t="s">
+      <c r="E114" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F114" s="17"/>
@@ -7889,13 +8005,13 @@
       <c r="B115" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C115" s="31">
+      <c r="C115" s="29">
         <v>10.06</v>
       </c>
       <c r="D115" s="18">
         <v>45400</v>
       </c>
-      <c r="E115" s="30" t="s">
+      <c r="E115" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F115" s="17"/>
@@ -7909,13 +8025,13 @@
       <c r="B116" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C116" s="31">
+      <c r="C116" s="29">
         <v>7.13</v>
       </c>
       <c r="D116" s="18">
         <v>45400</v>
       </c>
-      <c r="E116" s="30" t="s">
+      <c r="E116" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F116" s="17"/>
@@ -7929,13 +8045,13 @@
       <c r="B117" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="C117" s="31">
+      <c r="C117" s="29">
         <v>9.06</v>
       </c>
       <c r="D117" s="18">
         <v>45401</v>
       </c>
-      <c r="E117" s="30" t="s">
+      <c r="E117" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F117" s="17"/>
@@ -7949,13 +8065,13 @@
       <c r="B118" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C118" s="31">
+      <c r="C118" s="29">
         <v>10.49</v>
       </c>
       <c r="D118" s="18">
         <v>45401</v>
       </c>
-      <c r="E118" s="30" t="s">
+      <c r="E118" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F118" s="17"/>
@@ -7969,13 +8085,13 @@
       <c r="B119" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C119" s="31">
+      <c r="C119" s="29">
         <v>8.08</v>
       </c>
       <c r="D119" s="18">
         <v>45401</v>
       </c>
-      <c r="E119" s="30" t="s">
+      <c r="E119" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F119" s="17"/>
@@ -7989,13 +8105,13 @@
       <c r="B120" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C120" s="31">
+      <c r="C120" s="29">
         <v>13.4</v>
       </c>
       <c r="D120" s="18">
         <v>45401</v>
       </c>
-      <c r="E120" s="30" t="s">
+      <c r="E120" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F120" s="17"/>
@@ -8009,13 +8125,13 @@
       <c r="B121" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C121" s="31">
+      <c r="C121" s="29">
         <v>12.54</v>
       </c>
       <c r="D121" s="18">
         <v>45401</v>
       </c>
-      <c r="E121" s="30" t="s">
+      <c r="E121" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F121" s="17"/>
@@ -8029,13 +8145,13 @@
       <c r="B122" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C122" s="31">
+      <c r="C122" s="29">
         <v>9.57</v>
       </c>
       <c r="D122" s="18">
         <v>45401</v>
       </c>
-      <c r="E122" s="30" t="s">
+      <c r="E122" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F122" s="17"/>
@@ -8049,13 +8165,13 @@
       <c r="B123" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C123" s="31">
+      <c r="C123" s="29">
         <v>7.29</v>
       </c>
       <c r="D123" s="18">
         <v>45402</v>
       </c>
-      <c r="E123" s="30" t="s">
+      <c r="E123" s="2" t="s">
         <v>148</v>
       </c>
       <c r="F123" s="17"/>
@@ -8069,13 +8185,13 @@
       <c r="B124" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C124" s="31">
+      <c r="C124" s="29">
         <v>10.29</v>
       </c>
       <c r="D124" s="18">
         <v>45402</v>
       </c>
-      <c r="E124" s="30" t="s">
+      <c r="E124" s="2" t="s">
         <v>148</v>
       </c>
       <c r="F124" s="17"/>
@@ -8089,13 +8205,13 @@
       <c r="B125" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="C125" s="31">
+      <c r="C125" s="29">
         <v>9.01</v>
       </c>
       <c r="D125" s="18">
         <v>45402</v>
       </c>
-      <c r="E125" s="30" t="s">
+      <c r="E125" s="2" t="s">
         <v>148</v>
       </c>
       <c r="F125" s="17"/>
@@ -8109,13 +8225,13 @@
       <c r="B126" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C126" s="31">
+      <c r="C126" s="29">
         <v>7.38</v>
       </c>
       <c r="D126" s="18">
         <v>45402</v>
       </c>
-      <c r="E126" s="30" t="s">
+      <c r="E126" s="2" t="s">
         <v>148</v>
       </c>
       <c r="F126" s="17"/>
@@ -8129,13 +8245,13 @@
       <c r="B127" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C127" s="31">
+      <c r="C127" s="29">
         <v>9.29</v>
       </c>
       <c r="D127" s="18">
         <v>45402</v>
       </c>
-      <c r="E127" s="30" t="s">
+      <c r="E127" s="2" t="s">
         <v>148</v>
       </c>
       <c r="F127" s="17"/>
@@ -8149,13 +8265,13 @@
       <c r="B128" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="C128" s="31">
+      <c r="C128" s="29">
         <v>23.01</v>
       </c>
       <c r="D128" s="18">
         <v>45402</v>
       </c>
-      <c r="E128" s="30" t="s">
+      <c r="E128" s="2" t="s">
         <v>148</v>
       </c>
       <c r="F128" s="17"/>
@@ -8169,13 +8285,13 @@
       <c r="B129" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C129" s="31">
+      <c r="C129" s="29">
         <v>15.51</v>
       </c>
       <c r="D129" s="18">
         <v>45403</v>
       </c>
-      <c r="E129" s="30" t="s">
+      <c r="E129" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F129" s="17"/>
@@ -8189,13 +8305,13 @@
       <c r="B130" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C130" s="31">
+      <c r="C130" s="29">
         <v>9.19</v>
       </c>
       <c r="D130" s="18">
         <v>45403</v>
       </c>
-      <c r="E130" s="30" t="s">
+      <c r="E130" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F130" s="17"/>
@@ -8209,13 +8325,13 @@
       <c r="B131" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C131" s="31">
+      <c r="C131" s="29">
         <v>9.27</v>
       </c>
       <c r="D131" s="18">
         <v>45403</v>
       </c>
-      <c r="E131" s="30" t="s">
+      <c r="E131" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F131" s="17"/>
@@ -8229,13 +8345,13 @@
       <c r="B132" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="C132" s="31">
+      <c r="C132" s="29">
         <v>5.56</v>
       </c>
       <c r="D132" s="18">
         <v>45403</v>
       </c>
-      <c r="E132" s="30" t="s">
+      <c r="E132" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F132" s="17"/>
@@ -8249,13 +8365,13 @@
       <c r="B133" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C133" s="31">
+      <c r="C133" s="29">
         <v>8.48</v>
       </c>
       <c r="D133" s="18">
         <v>45403</v>
       </c>
-      <c r="E133" s="30" t="s">
+      <c r="E133" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F133" s="17"/>
@@ -8269,13 +8385,13 @@
       <c r="B134" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C134" s="31">
+      <c r="C134" s="29">
         <v>8.42</v>
       </c>
       <c r="D134" s="18">
         <v>45403</v>
       </c>
-      <c r="E134" s="30" t="s">
+      <c r="E134" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F134" s="17"/>
@@ -8289,13 +8405,13 @@
       <c r="B135" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="C135" s="31">
+      <c r="C135" s="29">
         <v>10.04</v>
       </c>
       <c r="D135" s="18">
         <v>45404</v>
       </c>
-      <c r="E135" s="30" t="s">
+      <c r="E135" s="2" t="s">
         <v>162</v>
       </c>
       <c r="F135" s="17"/>
@@ -8309,13 +8425,13 @@
       <c r="B136" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="C136" s="31">
+      <c r="C136" s="29">
         <v>8.35</v>
       </c>
       <c r="D136" s="18">
         <v>45404</v>
       </c>
-      <c r="E136" s="30" t="s">
+      <c r="E136" s="2" t="s">
         <v>162</v>
       </c>
       <c r="F136" s="17"/>
@@ -8329,13 +8445,13 @@
       <c r="B137" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C137" s="31">
+      <c r="C137" s="29">
         <v>19.21</v>
       </c>
       <c r="D137" s="18">
         <v>45404</v>
       </c>
-      <c r="E137" s="30" t="s">
+      <c r="E137" s="2" t="s">
         <v>162</v>
       </c>
       <c r="F137" s="17"/>
@@ -8349,13 +8465,13 @@
       <c r="B138" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C138" s="31">
+      <c r="C138" s="29">
         <v>12.06</v>
       </c>
       <c r="D138" s="18">
         <v>45404</v>
       </c>
-      <c r="E138" s="30" t="s">
+      <c r="E138" s="2" t="s">
         <v>162</v>
       </c>
       <c r="F138" s="17"/>
@@ -8369,13 +8485,13 @@
       <c r="B139" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C139" s="31">
+      <c r="C139" s="29">
         <v>12.52</v>
       </c>
       <c r="D139" s="18">
         <v>45404</v>
       </c>
-      <c r="E139" s="30" t="s">
+      <c r="E139" s="2" t="s">
         <v>162</v>
       </c>
       <c r="F139" s="17"/>
@@ -8389,13 +8505,13 @@
       <c r="B140" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C140" s="31">
+      <c r="C140" s="29">
         <v>14.16</v>
       </c>
       <c r="D140" s="18">
         <v>45405</v>
       </c>
-      <c r="E140" s="30" t="s">
+      <c r="E140" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F140" s="17"/>
@@ -8409,13 +8525,13 @@
       <c r="B141" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="C141" s="31">
+      <c r="C141" s="29">
         <v>12.49</v>
       </c>
       <c r="D141" s="18">
         <v>45405</v>
       </c>
-      <c r="E141" s="30" t="s">
+      <c r="E141" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F141" s="17"/>
@@ -8429,13 +8545,13 @@
       <c r="B142" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C142" s="31">
+      <c r="C142" s="29">
         <v>3.5</v>
       </c>
       <c r="D142" s="18">
         <v>45405</v>
       </c>
-      <c r="E142" s="30" t="s">
+      <c r="E142" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F142" s="17"/>
@@ -8449,13 +8565,13 @@
       <c r="B143" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C143" s="31">
+      <c r="C143" s="29">
         <v>7.54</v>
       </c>
       <c r="D143" s="18">
         <v>45405</v>
       </c>
-      <c r="E143" s="30" t="s">
+      <c r="E143" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F143" s="17"/>
@@ -8469,13 +8585,13 @@
       <c r="B144" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="C144" s="31">
+      <c r="C144" s="29">
         <v>6.43</v>
       </c>
       <c r="D144" s="18">
         <v>45405</v>
       </c>
-      <c r="E144" s="30" t="s">
+      <c r="E144" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F144" s="17"/>
@@ -8489,13 +8605,13 @@
       <c r="B145" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="C145" s="31">
+      <c r="C145" s="29">
         <v>9.41</v>
       </c>
       <c r="D145" s="18">
         <v>45405</v>
       </c>
-      <c r="E145" s="30" t="s">
+      <c r="E145" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F145" s="17"/>
@@ -8509,13 +8625,13 @@
       <c r="B146" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C146" s="31">
+      <c r="C146" s="29">
         <v>19.37</v>
       </c>
       <c r="D146" s="18">
         <v>45406</v>
       </c>
-      <c r="E146" s="30" t="s">
+      <c r="E146" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F146" s="17"/>
@@ -8529,13 +8645,13 @@
       <c r="B147" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="C147" s="31">
+      <c r="C147" s="29">
         <v>0.56</v>
       </c>
       <c r="D147" s="18">
         <v>45406</v>
       </c>
-      <c r="E147" s="30" t="s">
+      <c r="E147" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F147" s="17"/>
@@ -8549,13 +8665,13 @@
       <c r="B148" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="C148" s="34" t="s">
+      <c r="C148" s="32" t="s">
         <v>178</v>
       </c>
       <c r="D148" s="18">
         <v>45407</v>
       </c>
-      <c r="E148" s="30" t="s">
+      <c r="E148" s="2" t="s">
         <v>179</v>
       </c>
       <c r="F148" s="17"/>
@@ -8569,13 +8685,13 @@
       <c r="B149" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C149" s="34" t="s">
+      <c r="C149" s="32" t="s">
         <v>178</v>
       </c>
       <c r="D149" s="18">
         <v>45408</v>
       </c>
-      <c r="E149" s="30" t="s">
+      <c r="E149" s="2" t="s">
         <v>181</v>
       </c>
       <c r="F149" s="17"/>
@@ -8589,13 +8705,13 @@
       <c r="B150" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="C150" s="34" t="s">
+      <c r="C150" s="32" t="s">
         <v>178</v>
       </c>
       <c r="D150" s="18">
         <v>45409</v>
       </c>
-      <c r="E150" s="30" t="s">
+      <c r="E150" s="2" t="s">
         <v>183</v>
       </c>
       <c r="F150" s="17"/>
@@ -8609,13 +8725,13 @@
       <c r="B151" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C151" s="34" t="s">
+      <c r="C151" s="32" t="s">
         <v>178</v>
       </c>
       <c r="D151" s="18">
         <v>45410</v>
       </c>
-      <c r="E151" s="30" t="s">
+      <c r="E151" s="2" t="s">
         <v>185</v>
       </c>
       <c r="F151" s="17"/>
@@ -8629,13 +8745,13 @@
       <c r="B152" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C152" s="34" t="s">
+      <c r="C152" s="32" t="s">
         <v>178</v>
       </c>
       <c r="D152" s="18">
         <v>45411</v>
       </c>
-      <c r="E152" s="30" t="s">
+      <c r="E152" s="2" t="s">
         <v>187</v>
       </c>
       <c r="F152" s="17"/>
@@ -8649,13 +8765,13 @@
       <c r="B153" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C153" s="34" t="s">
+      <c r="C153" s="32" t="s">
         <v>178</v>
       </c>
       <c r="D153" s="18">
         <v>45412</v>
       </c>
-      <c r="E153" s="30" t="s">
+      <c r="E153" s="2" t="s">
         <v>189</v>
       </c>
       <c r="F153" s="17"/>
@@ -8665,9 +8781,9 @@
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="21"/>
       <c r="B154" s="22"/>
-      <c r="C154" s="32"/>
-      <c r="D154" s="33"/>
-      <c r="E154" s="30"/>
+      <c r="C154" s="30"/>
+      <c r="D154" s="31"/>
+      <c r="E154" s="2"/>
       <c r="F154" s="22"/>
       <c r="G154" s="22"/>
       <c r="H154" s="2"/>
@@ -8675,9 +8791,9 @@
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="21"/>
       <c r="B155" s="22"/>
-      <c r="C155" s="32"/>
-      <c r="D155" s="33"/>
-      <c r="E155" s="30"/>
+      <c r="C155" s="30"/>
+      <c r="D155" s="31"/>
+      <c r="E155" s="2"/>
       <c r="F155" s="22"/>
       <c r="G155" s="22"/>
       <c r="H155" s="2"/>
@@ -8685,9 +8801,9 @@
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="21"/>
       <c r="B156" s="22"/>
-      <c r="C156" s="32"/>
-      <c r="D156" s="33"/>
-      <c r="E156" s="30"/>
+      <c r="C156" s="30"/>
+      <c r="D156" s="31"/>
+      <c r="E156" s="2"/>
       <c r="F156" s="22"/>
       <c r="G156" s="22"/>
       <c r="H156" s="2"/>
@@ -8695,9 +8811,9 @@
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="21"/>
       <c r="B157" s="22"/>
-      <c r="C157" s="32"/>
-      <c r="D157" s="33"/>
-      <c r="E157" s="30"/>
+      <c r="C157" s="30"/>
+      <c r="D157" s="31"/>
+      <c r="E157" s="2"/>
       <c r="F157" s="22"/>
       <c r="G157" s="22"/>
       <c r="H157" s="2"/>
@@ -8705,9 +8821,9 @@
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="21"/>
       <c r="B158" s="22"/>
-      <c r="C158" s="32"/>
-      <c r="D158" s="33"/>
-      <c r="E158" s="30"/>
+      <c r="C158" s="30"/>
+      <c r="D158" s="31"/>
+      <c r="E158" s="2"/>
       <c r="F158" s="22"/>
       <c r="G158" s="22"/>
       <c r="H158" s="2"/>
@@ -8715,9 +8831,9 @@
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="21"/>
       <c r="B159" s="22"/>
-      <c r="C159" s="32"/>
-      <c r="D159" s="33"/>
-      <c r="E159" s="30"/>
+      <c r="C159" s="30"/>
+      <c r="D159" s="31"/>
+      <c r="E159" s="2"/>
       <c r="F159" s="22"/>
       <c r="G159" s="22"/>
       <c r="H159" s="2"/>
@@ -8725,9 +8841,9 @@
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="21"/>
       <c r="B160" s="22"/>
-      <c r="C160" s="32"/>
-      <c r="D160" s="33"/>
-      <c r="E160" s="30"/>
+      <c r="C160" s="30"/>
+      <c r="D160" s="31"/>
+      <c r="E160" s="2"/>
       <c r="F160" s="22"/>
       <c r="G160" s="22"/>
       <c r="H160" s="2"/>
@@ -8735,9 +8851,9 @@
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="21"/>
       <c r="B161" s="22"/>
-      <c r="C161" s="32"/>
-      <c r="D161" s="33"/>
-      <c r="E161" s="30"/>
+      <c r="C161" s="30"/>
+      <c r="D161" s="31"/>
+      <c r="E161" s="2"/>
       <c r="F161" s="22"/>
       <c r="G161" s="22"/>
       <c r="H161" s="2"/>
@@ -8745,9 +8861,9 @@
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="21"/>
       <c r="B162" s="22"/>
-      <c r="C162" s="32"/>
-      <c r="D162" s="33"/>
-      <c r="E162" s="30"/>
+      <c r="C162" s="30"/>
+      <c r="D162" s="31"/>
+      <c r="E162" s="2"/>
       <c r="F162" s="22"/>
       <c r="G162" s="22"/>
       <c r="H162" s="2"/>
@@ -8755,9 +8871,9 @@
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="21"/>
       <c r="B163" s="22"/>
-      <c r="C163" s="32"/>
-      <c r="D163" s="33"/>
-      <c r="E163" s="30"/>
+      <c r="C163" s="30"/>
+      <c r="D163" s="31"/>
+      <c r="E163" s="2"/>
       <c r="F163" s="22"/>
       <c r="G163" s="22"/>
       <c r="H163" s="2"/>
@@ -8765,9 +8881,9 @@
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="21"/>
       <c r="B164" s="22"/>
-      <c r="C164" s="32"/>
-      <c r="D164" s="33"/>
-      <c r="E164" s="30"/>
+      <c r="C164" s="30"/>
+      <c r="D164" s="31"/>
+      <c r="E164" s="2"/>
       <c r="F164" s="22"/>
       <c r="G164" s="22"/>
       <c r="H164" s="2"/>
@@ -8775,9 +8891,9 @@
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="21"/>
       <c r="B165" s="22"/>
-      <c r="C165" s="32"/>
-      <c r="D165" s="33"/>
-      <c r="E165" s="30"/>
+      <c r="C165" s="30"/>
+      <c r="D165" s="31"/>
+      <c r="E165" s="2"/>
       <c r="F165" s="22"/>
       <c r="G165" s="22"/>
       <c r="H165" s="2"/>
@@ -8785,9 +8901,9 @@
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="21"/>
       <c r="B166" s="22"/>
-      <c r="C166" s="32"/>
-      <c r="D166" s="33"/>
-      <c r="E166" s="30"/>
+      <c r="C166" s="30"/>
+      <c r="D166" s="31"/>
+      <c r="E166" s="2"/>
       <c r="F166" s="22"/>
       <c r="G166" s="22"/>
       <c r="H166" s="2"/>
@@ -8795,9 +8911,9 @@
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="21"/>
       <c r="B167" s="22"/>
-      <c r="C167" s="32"/>
-      <c r="D167" s="33"/>
-      <c r="E167" s="30"/>
+      <c r="C167" s="30"/>
+      <c r="D167" s="31"/>
+      <c r="E167" s="2"/>
       <c r="F167" s="22"/>
       <c r="G167" s="22"/>
       <c r="H167" s="2"/>
@@ -8805,9 +8921,9 @@
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="21"/>
       <c r="B168" s="22"/>
-      <c r="C168" s="32"/>
-      <c r="D168" s="33"/>
-      <c r="E168" s="30"/>
+      <c r="C168" s="30"/>
+      <c r="D168" s="31"/>
+      <c r="E168" s="2"/>
       <c r="F168" s="22"/>
       <c r="G168" s="22"/>
       <c r="H168" s="2"/>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="363">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -1120,7 +1120,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1178,12 +1178,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1232,7 +1226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="51">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1380,15 +1374,6 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1701,7 +1686,7 @@
     <col min="1" max="1" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="53" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="50" width="6.719285714285714" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="47" width="38.86214285714286" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="23" width="7.719285714285714" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="47" width="23.862142857142857" customWidth="1" bestFit="1"/>
@@ -2246,61 +2231,61 @@
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="22"/>
@@ -3946,7 +3931,9 @@
         <v>276</v>
       </c>
       <c r="F74" s="2"/>
-      <c r="G74" s="17"/>
+      <c r="G74" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H74" s="17"/>
       <c r="I74" s="35"/>
     </row>
@@ -3967,7 +3954,9 @@
         <v>280</v>
       </c>
       <c r="F75" s="2"/>
-      <c r="G75" s="17"/>
+      <c r="G75" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H75" s="17"/>
       <c r="I75" s="35"/>
     </row>
@@ -3988,7 +3977,9 @@
         <v>280</v>
       </c>
       <c r="F76" s="2"/>
-      <c r="G76" s="17"/>
+      <c r="G76" s="17" t="s">
+        <v>198</v>
+      </c>
       <c r="H76" s="17"/>
       <c r="I76" s="35"/>
     </row>
@@ -4051,7 +4042,7 @@
         <v>282</v>
       </c>
       <c r="C80" s="44">
-        <v>28.118275462962963</v>
+        <v>29.118159722222224</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -4072,7 +4063,7 @@
         <v>282</v>
       </c>
       <c r="C81" s="44">
-        <v>28.118275462962963</v>
+        <v>29.118159722222224</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -4093,7 +4084,7 @@
         <v>282</v>
       </c>
       <c r="C82" s="44">
-        <v>28.118275462962963</v>
+        <v>29.118159722222224</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -4114,7 +4105,7 @@
         <v>282</v>
       </c>
       <c r="C83" s="44">
-        <v>28.118275462962963</v>
+        <v>29.118159722222224</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Index"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="363">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>19-May</t>
+  </si>
+  <si>
+    <t>Completed</t>
   </si>
   <si>
     <t>End to End code discussed in the Section for reference</t>
@@ -616,9 +619,6 @@
   </si>
   <si>
     <t>20-Apr</t>
-  </si>
-  <si>
-    <t>Completed</t>
   </si>
   <si>
     <t>#2 - Var vs Let vs Const in JavaScript</t>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="H22" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="47.25">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="H25" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -2167,7 +2167,7 @@
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25">
       <c r="A27" s="22"/>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -2187,7 +2187,7 @@
         <v>358</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -2207,7 +2207,7 @@
         <v>360</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -2227,7 +2227,7 @@
         <v>362</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -2237,7 +2237,7 @@
       <c r="G30" s="35"/>
       <c r="H30" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -2247,7 +2247,7 @@
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
@@ -2257,7 +2257,7 @@
       <c r="G32" s="35"/>
       <c r="H32" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
@@ -2267,7 +2267,7 @@
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
@@ -2277,7 +2277,7 @@
       <c r="G34" s="35"/>
       <c r="H34" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
@@ -2287,7 +2287,7 @@
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20.25">
       <c r="A36" s="22"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -2324,7 +2324,7 @@
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="21"/>
       <c r="B1" s="35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C1" s="30"/>
       <c r="D1" s="31"/>
@@ -2339,7 +2339,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="31"/>
@@ -2354,7 +2354,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C3" s="30"/>
       <c r="D3" s="31"/>
@@ -2369,7 +2369,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="31"/>
@@ -2392,7 +2392,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B6" s="37"/>
       <c r="C6" s="38"/>
@@ -2420,7 +2420,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>5</v>
@@ -2435,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C8" s="29">
         <v>8.03</v>
@@ -2444,11 +2444,11 @@
         <v>45355</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="35"/>
@@ -2467,11 +2467,11 @@
         <v>45355</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="35"/>
@@ -2490,11 +2490,11 @@
         <v>45355</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="40" t="s">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="35"/>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="35"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="35"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="35"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="35"/>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="35"/>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="35"/>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="35"/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="35"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="35"/>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="35"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="35"/>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H23" s="17"/>
       <c r="I23" s="35"/>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H24" s="17"/>
       <c r="I24" s="35"/>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="35"/>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="35"/>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="35"/>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="35"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="35"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="35"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="35"/>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="35"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="35"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H34" s="17"/>
       <c r="I34" s="35"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="35"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="35"/>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="35"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H38" s="17"/>
       <c r="I38" s="35"/>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H39" s="17"/>
       <c r="I39" s="35"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H40" s="17"/>
       <c r="I40" s="35"/>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H41" s="17"/>
       <c r="I41" s="35"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H42" s="17"/>
       <c r="I42" s="35"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H43" s="17"/>
       <c r="I43" s="35"/>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="35"/>
@@ -3324,7 +3324,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>5</v>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H48" s="17"/>
       <c r="I48" s="35"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H49" s="17"/>
       <c r="I49" s="35"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H50" s="17"/>
       <c r="I50" s="35"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H51" s="17"/>
       <c r="I51" s="35"/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H52" s="17"/>
       <c r="I52" s="35"/>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H53" s="17"/>
       <c r="I53" s="35"/>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H54" s="17"/>
       <c r="I54" s="35"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H55" s="17"/>
       <c r="I55" s="35"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H56" s="17"/>
       <c r="I56" s="35"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H57" s="17"/>
       <c r="I57" s="35"/>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="35"/>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="35"/>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="35"/>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H61" s="17"/>
       <c r="I61" s="35"/>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H62" s="17"/>
       <c r="I62" s="35"/>
@@ -3720,7 +3720,7 @@
         <v>13</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G65" s="14" t="s">
         <v>5</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H66" s="17"/>
       <c r="I66" s="35"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H67" s="17"/>
       <c r="I67" s="35"/>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H68" s="17"/>
       <c r="I68" s="35"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H69" s="17"/>
       <c r="I69" s="35"/>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H70" s="17"/>
       <c r="I70" s="35"/>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="35"/>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H72" s="17"/>
       <c r="I72" s="35"/>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H73" s="17"/>
       <c r="I73" s="35"/>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H74" s="17"/>
       <c r="I74" s="35"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H75" s="17"/>
       <c r="I75" s="35"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="17" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="H76" s="17"/>
       <c r="I76" s="35"/>
@@ -4024,7 +4024,7 @@
         <v>13</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G79" s="14" t="s">
         <v>5</v>
@@ -4042,7 +4042,7 @@
         <v>282</v>
       </c>
       <c r="C80" s="44">
-        <v>29.118159722222224</v>
+        <v>30.11804398148148</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -4051,7 +4051,9 @@
         <v>283</v>
       </c>
       <c r="F80" s="2"/>
-      <c r="G80" s="19"/>
+      <c r="G80" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H80" s="19"/>
       <c r="I80" s="35"/>
     </row>
@@ -4063,7 +4065,7 @@
         <v>282</v>
       </c>
       <c r="C81" s="44">
-        <v>29.118159722222224</v>
+        <v>30.11804398148148</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -4072,7 +4074,9 @@
         <v>284</v>
       </c>
       <c r="F81" s="2"/>
-      <c r="G81" s="19"/>
+      <c r="G81" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H81" s="19"/>
       <c r="I81" s="35"/>
     </row>
@@ -4084,7 +4088,7 @@
         <v>282</v>
       </c>
       <c r="C82" s="44">
-        <v>29.118159722222224</v>
+        <v>30.11804398148148</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -4093,7 +4097,9 @@
         <v>285</v>
       </c>
       <c r="F82" s="2"/>
-      <c r="G82" s="19"/>
+      <c r="G82" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H82" s="19"/>
       <c r="I82" s="35"/>
     </row>
@@ -4105,7 +4111,7 @@
         <v>282</v>
       </c>
       <c r="C83" s="44">
-        <v>29.118159722222224</v>
+        <v>30.11804398148148</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
@@ -4114,7 +4120,9 @@
         <v>286</v>
       </c>
       <c r="F83" s="2"/>
-      <c r="G83" s="19"/>
+      <c r="G83" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H83" s="19"/>
       <c r="I83" s="35"/>
     </row>
@@ -4135,7 +4143,9 @@
         <v>288</v>
       </c>
       <c r="F84" s="2"/>
-      <c r="G84" s="17"/>
+      <c r="G84" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H84" s="17"/>
       <c r="I84" s="35"/>
     </row>
@@ -4156,7 +4166,9 @@
         <v>288</v>
       </c>
       <c r="F85" s="2"/>
-      <c r="G85" s="17"/>
+      <c r="G85" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H85" s="17"/>
       <c r="I85" s="35"/>
     </row>
@@ -4177,7 +4189,9 @@
         <v>288</v>
       </c>
       <c r="F86" s="2"/>
-      <c r="G86" s="17"/>
+      <c r="G86" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H86" s="17"/>
       <c r="I86" s="35"/>
     </row>
@@ -4198,7 +4212,9 @@
         <v>288</v>
       </c>
       <c r="F87" s="2"/>
-      <c r="G87" s="17"/>
+      <c r="G87" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H87" s="17"/>
       <c r="I87" s="35"/>
     </row>
@@ -4219,7 +4235,9 @@
         <v>288</v>
       </c>
       <c r="F88" s="2"/>
-      <c r="G88" s="17"/>
+      <c r="G88" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H88" s="17"/>
       <c r="I88" s="35"/>
     </row>
@@ -4240,7 +4258,9 @@
         <v>288</v>
       </c>
       <c r="F89" s="2"/>
-      <c r="G89" s="17"/>
+      <c r="G89" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H89" s="17"/>
       <c r="I89" s="35"/>
     </row>
@@ -4261,7 +4281,9 @@
         <v>288</v>
       </c>
       <c r="F90" s="2"/>
-      <c r="G90" s="17"/>
+      <c r="G90" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H90" s="17"/>
       <c r="I90" s="35"/>
     </row>
@@ -4282,7 +4304,9 @@
         <v>296</v>
       </c>
       <c r="F91" s="2"/>
-      <c r="G91" s="17"/>
+      <c r="G91" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H91" s="17"/>
       <c r="I91" s="35"/>
     </row>
@@ -4303,7 +4327,9 @@
         <v>296</v>
       </c>
       <c r="F92" s="2"/>
-      <c r="G92" s="17"/>
+      <c r="G92" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H92" s="17"/>
       <c r="I92" s="35"/>
     </row>
@@ -4324,7 +4350,9 @@
         <v>296</v>
       </c>
       <c r="F93" s="2"/>
-      <c r="G93" s="17"/>
+      <c r="G93" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H93" s="17"/>
       <c r="I93" s="35"/>
     </row>
@@ -4345,7 +4373,9 @@
         <v>296</v>
       </c>
       <c r="F94" s="2"/>
-      <c r="G94" s="17"/>
+      <c r="G94" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H94" s="17"/>
       <c r="I94" s="35"/>
     </row>
@@ -4366,7 +4396,9 @@
         <v>296</v>
       </c>
       <c r="F95" s="2"/>
-      <c r="G95" s="17"/>
+      <c r="G95" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H95" s="17"/>
       <c r="I95" s="35"/>
     </row>
@@ -4387,7 +4419,9 @@
         <v>302</v>
       </c>
       <c r="F96" s="2"/>
-      <c r="G96" s="18"/>
+      <c r="G96" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H96" s="17"/>
       <c r="I96" s="35"/>
     </row>
@@ -4408,7 +4442,9 @@
         <v>302</v>
       </c>
       <c r="F97" s="2"/>
-      <c r="G97" s="18"/>
+      <c r="G97" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H97" s="17"/>
       <c r="I97" s="35"/>
     </row>
@@ -4429,7 +4465,9 @@
         <v>302</v>
       </c>
       <c r="F98" s="2"/>
-      <c r="G98" s="18"/>
+      <c r="G98" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H98" s="17"/>
       <c r="I98" s="35"/>
     </row>
@@ -4450,7 +4488,9 @@
         <v>302</v>
       </c>
       <c r="F99" s="2"/>
-      <c r="G99" s="18"/>
+      <c r="G99" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H99" s="17"/>
       <c r="I99" s="35"/>
     </row>
@@ -4471,7 +4511,9 @@
         <v>302</v>
       </c>
       <c r="F100" s="2"/>
-      <c r="G100" s="18"/>
+      <c r="G100" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H100" s="17"/>
       <c r="I100" s="35"/>
     </row>
@@ -4492,7 +4534,9 @@
         <v>308</v>
       </c>
       <c r="F101" s="2"/>
-      <c r="G101" s="18"/>
+      <c r="G101" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H101" s="17"/>
       <c r="I101" s="35"/>
     </row>
@@ -4513,7 +4557,9 @@
         <v>310</v>
       </c>
       <c r="F102" s="2"/>
-      <c r="G102" s="18"/>
+      <c r="G102" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H102" s="17"/>
       <c r="I102" s="35"/>
     </row>
@@ -4534,7 +4580,9 @@
         <v>310</v>
       </c>
       <c r="F103" s="2"/>
-      <c r="G103" s="18"/>
+      <c r="G103" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H103" s="17"/>
       <c r="I103" s="35"/>
     </row>
@@ -4555,7 +4603,9 @@
         <v>310</v>
       </c>
       <c r="F104" s="2"/>
-      <c r="G104" s="18"/>
+      <c r="G104" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H104" s="17"/>
       <c r="I104" s="35"/>
     </row>
@@ -4576,7 +4626,9 @@
         <v>310</v>
       </c>
       <c r="F105" s="2"/>
-      <c r="G105" s="18"/>
+      <c r="G105" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H105" s="17"/>
       <c r="I105" s="35"/>
     </row>
@@ -4597,7 +4649,9 @@
         <v>315</v>
       </c>
       <c r="F106" s="2"/>
-      <c r="G106" s="18"/>
+      <c r="G106" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H106" s="17"/>
       <c r="I106" s="35"/>
     </row>
@@ -4618,7 +4672,9 @@
         <v>315</v>
       </c>
       <c r="F107" s="2"/>
-      <c r="G107" s="18"/>
+      <c r="G107" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H107" s="17"/>
       <c r="I107" s="35"/>
     </row>
@@ -4639,7 +4695,9 @@
         <v>315</v>
       </c>
       <c r="F108" s="2"/>
-      <c r="G108" s="18"/>
+      <c r="G108" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H108" s="17"/>
       <c r="I108" s="35"/>
     </row>
@@ -4660,7 +4718,9 @@
         <v>315</v>
       </c>
       <c r="F109" s="2"/>
-      <c r="G109" s="18"/>
+      <c r="G109" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H109" s="17"/>
       <c r="I109" s="35"/>
     </row>
@@ -5779,16 +5839,18 @@
       <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="19"/>
+      <c r="F3" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G3" s="19"/>
       <c r="H3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="33.75">
       <c r="A4" s="15">
         <v>2</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="29">
         <v>1.08</v>
@@ -5799,7 +5861,9 @@
       <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="19"/>
+      <c r="F4" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G4" s="19"/>
       <c r="H4" s="2"/>
     </row>
@@ -5808,7 +5872,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="29">
         <v>13.03</v>
@@ -5819,7 +5883,9 @@
       <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="17"/>
+      <c r="F5" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G5" s="19"/>
       <c r="H5" s="2"/>
     </row>
@@ -5828,7 +5894,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="29">
         <v>19.1</v>
@@ -5839,7 +5905,9 @@
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="17"/>
+      <c r="F6" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G6" s="19"/>
       <c r="H6" s="2"/>
     </row>
@@ -5848,7 +5916,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="29">
         <v>0.16</v>
@@ -5859,7 +5927,9 @@
       <c r="E7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="17"/>
+      <c r="F7" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G7" s="19"/>
       <c r="H7" s="2"/>
     </row>
@@ -5868,7 +5938,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="29">
         <v>14.01</v>
@@ -5879,16 +5949,18 @@
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="17"/>
+      <c r="F8" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G8" s="19"/>
       <c r="H8" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="33.75">
       <c r="A9" s="15">
         <v>7</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="29">
         <v>8.52</v>
@@ -5897,10 +5969,12 @@
         <v>45384</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+      <c r="G9" s="20">
+        <v>1</v>
+      </c>
       <c r="H9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -5908,7 +5982,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="29">
         <v>0.18</v>
@@ -5917,18 +5991,18 @@
         <v>45384</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="35.25">
       <c r="A11" s="15">
         <v>9</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="29">
         <v>8.35</v>
@@ -5937,18 +6011,18 @@
         <v>45384</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
       <c r="H11" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="33.75">
       <c r="A12" s="15">
         <v>10</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="29">
         <v>7.35</v>
@@ -5957,7 +6031,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
@@ -5968,7 +6042,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="29">
         <v>11.4</v>
@@ -5977,7 +6051,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
@@ -5988,7 +6062,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="29">
         <v>11.09</v>
@@ -5997,7 +6071,7 @@
         <v>45384</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="17"/>
@@ -6008,7 +6082,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="29">
         <v>15.16</v>
@@ -6017,7 +6091,7 @@
         <v>45384</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="17"/>
@@ -6028,7 +6102,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="29">
         <v>9.31</v>
@@ -6037,7 +6111,7 @@
         <v>45385</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
@@ -6048,7 +6122,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="29">
         <v>9.16</v>
@@ -6057,7 +6131,7 @@
         <v>45385</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
@@ -6068,7 +6142,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" s="29">
         <v>14.09</v>
@@ -6077,7 +6151,7 @@
         <v>45385</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
@@ -6088,7 +6162,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" s="29">
         <v>14.54</v>
@@ -6097,7 +6171,7 @@
         <v>45385</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
@@ -6108,7 +6182,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="29">
         <v>8.57</v>
@@ -6117,7 +6191,7 @@
         <v>45385</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
@@ -6128,7 +6202,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C21" s="29">
         <v>16.55</v>
@@ -6137,7 +6211,7 @@
         <v>45386</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
@@ -6148,7 +6222,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" s="15">
         <v>8</v>
@@ -6157,7 +6231,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
@@ -6168,7 +6242,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="29">
         <v>4.25</v>
@@ -6177,7 +6251,7 @@
         <v>45386</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
@@ -6188,7 +6262,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24" s="29">
         <v>10.16</v>
@@ -6197,7 +6271,7 @@
         <v>45386</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
@@ -6208,7 +6282,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" s="29">
         <v>24.08</v>
@@ -6217,10 +6291,12 @@
         <v>45386</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+      <c r="G25" s="20">
+        <v>1</v>
+      </c>
       <c r="H25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
@@ -6228,7 +6304,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" s="29">
         <v>0.29</v>
@@ -6237,10 +6313,12 @@
         <v>45387</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+      <c r="G26" s="20">
+        <v>2</v>
+      </c>
       <c r="H26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
@@ -6248,7 +6326,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" s="29">
         <v>24.46</v>
@@ -6257,7 +6335,7 @@
         <v>45387</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
@@ -6268,7 +6346,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C28" s="29">
         <v>0.19</v>
@@ -6277,7 +6355,7 @@
         <v>45387</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
@@ -6288,7 +6366,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C29" s="29">
         <v>15.03</v>
@@ -6297,7 +6375,7 @@
         <v>45387</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
@@ -6308,7 +6386,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="29">
         <v>5.51</v>
@@ -6317,7 +6395,7 @@
         <v>45387</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
@@ -6328,7 +6406,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" s="29">
         <v>8.45</v>
@@ -6337,7 +6415,7 @@
         <v>45387</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
@@ -6348,7 +6426,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C32" s="29">
         <v>0.18</v>
@@ -6357,7 +6435,7 @@
         <v>45387</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
@@ -6368,7 +6446,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" s="29">
         <v>8.36</v>
@@ -6377,7 +6455,7 @@
         <v>45387</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F33" s="17"/>
       <c r="G33" s="17"/>
@@ -6388,7 +6466,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C34" s="29">
         <v>16.52</v>
@@ -6397,7 +6475,7 @@
         <v>45388</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F34" s="17"/>
       <c r="G34" s="17"/>
@@ -6408,7 +6486,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35" s="29">
         <v>13.16</v>
@@ -6417,7 +6495,7 @@
         <v>45388</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F35" s="17"/>
       <c r="G35" s="17"/>
@@ -6428,7 +6506,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C36" s="29">
         <v>17.01</v>
@@ -6437,7 +6515,7 @@
         <v>45388</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F36" s="17"/>
       <c r="G36" s="17"/>
@@ -6448,7 +6526,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C37" s="29">
         <v>15.07</v>
@@ -6457,7 +6535,7 @@
         <v>45388</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
@@ -6468,7 +6546,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38" s="29">
         <v>10.21</v>
@@ -6477,7 +6555,7 @@
         <v>45389</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
@@ -6488,7 +6566,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C39" s="29">
         <v>0.34</v>
@@ -6497,7 +6575,7 @@
         <v>45389</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
@@ -6508,7 +6586,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C40" s="29">
         <v>14.22</v>
@@ -6517,7 +6595,7 @@
         <v>45389</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
@@ -6528,7 +6606,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C41" s="29">
         <v>10.5</v>
@@ -6537,7 +6615,7 @@
         <v>45389</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
@@ -6548,7 +6626,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C42" s="29">
         <v>7.57</v>
@@ -6557,7 +6635,7 @@
         <v>45389</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F42" s="17"/>
       <c r="G42" s="17"/>
@@ -6568,7 +6646,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C43" s="29">
         <v>5.11</v>
@@ -6577,7 +6655,7 @@
         <v>45389</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F43" s="17"/>
       <c r="G43" s="17"/>
@@ -6588,7 +6666,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C44" s="29">
         <v>10.07</v>
@@ -6597,10 +6675,12 @@
         <v>45389</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
+      <c r="G44" s="20">
+        <v>2</v>
+      </c>
       <c r="H44" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="33">
@@ -6608,7 +6688,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C45" s="29">
         <v>7.39</v>
@@ -6617,10 +6697,12 @@
         <v>45390</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
+      <c r="G45" s="20">
+        <v>3</v>
+      </c>
       <c r="H45" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="33">
@@ -6628,7 +6710,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C46" s="29">
         <v>9.22</v>
@@ -6637,7 +6719,7 @@
         <v>45390</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F46" s="17"/>
       <c r="G46" s="17"/>
@@ -6648,7 +6730,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C47" s="29">
         <v>9.29</v>
@@ -6657,7 +6739,7 @@
         <v>45390</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F47" s="17"/>
       <c r="G47" s="17"/>
@@ -6668,7 +6750,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C48" s="29">
         <v>7.16</v>
@@ -6677,7 +6759,7 @@
         <v>45390</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F48" s="17"/>
       <c r="G48" s="17"/>
@@ -6688,7 +6770,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C49" s="29">
         <v>6.1</v>
@@ -6697,7 +6779,7 @@
         <v>45390</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F49" s="17"/>
       <c r="G49" s="17"/>
@@ -6708,7 +6790,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="29">
         <v>6.36</v>
@@ -6717,7 +6799,7 @@
         <v>45390</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F50" s="17"/>
       <c r="G50" s="17"/>
@@ -6728,7 +6810,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C51" s="29">
         <v>7.32</v>
@@ -6737,7 +6819,7 @@
         <v>45390</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F51" s="17"/>
       <c r="G51" s="17"/>
@@ -6748,7 +6830,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C52" s="29">
         <v>6.15</v>
@@ -6757,7 +6839,7 @@
         <v>45390</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
@@ -6768,7 +6850,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C53" s="29">
         <v>6.07</v>
@@ -6777,7 +6859,7 @@
         <v>45391</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
@@ -6788,7 +6870,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C54" s="29">
         <v>5.04</v>
@@ -6797,7 +6879,7 @@
         <v>45391</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
@@ -6808,7 +6890,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C55" s="29">
         <v>9.41</v>
@@ -6817,7 +6899,7 @@
         <v>45391</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F55" s="17"/>
       <c r="G55" s="17"/>
@@ -6828,7 +6910,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C56" s="29">
         <v>6.12</v>
@@ -6837,7 +6919,7 @@
         <v>45391</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
@@ -6848,7 +6930,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C57" s="29">
         <v>4.11</v>
@@ -6857,7 +6939,7 @@
         <v>45391</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
@@ -6868,7 +6950,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C58" s="29">
         <v>9.3</v>
@@ -6877,7 +6959,7 @@
         <v>45391</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
@@ -6888,7 +6970,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C59" s="29">
         <v>8.06</v>
@@ -6897,7 +6979,7 @@
         <v>45391</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F59" s="17"/>
       <c r="G59" s="17"/>
@@ -6908,7 +6990,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C60" s="29">
         <v>10.35</v>
@@ -6917,7 +6999,7 @@
         <v>45391</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
@@ -6928,7 +7010,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C61" s="29">
         <v>9.22</v>
@@ -6937,7 +7019,7 @@
         <v>45392</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F61" s="17"/>
       <c r="G61" s="17"/>
@@ -6948,7 +7030,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C62" s="29">
         <v>8.05</v>
@@ -6957,7 +7039,7 @@
         <v>45392</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F62" s="17"/>
       <c r="G62" s="17"/>
@@ -6968,7 +7050,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C63" s="29">
         <v>14.14</v>
@@ -6977,7 +7059,7 @@
         <v>45392</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F63" s="17"/>
       <c r="G63" s="17"/>
@@ -6988,7 +7070,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C64" s="29">
         <v>14.38</v>
@@ -6997,7 +7079,7 @@
         <v>45392</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F64" s="17"/>
       <c r="G64" s="17"/>
@@ -7008,7 +7090,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C65" s="29">
         <v>13.16</v>
@@ -7017,10 +7099,12 @@
         <v>45392</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
+      <c r="G65" s="20">
+        <v>3</v>
+      </c>
       <c r="H65" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
@@ -7028,7 +7112,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C66" s="29">
         <v>5.57</v>
@@ -7037,10 +7121,12 @@
         <v>45393</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
+      <c r="G66" s="20">
+        <v>4</v>
+      </c>
       <c r="H66" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -7048,7 +7134,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C67" s="29">
         <v>12.55</v>
@@ -7057,7 +7143,7 @@
         <v>45393</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
@@ -7068,7 +7154,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C68" s="29">
         <v>0.15</v>
@@ -7077,7 +7163,7 @@
         <v>45393</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
@@ -7134,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C72" s="29">
         <v>4.13</v>
@@ -7143,7 +7229,7 @@
         <v>45394</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F72" s="19"/>
       <c r="G72" s="19"/>
@@ -7154,7 +7240,7 @@
         <v>2</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C73" s="29">
         <v>6.33</v>
@@ -7163,7 +7249,7 @@
         <v>45394</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F73" s="17"/>
       <c r="G73" s="19"/>
@@ -7174,7 +7260,7 @@
         <v>3</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C74" s="29">
         <v>7.05</v>
@@ -7183,7 +7269,7 @@
         <v>45394</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F74" s="17"/>
       <c r="G74" s="19"/>
@@ -7194,7 +7280,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C75" s="29">
         <v>5.05</v>
@@ -7203,7 +7289,7 @@
         <v>45394</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F75" s="17"/>
       <c r="G75" s="19"/>
@@ -7214,7 +7300,7 @@
         <v>5</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C76" s="29">
         <v>2.29</v>
@@ -7223,7 +7309,7 @@
         <v>45394</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F76" s="17"/>
       <c r="G76" s="19"/>
@@ -7234,7 +7320,7 @@
         <v>6</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C77" s="29">
         <v>4.42</v>
@@ -7243,7 +7329,7 @@
         <v>45394</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F77" s="17"/>
       <c r="G77" s="19"/>
@@ -7254,7 +7340,7 @@
         <v>7</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C78" s="29">
         <v>11.17</v>
@@ -7263,7 +7349,7 @@
         <v>45394</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F78" s="17"/>
       <c r="G78" s="19"/>
@@ -7274,7 +7360,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C79" s="29">
         <v>6.17</v>
@@ -7283,7 +7369,7 @@
         <v>45394</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F79" s="17"/>
       <c r="G79" s="19"/>
@@ -7294,7 +7380,7 @@
         <v>9</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C80" s="29">
         <v>9.02</v>
@@ -7303,7 +7389,7 @@
         <v>45394</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F80" s="17"/>
       <c r="G80" s="19"/>
@@ -7314,7 +7400,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C81" s="29">
         <v>8.02</v>
@@ -7323,7 +7409,7 @@
         <v>45394</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F81" s="17"/>
       <c r="G81" s="19"/>
@@ -7334,7 +7420,7 @@
         <v>11</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C82" s="29">
         <v>9.4</v>
@@ -7343,7 +7429,7 @@
         <v>45395</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F82" s="17"/>
       <c r="G82" s="19"/>
@@ -7354,7 +7440,7 @@
         <v>12</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C83" s="29">
         <v>8.21</v>
@@ -7363,7 +7449,7 @@
         <v>45395</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F83" s="17"/>
       <c r="G83" s="19"/>
@@ -7374,7 +7460,7 @@
         <v>13</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C84" s="29">
         <v>9.29</v>
@@ -7383,7 +7469,7 @@
         <v>45395</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F84" s="17"/>
       <c r="G84" s="19"/>
@@ -7394,7 +7480,7 @@
         <v>14</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C85" s="29">
         <v>15.19</v>
@@ -7403,7 +7489,7 @@
         <v>45395</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F85" s="17"/>
       <c r="G85" s="19"/>
@@ -7414,7 +7500,7 @@
         <v>15</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C86" s="29">
         <v>6.57</v>
@@ -7423,7 +7509,7 @@
         <v>45395</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F86" s="17"/>
       <c r="G86" s="19"/>
@@ -7434,7 +7520,7 @@
         <v>16</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C87" s="29">
         <v>6.18</v>
@@ -7443,7 +7529,7 @@
         <v>45395</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="19"/>
@@ -7454,7 +7540,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C88" s="29">
         <v>5.48</v>
@@ -7463,7 +7549,7 @@
         <v>45395</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
@@ -7474,7 +7560,7 @@
         <v>18</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C89" s="29">
         <v>7.1</v>
@@ -7483,7 +7569,7 @@
         <v>45396</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F89" s="17"/>
       <c r="G89" s="17"/>
@@ -7494,7 +7580,7 @@
         <v>19</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C90" s="29">
         <v>6.34</v>
@@ -7503,7 +7589,7 @@
         <v>45396</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F90" s="17"/>
       <c r="G90" s="17"/>
@@ -7514,7 +7600,7 @@
         <v>20</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C91" s="29">
         <v>7.14</v>
@@ -7523,7 +7609,7 @@
         <v>45396</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F91" s="17"/>
       <c r="G91" s="17"/>
@@ -7534,7 +7620,7 @@
         <v>21</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C92" s="29">
         <v>9.45</v>
@@ -7543,7 +7629,7 @@
         <v>45396</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F92" s="17"/>
       <c r="G92" s="17"/>
@@ -7554,7 +7640,7 @@
         <v>22</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C93" s="29">
         <v>7.12</v>
@@ -7563,7 +7649,7 @@
         <v>45396</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F93" s="17"/>
       <c r="G93" s="17"/>
@@ -7574,7 +7660,7 @@
         <v>23</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C94" s="29">
         <v>5.46</v>
@@ -7583,7 +7669,7 @@
         <v>45396</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F94" s="17"/>
       <c r="G94" s="17"/>
@@ -7594,7 +7680,7 @@
         <v>24</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C95" s="29">
         <v>13.51</v>
@@ -7603,10 +7689,12 @@
         <v>45396</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F95" s="17"/>
-      <c r="G95" s="17"/>
+      <c r="G95" s="20">
+        <v>4</v>
+      </c>
       <c r="H95" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
@@ -7614,7 +7702,7 @@
         <v>25</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C96" s="29">
         <v>12.21</v>
@@ -7623,10 +7711,12 @@
         <v>45397</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F96" s="17"/>
-      <c r="G96" s="17"/>
+      <c r="G96" s="20">
+        <v>5</v>
+      </c>
       <c r="H96" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
@@ -7634,7 +7724,7 @@
         <v>26</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C97" s="29">
         <v>8.45</v>
@@ -7643,7 +7733,7 @@
         <v>45397</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F97" s="17"/>
       <c r="G97" s="17"/>
@@ -7654,7 +7744,7 @@
         <v>27</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C98" s="29">
         <v>12.35</v>
@@ -7663,7 +7753,7 @@
         <v>45397</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F98" s="17"/>
       <c r="G98" s="17"/>
@@ -7674,7 +7764,7 @@
         <v>28</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C99" s="29">
         <v>5.39</v>
@@ -7683,7 +7773,7 @@
         <v>45397</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F99" s="17"/>
       <c r="G99" s="17"/>
@@ -7694,7 +7784,7 @@
         <v>29</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C100" s="29">
         <v>9.59</v>
@@ -7703,7 +7793,7 @@
         <v>45397</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F100" s="17"/>
       <c r="G100" s="17"/>
@@ -7714,7 +7804,7 @@
         <v>30</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C101" s="29">
         <v>9.57</v>
@@ -7723,7 +7813,7 @@
         <v>45397</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F101" s="17"/>
       <c r="G101" s="17"/>
@@ -7734,7 +7824,7 @@
         <v>31</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C102" s="29">
         <v>17.55</v>
@@ -7743,7 +7833,7 @@
         <v>45398</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F102" s="17"/>
       <c r="G102" s="17"/>
@@ -7754,7 +7844,7 @@
         <v>32</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C103" s="29">
         <v>12.14</v>
@@ -7763,7 +7853,7 @@
         <v>45398</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F103" s="17"/>
       <c r="G103" s="17"/>
@@ -7774,7 +7864,7 @@
         <v>33</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C104" s="29">
         <v>8.33</v>
@@ -7783,7 +7873,7 @@
         <v>45398</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F104" s="17"/>
       <c r="G104" s="17"/>
@@ -7794,7 +7884,7 @@
         <v>34</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C105" s="29">
         <v>7.41</v>
@@ -7803,7 +7893,7 @@
         <v>45398</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F105" s="17"/>
       <c r="G105" s="17"/>
@@ -7814,7 +7904,7 @@
         <v>35</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C106" s="29">
         <v>8.54</v>
@@ -7823,7 +7913,7 @@
         <v>45398</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F106" s="17"/>
       <c r="G106" s="17"/>
@@ -7834,7 +7924,7 @@
         <v>36</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C107" s="29">
         <v>16.08</v>
@@ -7843,7 +7933,7 @@
         <v>45399</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F107" s="17"/>
       <c r="G107" s="17"/>
@@ -7854,7 +7944,7 @@
         <v>37</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C108" s="29">
         <v>7.01</v>
@@ -7863,7 +7953,7 @@
         <v>45399</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F108" s="17"/>
       <c r="G108" s="17"/>
@@ -7874,7 +7964,7 @@
         <v>38</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C109" s="29">
         <v>7.29</v>
@@ -7883,7 +7973,7 @@
         <v>45399</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F109" s="17"/>
       <c r="G109" s="17"/>
@@ -7894,7 +7984,7 @@
         <v>39</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C110" s="29">
         <v>16.33</v>
@@ -7903,7 +7993,7 @@
         <v>45399</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F110" s="17"/>
       <c r="G110" s="17"/>
@@ -7914,7 +8004,7 @@
         <v>40</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C111" s="29">
         <v>10.58</v>
@@ -7923,10 +8013,12 @@
         <v>45399</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F111" s="17"/>
-      <c r="G111" s="17"/>
+      <c r="G111" s="20">
+        <v>5</v>
+      </c>
       <c r="H111" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
@@ -7934,7 +8026,7 @@
         <v>41</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C112" s="29">
         <v>7.33</v>
@@ -7943,10 +8035,12 @@
         <v>45400</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F112" s="17"/>
-      <c r="G112" s="17"/>
+      <c r="G112" s="20">
+        <v>6</v>
+      </c>
       <c r="H112" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
@@ -7954,7 +8048,7 @@
         <v>42</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C113" s="29">
         <v>17.3</v>
@@ -7963,7 +8057,7 @@
         <v>45400</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F113" s="17"/>
       <c r="G113" s="17"/>
@@ -7974,7 +8068,7 @@
         <v>43</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C114" s="29">
         <v>16.01</v>
@@ -7983,7 +8077,7 @@
         <v>45400</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F114" s="17"/>
       <c r="G114" s="17"/>
@@ -7994,7 +8088,7 @@
         <v>44</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C115" s="29">
         <v>10.06</v>
@@ -8003,7 +8097,7 @@
         <v>45400</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F115" s="17"/>
       <c r="G115" s="17"/>
@@ -8014,7 +8108,7 @@
         <v>45</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C116" s="29">
         <v>7.13</v>
@@ -8023,7 +8117,7 @@
         <v>45400</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
@@ -8034,7 +8128,7 @@
         <v>46</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C117" s="29">
         <v>9.06</v>
@@ -8043,7 +8137,7 @@
         <v>45401</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F117" s="17"/>
       <c r="G117" s="17"/>
@@ -8054,7 +8148,7 @@
         <v>47</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C118" s="29">
         <v>10.49</v>
@@ -8063,7 +8157,7 @@
         <v>45401</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F118" s="17"/>
       <c r="G118" s="17"/>
@@ -8074,7 +8168,7 @@
         <v>48</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C119" s="29">
         <v>8.08</v>
@@ -8083,7 +8177,7 @@
         <v>45401</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F119" s="17"/>
       <c r="G119" s="17"/>
@@ -8094,7 +8188,7 @@
         <v>49</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C120" s="29">
         <v>13.4</v>
@@ -8103,7 +8197,7 @@
         <v>45401</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F120" s="17"/>
       <c r="G120" s="17"/>
@@ -8114,7 +8208,7 @@
         <v>50</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C121" s="29">
         <v>12.54</v>
@@ -8123,7 +8217,7 @@
         <v>45401</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F121" s="17"/>
       <c r="G121" s="17"/>
@@ -8134,7 +8228,7 @@
         <v>51</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C122" s="29">
         <v>9.57</v>
@@ -8143,7 +8237,7 @@
         <v>45401</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F122" s="17"/>
       <c r="G122" s="17"/>
@@ -8154,7 +8248,7 @@
         <v>52</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C123" s="29">
         <v>7.29</v>
@@ -8163,7 +8257,7 @@
         <v>45402</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F123" s="17"/>
       <c r="G123" s="17"/>
@@ -8174,7 +8268,7 @@
         <v>53</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C124" s="29">
         <v>10.29</v>
@@ -8183,7 +8277,7 @@
         <v>45402</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F124" s="17"/>
       <c r="G124" s="17"/>
@@ -8194,7 +8288,7 @@
         <v>54</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C125" s="29">
         <v>9.01</v>
@@ -8203,7 +8297,7 @@
         <v>45402</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F125" s="17"/>
       <c r="G125" s="17"/>
@@ -8214,7 +8308,7 @@
         <v>55</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C126" s="29">
         <v>7.38</v>
@@ -8223,7 +8317,7 @@
         <v>45402</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F126" s="17"/>
       <c r="G126" s="17"/>
@@ -8234,7 +8328,7 @@
         <v>56</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C127" s="29">
         <v>9.29</v>
@@ -8243,7 +8337,7 @@
         <v>45402</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F127" s="17"/>
       <c r="G127" s="17"/>
@@ -8254,7 +8348,7 @@
         <v>57</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C128" s="29">
         <v>23.01</v>
@@ -8263,10 +8357,12 @@
         <v>45402</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F128" s="17"/>
-      <c r="G128" s="17"/>
+      <c r="G128" s="20">
+        <v>6</v>
+      </c>
       <c r="H128" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
@@ -8274,7 +8370,7 @@
         <v>58</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C129" s="29">
         <v>15.51</v>
@@ -8283,10 +8379,12 @@
         <v>45403</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F129" s="17"/>
-      <c r="G129" s="17"/>
+      <c r="G129" s="20">
+        <v>7</v>
+      </c>
       <c r="H129" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
@@ -8294,7 +8392,7 @@
         <v>59</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C130" s="29">
         <v>9.19</v>
@@ -8303,7 +8401,7 @@
         <v>45403</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F130" s="17"/>
       <c r="G130" s="17"/>
@@ -8314,7 +8412,7 @@
         <v>60</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C131" s="29">
         <v>9.27</v>
@@ -8323,7 +8421,7 @@
         <v>45403</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F131" s="17"/>
       <c r="G131" s="17"/>
@@ -8334,7 +8432,7 @@
         <v>61</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C132" s="29">
         <v>5.56</v>
@@ -8343,7 +8441,7 @@
         <v>45403</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F132" s="17"/>
       <c r="G132" s="17"/>
@@ -8354,7 +8452,7 @@
         <v>62</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C133" s="29">
         <v>8.48</v>
@@ -8363,7 +8461,7 @@
         <v>45403</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F133" s="17"/>
       <c r="G133" s="17"/>
@@ -8374,7 +8472,7 @@
         <v>63</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C134" s="29">
         <v>8.42</v>
@@ -8383,7 +8481,7 @@
         <v>45403</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F134" s="17"/>
       <c r="G134" s="17"/>
@@ -8394,7 +8492,7 @@
         <v>64</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C135" s="29">
         <v>10.04</v>
@@ -8403,7 +8501,7 @@
         <v>45404</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F135" s="17"/>
       <c r="G135" s="17"/>
@@ -8414,7 +8512,7 @@
         <v>65</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C136" s="29">
         <v>8.35</v>
@@ -8423,7 +8521,7 @@
         <v>45404</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F136" s="17"/>
       <c r="G136" s="17"/>
@@ -8434,7 +8532,7 @@
         <v>66</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C137" s="29">
         <v>19.21</v>
@@ -8443,7 +8541,7 @@
         <v>45404</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F137" s="17"/>
       <c r="G137" s="17"/>
@@ -8454,7 +8552,7 @@
         <v>67</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C138" s="29">
         <v>12.06</v>
@@ -8463,7 +8561,7 @@
         <v>45404</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F138" s="17"/>
       <c r="G138" s="17"/>
@@ -8474,7 +8572,7 @@
         <v>68</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C139" s="29">
         <v>12.52</v>
@@ -8483,7 +8581,7 @@
         <v>45404</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F139" s="17"/>
       <c r="G139" s="17"/>
@@ -8494,7 +8592,7 @@
         <v>69</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C140" s="29">
         <v>14.16</v>
@@ -8503,7 +8601,7 @@
         <v>45405</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F140" s="17"/>
       <c r="G140" s="17"/>
@@ -8514,7 +8612,7 @@
         <v>70</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C141" s="29">
         <v>12.49</v>
@@ -8523,7 +8621,7 @@
         <v>45405</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F141" s="17"/>
       <c r="G141" s="17"/>
@@ -8534,7 +8632,7 @@
         <v>71</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C142" s="29">
         <v>3.5</v>
@@ -8543,7 +8641,7 @@
         <v>45405</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F142" s="17"/>
       <c r="G142" s="17"/>
@@ -8554,7 +8652,7 @@
         <v>72</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C143" s="29">
         <v>7.54</v>
@@ -8563,7 +8661,7 @@
         <v>45405</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F143" s="17"/>
       <c r="G143" s="17"/>
@@ -8574,7 +8672,7 @@
         <v>73</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C144" s="29">
         <v>6.43</v>
@@ -8583,7 +8681,7 @@
         <v>45405</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F144" s="17"/>
       <c r="G144" s="17"/>
@@ -8594,7 +8692,7 @@
         <v>74</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C145" s="29">
         <v>9.41</v>
@@ -8603,7 +8701,7 @@
         <v>45405</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F145" s="17"/>
       <c r="G145" s="17"/>
@@ -8614,7 +8712,7 @@
         <v>75</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C146" s="29">
         <v>19.37</v>
@@ -8623,10 +8721,12 @@
         <v>45406</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F146" s="17"/>
-      <c r="G146" s="17"/>
+      <c r="G146" s="20">
+        <v>7</v>
+      </c>
       <c r="H146" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
@@ -8634,7 +8734,7 @@
         <v>76</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C147" s="29">
         <v>0.56</v>
@@ -8643,7 +8743,7 @@
         <v>45406</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F147" s="17"/>
       <c r="G147" s="17"/>
@@ -8654,16 +8754,16 @@
         <v>77</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C148" s="32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D148" s="18">
         <v>45407</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F148" s="17"/>
       <c r="G148" s="17"/>
@@ -8674,16 +8774,16 @@
         <v>78</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C149" s="32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D149" s="18">
         <v>45408</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F149" s="17"/>
       <c r="G149" s="17"/>
@@ -8694,16 +8794,16 @@
         <v>79</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C150" s="32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D150" s="18">
         <v>45409</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F150" s="17"/>
       <c r="G150" s="17"/>
@@ -8714,16 +8814,16 @@
         <v>80</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C151" s="32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D151" s="18">
         <v>45410</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F151" s="17"/>
       <c r="G151" s="17"/>
@@ -8734,16 +8834,16 @@
         <v>81</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C152" s="32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D152" s="18">
         <v>45411</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F152" s="17"/>
       <c r="G152" s="17"/>
@@ -8754,16 +8854,16 @@
         <v>82</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C153" s="32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D153" s="18">
         <v>45412</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F153" s="17"/>
       <c r="G153" s="17"/>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="363">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -1120,7 +1120,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1168,6 +1168,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1226,7 +1232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1315,11 +1321,17 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1329,6 +1341,9 @@
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1372,7 +1387,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1686,11 +1701,11 @@
     <col min="1" max="1" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="50" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="47" width="38.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="53" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="50" width="38.86214285714286" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="23" width="7.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="47" width="23.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="47" width="41.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="50" width="23.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="50" width="41.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -1698,10 +1713,10 @@
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
       <c r="D1" s="21"/>
-      <c r="E1" s="35"/>
+      <c r="E1" s="38"/>
       <c r="F1" s="21"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="22"/>
@@ -1713,7 +1728,7 @@
       <c r="E2" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="51" t="s">
         <v>320</v>
       </c>
       <c r="G2" s="14" t="s">
@@ -1813,7 +1828,7 @@
       <c r="G7" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="H7" s="49" t="s">
+      <c r="H7" s="52" t="s">
         <v>329</v>
       </c>
     </row>
@@ -1959,7 +1974,7 @@
       <c r="G15" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H15" s="49" t="s">
+      <c r="H15" s="52" t="s">
         <v>340</v>
       </c>
     </row>
@@ -1979,7 +1994,7 @@
       <c r="G16" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="52" t="s">
         <v>342</v>
       </c>
     </row>
@@ -1999,7 +2014,7 @@
       <c r="G17" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H17" s="49" t="s">
+      <c r="H17" s="52" t="s">
         <v>344</v>
       </c>
     </row>
@@ -2034,82 +2049,82 @@
       <c r="F19" s="21">
         <v>1</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="48">
+      <c r="D20" s="51">
         <v>18</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="38" t="s">
         <v>347</v>
       </c>
       <c r="F20" s="21">
         <v>2</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="H20" s="35"/>
+      <c r="H20" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="48">
+      <c r="D21" s="51">
         <v>19</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="38" t="s">
         <v>348</v>
       </c>
       <c r="F21" s="21">
         <v>1</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G21" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="H21" s="35"/>
+      <c r="H21" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="48">
+      <c r="D22" s="51">
         <v>20</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="38" t="s">
         <v>349</v>
       </c>
       <c r="F22" s="21">
         <v>1</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="H22" s="35"/>
+      <c r="H22" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
-      <c r="D23" s="48">
+      <c r="D23" s="51">
         <v>21</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="38" t="s">
         <v>350</v>
       </c>
       <c r="F23" s="21">
         <v>1</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="38" t="s">
         <v>351</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H23" s="38" t="s">
         <v>352</v>
       </c>
     </row>
@@ -2117,19 +2132,19 @@
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="48">
+      <c r="D24" s="51">
         <v>22</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="38" t="s">
         <v>353</v>
       </c>
       <c r="F24" s="21">
         <v>1</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="38" t="s">
         <v>331</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="38" t="s">
         <v>354</v>
       </c>
     </row>
@@ -2137,35 +2152,35 @@
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
-      <c r="D25" s="48">
+      <c r="D25" s="51">
         <v>23</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="E25" s="38" t="s">
         <v>355</v>
       </c>
       <c r="F25" s="21">
         <v>1</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="H25" s="35"/>
+      <c r="H25" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
-      <c r="D26" s="48">
+      <c r="D26" s="51">
         <v>24</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="38" t="s">
         <v>356</v>
       </c>
       <c r="F26" s="21">
         <v>1</v>
       </c>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25">
       <c r="A27" s="22"/>
@@ -2180,7 +2195,7 @@
       <c r="F27" s="21">
         <v>1</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="38" t="s">
         <v>331</v>
       </c>
       <c r="H27" s="17" t="s">
@@ -2191,19 +2206,19 @@
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
-      <c r="D28" s="48">
+      <c r="D28" s="51">
         <v>26</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="38" t="s">
         <v>359</v>
       </c>
       <c r="F28" s="21">
         <v>1</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="38" t="s">
         <v>339</v>
       </c>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="38" t="s">
         <v>360</v>
       </c>
     </row>
@@ -2211,19 +2226,19 @@
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
-      <c r="D29" s="48">
+      <c r="D29" s="51">
         <v>27</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="E29" s="38" t="s">
         <v>361</v>
       </c>
       <c r="F29" s="21">
         <v>1</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="38" t="s">
         <v>339</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H29" s="38" t="s">
         <v>362</v>
       </c>
     </row>
@@ -2231,61 +2246,61 @@
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="35"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="38"/>
       <c r="F30" s="21"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="35"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="38"/>
       <c r="F31" s="21"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="35"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="38"/>
       <c r="F32" s="21"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="35"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="38"/>
       <c r="F33" s="21"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="35"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="38"/>
       <c r="F34" s="21"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="35"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="38"/>
       <c r="F35" s="21"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20.25">
       <c r="A36" s="22"/>
@@ -2294,7 +2309,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="17"/>
       <c r="F36" s="21"/>
-      <c r="G36" s="35"/>
+      <c r="G36" s="38"/>
       <c r="H36" s="17"/>
     </row>
   </sheetData>
@@ -2311,97 +2326,97 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="23" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="47" width="60.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="33" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="34" width="7.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="50" width="60.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="35" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="36" width="7.719285714285714" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="47" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="47" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="50" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="50" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="50" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="21"/>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="32"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="47.25">
       <c r="A2" s="21">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="21">
         <v>2</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="21">
         <v>3</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="21"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="35"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="13" t="s">
@@ -2428,7 +2443,7 @@
       <c r="H7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="35"/>
+      <c r="I7" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="33.75">
       <c r="A8" s="15">
@@ -2451,7 +2466,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="17"/>
-      <c r="I8" s="35"/>
+      <c r="I8" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="15">
@@ -2474,7 +2489,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="17"/>
-      <c r="I9" s="35"/>
+      <c r="I9" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="15">
@@ -2497,7 +2512,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="17"/>
-      <c r="I10" s="40" t="s">
+      <c r="I10" s="43" t="s">
         <v>201</v>
       </c>
     </row>
@@ -2522,7 +2537,7 @@
         <v>16</v>
       </c>
       <c r="H11" s="17"/>
-      <c r="I11" s="35"/>
+      <c r="I11" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="15">
@@ -2545,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="17"/>
-      <c r="I12" s="35"/>
+      <c r="I12" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="15">
@@ -2568,7 +2583,7 @@
         <v>16</v>
       </c>
       <c r="H13" s="17"/>
-      <c r="I13" s="35"/>
+      <c r="I13" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="15">
@@ -2591,7 +2606,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="17"/>
-      <c r="I14" s="35"/>
+      <c r="I14" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="15">
@@ -2614,7 +2629,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="17"/>
-      <c r="I15" s="35"/>
+      <c r="I15" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="15">
@@ -2637,7 +2652,7 @@
         <v>16</v>
       </c>
       <c r="H16" s="17"/>
-      <c r="I16" s="35"/>
+      <c r="I16" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="15">
@@ -2660,7 +2675,7 @@
         <v>16</v>
       </c>
       <c r="H17" s="17"/>
-      <c r="I17" s="35"/>
+      <c r="I17" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="15">
@@ -2683,7 +2698,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="17"/>
-      <c r="I18" s="35"/>
+      <c r="I18" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="15">
@@ -2706,7 +2721,7 @@
         <v>16</v>
       </c>
       <c r="H19" s="17"/>
-      <c r="I19" s="35"/>
+      <c r="I19" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="33.75">
       <c r="A20" s="15">
@@ -2729,7 +2744,7 @@
         <v>16</v>
       </c>
       <c r="H20" s="17"/>
-      <c r="I20" s="35"/>
+      <c r="I20" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="15">
@@ -2752,7 +2767,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="17"/>
-      <c r="I21" s="35"/>
+      <c r="I21" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="15">
@@ -2775,7 +2790,7 @@
         <v>16</v>
       </c>
       <c r="H22" s="17"/>
-      <c r="I22" s="35"/>
+      <c r="I22" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="15">
@@ -2798,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="H23" s="17"/>
-      <c r="I23" s="35"/>
+      <c r="I23" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="15">
@@ -2821,7 +2836,7 @@
         <v>16</v>
       </c>
       <c r="H24" s="17"/>
-      <c r="I24" s="35"/>
+      <c r="I24" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="15">
@@ -2844,7 +2859,7 @@
         <v>16</v>
       </c>
       <c r="H25" s="17"/>
-      <c r="I25" s="35"/>
+      <c r="I25" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="15">
@@ -2867,7 +2882,7 @@
         <v>16</v>
       </c>
       <c r="H26" s="17"/>
-      <c r="I26" s="35"/>
+      <c r="I26" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="33.75">
       <c r="A27" s="15">
@@ -2890,7 +2905,7 @@
         <v>16</v>
       </c>
       <c r="H27" s="17"/>
-      <c r="I27" s="35"/>
+      <c r="I27" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="15">
@@ -2913,7 +2928,7 @@
         <v>16</v>
       </c>
       <c r="H28" s="17"/>
-      <c r="I28" s="35"/>
+      <c r="I28" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="15">
@@ -2936,7 +2951,7 @@
         <v>16</v>
       </c>
       <c r="H29" s="17"/>
-      <c r="I29" s="35"/>
+      <c r="I29" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="15">
@@ -2959,7 +2974,7 @@
         <v>16</v>
       </c>
       <c r="H30" s="17"/>
-      <c r="I30" s="35"/>
+      <c r="I30" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="15">
@@ -2982,7 +2997,7 @@
         <v>16</v>
       </c>
       <c r="H31" s="17"/>
-      <c r="I31" s="35"/>
+      <c r="I31" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="15">
@@ -3005,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="H32" s="17"/>
-      <c r="I32" s="35"/>
+      <c r="I32" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="15">
@@ -3028,7 +3043,7 @@
         <v>16</v>
       </c>
       <c r="H33" s="17"/>
-      <c r="I33" s="35"/>
+      <c r="I33" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="15">
@@ -3051,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="H34" s="17"/>
-      <c r="I34" s="35"/>
+      <c r="I34" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="33.75">
       <c r="A35" s="15">
@@ -3074,7 +3089,7 @@
         <v>16</v>
       </c>
       <c r="H35" s="17"/>
-      <c r="I35" s="35"/>
+      <c r="I35" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="15">
@@ -3097,7 +3112,7 @@
         <v>16</v>
       </c>
       <c r="H36" s="17"/>
-      <c r="I36" s="35"/>
+      <c r="I36" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="15">
@@ -3120,7 +3135,7 @@
         <v>16</v>
       </c>
       <c r="H37" s="17"/>
-      <c r="I37" s="35"/>
+      <c r="I37" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="15">
@@ -3143,7 +3158,7 @@
         <v>16</v>
       </c>
       <c r="H38" s="17"/>
-      <c r="I38" s="35"/>
+      <c r="I38" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="33.75">
       <c r="A39" s="15">
@@ -3166,7 +3181,7 @@
         <v>16</v>
       </c>
       <c r="H39" s="17"/>
-      <c r="I39" s="35"/>
+      <c r="I39" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="15">
@@ -3189,7 +3204,7 @@
         <v>16</v>
       </c>
       <c r="H40" s="17"/>
-      <c r="I40" s="35"/>
+      <c r="I40" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="15">
@@ -3212,7 +3227,7 @@
         <v>16</v>
       </c>
       <c r="H41" s="17"/>
-      <c r="I41" s="35"/>
+      <c r="I41" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="15">
@@ -3235,7 +3250,7 @@
         <v>16</v>
       </c>
       <c r="H42" s="17"/>
-      <c r="I42" s="35"/>
+      <c r="I42" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="15">
@@ -3258,7 +3273,7 @@
         <v>16</v>
       </c>
       <c r="H43" s="17"/>
-      <c r="I43" s="35"/>
+      <c r="I43" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20.25">
       <c r="A44" s="15">
@@ -3281,18 +3296,18 @@
         <v>16</v>
       </c>
       <c r="H44" s="17"/>
-      <c r="I44" s="35"/>
+      <c r="I44" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="21"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="31"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="32"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A46" s="11" t="s">
@@ -3332,7 +3347,7 @@
       <c r="H47" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I47" s="35"/>
+      <c r="I47" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="33.75">
       <c r="A48" s="15">
@@ -3355,7 +3370,7 @@
         <v>16</v>
       </c>
       <c r="H48" s="17"/>
-      <c r="I48" s="35"/>
+      <c r="I48" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="15">
@@ -3378,7 +3393,7 @@
         <v>16</v>
       </c>
       <c r="H49" s="17"/>
-      <c r="I49" s="35"/>
+      <c r="I49" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="15">
@@ -3401,7 +3416,7 @@
         <v>16</v>
       </c>
       <c r="H50" s="17"/>
-      <c r="I50" s="35"/>
+      <c r="I50" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
       <c r="A51" s="15">
@@ -3424,7 +3439,7 @@
         <v>16</v>
       </c>
       <c r="H51" s="17"/>
-      <c r="I51" s="35"/>
+      <c r="I51" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="15">
@@ -3447,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="H52" s="17"/>
-      <c r="I52" s="35"/>
+      <c r="I52" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="15">
@@ -3470,7 +3485,7 @@
         <v>16</v>
       </c>
       <c r="H53" s="17"/>
-      <c r="I53" s="35"/>
+      <c r="I53" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="15">
@@ -3493,7 +3508,7 @@
         <v>16</v>
       </c>
       <c r="H54" s="17"/>
-      <c r="I54" s="35"/>
+      <c r="I54" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
       <c r="A55" s="15">
@@ -3516,7 +3531,7 @@
         <v>16</v>
       </c>
       <c r="H55" s="17"/>
-      <c r="I55" s="35"/>
+      <c r="I55" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
       <c r="A56" s="15">
@@ -3539,7 +3554,7 @@
         <v>16</v>
       </c>
       <c r="H56" s="17"/>
-      <c r="I56" s="35"/>
+      <c r="I56" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="15">
@@ -3562,7 +3577,7 @@
         <v>16</v>
       </c>
       <c r="H57" s="17"/>
-      <c r="I57" s="35"/>
+      <c r="I57" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="33.75">
       <c r="A58" s="15">
@@ -3585,7 +3600,7 @@
         <v>16</v>
       </c>
       <c r="H58" s="17"/>
-      <c r="I58" s="35"/>
+      <c r="I58" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
       <c r="A59" s="15">
@@ -3608,7 +3623,7 @@
         <v>16</v>
       </c>
       <c r="H59" s="17"/>
-      <c r="I59" s="35"/>
+      <c r="I59" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="15">
@@ -3631,7 +3646,7 @@
         <v>16</v>
       </c>
       <c r="H60" s="17"/>
-      <c r="I60" s="35"/>
+      <c r="I60" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="15">
@@ -3654,7 +3669,7 @@
         <v>16</v>
       </c>
       <c r="H61" s="17"/>
-      <c r="I61" s="35"/>
+      <c r="I61" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="20.25">
       <c r="A62" s="15">
@@ -3677,13 +3692,13 @@
         <v>16</v>
       </c>
       <c r="H62" s="17"/>
-      <c r="I62" s="35"/>
+      <c r="I62" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A63" s="41"/>
+      <c r="A63" s="44"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="42"/>
-      <c r="D63" s="43"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="46"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -3728,7 +3743,7 @@
       <c r="H65" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I65" s="35"/>
+      <c r="I65" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="15">
@@ -3751,7 +3766,7 @@
         <v>16</v>
       </c>
       <c r="H66" s="17"/>
-      <c r="I66" s="35"/>
+      <c r="I66" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="33.75">
       <c r="A67" s="15">
@@ -3774,7 +3789,7 @@
         <v>16</v>
       </c>
       <c r="H67" s="17"/>
-      <c r="I67" s="35"/>
+      <c r="I67" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="33.75">
       <c r="A68" s="15">
@@ -3797,7 +3812,7 @@
         <v>16</v>
       </c>
       <c r="H68" s="17"/>
-      <c r="I68" s="35"/>
+      <c r="I68" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="33.75">
       <c r="A69" s="15">
@@ -3820,7 +3835,7 @@
         <v>16</v>
       </c>
       <c r="H69" s="17"/>
-      <c r="I69" s="35"/>
+      <c r="I69" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="33.75">
       <c r="A70" s="15">
@@ -3843,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="H70" s="17"/>
-      <c r="I70" s="35"/>
+      <c r="I70" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="33.75">
       <c r="A71" s="15">
@@ -3866,7 +3881,7 @@
         <v>16</v>
       </c>
       <c r="H71" s="17"/>
-      <c r="I71" s="35"/>
+      <c r="I71" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="33.75">
       <c r="A72" s="15">
@@ -3889,7 +3904,7 @@
         <v>16</v>
       </c>
       <c r="H72" s="17"/>
-      <c r="I72" s="35"/>
+      <c r="I72" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="33.75">
       <c r="A73" s="15">
@@ -3912,7 +3927,7 @@
         <v>16</v>
       </c>
       <c r="H73" s="17"/>
-      <c r="I73" s="35"/>
+      <c r="I73" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="33.75">
       <c r="A74" s="15">
@@ -3935,7 +3950,7 @@
         <v>16</v>
       </c>
       <c r="H74" s="17"/>
-      <c r="I74" s="35"/>
+      <c r="I74" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="33.75">
       <c r="A75" s="15">
@@ -3958,7 +3973,7 @@
         <v>16</v>
       </c>
       <c r="H75" s="17"/>
-      <c r="I75" s="35"/>
+      <c r="I75" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="20.25">
       <c r="A76" s="15">
@@ -3981,18 +3996,18 @@
         <v>16</v>
       </c>
       <c r="H76" s="17"/>
-      <c r="I76" s="35"/>
+      <c r="I76" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="21"/>
-      <c r="B77" s="35"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="31"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="31"/>
+      <c r="D77" s="32"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A78" s="11" t="s">
@@ -4032,7 +4047,7 @@
       <c r="H79" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I79" s="35"/>
+      <c r="I79" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="15">
@@ -4041,8 +4056,8 @@
       <c r="B80" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C80" s="44">
-        <v>30.11804398148148</v>
+      <c r="C80" s="47">
+        <v>32.1178125</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -4055,7 +4070,7 @@
         <v>16</v>
       </c>
       <c r="H80" s="19"/>
-      <c r="I80" s="35"/>
+      <c r="I80" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="15">
@@ -4064,8 +4079,8 @@
       <c r="B81" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C81" s="44">
-        <v>30.11804398148148</v>
+      <c r="C81" s="47">
+        <v>32.1178125</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -4078,7 +4093,7 @@
         <v>16</v>
       </c>
       <c r="H81" s="19"/>
-      <c r="I81" s="35"/>
+      <c r="I81" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="15">
@@ -4087,8 +4102,8 @@
       <c r="B82" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C82" s="44">
-        <v>30.11804398148148</v>
+      <c r="C82" s="47">
+        <v>32.1178125</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -4101,7 +4116,7 @@
         <v>16</v>
       </c>
       <c r="H82" s="19"/>
-      <c r="I82" s="35"/>
+      <c r="I82" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="15">
@@ -4110,8 +4125,8 @@
       <c r="B83" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C83" s="44">
-        <v>30.11804398148148</v>
+      <c r="C83" s="47">
+        <v>32.1178125</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
@@ -4124,7 +4139,7 @@
         <v>16</v>
       </c>
       <c r="H83" s="19"/>
-      <c r="I83" s="35"/>
+      <c r="I83" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="15">
@@ -4147,7 +4162,7 @@
         <v>16</v>
       </c>
       <c r="H84" s="17"/>
-      <c r="I84" s="35"/>
+      <c r="I84" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="15">
@@ -4170,7 +4185,7 @@
         <v>16</v>
       </c>
       <c r="H85" s="17"/>
-      <c r="I85" s="35"/>
+      <c r="I85" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="15">
@@ -4193,7 +4208,7 @@
         <v>16</v>
       </c>
       <c r="H86" s="17"/>
-      <c r="I86" s="35"/>
+      <c r="I86" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="15">
@@ -4216,7 +4231,7 @@
         <v>16</v>
       </c>
       <c r="H87" s="17"/>
-      <c r="I87" s="35"/>
+      <c r="I87" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="15">
@@ -4239,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="H88" s="17"/>
-      <c r="I88" s="35"/>
+      <c r="I88" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="15">
@@ -4262,7 +4277,7 @@
         <v>16</v>
       </c>
       <c r="H89" s="17"/>
-      <c r="I89" s="35"/>
+      <c r="I89" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="15">
@@ -4285,7 +4300,7 @@
         <v>16</v>
       </c>
       <c r="H90" s="17"/>
-      <c r="I90" s="35"/>
+      <c r="I90" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="15">
@@ -4308,7 +4323,7 @@
         <v>16</v>
       </c>
       <c r="H91" s="17"/>
-      <c r="I91" s="35"/>
+      <c r="I91" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="15">
@@ -4331,7 +4346,7 @@
         <v>16</v>
       </c>
       <c r="H92" s="17"/>
-      <c r="I92" s="35"/>
+      <c r="I92" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="15">
@@ -4354,7 +4369,7 @@
         <v>16</v>
       </c>
       <c r="H93" s="17"/>
-      <c r="I93" s="35"/>
+      <c r="I93" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="15">
@@ -4377,7 +4392,7 @@
         <v>16</v>
       </c>
       <c r="H94" s="17"/>
-      <c r="I94" s="35"/>
+      <c r="I94" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="15">
@@ -4400,7 +4415,7 @@
         <v>16</v>
       </c>
       <c r="H95" s="17"/>
-      <c r="I95" s="35"/>
+      <c r="I95" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="15">
@@ -4423,7 +4438,7 @@
         <v>16</v>
       </c>
       <c r="H96" s="17"/>
-      <c r="I96" s="35"/>
+      <c r="I96" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="15">
@@ -4446,7 +4461,7 @@
         <v>16</v>
       </c>
       <c r="H97" s="17"/>
-      <c r="I97" s="35"/>
+      <c r="I97" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="15">
@@ -4469,7 +4484,7 @@
         <v>16</v>
       </c>
       <c r="H98" s="17"/>
-      <c r="I98" s="35"/>
+      <c r="I98" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="15">
@@ -4492,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="H99" s="17"/>
-      <c r="I99" s="35"/>
+      <c r="I99" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="15">
@@ -4515,7 +4530,7 @@
         <v>16</v>
       </c>
       <c r="H100" s="17"/>
-      <c r="I100" s="35"/>
+      <c r="I100" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="15">
@@ -4538,7 +4553,7 @@
         <v>16</v>
       </c>
       <c r="H101" s="17"/>
-      <c r="I101" s="35"/>
+      <c r="I101" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="15">
@@ -4561,7 +4576,7 @@
         <v>16</v>
       </c>
       <c r="H102" s="17"/>
-      <c r="I102" s="35"/>
+      <c r="I102" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="33">
       <c r="A103" s="15">
@@ -4584,7 +4599,7 @@
         <v>16</v>
       </c>
       <c r="H103" s="17"/>
-      <c r="I103" s="35"/>
+      <c r="I103" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="33.75">
       <c r="A104" s="15">
@@ -4607,7 +4622,7 @@
         <v>16</v>
       </c>
       <c r="H104" s="17"/>
-      <c r="I104" s="35"/>
+      <c r="I104" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="33">
       <c r="A105" s="15">
@@ -4630,7 +4645,7 @@
         <v>16</v>
       </c>
       <c r="H105" s="17"/>
-      <c r="I105" s="35"/>
+      <c r="I105" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="15">
@@ -4653,7 +4668,7 @@
         <v>16</v>
       </c>
       <c r="H106" s="17"/>
-      <c r="I106" s="35"/>
+      <c r="I106" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="15">
@@ -4676,7 +4691,7 @@
         <v>16</v>
       </c>
       <c r="H107" s="17"/>
-      <c r="I107" s="35"/>
+      <c r="I107" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="33">
       <c r="A108" s="15">
@@ -4699,7 +4714,7 @@
         <v>16</v>
       </c>
       <c r="H108" s="17"/>
-      <c r="I108" s="35"/>
+      <c r="I108" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="15">
@@ -4722,750 +4737,750 @@
         <v>16</v>
       </c>
       <c r="H109" s="17"/>
-      <c r="I109" s="35"/>
+      <c r="I109" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="21"/>
-      <c r="B110" s="35"/>
-      <c r="C110" s="30"/>
-      <c r="D110" s="31"/>
+      <c r="B110" s="38"/>
+      <c r="C110" s="31"/>
+      <c r="D110" s="32"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="45"/>
-      <c r="H110" s="35"/>
-      <c r="I110" s="35"/>
+      <c r="G110" s="48"/>
+      <c r="H110" s="38"/>
+      <c r="I110" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="21"/>
-      <c r="B111" s="35"/>
-      <c r="C111" s="30"/>
-      <c r="D111" s="31"/>
+      <c r="B111" s="38"/>
+      <c r="C111" s="31"/>
+      <c r="D111" s="32"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="45"/>
-      <c r="H111" s="35"/>
-      <c r="I111" s="35"/>
+      <c r="G111" s="48"/>
+      <c r="H111" s="38"/>
+      <c r="I111" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="21"/>
-      <c r="B112" s="35"/>
-      <c r="C112" s="30"/>
-      <c r="D112" s="31"/>
+      <c r="B112" s="38"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="32"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="45"/>
-      <c r="H112" s="35"/>
-      <c r="I112" s="35"/>
+      <c r="G112" s="48"/>
+      <c r="H112" s="38"/>
+      <c r="I112" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="21"/>
-      <c r="B113" s="35"/>
-      <c r="C113" s="30"/>
-      <c r="D113" s="31"/>
+      <c r="B113" s="38"/>
+      <c r="C113" s="31"/>
+      <c r="D113" s="32"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
-      <c r="G113" s="45"/>
-      <c r="H113" s="35"/>
-      <c r="I113" s="35"/>
+      <c r="G113" s="48"/>
+      <c r="H113" s="38"/>
+      <c r="I113" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="21"/>
-      <c r="B114" s="35"/>
-      <c r="C114" s="30"/>
-      <c r="D114" s="31"/>
+      <c r="B114" s="38"/>
+      <c r="C114" s="31"/>
+      <c r="D114" s="32"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
-      <c r="G114" s="45"/>
-      <c r="H114" s="35"/>
-      <c r="I114" s="35"/>
+      <c r="G114" s="48"/>
+      <c r="H114" s="38"/>
+      <c r="I114" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="21"/>
-      <c r="B115" s="35"/>
-      <c r="C115" s="30"/>
-      <c r="D115" s="31"/>
+      <c r="B115" s="38"/>
+      <c r="C115" s="31"/>
+      <c r="D115" s="32"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
-      <c r="G115" s="45"/>
-      <c r="H115" s="35"/>
-      <c r="I115" s="35"/>
+      <c r="G115" s="48"/>
+      <c r="H115" s="38"/>
+      <c r="I115" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="21"/>
-      <c r="B116" s="35"/>
-      <c r="C116" s="30"/>
-      <c r="D116" s="31"/>
+      <c r="B116" s="38"/>
+      <c r="C116" s="31"/>
+      <c r="D116" s="32"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
-      <c r="G116" s="45"/>
-      <c r="H116" s="35"/>
-      <c r="I116" s="35"/>
+      <c r="G116" s="48"/>
+      <c r="H116" s="38"/>
+      <c r="I116" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="21"/>
-      <c r="B117" s="35"/>
-      <c r="C117" s="30"/>
-      <c r="D117" s="31"/>
+      <c r="B117" s="38"/>
+      <c r="C117" s="31"/>
+      <c r="D117" s="32"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
-      <c r="G117" s="45"/>
-      <c r="H117" s="35"/>
-      <c r="I117" s="35"/>
+      <c r="G117" s="48"/>
+      <c r="H117" s="38"/>
+      <c r="I117" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="21"/>
-      <c r="B118" s="35"/>
-      <c r="C118" s="30"/>
-      <c r="D118" s="31"/>
+      <c r="B118" s="38"/>
+      <c r="C118" s="31"/>
+      <c r="D118" s="32"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
-      <c r="G118" s="45"/>
-      <c r="H118" s="35"/>
-      <c r="I118" s="35"/>
+      <c r="G118" s="48"/>
+      <c r="H118" s="38"/>
+      <c r="I118" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="21"/>
-      <c r="B119" s="35"/>
-      <c r="C119" s="30"/>
-      <c r="D119" s="31"/>
+      <c r="B119" s="38"/>
+      <c r="C119" s="31"/>
+      <c r="D119" s="32"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
-      <c r="G119" s="45"/>
-      <c r="H119" s="35"/>
-      <c r="I119" s="35"/>
+      <c r="G119" s="48"/>
+      <c r="H119" s="38"/>
+      <c r="I119" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="21"/>
-      <c r="B120" s="35"/>
-      <c r="C120" s="30"/>
-      <c r="D120" s="31"/>
+      <c r="B120" s="38"/>
+      <c r="C120" s="31"/>
+      <c r="D120" s="32"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
-      <c r="G120" s="45"/>
-      <c r="H120" s="35"/>
-      <c r="I120" s="35"/>
+      <c r="G120" s="48"/>
+      <c r="H120" s="38"/>
+      <c r="I120" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="21"/>
-      <c r="B121" s="35"/>
-      <c r="C121" s="30"/>
-      <c r="D121" s="31"/>
+      <c r="B121" s="38"/>
+      <c r="C121" s="31"/>
+      <c r="D121" s="32"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
-      <c r="G121" s="45"/>
-      <c r="H121" s="35"/>
-      <c r="I121" s="35"/>
+      <c r="G121" s="48"/>
+      <c r="H121" s="38"/>
+      <c r="I121" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="21"/>
-      <c r="B122" s="35"/>
-      <c r="C122" s="30"/>
-      <c r="D122" s="31"/>
+      <c r="B122" s="38"/>
+      <c r="C122" s="31"/>
+      <c r="D122" s="32"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
-      <c r="G122" s="45"/>
-      <c r="H122" s="35"/>
-      <c r="I122" s="35"/>
+      <c r="G122" s="48"/>
+      <c r="H122" s="38"/>
+      <c r="I122" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="21"/>
-      <c r="B123" s="35"/>
-      <c r="C123" s="30"/>
-      <c r="D123" s="31"/>
+      <c r="B123" s="38"/>
+      <c r="C123" s="31"/>
+      <c r="D123" s="32"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
-      <c r="G123" s="45"/>
-      <c r="H123" s="35"/>
-      <c r="I123" s="35"/>
+      <c r="G123" s="48"/>
+      <c r="H123" s="38"/>
+      <c r="I123" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="21"/>
-      <c r="B124" s="35"/>
-      <c r="C124" s="30"/>
-      <c r="D124" s="31"/>
+      <c r="B124" s="38"/>
+      <c r="C124" s="31"/>
+      <c r="D124" s="32"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
-      <c r="G124" s="45"/>
-      <c r="H124" s="35"/>
-      <c r="I124" s="35"/>
+      <c r="G124" s="48"/>
+      <c r="H124" s="38"/>
+      <c r="I124" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="21"/>
-      <c r="B125" s="35"/>
-      <c r="C125" s="30"/>
-      <c r="D125" s="31"/>
+      <c r="B125" s="38"/>
+      <c r="C125" s="31"/>
+      <c r="D125" s="32"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
-      <c r="G125" s="45"/>
-      <c r="H125" s="35"/>
-      <c r="I125" s="35"/>
+      <c r="G125" s="48"/>
+      <c r="H125" s="38"/>
+      <c r="I125" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="21"/>
-      <c r="B126" s="35"/>
-      <c r="C126" s="30"/>
-      <c r="D126" s="31"/>
+      <c r="B126" s="38"/>
+      <c r="C126" s="31"/>
+      <c r="D126" s="32"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
-      <c r="G126" s="45"/>
-      <c r="H126" s="35"/>
-      <c r="I126" s="35"/>
+      <c r="G126" s="48"/>
+      <c r="H126" s="38"/>
+      <c r="I126" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="21"/>
-      <c r="B127" s="35"/>
-      <c r="C127" s="30"/>
-      <c r="D127" s="31"/>
+      <c r="B127" s="38"/>
+      <c r="C127" s="31"/>
+      <c r="D127" s="32"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
-      <c r="G127" s="45"/>
-      <c r="H127" s="35"/>
-      <c r="I127" s="35"/>
+      <c r="G127" s="48"/>
+      <c r="H127" s="38"/>
+      <c r="I127" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="21"/>
-      <c r="B128" s="35"/>
-      <c r="C128" s="30"/>
-      <c r="D128" s="31"/>
+      <c r="B128" s="38"/>
+      <c r="C128" s="31"/>
+      <c r="D128" s="32"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
-      <c r="G128" s="45"/>
-      <c r="H128" s="35"/>
-      <c r="I128" s="35"/>
+      <c r="G128" s="48"/>
+      <c r="H128" s="38"/>
+      <c r="I128" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="21"/>
-      <c r="B129" s="35"/>
-      <c r="C129" s="30"/>
-      <c r="D129" s="31"/>
+      <c r="B129" s="38"/>
+      <c r="C129" s="31"/>
+      <c r="D129" s="32"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
-      <c r="G129" s="45"/>
-      <c r="H129" s="35"/>
-      <c r="I129" s="35"/>
+      <c r="G129" s="48"/>
+      <c r="H129" s="38"/>
+      <c r="I129" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="21"/>
-      <c r="B130" s="35"/>
-      <c r="C130" s="30"/>
-      <c r="D130" s="31"/>
+      <c r="B130" s="38"/>
+      <c r="C130" s="31"/>
+      <c r="D130" s="32"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
-      <c r="G130" s="45"/>
-      <c r="H130" s="35"/>
-      <c r="I130" s="35"/>
+      <c r="G130" s="48"/>
+      <c r="H130" s="38"/>
+      <c r="I130" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
       <c r="A131" s="21"/>
-      <c r="B131" s="35"/>
-      <c r="C131" s="30"/>
-      <c r="D131" s="31"/>
+      <c r="B131" s="38"/>
+      <c r="C131" s="31"/>
+      <c r="D131" s="32"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
-      <c r="G131" s="45"/>
-      <c r="H131" s="35"/>
-      <c r="I131" s="35"/>
+      <c r="G131" s="48"/>
+      <c r="H131" s="38"/>
+      <c r="I131" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
       <c r="A132" s="21"/>
-      <c r="B132" s="35"/>
-      <c r="C132" s="30"/>
-      <c r="D132" s="31"/>
+      <c r="B132" s="38"/>
+      <c r="C132" s="31"/>
+      <c r="D132" s="32"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="45"/>
-      <c r="H132" s="35"/>
-      <c r="I132" s="35"/>
+      <c r="G132" s="48"/>
+      <c r="H132" s="38"/>
+      <c r="I132" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
       <c r="A133" s="21"/>
-      <c r="B133" s="35"/>
-      <c r="C133" s="30"/>
-      <c r="D133" s="31"/>
+      <c r="B133" s="38"/>
+      <c r="C133" s="31"/>
+      <c r="D133" s="32"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
-      <c r="G133" s="45"/>
-      <c r="H133" s="35"/>
-      <c r="I133" s="35"/>
+      <c r="G133" s="48"/>
+      <c r="H133" s="38"/>
+      <c r="I133" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="21"/>
-      <c r="B134" s="35"/>
-      <c r="C134" s="30"/>
-      <c r="D134" s="31"/>
+      <c r="B134" s="38"/>
+      <c r="C134" s="31"/>
+      <c r="D134" s="32"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
-      <c r="G134" s="45"/>
-      <c r="H134" s="35"/>
-      <c r="I134" s="35"/>
+      <c r="G134" s="48"/>
+      <c r="H134" s="38"/>
+      <c r="I134" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
       <c r="A135" s="21"/>
-      <c r="B135" s="35"/>
-      <c r="C135" s="30"/>
-      <c r="D135" s="31"/>
+      <c r="B135" s="38"/>
+      <c r="C135" s="31"/>
+      <c r="D135" s="32"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
-      <c r="G135" s="45"/>
-      <c r="H135" s="35"/>
-      <c r="I135" s="35"/>
+      <c r="G135" s="48"/>
+      <c r="H135" s="38"/>
+      <c r="I135" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
       <c r="A136" s="21"/>
-      <c r="B136" s="35"/>
-      <c r="C136" s="30"/>
-      <c r="D136" s="31"/>
+      <c r="B136" s="38"/>
+      <c r="C136" s="31"/>
+      <c r="D136" s="32"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
-      <c r="G136" s="45"/>
-      <c r="H136" s="35"/>
-      <c r="I136" s="35"/>
+      <c r="G136" s="48"/>
+      <c r="H136" s="38"/>
+      <c r="I136" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
       <c r="A137" s="21"/>
-      <c r="B137" s="35"/>
-      <c r="C137" s="30"/>
-      <c r="D137" s="31"/>
+      <c r="B137" s="38"/>
+      <c r="C137" s="31"/>
+      <c r="D137" s="32"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
-      <c r="G137" s="45"/>
-      <c r="H137" s="35"/>
-      <c r="I137" s="35"/>
+      <c r="G137" s="48"/>
+      <c r="H137" s="38"/>
+      <c r="I137" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
       <c r="A138" s="21"/>
-      <c r="B138" s="35"/>
-      <c r="C138" s="30"/>
-      <c r="D138" s="31"/>
+      <c r="B138" s="38"/>
+      <c r="C138" s="31"/>
+      <c r="D138" s="32"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
-      <c r="G138" s="45"/>
-      <c r="H138" s="35"/>
-      <c r="I138" s="35"/>
+      <c r="G138" s="48"/>
+      <c r="H138" s="38"/>
+      <c r="I138" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
       <c r="A139" s="21"/>
-      <c r="B139" s="35"/>
-      <c r="C139" s="30"/>
-      <c r="D139" s="31"/>
+      <c r="B139" s="38"/>
+      <c r="C139" s="31"/>
+      <c r="D139" s="32"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
-      <c r="G139" s="45"/>
-      <c r="H139" s="35"/>
-      <c r="I139" s="35"/>
+      <c r="G139" s="48"/>
+      <c r="H139" s="38"/>
+      <c r="I139" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
       <c r="A140" s="21"/>
-      <c r="B140" s="35"/>
-      <c r="C140" s="30"/>
-      <c r="D140" s="31"/>
+      <c r="B140" s="38"/>
+      <c r="C140" s="31"/>
+      <c r="D140" s="32"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
-      <c r="G140" s="45"/>
-      <c r="H140" s="35"/>
-      <c r="I140" s="35"/>
+      <c r="G140" s="48"/>
+      <c r="H140" s="38"/>
+      <c r="I140" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
       <c r="A141" s="21"/>
-      <c r="B141" s="35"/>
-      <c r="C141" s="30"/>
-      <c r="D141" s="31"/>
+      <c r="B141" s="38"/>
+      <c r="C141" s="31"/>
+      <c r="D141" s="32"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
-      <c r="G141" s="45"/>
-      <c r="H141" s="35"/>
-      <c r="I141" s="35"/>
+      <c r="G141" s="48"/>
+      <c r="H141" s="38"/>
+      <c r="I141" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
       <c r="A142" s="21"/>
-      <c r="B142" s="35"/>
-      <c r="C142" s="30"/>
-      <c r="D142" s="31"/>
+      <c r="B142" s="38"/>
+      <c r="C142" s="31"/>
+      <c r="D142" s="32"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
-      <c r="G142" s="45"/>
-      <c r="H142" s="35"/>
-      <c r="I142" s="35"/>
+      <c r="G142" s="48"/>
+      <c r="H142" s="38"/>
+      <c r="I142" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
       <c r="A143" s="21"/>
-      <c r="B143" s="35"/>
-      <c r="C143" s="30"/>
-      <c r="D143" s="31"/>
+      <c r="B143" s="38"/>
+      <c r="C143" s="31"/>
+      <c r="D143" s="32"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
-      <c r="G143" s="45"/>
-      <c r="H143" s="35"/>
-      <c r="I143" s="35"/>
+      <c r="G143" s="48"/>
+      <c r="H143" s="38"/>
+      <c r="I143" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
       <c r="A144" s="21"/>
-      <c r="B144" s="35"/>
-      <c r="C144" s="30"/>
-      <c r="D144" s="31"/>
+      <c r="B144" s="38"/>
+      <c r="C144" s="31"/>
+      <c r="D144" s="32"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
-      <c r="G144" s="45"/>
-      <c r="H144" s="35"/>
-      <c r="I144" s="35"/>
+      <c r="G144" s="48"/>
+      <c r="H144" s="38"/>
+      <c r="I144" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
       <c r="A145" s="21"/>
-      <c r="B145" s="35"/>
-      <c r="C145" s="30"/>
-      <c r="D145" s="31"/>
+      <c r="B145" s="38"/>
+      <c r="C145" s="31"/>
+      <c r="D145" s="32"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
-      <c r="G145" s="45"/>
-      <c r="H145" s="35"/>
-      <c r="I145" s="35"/>
+      <c r="G145" s="48"/>
+      <c r="H145" s="38"/>
+      <c r="I145" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
       <c r="A146" s="21"/>
-      <c r="B146" s="35"/>
-      <c r="C146" s="30"/>
-      <c r="D146" s="31"/>
+      <c r="B146" s="38"/>
+      <c r="C146" s="31"/>
+      <c r="D146" s="32"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
-      <c r="G146" s="45"/>
-      <c r="H146" s="35"/>
-      <c r="I146" s="35"/>
+      <c r="G146" s="48"/>
+      <c r="H146" s="38"/>
+      <c r="I146" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
       <c r="A147" s="21"/>
-      <c r="B147" s="35"/>
-      <c r="C147" s="30"/>
-      <c r="D147" s="31"/>
+      <c r="B147" s="38"/>
+      <c r="C147" s="31"/>
+      <c r="D147" s="32"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
-      <c r="G147" s="45"/>
-      <c r="H147" s="35"/>
-      <c r="I147" s="35"/>
+      <c r="G147" s="48"/>
+      <c r="H147" s="38"/>
+      <c r="I147" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
       <c r="A148" s="21"/>
-      <c r="B148" s="35"/>
-      <c r="C148" s="30"/>
-      <c r="D148" s="31"/>
+      <c r="B148" s="38"/>
+      <c r="C148" s="31"/>
+      <c r="D148" s="32"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="45"/>
-      <c r="H148" s="35"/>
-      <c r="I148" s="35"/>
+      <c r="G148" s="48"/>
+      <c r="H148" s="38"/>
+      <c r="I148" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
       <c r="A149" s="21"/>
-      <c r="B149" s="35"/>
-      <c r="C149" s="30"/>
-      <c r="D149" s="31"/>
+      <c r="B149" s="38"/>
+      <c r="C149" s="31"/>
+      <c r="D149" s="32"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
-      <c r="G149" s="45"/>
-      <c r="H149" s="35"/>
-      <c r="I149" s="35"/>
+      <c r="G149" s="48"/>
+      <c r="H149" s="38"/>
+      <c r="I149" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
       <c r="A150" s="21"/>
-      <c r="B150" s="35"/>
-      <c r="C150" s="30"/>
-      <c r="D150" s="31"/>
+      <c r="B150" s="38"/>
+      <c r="C150" s="31"/>
+      <c r="D150" s="32"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
-      <c r="G150" s="45"/>
-      <c r="H150" s="35"/>
-      <c r="I150" s="35"/>
+      <c r="G150" s="48"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
       <c r="A151" s="21"/>
-      <c r="B151" s="35"/>
-      <c r="C151" s="30"/>
-      <c r="D151" s="31"/>
+      <c r="B151" s="38"/>
+      <c r="C151" s="31"/>
+      <c r="D151" s="32"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="45"/>
-      <c r="H151" s="35"/>
-      <c r="I151" s="35"/>
+      <c r="G151" s="48"/>
+      <c r="H151" s="38"/>
+      <c r="I151" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
       <c r="A152" s="21"/>
-      <c r="B152" s="35"/>
-      <c r="C152" s="30"/>
-      <c r="D152" s="31"/>
+      <c r="B152" s="38"/>
+      <c r="C152" s="31"/>
+      <c r="D152" s="32"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="45"/>
-      <c r="H152" s="35"/>
-      <c r="I152" s="35"/>
+      <c r="G152" s="48"/>
+      <c r="H152" s="38"/>
+      <c r="I152" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
       <c r="A153" s="21"/>
-      <c r="B153" s="35"/>
-      <c r="C153" s="30"/>
-      <c r="D153" s="31"/>
+      <c r="B153" s="38"/>
+      <c r="C153" s="31"/>
+      <c r="D153" s="32"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
-      <c r="G153" s="45"/>
-      <c r="H153" s="35"/>
-      <c r="I153" s="35"/>
+      <c r="G153" s="48"/>
+      <c r="H153" s="38"/>
+      <c r="I153" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="21"/>
-      <c r="B154" s="35"/>
-      <c r="C154" s="30"/>
-      <c r="D154" s="31"/>
+      <c r="B154" s="38"/>
+      <c r="C154" s="31"/>
+      <c r="D154" s="32"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
-      <c r="G154" s="45"/>
-      <c r="H154" s="35"/>
-      <c r="I154" s="35"/>
+      <c r="G154" s="48"/>
+      <c r="H154" s="38"/>
+      <c r="I154" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="21"/>
-      <c r="B155" s="35"/>
-      <c r="C155" s="30"/>
-      <c r="D155" s="31"/>
+      <c r="B155" s="38"/>
+      <c r="C155" s="31"/>
+      <c r="D155" s="32"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
-      <c r="G155" s="45"/>
-      <c r="H155" s="35"/>
-      <c r="I155" s="35"/>
+      <c r="G155" s="48"/>
+      <c r="H155" s="38"/>
+      <c r="I155" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="21"/>
-      <c r="B156" s="35"/>
-      <c r="C156" s="30"/>
-      <c r="D156" s="31"/>
+      <c r="B156" s="38"/>
+      <c r="C156" s="31"/>
+      <c r="D156" s="32"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
-      <c r="G156" s="45"/>
-      <c r="H156" s="35"/>
-      <c r="I156" s="35"/>
+      <c r="G156" s="48"/>
+      <c r="H156" s="38"/>
+      <c r="I156" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="21"/>
-      <c r="B157" s="35"/>
-      <c r="C157" s="30"/>
-      <c r="D157" s="31"/>
+      <c r="B157" s="38"/>
+      <c r="C157" s="31"/>
+      <c r="D157" s="32"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
-      <c r="G157" s="45"/>
-      <c r="H157" s="35"/>
-      <c r="I157" s="35"/>
+      <c r="G157" s="48"/>
+      <c r="H157" s="38"/>
+      <c r="I157" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="21"/>
-      <c r="B158" s="35"/>
-      <c r="C158" s="30"/>
-      <c r="D158" s="31"/>
+      <c r="B158" s="38"/>
+      <c r="C158" s="31"/>
+      <c r="D158" s="32"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
-      <c r="G158" s="45"/>
-      <c r="H158" s="35"/>
-      <c r="I158" s="35"/>
+      <c r="G158" s="48"/>
+      <c r="H158" s="38"/>
+      <c r="I158" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="21"/>
-      <c r="B159" s="35"/>
-      <c r="C159" s="30"/>
-      <c r="D159" s="31"/>
+      <c r="B159" s="38"/>
+      <c r="C159" s="31"/>
+      <c r="D159" s="32"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
-      <c r="G159" s="45"/>
-      <c r="H159" s="35"/>
-      <c r="I159" s="35"/>
+      <c r="G159" s="48"/>
+      <c r="H159" s="38"/>
+      <c r="I159" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="21"/>
-      <c r="B160" s="35"/>
-      <c r="C160" s="30"/>
-      <c r="D160" s="31"/>
+      <c r="B160" s="38"/>
+      <c r="C160" s="31"/>
+      <c r="D160" s="32"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
-      <c r="G160" s="45"/>
-      <c r="H160" s="35"/>
-      <c r="I160" s="35"/>
+      <c r="G160" s="48"/>
+      <c r="H160" s="38"/>
+      <c r="I160" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="21"/>
-      <c r="B161" s="35"/>
-      <c r="C161" s="30"/>
-      <c r="D161" s="31"/>
+      <c r="B161" s="38"/>
+      <c r="C161" s="31"/>
+      <c r="D161" s="32"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
-      <c r="G161" s="45"/>
-      <c r="H161" s="35"/>
-      <c r="I161" s="35"/>
+      <c r="G161" s="48"/>
+      <c r="H161" s="38"/>
+      <c r="I161" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="21"/>
-      <c r="B162" s="35"/>
-      <c r="C162" s="30"/>
-      <c r="D162" s="31"/>
+      <c r="B162" s="38"/>
+      <c r="C162" s="31"/>
+      <c r="D162" s="32"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="45"/>
-      <c r="H162" s="35"/>
-      <c r="I162" s="35"/>
+      <c r="G162" s="48"/>
+      <c r="H162" s="38"/>
+      <c r="I162" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="21"/>
-      <c r="B163" s="35"/>
-      <c r="C163" s="30"/>
-      <c r="D163" s="31"/>
+      <c r="B163" s="38"/>
+      <c r="C163" s="31"/>
+      <c r="D163" s="32"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
-      <c r="G163" s="45"/>
-      <c r="H163" s="35"/>
-      <c r="I163" s="35"/>
+      <c r="G163" s="48"/>
+      <c r="H163" s="38"/>
+      <c r="I163" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="21"/>
-      <c r="B164" s="35"/>
-      <c r="C164" s="30"/>
-      <c r="D164" s="31"/>
+      <c r="B164" s="38"/>
+      <c r="C164" s="31"/>
+      <c r="D164" s="32"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
-      <c r="G164" s="45"/>
-      <c r="H164" s="35"/>
-      <c r="I164" s="35"/>
+      <c r="G164" s="48"/>
+      <c r="H164" s="38"/>
+      <c r="I164" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="21"/>
-      <c r="B165" s="35"/>
-      <c r="C165" s="30"/>
-      <c r="D165" s="31"/>
+      <c r="B165" s="38"/>
+      <c r="C165" s="31"/>
+      <c r="D165" s="32"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
-      <c r="G165" s="45"/>
-      <c r="H165" s="35"/>
-      <c r="I165" s="35"/>
+      <c r="G165" s="48"/>
+      <c r="H165" s="38"/>
+      <c r="I165" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="21"/>
-      <c r="B166" s="35"/>
-      <c r="C166" s="30"/>
-      <c r="D166" s="31"/>
+      <c r="B166" s="38"/>
+      <c r="C166" s="31"/>
+      <c r="D166" s="32"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
-      <c r="G166" s="45"/>
-      <c r="H166" s="35"/>
-      <c r="I166" s="35"/>
+      <c r="G166" s="48"/>
+      <c r="H166" s="38"/>
+      <c r="I166" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="21"/>
-      <c r="B167" s="35"/>
-      <c r="C167" s="30"/>
-      <c r="D167" s="31"/>
+      <c r="B167" s="38"/>
+      <c r="C167" s="31"/>
+      <c r="D167" s="32"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
-      <c r="G167" s="45"/>
-      <c r="H167" s="35"/>
-      <c r="I167" s="35"/>
+      <c r="G167" s="48"/>
+      <c r="H167" s="38"/>
+      <c r="I167" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="21"/>
-      <c r="B168" s="35"/>
-      <c r="C168" s="30"/>
-      <c r="D168" s="31"/>
+      <c r="B168" s="38"/>
+      <c r="C168" s="31"/>
+      <c r="D168" s="32"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
-      <c r="G168" s="45"/>
-      <c r="H168" s="35"/>
-      <c r="I168" s="35"/>
+      <c r="G168" s="48"/>
+      <c r="H168" s="38"/>
+      <c r="I168" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
       <c r="A169" s="21"/>
-      <c r="B169" s="35"/>
-      <c r="C169" s="30"/>
-      <c r="D169" s="31"/>
+      <c r="B169" s="38"/>
+      <c r="C169" s="31"/>
+      <c r="D169" s="32"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
-      <c r="G169" s="45"/>
-      <c r="H169" s="35"/>
-      <c r="I169" s="35"/>
+      <c r="G169" s="48"/>
+      <c r="H169" s="38"/>
+      <c r="I169" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
       <c r="A170" s="21"/>
-      <c r="B170" s="35"/>
-      <c r="C170" s="30"/>
-      <c r="D170" s="31"/>
+      <c r="B170" s="38"/>
+      <c r="C170" s="31"/>
+      <c r="D170" s="32"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
-      <c r="G170" s="45"/>
-      <c r="H170" s="35"/>
-      <c r="I170" s="35"/>
+      <c r="G170" s="48"/>
+      <c r="H170" s="38"/>
+      <c r="I170" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
       <c r="A171" s="21"/>
-      <c r="B171" s="35"/>
-      <c r="C171" s="30"/>
-      <c r="D171" s="31"/>
+      <c r="B171" s="38"/>
+      <c r="C171" s="31"/>
+      <c r="D171" s="32"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
-      <c r="G171" s="45"/>
-      <c r="H171" s="35"/>
-      <c r="I171" s="35"/>
+      <c r="G171" s="48"/>
+      <c r="H171" s="38"/>
+      <c r="I171" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
       <c r="A172" s="21"/>
-      <c r="B172" s="35"/>
-      <c r="C172" s="30"/>
-      <c r="D172" s="31"/>
+      <c r="B172" s="38"/>
+      <c r="C172" s="31"/>
+      <c r="D172" s="32"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
-      <c r="G172" s="45"/>
-      <c r="H172" s="35"/>
-      <c r="I172" s="35"/>
+      <c r="G172" s="48"/>
+      <c r="H172" s="38"/>
+      <c r="I172" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
       <c r="A173" s="21"/>
-      <c r="B173" s="35"/>
-      <c r="C173" s="30"/>
-      <c r="D173" s="31"/>
+      <c r="B173" s="38"/>
+      <c r="C173" s="31"/>
+      <c r="D173" s="32"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
-      <c r="G173" s="45"/>
-      <c r="H173" s="35"/>
-      <c r="I173" s="35"/>
+      <c r="G173" s="48"/>
+      <c r="H173" s="38"/>
+      <c r="I173" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
       <c r="A174" s="21"/>
-      <c r="B174" s="35"/>
-      <c r="C174" s="30"/>
-      <c r="D174" s="31"/>
+      <c r="B174" s="38"/>
+      <c r="C174" s="31"/>
+      <c r="D174" s="32"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
-      <c r="G174" s="45"/>
-      <c r="H174" s="35"/>
-      <c r="I174" s="35"/>
+      <c r="G174" s="48"/>
+      <c r="H174" s="38"/>
+      <c r="I174" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
       <c r="A175" s="21"/>
-      <c r="B175" s="35"/>
-      <c r="C175" s="30"/>
-      <c r="D175" s="31"/>
+      <c r="B175" s="38"/>
+      <c r="C175" s="31"/>
+      <c r="D175" s="32"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
-      <c r="G175" s="45"/>
-      <c r="H175" s="35"/>
-      <c r="I175" s="35"/>
+      <c r="G175" s="48"/>
+      <c r="H175" s="38"/>
+      <c r="I175" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
       <c r="A176" s="21"/>
       <c r="B176" s="2"/>
-      <c r="C176" s="46"/>
-      <c r="D176" s="31"/>
+      <c r="C176" s="49"/>
+      <c r="D176" s="32"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
-      <c r="G176" s="35"/>
-      <c r="H176" s="35"/>
-      <c r="I176" s="35"/>
+      <c r="G176" s="38"/>
+      <c r="H176" s="38"/>
+      <c r="I176" s="38"/>
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A177" s="41"/>
+      <c r="A177" s="44"/>
       <c r="B177" s="2"/>
-      <c r="C177" s="42"/>
-      <c r="D177" s="43"/>
+      <c r="C177" s="45"/>
+      <c r="D177" s="46"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
@@ -5473,10 +5488,10 @@
       <c r="I177" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A178" s="41"/>
+      <c r="A178" s="44"/>
       <c r="B178" s="2"/>
-      <c r="C178" s="42"/>
-      <c r="D178" s="43"/>
+      <c r="C178" s="45"/>
+      <c r="D178" s="46"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
@@ -5484,10 +5499,10 @@
       <c r="I178" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A179" s="41"/>
+      <c r="A179" s="44"/>
       <c r="B179" s="2"/>
-      <c r="C179" s="42"/>
-      <c r="D179" s="43"/>
+      <c r="C179" s="45"/>
+      <c r="D179" s="46"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
@@ -5495,10 +5510,10 @@
       <c r="I179" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A180" s="41"/>
+      <c r="A180" s="44"/>
       <c r="B180" s="2"/>
-      <c r="C180" s="42"/>
-      <c r="D180" s="43"/>
+      <c r="C180" s="45"/>
+      <c r="D180" s="46"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
@@ -5506,10 +5521,10 @@
       <c r="I180" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A181" s="41"/>
+      <c r="A181" s="44"/>
       <c r="B181" s="2"/>
-      <c r="C181" s="42"/>
-      <c r="D181" s="43"/>
+      <c r="C181" s="45"/>
+      <c r="D181" s="46"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
@@ -5517,10 +5532,10 @@
       <c r="I181" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A182" s="41"/>
+      <c r="A182" s="44"/>
       <c r="B182" s="2"/>
-      <c r="C182" s="42"/>
-      <c r="D182" s="43"/>
+      <c r="C182" s="45"/>
+      <c r="D182" s="46"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
@@ -5528,10 +5543,10 @@
       <c r="I182" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A183" s="41"/>
+      <c r="A183" s="44"/>
       <c r="B183" s="2"/>
-      <c r="C183" s="42"/>
-      <c r="D183" s="43"/>
+      <c r="C183" s="45"/>
+      <c r="D183" s="46"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
@@ -5539,10 +5554,10 @@
       <c r="I183" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A184" s="41"/>
+      <c r="A184" s="44"/>
       <c r="B184" s="2"/>
-      <c r="C184" s="42"/>
-      <c r="D184" s="43"/>
+      <c r="C184" s="45"/>
+      <c r="D184" s="46"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -5550,10 +5565,10 @@
       <c r="I184" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A185" s="41"/>
+      <c r="A185" s="44"/>
       <c r="B185" s="2"/>
-      <c r="C185" s="42"/>
-      <c r="D185" s="43"/>
+      <c r="C185" s="45"/>
+      <c r="D185" s="46"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
@@ -5561,10 +5576,10 @@
       <c r="I185" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A186" s="41"/>
+      <c r="A186" s="44"/>
       <c r="B186" s="2"/>
-      <c r="C186" s="42"/>
-      <c r="D186" s="43"/>
+      <c r="C186" s="45"/>
+      <c r="D186" s="46"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
@@ -5572,10 +5587,10 @@
       <c r="I186" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A187" s="41"/>
+      <c r="A187" s="44"/>
       <c r="B187" s="2"/>
-      <c r="C187" s="42"/>
-      <c r="D187" s="43"/>
+      <c r="C187" s="45"/>
+      <c r="D187" s="46"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
@@ -5583,10 +5598,10 @@
       <c r="I187" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A188" s="41"/>
+      <c r="A188" s="44"/>
       <c r="B188" s="2"/>
-      <c r="C188" s="42"/>
-      <c r="D188" s="43"/>
+      <c r="C188" s="45"/>
+      <c r="D188" s="46"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
@@ -5594,10 +5609,10 @@
       <c r="I188" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A189" s="41"/>
+      <c r="A189" s="44"/>
       <c r="B189" s="2"/>
-      <c r="C189" s="42"/>
-      <c r="D189" s="43"/>
+      <c r="C189" s="45"/>
+      <c r="D189" s="46"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
@@ -5605,10 +5620,10 @@
       <c r="I189" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A190" s="41"/>
+      <c r="A190" s="44"/>
       <c r="B190" s="2"/>
-      <c r="C190" s="42"/>
-      <c r="D190" s="43"/>
+      <c r="C190" s="45"/>
+      <c r="D190" s="46"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
@@ -5616,10 +5631,10 @@
       <c r="I190" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A191" s="41"/>
+      <c r="A191" s="44"/>
       <c r="B191" s="2"/>
-      <c r="C191" s="42"/>
-      <c r="D191" s="43"/>
+      <c r="C191" s="45"/>
+      <c r="D191" s="46"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
@@ -5627,10 +5642,10 @@
       <c r="I191" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A192" s="41"/>
+      <c r="A192" s="44"/>
       <c r="B192" s="2"/>
-      <c r="C192" s="42"/>
-      <c r="D192" s="43"/>
+      <c r="C192" s="45"/>
+      <c r="D192" s="46"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
@@ -5638,10 +5653,10 @@
       <c r="I192" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A193" s="41"/>
+      <c r="A193" s="44"/>
       <c r="B193" s="2"/>
-      <c r="C193" s="42"/>
-      <c r="D193" s="43"/>
+      <c r="C193" s="45"/>
+      <c r="D193" s="46"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
@@ -5649,10 +5664,10 @@
       <c r="I193" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A194" s="41"/>
+      <c r="A194" s="44"/>
       <c r="B194" s="2"/>
-      <c r="C194" s="42"/>
-      <c r="D194" s="43"/>
+      <c r="C194" s="45"/>
+      <c r="D194" s="46"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
@@ -5660,10 +5675,10 @@
       <c r="I194" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A195" s="41"/>
+      <c r="A195" s="44"/>
       <c r="B195" s="2"/>
-      <c r="C195" s="42"/>
-      <c r="D195" s="43"/>
+      <c r="C195" s="45"/>
+      <c r="D195" s="46"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
@@ -5671,10 +5686,10 @@
       <c r="I195" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A196" s="41"/>
+      <c r="A196" s="44"/>
       <c r="B196" s="2"/>
-      <c r="C196" s="42"/>
-      <c r="D196" s="43"/>
+      <c r="C196" s="45"/>
+      <c r="D196" s="46"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
@@ -5682,10 +5697,10 @@
       <c r="I196" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A197" s="41"/>
+      <c r="A197" s="44"/>
       <c r="B197" s="2"/>
-      <c r="C197" s="42"/>
-      <c r="D197" s="43"/>
+      <c r="C197" s="45"/>
+      <c r="D197" s="46"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
@@ -5693,10 +5708,10 @@
       <c r="I197" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A198" s="41"/>
+      <c r="A198" s="44"/>
       <c r="B198" s="2"/>
-      <c r="C198" s="42"/>
-      <c r="D198" s="43"/>
+      <c r="C198" s="45"/>
+      <c r="D198" s="46"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
@@ -5704,10 +5719,10 @@
       <c r="I198" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A199" s="41"/>
+      <c r="A199" s="44"/>
       <c r="B199" s="2"/>
-      <c r="C199" s="42"/>
-      <c r="D199" s="43"/>
+      <c r="C199" s="45"/>
+      <c r="D199" s="46"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
@@ -5715,10 +5730,10 @@
       <c r="I199" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A200" s="41"/>
+      <c r="A200" s="44"/>
       <c r="B200" s="2"/>
-      <c r="C200" s="42"/>
-      <c r="D200" s="43"/>
+      <c r="C200" s="45"/>
+      <c r="D200" s="46"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
@@ -5726,10 +5741,10 @@
       <c r="I200" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A201" s="41"/>
+      <c r="A201" s="44"/>
       <c r="B201" s="2"/>
-      <c r="C201" s="42"/>
-      <c r="D201" s="43"/>
+      <c r="C201" s="45"/>
+      <c r="D201" s="46"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
@@ -5737,10 +5752,10 @@
       <c r="I201" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A202" s="41"/>
+      <c r="A202" s="44"/>
       <c r="B202" s="2"/>
-      <c r="C202" s="42"/>
-      <c r="D202" s="43"/>
+      <c r="C202" s="45"/>
+      <c r="D202" s="46"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
@@ -5748,10 +5763,10 @@
       <c r="I202" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A203" s="41"/>
+      <c r="A203" s="44"/>
       <c r="B203" s="2"/>
-      <c r="C203" s="42"/>
-      <c r="D203" s="43"/>
+      <c r="C203" s="45"/>
+      <c r="D203" s="46"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
@@ -5779,11 +5794,11 @@
   <cols>
     <col min="1" max="1" style="23" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="43.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="33" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="34" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="35" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="36" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="24" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="24" width="16.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="37" width="16.433571428571426" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -5796,7 +5811,7 @@
       <c r="D1" s="26"/>
       <c r="E1" s="2"/>
       <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="G1" s="11"/>
       <c r="H1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
@@ -5818,7 +5833,7 @@
       <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="2"/>
@@ -5842,7 +5857,7 @@
       <c r="F3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="30"/>
       <c r="H3" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="33.75">
@@ -5864,7 +5879,7 @@
       <c r="F4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="19"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -5886,7 +5901,7 @@
       <c r="F5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="19"/>
+      <c r="G5" s="30"/>
       <c r="H5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -5908,7 +5923,7 @@
       <c r="F6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="19"/>
+      <c r="G6" s="30"/>
       <c r="H6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -5930,7 +5945,7 @@
       <c r="F7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -5952,7 +5967,7 @@
       <c r="F8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="19"/>
+      <c r="G8" s="30"/>
       <c r="H8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="33.75">
@@ -5971,7 +5986,9 @@
       <c r="E9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="17"/>
+      <c r="F9" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G9" s="20">
         <v>1</v>
       </c>
@@ -5993,8 +6010,10 @@
       <c r="E10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="F10" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="20"/>
       <c r="H10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="35.25">
@@ -6013,8 +6032,10 @@
       <c r="E11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="F11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="20"/>
       <c r="H11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="33.75">
@@ -6033,8 +6054,10 @@
       <c r="E12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="F12" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="20"/>
       <c r="H12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -6053,11 +6076,13 @@
       <c r="E13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="20"/>
       <c r="H13" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="33.75">
       <c r="A14" s="15">
         <v>12</v>
       </c>
@@ -6073,11 +6098,13 @@
       <c r="E14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="20"/>
       <c r="H14" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="33.75">
       <c r="A15" s="15">
         <v>13</v>
       </c>
@@ -6093,11 +6120,13 @@
       <c r="E15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+      <c r="F15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="20"/>
       <c r="H15" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="33.75">
       <c r="A16" s="15">
         <v>14</v>
       </c>
@@ -6113,11 +6142,13 @@
       <c r="E16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+      <c r="F16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="20"/>
       <c r="H16" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="33.75">
       <c r="A17" s="15">
         <v>15</v>
       </c>
@@ -6133,11 +6164,13 @@
       <c r="E17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
+      <c r="F17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="20"/>
       <c r="H17" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="33.75">
       <c r="A18" s="15">
         <v>16</v>
       </c>
@@ -6153,11 +6186,13 @@
       <c r="E18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+      <c r="F18" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="20"/>
       <c r="H18" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="33.75">
       <c r="A19" s="15">
         <v>17</v>
       </c>
@@ -6173,11 +6208,13 @@
       <c r="E19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="F19" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="20"/>
       <c r="H19" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="33.75">
       <c r="A20" s="15">
         <v>18</v>
       </c>
@@ -6193,11 +6230,13 @@
       <c r="E20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="F20" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="20"/>
       <c r="H20" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="33.75">
       <c r="A21" s="15">
         <v>19</v>
       </c>
@@ -6213,11 +6252,13 @@
       <c r="E21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="F21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="20"/>
       <c r="H21" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="33.75">
       <c r="A22" s="15">
         <v>20</v>
       </c>
@@ -6234,10 +6275,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+      <c r="G22" s="20"/>
       <c r="H22" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="33.75">
       <c r="A23" s="15">
         <v>21</v>
       </c>
@@ -6254,10 +6295,10 @@
         <v>37</v>
       </c>
       <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
+      <c r="G23" s="20"/>
       <c r="H23" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="33.75">
       <c r="A24" s="15">
         <v>22</v>
       </c>
@@ -6274,10 +6315,10 @@
         <v>37</v>
       </c>
       <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
+      <c r="G24" s="20"/>
       <c r="H24" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="33.75">
       <c r="A25" s="15">
         <v>23</v>
       </c>
@@ -6299,7 +6340,7 @@
       </c>
       <c r="H25" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="15">
         <v>24</v>
       </c>
@@ -6321,7 +6362,7 @@
       </c>
       <c r="H26" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="33.75">
       <c r="A27" s="15">
         <v>25</v>
       </c>
@@ -6338,10 +6379,10 @@
         <v>42</v>
       </c>
       <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+      <c r="G27" s="20"/>
       <c r="H27" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="15">
         <v>26</v>
       </c>
@@ -6358,10 +6399,10 @@
         <v>42</v>
       </c>
       <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+      <c r="G28" s="20"/>
       <c r="H28" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="33.75">
       <c r="A29" s="15">
         <v>27</v>
       </c>
@@ -6378,10 +6419,10 @@
         <v>42</v>
       </c>
       <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+      <c r="G29" s="20"/>
       <c r="H29" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="33.75">
       <c r="A30" s="15">
         <v>28</v>
       </c>
@@ -6398,10 +6439,10 @@
         <v>42</v>
       </c>
       <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
+      <c r="G30" s="20"/>
       <c r="H30" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="33.75">
       <c r="A31" s="15">
         <v>29</v>
       </c>
@@ -6418,7 +6459,7 @@
         <v>42</v>
       </c>
       <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
+      <c r="G31" s="20"/>
       <c r="H31" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -6438,7 +6479,7 @@
         <v>42</v>
       </c>
       <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+      <c r="G32" s="20"/>
       <c r="H32" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="33">
@@ -6458,7 +6499,7 @@
         <v>42</v>
       </c>
       <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+      <c r="G33" s="20"/>
       <c r="H33" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="33">
@@ -6478,7 +6519,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
+      <c r="G34" s="20"/>
       <c r="H34" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="33">
@@ -6498,7 +6539,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+      <c r="G35" s="20"/>
       <c r="H35" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="33">
@@ -6518,7 +6559,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
+      <c r="G36" s="20"/>
       <c r="H36" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="33">
@@ -6538,7 +6579,7 @@
         <v>50</v>
       </c>
       <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
+      <c r="G37" s="20"/>
       <c r="H37" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="33">
@@ -6558,7 +6599,7 @@
         <v>55</v>
       </c>
       <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
+      <c r="G38" s="20"/>
       <c r="H38" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
@@ -6578,7 +6619,7 @@
         <v>55</v>
       </c>
       <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
+      <c r="G39" s="20"/>
       <c r="H39" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="33">
@@ -6598,7 +6639,7 @@
         <v>55</v>
       </c>
       <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
+      <c r="G40" s="20"/>
       <c r="H40" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="33">
@@ -6618,7 +6659,7 @@
         <v>55</v>
       </c>
       <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
+      <c r="G41" s="20"/>
       <c r="H41" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="33">
@@ -6638,7 +6679,7 @@
         <v>55</v>
       </c>
       <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
+      <c r="G42" s="20"/>
       <c r="H42" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="33">
@@ -6658,7 +6699,7 @@
         <v>55</v>
       </c>
       <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
+      <c r="G43" s="20"/>
       <c r="H43" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="33">
@@ -6722,7 +6763,7 @@
         <v>62</v>
       </c>
       <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
+      <c r="G46" s="20"/>
       <c r="H46" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="33">
@@ -6742,7 +6783,7 @@
         <v>62</v>
       </c>
       <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
+      <c r="G47" s="20"/>
       <c r="H47" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="33">
@@ -6762,7 +6803,7 @@
         <v>62</v>
       </c>
       <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
+      <c r="G48" s="20"/>
       <c r="H48" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="33">
@@ -6782,7 +6823,7 @@
         <v>62</v>
       </c>
       <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
+      <c r="G49" s="20"/>
       <c r="H49" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="33">
@@ -6802,7 +6843,7 @@
         <v>62</v>
       </c>
       <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
+      <c r="G50" s="20"/>
       <c r="H50" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="33">
@@ -6822,7 +6863,7 @@
         <v>62</v>
       </c>
       <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
+      <c r="G51" s="20"/>
       <c r="H51" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="33">
@@ -6842,7 +6883,7 @@
         <v>62</v>
       </c>
       <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
+      <c r="G52" s="20"/>
       <c r="H52" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="33">
@@ -6862,7 +6903,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
+      <c r="G53" s="20"/>
       <c r="H53" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
@@ -6882,7 +6923,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
+      <c r="G54" s="20"/>
       <c r="H54" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
@@ -6902,7 +6943,7 @@
         <v>71</v>
       </c>
       <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
+      <c r="G55" s="20"/>
       <c r="H55" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -6922,7 +6963,7 @@
         <v>71</v>
       </c>
       <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
+      <c r="G56" s="20"/>
       <c r="H56" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
@@ -6942,7 +6983,7 @@
         <v>71</v>
       </c>
       <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
+      <c r="G57" s="20"/>
       <c r="H57" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
@@ -6962,7 +7003,7 @@
         <v>71</v>
       </c>
       <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
+      <c r="G58" s="20"/>
       <c r="H58" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -6982,7 +7023,7 @@
         <v>71</v>
       </c>
       <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
+      <c r="G59" s="20"/>
       <c r="H59" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
@@ -7002,7 +7043,7 @@
         <v>71</v>
       </c>
       <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
+      <c r="G60" s="20"/>
       <c r="H60" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
@@ -7022,7 +7063,7 @@
         <v>80</v>
       </c>
       <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
+      <c r="G61" s="20"/>
       <c r="H61" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
@@ -7042,7 +7083,7 @@
         <v>80</v>
       </c>
       <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
+      <c r="G62" s="20"/>
       <c r="H62" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -7062,7 +7103,7 @@
         <v>80</v>
       </c>
       <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
+      <c r="G63" s="20"/>
       <c r="H63" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
@@ -7082,7 +7123,7 @@
         <v>80</v>
       </c>
       <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
+      <c r="G64" s="20"/>
       <c r="H64" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -7146,7 +7187,7 @@
         <v>86</v>
       </c>
       <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
+      <c r="G67" s="20"/>
       <c r="H67" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -7166,17 +7207,17 @@
         <v>86</v>
       </c>
       <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
+      <c r="G68" s="20"/>
       <c r="H68" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="21"/>
       <c r="B69" s="22"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="32"/>
       <c r="E69" s="2"/>
       <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
+      <c r="G69" s="33"/>
       <c r="H69" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="29" customFormat="1" s="1">
@@ -7188,7 +7229,7 @@
       <c r="D70" s="26"/>
       <c r="E70" s="2"/>
       <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
+      <c r="G70" s="11"/>
       <c r="H70" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -7210,7 +7251,7 @@
       <c r="F71" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G71" s="14" t="s">
+      <c r="G71" s="13" t="s">
         <v>6</v>
       </c>
       <c r="H71" s="2"/>
@@ -7232,7 +7273,7 @@
         <v>90</v>
       </c>
       <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
+      <c r="G72" s="30"/>
       <c r="H72" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -7252,7 +7293,7 @@
         <v>90</v>
       </c>
       <c r="F73" s="17"/>
-      <c r="G73" s="19"/>
+      <c r="G73" s="30"/>
       <c r="H73" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -7272,7 +7313,7 @@
         <v>90</v>
       </c>
       <c r="F74" s="17"/>
-      <c r="G74" s="19"/>
+      <c r="G74" s="30"/>
       <c r="H74" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -7292,7 +7333,7 @@
         <v>90</v>
       </c>
       <c r="F75" s="17"/>
-      <c r="G75" s="19"/>
+      <c r="G75" s="30"/>
       <c r="H75" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -7312,7 +7353,7 @@
         <v>90</v>
       </c>
       <c r="F76" s="17"/>
-      <c r="G76" s="19"/>
+      <c r="G76" s="30"/>
       <c r="H76" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -7332,7 +7373,7 @@
         <v>90</v>
       </c>
       <c r="F77" s="17"/>
-      <c r="G77" s="19"/>
+      <c r="G77" s="30"/>
       <c r="H77" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -7352,7 +7393,7 @@
         <v>90</v>
       </c>
       <c r="F78" s="17"/>
-      <c r="G78" s="19"/>
+      <c r="G78" s="30"/>
       <c r="H78" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
@@ -7372,7 +7413,7 @@
         <v>90</v>
       </c>
       <c r="F79" s="17"/>
-      <c r="G79" s="19"/>
+      <c r="G79" s="30"/>
       <c r="H79" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
@@ -7392,7 +7433,7 @@
         <v>90</v>
       </c>
       <c r="F80" s="17"/>
-      <c r="G80" s="19"/>
+      <c r="G80" s="30"/>
       <c r="H80" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
@@ -7412,7 +7453,7 @@
         <v>90</v>
       </c>
       <c r="F81" s="17"/>
-      <c r="G81" s="19"/>
+      <c r="G81" s="30"/>
       <c r="H81" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
@@ -7432,7 +7473,7 @@
         <v>101</v>
       </c>
       <c r="F82" s="17"/>
-      <c r="G82" s="19"/>
+      <c r="G82" s="30"/>
       <c r="H82" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
@@ -7452,7 +7493,7 @@
         <v>101</v>
       </c>
       <c r="F83" s="17"/>
-      <c r="G83" s="19"/>
+      <c r="G83" s="30"/>
       <c r="H83" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
@@ -7472,7 +7513,7 @@
         <v>101</v>
       </c>
       <c r="F84" s="17"/>
-      <c r="G84" s="19"/>
+      <c r="G84" s="30"/>
       <c r="H84" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
@@ -7492,7 +7533,7 @@
         <v>101</v>
       </c>
       <c r="F85" s="17"/>
-      <c r="G85" s="19"/>
+      <c r="G85" s="30"/>
       <c r="H85" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
@@ -7512,7 +7553,7 @@
         <v>101</v>
       </c>
       <c r="F86" s="17"/>
-      <c r="G86" s="19"/>
+      <c r="G86" s="30"/>
       <c r="H86" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
@@ -7532,7 +7573,7 @@
         <v>101</v>
       </c>
       <c r="F87" s="17"/>
-      <c r="G87" s="19"/>
+      <c r="G87" s="30"/>
       <c r="H87" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
@@ -7552,7 +7593,7 @@
         <v>101</v>
       </c>
       <c r="F88" s="17"/>
-      <c r="G88" s="17"/>
+      <c r="G88" s="20"/>
       <c r="H88" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
@@ -7572,7 +7613,7 @@
         <v>109</v>
       </c>
       <c r="F89" s="17"/>
-      <c r="G89" s="17"/>
+      <c r="G89" s="20"/>
       <c r="H89" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
@@ -7592,7 +7633,7 @@
         <v>109</v>
       </c>
       <c r="F90" s="17"/>
-      <c r="G90" s="17"/>
+      <c r="G90" s="20"/>
       <c r="H90" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
@@ -7612,7 +7653,7 @@
         <v>109</v>
       </c>
       <c r="F91" s="17"/>
-      <c r="G91" s="17"/>
+      <c r="G91" s="20"/>
       <c r="H91" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
@@ -7632,7 +7673,7 @@
         <v>109</v>
       </c>
       <c r="F92" s="17"/>
-      <c r="G92" s="17"/>
+      <c r="G92" s="20"/>
       <c r="H92" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
@@ -7652,7 +7693,7 @@
         <v>109</v>
       </c>
       <c r="F93" s="17"/>
-      <c r="G93" s="17"/>
+      <c r="G93" s="20"/>
       <c r="H93" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
@@ -7672,7 +7713,7 @@
         <v>109</v>
       </c>
       <c r="F94" s="17"/>
-      <c r="G94" s="17"/>
+      <c r="G94" s="20"/>
       <c r="H94" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
@@ -7736,7 +7777,7 @@
         <v>117</v>
       </c>
       <c r="F97" s="17"/>
-      <c r="G97" s="17"/>
+      <c r="G97" s="20"/>
       <c r="H97" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="19.5">
@@ -7756,7 +7797,7 @@
         <v>117</v>
       </c>
       <c r="F98" s="17"/>
-      <c r="G98" s="17"/>
+      <c r="G98" s="20"/>
       <c r="H98" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="19.5">
@@ -7776,7 +7817,7 @@
         <v>117</v>
       </c>
       <c r="F99" s="17"/>
-      <c r="G99" s="17"/>
+      <c r="G99" s="20"/>
       <c r="H99" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="19.5">
@@ -7796,7 +7837,7 @@
         <v>117</v>
       </c>
       <c r="F100" s="17"/>
-      <c r="G100" s="17"/>
+      <c r="G100" s="20"/>
       <c r="H100" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="19.5">
@@ -7816,7 +7857,7 @@
         <v>117</v>
       </c>
       <c r="F101" s="17"/>
-      <c r="G101" s="17"/>
+      <c r="G101" s="20"/>
       <c r="H101" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="19.5">
@@ -7836,7 +7877,7 @@
         <v>124</v>
       </c>
       <c r="F102" s="17"/>
-      <c r="G102" s="17"/>
+      <c r="G102" s="20"/>
       <c r="H102" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="19.5">
@@ -7856,7 +7897,7 @@
         <v>124</v>
       </c>
       <c r="F103" s="17"/>
-      <c r="G103" s="17"/>
+      <c r="G103" s="20"/>
       <c r="H103" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="19.5">
@@ -7876,7 +7917,7 @@
         <v>124</v>
       </c>
       <c r="F104" s="17"/>
-      <c r="G104" s="17"/>
+      <c r="G104" s="20"/>
       <c r="H104" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="19.5">
@@ -7896,7 +7937,7 @@
         <v>124</v>
       </c>
       <c r="F105" s="17"/>
-      <c r="G105" s="17"/>
+      <c r="G105" s="20"/>
       <c r="H105" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
@@ -7916,7 +7957,7 @@
         <v>124</v>
       </c>
       <c r="F106" s="17"/>
-      <c r="G106" s="17"/>
+      <c r="G106" s="20"/>
       <c r="H106" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
@@ -7936,7 +7977,7 @@
         <v>130</v>
       </c>
       <c r="F107" s="17"/>
-      <c r="G107" s="17"/>
+      <c r="G107" s="20"/>
       <c r="H107" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
@@ -7956,7 +7997,7 @@
         <v>130</v>
       </c>
       <c r="F108" s="17"/>
-      <c r="G108" s="17"/>
+      <c r="G108" s="20"/>
       <c r="H108" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
@@ -7976,7 +8017,7 @@
         <v>130</v>
       </c>
       <c r="F109" s="17"/>
-      <c r="G109" s="17"/>
+      <c r="G109" s="20"/>
       <c r="H109" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
@@ -7996,7 +8037,7 @@
         <v>130</v>
       </c>
       <c r="F110" s="17"/>
-      <c r="G110" s="17"/>
+      <c r="G110" s="20"/>
       <c r="H110" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
@@ -8060,7 +8101,7 @@
         <v>136</v>
       </c>
       <c r="F113" s="17"/>
-      <c r="G113" s="17"/>
+      <c r="G113" s="20"/>
       <c r="H113" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
@@ -8080,7 +8121,7 @@
         <v>136</v>
       </c>
       <c r="F114" s="17"/>
-      <c r="G114" s="17"/>
+      <c r="G114" s="20"/>
       <c r="H114" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
@@ -8100,7 +8141,7 @@
         <v>136</v>
       </c>
       <c r="F115" s="17"/>
-      <c r="G115" s="17"/>
+      <c r="G115" s="20"/>
       <c r="H115" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
@@ -8120,7 +8161,7 @@
         <v>136</v>
       </c>
       <c r="F116" s="17"/>
-      <c r="G116" s="17"/>
+      <c r="G116" s="20"/>
       <c r="H116" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
@@ -8140,7 +8181,7 @@
         <v>142</v>
       </c>
       <c r="F117" s="17"/>
-      <c r="G117" s="17"/>
+      <c r="G117" s="20"/>
       <c r="H117" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
@@ -8160,7 +8201,7 @@
         <v>142</v>
       </c>
       <c r="F118" s="17"/>
-      <c r="G118" s="17"/>
+      <c r="G118" s="20"/>
       <c r="H118" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
@@ -8180,7 +8221,7 @@
         <v>142</v>
       </c>
       <c r="F119" s="17"/>
-      <c r="G119" s="17"/>
+      <c r="G119" s="20"/>
       <c r="H119" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
@@ -8200,7 +8241,7 @@
         <v>142</v>
       </c>
       <c r="F120" s="17"/>
-      <c r="G120" s="17"/>
+      <c r="G120" s="20"/>
       <c r="H120" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
@@ -8220,7 +8261,7 @@
         <v>142</v>
       </c>
       <c r="F121" s="17"/>
-      <c r="G121" s="17"/>
+      <c r="G121" s="20"/>
       <c r="H121" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
@@ -8240,7 +8281,7 @@
         <v>142</v>
       </c>
       <c r="F122" s="17"/>
-      <c r="G122" s="17"/>
+      <c r="G122" s="20"/>
       <c r="H122" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
@@ -8260,7 +8301,7 @@
         <v>149</v>
       </c>
       <c r="F123" s="17"/>
-      <c r="G123" s="17"/>
+      <c r="G123" s="20"/>
       <c r="H123" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
@@ -8280,7 +8321,7 @@
         <v>149</v>
       </c>
       <c r="F124" s="17"/>
-      <c r="G124" s="17"/>
+      <c r="G124" s="20"/>
       <c r="H124" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
@@ -8300,7 +8341,7 @@
         <v>149</v>
       </c>
       <c r="F125" s="17"/>
-      <c r="G125" s="17"/>
+      <c r="G125" s="20"/>
       <c r="H125" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
@@ -8320,7 +8361,7 @@
         <v>149</v>
       </c>
       <c r="F126" s="17"/>
-      <c r="G126" s="17"/>
+      <c r="G126" s="20"/>
       <c r="H126" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
@@ -8340,7 +8381,7 @@
         <v>149</v>
       </c>
       <c r="F127" s="17"/>
-      <c r="G127" s="17"/>
+      <c r="G127" s="20"/>
       <c r="H127" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
@@ -8404,7 +8445,7 @@
         <v>156</v>
       </c>
       <c r="F130" s="17"/>
-      <c r="G130" s="17"/>
+      <c r="G130" s="20"/>
       <c r="H130" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
@@ -8424,7 +8465,7 @@
         <v>156</v>
       </c>
       <c r="F131" s="17"/>
-      <c r="G131" s="17"/>
+      <c r="G131" s="20"/>
       <c r="H131" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
@@ -8444,7 +8485,7 @@
         <v>156</v>
       </c>
       <c r="F132" s="17"/>
-      <c r="G132" s="17"/>
+      <c r="G132" s="20"/>
       <c r="H132" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
@@ -8464,7 +8505,7 @@
         <v>156</v>
       </c>
       <c r="F133" s="17"/>
-      <c r="G133" s="17"/>
+      <c r="G133" s="20"/>
       <c r="H133" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
@@ -8484,7 +8525,7 @@
         <v>156</v>
       </c>
       <c r="F134" s="17"/>
-      <c r="G134" s="17"/>
+      <c r="G134" s="20"/>
       <c r="H134" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
@@ -8504,7 +8545,7 @@
         <v>163</v>
       </c>
       <c r="F135" s="17"/>
-      <c r="G135" s="17"/>
+      <c r="G135" s="20"/>
       <c r="H135" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
@@ -8524,7 +8565,7 @@
         <v>163</v>
       </c>
       <c r="F136" s="17"/>
-      <c r="G136" s="17"/>
+      <c r="G136" s="20"/>
       <c r="H136" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
@@ -8544,7 +8585,7 @@
         <v>163</v>
       </c>
       <c r="F137" s="17"/>
-      <c r="G137" s="17"/>
+      <c r="G137" s="20"/>
       <c r="H137" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
@@ -8564,7 +8605,7 @@
         <v>163</v>
       </c>
       <c r="F138" s="17"/>
-      <c r="G138" s="17"/>
+      <c r="G138" s="20"/>
       <c r="H138" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
@@ -8584,7 +8625,7 @@
         <v>163</v>
       </c>
       <c r="F139" s="17"/>
-      <c r="G139" s="17"/>
+      <c r="G139" s="20"/>
       <c r="H139" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
@@ -8604,7 +8645,7 @@
         <v>169</v>
       </c>
       <c r="F140" s="17"/>
-      <c r="G140" s="17"/>
+      <c r="G140" s="20"/>
       <c r="H140" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
@@ -8624,7 +8665,7 @@
         <v>169</v>
       </c>
       <c r="F141" s="17"/>
-      <c r="G141" s="17"/>
+      <c r="G141" s="20"/>
       <c r="H141" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
@@ -8644,7 +8685,7 @@
         <v>169</v>
       </c>
       <c r="F142" s="17"/>
-      <c r="G142" s="17"/>
+      <c r="G142" s="20"/>
       <c r="H142" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
@@ -8664,7 +8705,7 @@
         <v>169</v>
       </c>
       <c r="F143" s="17"/>
-      <c r="G143" s="17"/>
+      <c r="G143" s="20"/>
       <c r="H143" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
@@ -8684,7 +8725,7 @@
         <v>169</v>
       </c>
       <c r="F144" s="17"/>
-      <c r="G144" s="17"/>
+      <c r="G144" s="20"/>
       <c r="H144" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
@@ -8704,7 +8745,7 @@
         <v>169</v>
       </c>
       <c r="F145" s="17"/>
-      <c r="G145" s="17"/>
+      <c r="G145" s="20"/>
       <c r="H145" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
@@ -8746,7 +8787,7 @@
         <v>176</v>
       </c>
       <c r="F147" s="17"/>
-      <c r="G147" s="17"/>
+      <c r="G147" s="20"/>
       <c r="H147" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
@@ -8756,7 +8797,7 @@
       <c r="B148" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="C148" s="32" t="s">
+      <c r="C148" s="34" t="s">
         <v>179</v>
       </c>
       <c r="D148" s="18">
@@ -8766,7 +8807,7 @@
         <v>180</v>
       </c>
       <c r="F148" s="17"/>
-      <c r="G148" s="17"/>
+      <c r="G148" s="20"/>
       <c r="H148" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
@@ -8776,7 +8817,7 @@
       <c r="B149" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C149" s="32" t="s">
+      <c r="C149" s="34" t="s">
         <v>179</v>
       </c>
       <c r="D149" s="18">
@@ -8786,7 +8827,7 @@
         <v>182</v>
       </c>
       <c r="F149" s="17"/>
-      <c r="G149" s="17"/>
+      <c r="G149" s="20"/>
       <c r="H149" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
@@ -8796,7 +8837,7 @@
       <c r="B150" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C150" s="32" t="s">
+      <c r="C150" s="34" t="s">
         <v>179</v>
       </c>
       <c r="D150" s="18">
@@ -8806,7 +8847,7 @@
         <v>184</v>
       </c>
       <c r="F150" s="17"/>
-      <c r="G150" s="17"/>
+      <c r="G150" s="20"/>
       <c r="H150" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
@@ -8816,7 +8857,7 @@
       <c r="B151" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="C151" s="32" t="s">
+      <c r="C151" s="34" t="s">
         <v>179</v>
       </c>
       <c r="D151" s="18">
@@ -8826,7 +8867,7 @@
         <v>186</v>
       </c>
       <c r="F151" s="17"/>
-      <c r="G151" s="17"/>
+      <c r="G151" s="20"/>
       <c r="H151" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
@@ -8836,7 +8877,7 @@
       <c r="B152" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C152" s="32" t="s">
+      <c r="C152" s="34" t="s">
         <v>179</v>
       </c>
       <c r="D152" s="18">
@@ -8846,7 +8887,7 @@
         <v>188</v>
       </c>
       <c r="F152" s="17"/>
-      <c r="G152" s="17"/>
+      <c r="G152" s="20"/>
       <c r="H152" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
@@ -8856,7 +8897,7 @@
       <c r="B153" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="C153" s="32" t="s">
+      <c r="C153" s="34" t="s">
         <v>179</v>
       </c>
       <c r="D153" s="18">
@@ -8866,157 +8907,157 @@
         <v>190</v>
       </c>
       <c r="F153" s="17"/>
-      <c r="G153" s="17"/>
+      <c r="G153" s="20"/>
       <c r="H153" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="21"/>
       <c r="B154" s="22"/>
-      <c r="C154" s="30"/>
-      <c r="D154" s="31"/>
+      <c r="C154" s="31"/>
+      <c r="D154" s="32"/>
       <c r="E154" s="2"/>
       <c r="F154" s="22"/>
-      <c r="G154" s="22"/>
+      <c r="G154" s="33"/>
       <c r="H154" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="21"/>
       <c r="B155" s="22"/>
-      <c r="C155" s="30"/>
-      <c r="D155" s="31"/>
+      <c r="C155" s="31"/>
+      <c r="D155" s="32"/>
       <c r="E155" s="2"/>
       <c r="F155" s="22"/>
-      <c r="G155" s="22"/>
+      <c r="G155" s="33"/>
       <c r="H155" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="21"/>
       <c r="B156" s="22"/>
-      <c r="C156" s="30"/>
-      <c r="D156" s="31"/>
+      <c r="C156" s="31"/>
+      <c r="D156" s="32"/>
       <c r="E156" s="2"/>
       <c r="F156" s="22"/>
-      <c r="G156" s="22"/>
+      <c r="G156" s="33"/>
       <c r="H156" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="21"/>
       <c r="B157" s="22"/>
-      <c r="C157" s="30"/>
-      <c r="D157" s="31"/>
+      <c r="C157" s="31"/>
+      <c r="D157" s="32"/>
       <c r="E157" s="2"/>
       <c r="F157" s="22"/>
-      <c r="G157" s="22"/>
+      <c r="G157" s="33"/>
       <c r="H157" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="21"/>
       <c r="B158" s="22"/>
-      <c r="C158" s="30"/>
-      <c r="D158" s="31"/>
+      <c r="C158" s="31"/>
+      <c r="D158" s="32"/>
       <c r="E158" s="2"/>
       <c r="F158" s="22"/>
-      <c r="G158" s="22"/>
+      <c r="G158" s="33"/>
       <c r="H158" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="21"/>
       <c r="B159" s="22"/>
-      <c r="C159" s="30"/>
-      <c r="D159" s="31"/>
+      <c r="C159" s="31"/>
+      <c r="D159" s="32"/>
       <c r="E159" s="2"/>
       <c r="F159" s="22"/>
-      <c r="G159" s="22"/>
+      <c r="G159" s="33"/>
       <c r="H159" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="21"/>
       <c r="B160" s="22"/>
-      <c r="C160" s="30"/>
-      <c r="D160" s="31"/>
+      <c r="C160" s="31"/>
+      <c r="D160" s="32"/>
       <c r="E160" s="2"/>
       <c r="F160" s="22"/>
-      <c r="G160" s="22"/>
+      <c r="G160" s="33"/>
       <c r="H160" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="21"/>
       <c r="B161" s="22"/>
-      <c r="C161" s="30"/>
-      <c r="D161" s="31"/>
+      <c r="C161" s="31"/>
+      <c r="D161" s="32"/>
       <c r="E161" s="2"/>
       <c r="F161" s="22"/>
-      <c r="G161" s="22"/>
+      <c r="G161" s="33"/>
       <c r="H161" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="21"/>
       <c r="B162" s="22"/>
-      <c r="C162" s="30"/>
-      <c r="D162" s="31"/>
+      <c r="C162" s="31"/>
+      <c r="D162" s="32"/>
       <c r="E162" s="2"/>
       <c r="F162" s="22"/>
-      <c r="G162" s="22"/>
+      <c r="G162" s="33"/>
       <c r="H162" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="21"/>
       <c r="B163" s="22"/>
-      <c r="C163" s="30"/>
-      <c r="D163" s="31"/>
+      <c r="C163" s="31"/>
+      <c r="D163" s="32"/>
       <c r="E163" s="2"/>
       <c r="F163" s="22"/>
-      <c r="G163" s="22"/>
+      <c r="G163" s="33"/>
       <c r="H163" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="21"/>
       <c r="B164" s="22"/>
-      <c r="C164" s="30"/>
-      <c r="D164" s="31"/>
+      <c r="C164" s="31"/>
+      <c r="D164" s="32"/>
       <c r="E164" s="2"/>
       <c r="F164" s="22"/>
-      <c r="G164" s="22"/>
+      <c r="G164" s="33"/>
       <c r="H164" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="21"/>
       <c r="B165" s="22"/>
-      <c r="C165" s="30"/>
-      <c r="D165" s="31"/>
+      <c r="C165" s="31"/>
+      <c r="D165" s="32"/>
       <c r="E165" s="2"/>
       <c r="F165" s="22"/>
-      <c r="G165" s="22"/>
+      <c r="G165" s="33"/>
       <c r="H165" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="21"/>
       <c r="B166" s="22"/>
-      <c r="C166" s="30"/>
-      <c r="D166" s="31"/>
+      <c r="C166" s="31"/>
+      <c r="D166" s="32"/>
       <c r="E166" s="2"/>
       <c r="F166" s="22"/>
-      <c r="G166" s="22"/>
+      <c r="G166" s="33"/>
       <c r="H166" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="21"/>
       <c r="B167" s="22"/>
-      <c r="C167" s="30"/>
-      <c r="D167" s="31"/>
+      <c r="C167" s="31"/>
+      <c r="D167" s="32"/>
       <c r="E167" s="2"/>
       <c r="F167" s="22"/>
-      <c r="G167" s="22"/>
+      <c r="G167" s="33"/>
       <c r="H167" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="21"/>
       <c r="B168" s="22"/>
-      <c r="C168" s="30"/>
-      <c r="D168" s="31"/>
+      <c r="C168" s="31"/>
+      <c r="D168" s="32"/>
       <c r="E168" s="2"/>
       <c r="F168" s="22"/>
-      <c r="G168" s="22"/>
+      <c r="G168" s="33"/>
       <c r="H168" s="2"/>
     </row>
   </sheetData>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="363">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -1120,7 +1120,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1168,12 +1168,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1232,7 +1226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1330,9 +1324,6 @@
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1341,9 +1332,6 @@
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1387,7 +1375,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1701,11 +1689,11 @@
     <col min="1" max="1" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="53" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="50" width="38.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="51" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="48" width="38.86214285714286" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="23" width="7.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="50" width="23.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="50" width="41.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="48" width="23.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="48" width="41.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -1713,10 +1701,10 @@
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
       <c r="D1" s="21"/>
-      <c r="E1" s="38"/>
+      <c r="E1" s="36"/>
       <c r="F1" s="21"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="22"/>
@@ -1728,7 +1716,7 @@
       <c r="E2" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="49" t="s">
         <v>320</v>
       </c>
       <c r="G2" s="14" t="s">
@@ -1828,7 +1816,7 @@
       <c r="G7" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="50" t="s">
         <v>329</v>
       </c>
     </row>
@@ -1974,7 +1962,7 @@
       <c r="G15" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="50" t="s">
         <v>340</v>
       </c>
     </row>
@@ -1994,7 +1982,7 @@
       <c r="G16" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="50" t="s">
         <v>342</v>
       </c>
     </row>
@@ -2014,7 +2002,7 @@
       <c r="G17" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="50" t="s">
         <v>344</v>
       </c>
     </row>
@@ -2049,82 +2037,82 @@
       <c r="F19" s="21">
         <v>1</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="H19" s="38"/>
+      <c r="H19" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="51">
+      <c r="D20" s="49">
         <v>18</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="36" t="s">
         <v>347</v>
       </c>
       <c r="F20" s="21">
         <v>2</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="H20" s="38"/>
+      <c r="H20" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="51">
+      <c r="D21" s="49">
         <v>19</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="36" t="s">
         <v>348</v>
       </c>
       <c r="F21" s="21">
         <v>1</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G21" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="H21" s="38"/>
+      <c r="H21" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="51">
+      <c r="D22" s="49">
         <v>20</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="36" t="s">
         <v>349</v>
       </c>
       <c r="F22" s="21">
         <v>1</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="G22" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="H22" s="38"/>
+      <c r="H22" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
-      <c r="D23" s="51">
+      <c r="D23" s="49">
         <v>21</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="36" t="s">
         <v>350</v>
       </c>
       <c r="F23" s="21">
         <v>1</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="G23" s="36" t="s">
         <v>351</v>
       </c>
-      <c r="H23" s="38" t="s">
+      <c r="H23" s="36" t="s">
         <v>352</v>
       </c>
     </row>
@@ -2132,19 +2120,19 @@
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="51">
+      <c r="D24" s="49">
         <v>22</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="36" t="s">
         <v>353</v>
       </c>
       <c r="F24" s="21">
         <v>1</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="36" t="s">
         <v>331</v>
       </c>
-      <c r="H24" s="38" t="s">
+      <c r="H24" s="36" t="s">
         <v>354</v>
       </c>
     </row>
@@ -2152,35 +2140,35 @@
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
-      <c r="D25" s="51">
+      <c r="D25" s="49">
         <v>23</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="36" t="s">
         <v>355</v>
       </c>
       <c r="F25" s="21">
         <v>1</v>
       </c>
-      <c r="G25" s="38" t="s">
+      <c r="G25" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="H25" s="38"/>
+      <c r="H25" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
-      <c r="D26" s="51">
+      <c r="D26" s="49">
         <v>24</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="36" t="s">
         <v>356</v>
       </c>
       <c r="F26" s="21">
         <v>1</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25">
       <c r="A27" s="22"/>
@@ -2195,7 +2183,7 @@
       <c r="F27" s="21">
         <v>1</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="36" t="s">
         <v>331</v>
       </c>
       <c r="H27" s="17" t="s">
@@ -2206,19 +2194,19 @@
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
-      <c r="D28" s="51">
+      <c r="D28" s="49">
         <v>26</v>
       </c>
-      <c r="E28" s="38" t="s">
+      <c r="E28" s="36" t="s">
         <v>359</v>
       </c>
       <c r="F28" s="21">
         <v>1</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="H28" s="38" t="s">
+      <c r="H28" s="36" t="s">
         <v>360</v>
       </c>
     </row>
@@ -2226,19 +2214,19 @@
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
-      <c r="D29" s="51">
+      <c r="D29" s="49">
         <v>27</v>
       </c>
-      <c r="E29" s="38" t="s">
+      <c r="E29" s="36" t="s">
         <v>361</v>
       </c>
       <c r="F29" s="21">
         <v>1</v>
       </c>
-      <c r="G29" s="38" t="s">
+      <c r="G29" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="H29" s="38" t="s">
+      <c r="H29" s="36" t="s">
         <v>362</v>
       </c>
     </row>
@@ -2246,61 +2234,61 @@
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="38"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="36"/>
       <c r="F30" s="21"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="38"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="36"/>
       <c r="F31" s="21"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="38"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="21"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="38"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="36"/>
       <c r="F33" s="21"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="38"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="36"/>
       <c r="F34" s="21"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="38"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="36"/>
       <c r="F35" s="21"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20.25">
       <c r="A36" s="22"/>
@@ -2309,7 +2297,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="17"/>
       <c r="F36" s="21"/>
-      <c r="G36" s="38"/>
+      <c r="G36" s="36"/>
       <c r="H36" s="17"/>
     </row>
   </sheetData>
@@ -2326,97 +2314,97 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="23" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="50" width="60.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="35" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="36" width="7.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="48" width="60.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="34" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="35" width="7.719285714285714" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="50" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="50" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="50" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="48" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="48" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="48" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="21"/>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="36" t="s">
         <v>191</v>
       </c>
       <c r="C1" s="31"/>
       <c r="D1" s="32"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="47.25">
       <c r="A2" s="21">
         <v>1</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="36" t="s">
         <v>192</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="32"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="21">
         <v>2</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="36" t="s">
         <v>193</v>
       </c>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="21">
         <v>3</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="36" t="s">
         <v>194</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="32"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="21"/>
-      <c r="B5" s="38"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="31"/>
       <c r="D5" s="32"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="13" t="s">
@@ -2443,7 +2431,7 @@
       <c r="H7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="38"/>
+      <c r="I7" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="33.75">
       <c r="A8" s="15">
@@ -2466,7 +2454,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="17"/>
-      <c r="I8" s="38"/>
+      <c r="I8" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="15">
@@ -2489,7 +2477,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="17"/>
-      <c r="I9" s="38"/>
+      <c r="I9" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="15">
@@ -2512,7 +2500,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="17"/>
-      <c r="I10" s="43" t="s">
+      <c r="I10" s="41" t="s">
         <v>201</v>
       </c>
     </row>
@@ -2537,7 +2525,7 @@
         <v>16</v>
       </c>
       <c r="H11" s="17"/>
-      <c r="I11" s="38"/>
+      <c r="I11" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="15">
@@ -2560,7 +2548,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="17"/>
-      <c r="I12" s="38"/>
+      <c r="I12" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="15">
@@ -2583,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="H13" s="17"/>
-      <c r="I13" s="38"/>
+      <c r="I13" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="15">
@@ -2606,7 +2594,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="17"/>
-      <c r="I14" s="38"/>
+      <c r="I14" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="15">
@@ -2629,7 +2617,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="17"/>
-      <c r="I15" s="38"/>
+      <c r="I15" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="15">
@@ -2652,7 +2640,7 @@
         <v>16</v>
       </c>
       <c r="H16" s="17"/>
-      <c r="I16" s="38"/>
+      <c r="I16" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="15">
@@ -2675,7 +2663,7 @@
         <v>16</v>
       </c>
       <c r="H17" s="17"/>
-      <c r="I17" s="38"/>
+      <c r="I17" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="15">
@@ -2698,7 +2686,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="17"/>
-      <c r="I18" s="38"/>
+      <c r="I18" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="15">
@@ -2721,7 +2709,7 @@
         <v>16</v>
       </c>
       <c r="H19" s="17"/>
-      <c r="I19" s="38"/>
+      <c r="I19" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="33.75">
       <c r="A20" s="15">
@@ -2744,7 +2732,7 @@
         <v>16</v>
       </c>
       <c r="H20" s="17"/>
-      <c r="I20" s="38"/>
+      <c r="I20" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="15">
@@ -2767,7 +2755,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="17"/>
-      <c r="I21" s="38"/>
+      <c r="I21" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="15">
@@ -2790,7 +2778,7 @@
         <v>16</v>
       </c>
       <c r="H22" s="17"/>
-      <c r="I22" s="38"/>
+      <c r="I22" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="15">
@@ -2813,7 +2801,7 @@
         <v>16</v>
       </c>
       <c r="H23" s="17"/>
-      <c r="I23" s="38"/>
+      <c r="I23" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="15">
@@ -2836,7 +2824,7 @@
         <v>16</v>
       </c>
       <c r="H24" s="17"/>
-      <c r="I24" s="38"/>
+      <c r="I24" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="15">
@@ -2859,7 +2847,7 @@
         <v>16</v>
       </c>
       <c r="H25" s="17"/>
-      <c r="I25" s="38"/>
+      <c r="I25" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="15">
@@ -2882,7 +2870,7 @@
         <v>16</v>
       </c>
       <c r="H26" s="17"/>
-      <c r="I26" s="38"/>
+      <c r="I26" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="33.75">
       <c r="A27" s="15">
@@ -2905,7 +2893,7 @@
         <v>16</v>
       </c>
       <c r="H27" s="17"/>
-      <c r="I27" s="38"/>
+      <c r="I27" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="15">
@@ -2928,7 +2916,7 @@
         <v>16</v>
       </c>
       <c r="H28" s="17"/>
-      <c r="I28" s="38"/>
+      <c r="I28" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="15">
@@ -2951,7 +2939,7 @@
         <v>16</v>
       </c>
       <c r="H29" s="17"/>
-      <c r="I29" s="38"/>
+      <c r="I29" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="15">
@@ -2974,7 +2962,7 @@
         <v>16</v>
       </c>
       <c r="H30" s="17"/>
-      <c r="I30" s="38"/>
+      <c r="I30" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="15">
@@ -2997,7 +2985,7 @@
         <v>16</v>
       </c>
       <c r="H31" s="17"/>
-      <c r="I31" s="38"/>
+      <c r="I31" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="15">
@@ -3020,7 +3008,7 @@
         <v>16</v>
       </c>
       <c r="H32" s="17"/>
-      <c r="I32" s="38"/>
+      <c r="I32" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="15">
@@ -3043,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="H33" s="17"/>
-      <c r="I33" s="38"/>
+      <c r="I33" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="15">
@@ -3066,7 +3054,7 @@
         <v>16</v>
       </c>
       <c r="H34" s="17"/>
-      <c r="I34" s="38"/>
+      <c r="I34" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="33.75">
       <c r="A35" s="15">
@@ -3089,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="H35" s="17"/>
-      <c r="I35" s="38"/>
+      <c r="I35" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="15">
@@ -3112,7 +3100,7 @@
         <v>16</v>
       </c>
       <c r="H36" s="17"/>
-      <c r="I36" s="38"/>
+      <c r="I36" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="15">
@@ -3135,7 +3123,7 @@
         <v>16</v>
       </c>
       <c r="H37" s="17"/>
-      <c r="I37" s="38"/>
+      <c r="I37" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="15">
@@ -3158,7 +3146,7 @@
         <v>16</v>
       </c>
       <c r="H38" s="17"/>
-      <c r="I38" s="38"/>
+      <c r="I38" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="33.75">
       <c r="A39" s="15">
@@ -3181,7 +3169,7 @@
         <v>16</v>
       </c>
       <c r="H39" s="17"/>
-      <c r="I39" s="38"/>
+      <c r="I39" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="15">
@@ -3204,7 +3192,7 @@
         <v>16</v>
       </c>
       <c r="H40" s="17"/>
-      <c r="I40" s="38"/>
+      <c r="I40" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="15">
@@ -3227,7 +3215,7 @@
         <v>16</v>
       </c>
       <c r="H41" s="17"/>
-      <c r="I41" s="38"/>
+      <c r="I41" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="15">
@@ -3250,7 +3238,7 @@
         <v>16</v>
       </c>
       <c r="H42" s="17"/>
-      <c r="I42" s="38"/>
+      <c r="I42" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="15">
@@ -3273,7 +3261,7 @@
         <v>16</v>
       </c>
       <c r="H43" s="17"/>
-      <c r="I43" s="38"/>
+      <c r="I43" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20.25">
       <c r="A44" s="15">
@@ -3296,18 +3284,18 @@
         <v>16</v>
       </c>
       <c r="H44" s="17"/>
-      <c r="I44" s="38"/>
+      <c r="I44" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="21"/>
-      <c r="B45" s="38"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="31"/>
       <c r="D45" s="32"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A46" s="11" t="s">
@@ -3347,7 +3335,7 @@
       <c r="H47" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I47" s="38"/>
+      <c r="I47" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="33.75">
       <c r="A48" s="15">
@@ -3370,7 +3358,7 @@
         <v>16</v>
       </c>
       <c r="H48" s="17"/>
-      <c r="I48" s="38"/>
+      <c r="I48" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="15">
@@ -3393,7 +3381,7 @@
         <v>16</v>
       </c>
       <c r="H49" s="17"/>
-      <c r="I49" s="38"/>
+      <c r="I49" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="15">
@@ -3416,7 +3404,7 @@
         <v>16</v>
       </c>
       <c r="H50" s="17"/>
-      <c r="I50" s="38"/>
+      <c r="I50" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
       <c r="A51" s="15">
@@ -3439,7 +3427,7 @@
         <v>16</v>
       </c>
       <c r="H51" s="17"/>
-      <c r="I51" s="38"/>
+      <c r="I51" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="15">
@@ -3462,7 +3450,7 @@
         <v>16</v>
       </c>
       <c r="H52" s="17"/>
-      <c r="I52" s="38"/>
+      <c r="I52" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="15">
@@ -3485,7 +3473,7 @@
         <v>16</v>
       </c>
       <c r="H53" s="17"/>
-      <c r="I53" s="38"/>
+      <c r="I53" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="15">
@@ -3508,7 +3496,7 @@
         <v>16</v>
       </c>
       <c r="H54" s="17"/>
-      <c r="I54" s="38"/>
+      <c r="I54" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
       <c r="A55" s="15">
@@ -3531,7 +3519,7 @@
         <v>16</v>
       </c>
       <c r="H55" s="17"/>
-      <c r="I55" s="38"/>
+      <c r="I55" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
       <c r="A56" s="15">
@@ -3554,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="H56" s="17"/>
-      <c r="I56" s="38"/>
+      <c r="I56" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="15">
@@ -3577,7 +3565,7 @@
         <v>16</v>
       </c>
       <c r="H57" s="17"/>
-      <c r="I57" s="38"/>
+      <c r="I57" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="33.75">
       <c r="A58" s="15">
@@ -3600,7 +3588,7 @@
         <v>16</v>
       </c>
       <c r="H58" s="17"/>
-      <c r="I58" s="38"/>
+      <c r="I58" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
       <c r="A59" s="15">
@@ -3623,7 +3611,7 @@
         <v>16</v>
       </c>
       <c r="H59" s="17"/>
-      <c r="I59" s="38"/>
+      <c r="I59" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="15">
@@ -3646,7 +3634,7 @@
         <v>16</v>
       </c>
       <c r="H60" s="17"/>
-      <c r="I60" s="38"/>
+      <c r="I60" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="15">
@@ -3669,7 +3657,7 @@
         <v>16</v>
       </c>
       <c r="H61" s="17"/>
-      <c r="I61" s="38"/>
+      <c r="I61" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="20.25">
       <c r="A62" s="15">
@@ -3692,13 +3680,13 @@
         <v>16</v>
       </c>
       <c r="H62" s="17"/>
-      <c r="I62" s="38"/>
+      <c r="I62" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A63" s="44"/>
+      <c r="A63" s="42"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="46"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="44"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -3743,7 +3731,7 @@
       <c r="H65" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I65" s="38"/>
+      <c r="I65" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="15">
@@ -3766,7 +3754,7 @@
         <v>16</v>
       </c>
       <c r="H66" s="17"/>
-      <c r="I66" s="38"/>
+      <c r="I66" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="33.75">
       <c r="A67" s="15">
@@ -3789,7 +3777,7 @@
         <v>16</v>
       </c>
       <c r="H67" s="17"/>
-      <c r="I67" s="38"/>
+      <c r="I67" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="33.75">
       <c r="A68" s="15">
@@ -3812,7 +3800,7 @@
         <v>16</v>
       </c>
       <c r="H68" s="17"/>
-      <c r="I68" s="38"/>
+      <c r="I68" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="33.75">
       <c r="A69" s="15">
@@ -3835,7 +3823,7 @@
         <v>16</v>
       </c>
       <c r="H69" s="17"/>
-      <c r="I69" s="38"/>
+      <c r="I69" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="33.75">
       <c r="A70" s="15">
@@ -3858,7 +3846,7 @@
         <v>16</v>
       </c>
       <c r="H70" s="17"/>
-      <c r="I70" s="38"/>
+      <c r="I70" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="33.75">
       <c r="A71" s="15">
@@ -3881,7 +3869,7 @@
         <v>16</v>
       </c>
       <c r="H71" s="17"/>
-      <c r="I71" s="38"/>
+      <c r="I71" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="33.75">
       <c r="A72" s="15">
@@ -3904,7 +3892,7 @@
         <v>16</v>
       </c>
       <c r="H72" s="17"/>
-      <c r="I72" s="38"/>
+      <c r="I72" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="33.75">
       <c r="A73" s="15">
@@ -3927,7 +3915,7 @@
         <v>16</v>
       </c>
       <c r="H73" s="17"/>
-      <c r="I73" s="38"/>
+      <c r="I73" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="33.75">
       <c r="A74" s="15">
@@ -3950,7 +3938,7 @@
         <v>16</v>
       </c>
       <c r="H74" s="17"/>
-      <c r="I74" s="38"/>
+      <c r="I74" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="33.75">
       <c r="A75" s="15">
@@ -3973,7 +3961,7 @@
         <v>16</v>
       </c>
       <c r="H75" s="17"/>
-      <c r="I75" s="38"/>
+      <c r="I75" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="20.25">
       <c r="A76" s="15">
@@ -3996,18 +3984,18 @@
         <v>16</v>
       </c>
       <c r="H76" s="17"/>
-      <c r="I76" s="38"/>
+      <c r="I76" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="21"/>
-      <c r="B77" s="38"/>
+      <c r="B77" s="36"/>
       <c r="C77" s="31"/>
       <c r="D77" s="32"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38"/>
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A78" s="11" t="s">
@@ -4047,7 +4035,7 @@
       <c r="H79" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I79" s="38"/>
+      <c r="I79" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="15">
@@ -4056,8 +4044,8 @@
       <c r="B80" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C80" s="47">
-        <v>32.1178125</v>
+      <c r="C80" s="45">
+        <v>33.11769675925926</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -4070,7 +4058,7 @@
         <v>16</v>
       </c>
       <c r="H80" s="19"/>
-      <c r="I80" s="38"/>
+      <c r="I80" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="15">
@@ -4079,8 +4067,8 @@
       <c r="B81" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C81" s="47">
-        <v>32.1178125</v>
+      <c r="C81" s="45">
+        <v>33.11769675925926</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -4093,7 +4081,7 @@
         <v>16</v>
       </c>
       <c r="H81" s="19"/>
-      <c r="I81" s="38"/>
+      <c r="I81" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="15">
@@ -4102,8 +4090,8 @@
       <c r="B82" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C82" s="47">
-        <v>32.1178125</v>
+      <c r="C82" s="45">
+        <v>33.11769675925926</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -4116,7 +4104,7 @@
         <v>16</v>
       </c>
       <c r="H82" s="19"/>
-      <c r="I82" s="38"/>
+      <c r="I82" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="15">
@@ -4125,8 +4113,8 @@
       <c r="B83" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C83" s="47">
-        <v>32.1178125</v>
+      <c r="C83" s="45">
+        <v>33.11769675925926</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
@@ -4139,7 +4127,7 @@
         <v>16</v>
       </c>
       <c r="H83" s="19"/>
-      <c r="I83" s="38"/>
+      <c r="I83" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="15">
@@ -4162,7 +4150,7 @@
         <v>16</v>
       </c>
       <c r="H84" s="17"/>
-      <c r="I84" s="38"/>
+      <c r="I84" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="15">
@@ -4185,7 +4173,7 @@
         <v>16</v>
       </c>
       <c r="H85" s="17"/>
-      <c r="I85" s="38"/>
+      <c r="I85" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="15">
@@ -4208,7 +4196,7 @@
         <v>16</v>
       </c>
       <c r="H86" s="17"/>
-      <c r="I86" s="38"/>
+      <c r="I86" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="15">
@@ -4231,7 +4219,7 @@
         <v>16</v>
       </c>
       <c r="H87" s="17"/>
-      <c r="I87" s="38"/>
+      <c r="I87" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="15">
@@ -4254,7 +4242,7 @@
         <v>16</v>
       </c>
       <c r="H88" s="17"/>
-      <c r="I88" s="38"/>
+      <c r="I88" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="15">
@@ -4277,7 +4265,7 @@
         <v>16</v>
       </c>
       <c r="H89" s="17"/>
-      <c r="I89" s="38"/>
+      <c r="I89" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="15">
@@ -4300,7 +4288,7 @@
         <v>16</v>
       </c>
       <c r="H90" s="17"/>
-      <c r="I90" s="38"/>
+      <c r="I90" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="15">
@@ -4323,7 +4311,7 @@
         <v>16</v>
       </c>
       <c r="H91" s="17"/>
-      <c r="I91" s="38"/>
+      <c r="I91" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="15">
@@ -4346,7 +4334,7 @@
         <v>16</v>
       </c>
       <c r="H92" s="17"/>
-      <c r="I92" s="38"/>
+      <c r="I92" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="15">
@@ -4369,7 +4357,7 @@
         <v>16</v>
       </c>
       <c r="H93" s="17"/>
-      <c r="I93" s="38"/>
+      <c r="I93" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="15">
@@ -4392,7 +4380,7 @@
         <v>16</v>
       </c>
       <c r="H94" s="17"/>
-      <c r="I94" s="38"/>
+      <c r="I94" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="15">
@@ -4415,7 +4403,7 @@
         <v>16</v>
       </c>
       <c r="H95" s="17"/>
-      <c r="I95" s="38"/>
+      <c r="I95" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="15">
@@ -4438,7 +4426,7 @@
         <v>16</v>
       </c>
       <c r="H96" s="17"/>
-      <c r="I96" s="38"/>
+      <c r="I96" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="15">
@@ -4461,7 +4449,7 @@
         <v>16</v>
       </c>
       <c r="H97" s="17"/>
-      <c r="I97" s="38"/>
+      <c r="I97" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="15">
@@ -4484,7 +4472,7 @@
         <v>16</v>
       </c>
       <c r="H98" s="17"/>
-      <c r="I98" s="38"/>
+      <c r="I98" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="15">
@@ -4507,7 +4495,7 @@
         <v>16</v>
       </c>
       <c r="H99" s="17"/>
-      <c r="I99" s="38"/>
+      <c r="I99" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="15">
@@ -4530,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="H100" s="17"/>
-      <c r="I100" s="38"/>
+      <c r="I100" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="15">
@@ -4553,7 +4541,7 @@
         <v>16</v>
       </c>
       <c r="H101" s="17"/>
-      <c r="I101" s="38"/>
+      <c r="I101" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="15">
@@ -4576,7 +4564,7 @@
         <v>16</v>
       </c>
       <c r="H102" s="17"/>
-      <c r="I102" s="38"/>
+      <c r="I102" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="33">
       <c r="A103" s="15">
@@ -4599,7 +4587,7 @@
         <v>16</v>
       </c>
       <c r="H103" s="17"/>
-      <c r="I103" s="38"/>
+      <c r="I103" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="33.75">
       <c r="A104" s="15">
@@ -4622,7 +4610,7 @@
         <v>16</v>
       </c>
       <c r="H104" s="17"/>
-      <c r="I104" s="38"/>
+      <c r="I104" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="33">
       <c r="A105" s="15">
@@ -4645,7 +4633,7 @@
         <v>16</v>
       </c>
       <c r="H105" s="17"/>
-      <c r="I105" s="38"/>
+      <c r="I105" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="15">
@@ -4668,7 +4656,7 @@
         <v>16</v>
       </c>
       <c r="H106" s="17"/>
-      <c r="I106" s="38"/>
+      <c r="I106" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="15">
@@ -4691,7 +4679,7 @@
         <v>16</v>
       </c>
       <c r="H107" s="17"/>
-      <c r="I107" s="38"/>
+      <c r="I107" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="33">
       <c r="A108" s="15">
@@ -4714,7 +4702,7 @@
         <v>16</v>
       </c>
       <c r="H108" s="17"/>
-      <c r="I108" s="38"/>
+      <c r="I108" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="15">
@@ -4737,750 +4725,750 @@
         <v>16</v>
       </c>
       <c r="H109" s="17"/>
-      <c r="I109" s="38"/>
+      <c r="I109" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="21"/>
-      <c r="B110" s="38"/>
+      <c r="B110" s="36"/>
       <c r="C110" s="31"/>
       <c r="D110" s="32"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="48"/>
-      <c r="H110" s="38"/>
-      <c r="I110" s="38"/>
+      <c r="G110" s="46"/>
+      <c r="H110" s="36"/>
+      <c r="I110" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="21"/>
-      <c r="B111" s="38"/>
+      <c r="B111" s="36"/>
       <c r="C111" s="31"/>
       <c r="D111" s="32"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="48"/>
-      <c r="H111" s="38"/>
-      <c r="I111" s="38"/>
+      <c r="G111" s="46"/>
+      <c r="H111" s="36"/>
+      <c r="I111" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="21"/>
-      <c r="B112" s="38"/>
+      <c r="B112" s="36"/>
       <c r="C112" s="31"/>
       <c r="D112" s="32"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="48"/>
-      <c r="H112" s="38"/>
-      <c r="I112" s="38"/>
+      <c r="G112" s="46"/>
+      <c r="H112" s="36"/>
+      <c r="I112" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="21"/>
-      <c r="B113" s="38"/>
+      <c r="B113" s="36"/>
       <c r="C113" s="31"/>
       <c r="D113" s="32"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
-      <c r="G113" s="48"/>
-      <c r="H113" s="38"/>
-      <c r="I113" s="38"/>
+      <c r="G113" s="46"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="21"/>
-      <c r="B114" s="38"/>
+      <c r="B114" s="36"/>
       <c r="C114" s="31"/>
       <c r="D114" s="32"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
-      <c r="G114" s="48"/>
-      <c r="H114" s="38"/>
-      <c r="I114" s="38"/>
+      <c r="G114" s="46"/>
+      <c r="H114" s="36"/>
+      <c r="I114" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="21"/>
-      <c r="B115" s="38"/>
+      <c r="B115" s="36"/>
       <c r="C115" s="31"/>
       <c r="D115" s="32"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
-      <c r="G115" s="48"/>
-      <c r="H115" s="38"/>
-      <c r="I115" s="38"/>
+      <c r="G115" s="46"/>
+      <c r="H115" s="36"/>
+      <c r="I115" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="21"/>
-      <c r="B116" s="38"/>
+      <c r="B116" s="36"/>
       <c r="C116" s="31"/>
       <c r="D116" s="32"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
-      <c r="G116" s="48"/>
-      <c r="H116" s="38"/>
-      <c r="I116" s="38"/>
+      <c r="G116" s="46"/>
+      <c r="H116" s="36"/>
+      <c r="I116" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="21"/>
-      <c r="B117" s="38"/>
+      <c r="B117" s="36"/>
       <c r="C117" s="31"/>
       <c r="D117" s="32"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
-      <c r="G117" s="48"/>
-      <c r="H117" s="38"/>
-      <c r="I117" s="38"/>
+      <c r="G117" s="46"/>
+      <c r="H117" s="36"/>
+      <c r="I117" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="21"/>
-      <c r="B118" s="38"/>
+      <c r="B118" s="36"/>
       <c r="C118" s="31"/>
       <c r="D118" s="32"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
-      <c r="G118" s="48"/>
-      <c r="H118" s="38"/>
-      <c r="I118" s="38"/>
+      <c r="G118" s="46"/>
+      <c r="H118" s="36"/>
+      <c r="I118" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="21"/>
-      <c r="B119" s="38"/>
+      <c r="B119" s="36"/>
       <c r="C119" s="31"/>
       <c r="D119" s="32"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
-      <c r="G119" s="48"/>
-      <c r="H119" s="38"/>
-      <c r="I119" s="38"/>
+      <c r="G119" s="46"/>
+      <c r="H119" s="36"/>
+      <c r="I119" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="21"/>
-      <c r="B120" s="38"/>
+      <c r="B120" s="36"/>
       <c r="C120" s="31"/>
       <c r="D120" s="32"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
-      <c r="G120" s="48"/>
-      <c r="H120" s="38"/>
-      <c r="I120" s="38"/>
+      <c r="G120" s="46"/>
+      <c r="H120" s="36"/>
+      <c r="I120" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="21"/>
-      <c r="B121" s="38"/>
+      <c r="B121" s="36"/>
       <c r="C121" s="31"/>
       <c r="D121" s="32"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
-      <c r="G121" s="48"/>
-      <c r="H121" s="38"/>
-      <c r="I121" s="38"/>
+      <c r="G121" s="46"/>
+      <c r="H121" s="36"/>
+      <c r="I121" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="21"/>
-      <c r="B122" s="38"/>
+      <c r="B122" s="36"/>
       <c r="C122" s="31"/>
       <c r="D122" s="32"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
-      <c r="G122" s="48"/>
-      <c r="H122" s="38"/>
-      <c r="I122" s="38"/>
+      <c r="G122" s="46"/>
+      <c r="H122" s="36"/>
+      <c r="I122" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="21"/>
-      <c r="B123" s="38"/>
+      <c r="B123" s="36"/>
       <c r="C123" s="31"/>
       <c r="D123" s="32"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
-      <c r="G123" s="48"/>
-      <c r="H123" s="38"/>
-      <c r="I123" s="38"/>
+      <c r="G123" s="46"/>
+      <c r="H123" s="36"/>
+      <c r="I123" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="21"/>
-      <c r="B124" s="38"/>
+      <c r="B124" s="36"/>
       <c r="C124" s="31"/>
       <c r="D124" s="32"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
-      <c r="G124" s="48"/>
-      <c r="H124" s="38"/>
-      <c r="I124" s="38"/>
+      <c r="G124" s="46"/>
+      <c r="H124" s="36"/>
+      <c r="I124" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="21"/>
-      <c r="B125" s="38"/>
+      <c r="B125" s="36"/>
       <c r="C125" s="31"/>
       <c r="D125" s="32"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
-      <c r="G125" s="48"/>
-      <c r="H125" s="38"/>
-      <c r="I125" s="38"/>
+      <c r="G125" s="46"/>
+      <c r="H125" s="36"/>
+      <c r="I125" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="21"/>
-      <c r="B126" s="38"/>
+      <c r="B126" s="36"/>
       <c r="C126" s="31"/>
       <c r="D126" s="32"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
-      <c r="G126" s="48"/>
-      <c r="H126" s="38"/>
-      <c r="I126" s="38"/>
+      <c r="G126" s="46"/>
+      <c r="H126" s="36"/>
+      <c r="I126" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="21"/>
-      <c r="B127" s="38"/>
+      <c r="B127" s="36"/>
       <c r="C127" s="31"/>
       <c r="D127" s="32"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
-      <c r="G127" s="48"/>
-      <c r="H127" s="38"/>
-      <c r="I127" s="38"/>
+      <c r="G127" s="46"/>
+      <c r="H127" s="36"/>
+      <c r="I127" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="21"/>
-      <c r="B128" s="38"/>
+      <c r="B128" s="36"/>
       <c r="C128" s="31"/>
       <c r="D128" s="32"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
-      <c r="G128" s="48"/>
-      <c r="H128" s="38"/>
-      <c r="I128" s="38"/>
+      <c r="G128" s="46"/>
+      <c r="H128" s="36"/>
+      <c r="I128" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="21"/>
-      <c r="B129" s="38"/>
+      <c r="B129" s="36"/>
       <c r="C129" s="31"/>
       <c r="D129" s="32"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
-      <c r="G129" s="48"/>
-      <c r="H129" s="38"/>
-      <c r="I129" s="38"/>
+      <c r="G129" s="46"/>
+      <c r="H129" s="36"/>
+      <c r="I129" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="21"/>
-      <c r="B130" s="38"/>
+      <c r="B130" s="36"/>
       <c r="C130" s="31"/>
       <c r="D130" s="32"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
-      <c r="G130" s="48"/>
-      <c r="H130" s="38"/>
-      <c r="I130" s="38"/>
+      <c r="G130" s="46"/>
+      <c r="H130" s="36"/>
+      <c r="I130" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
       <c r="A131" s="21"/>
-      <c r="B131" s="38"/>
+      <c r="B131" s="36"/>
       <c r="C131" s="31"/>
       <c r="D131" s="32"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
-      <c r="G131" s="48"/>
-      <c r="H131" s="38"/>
-      <c r="I131" s="38"/>
+      <c r="G131" s="46"/>
+      <c r="H131" s="36"/>
+      <c r="I131" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
       <c r="A132" s="21"/>
-      <c r="B132" s="38"/>
+      <c r="B132" s="36"/>
       <c r="C132" s="31"/>
       <c r="D132" s="32"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="48"/>
-      <c r="H132" s="38"/>
-      <c r="I132" s="38"/>
+      <c r="G132" s="46"/>
+      <c r="H132" s="36"/>
+      <c r="I132" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
       <c r="A133" s="21"/>
-      <c r="B133" s="38"/>
+      <c r="B133" s="36"/>
       <c r="C133" s="31"/>
       <c r="D133" s="32"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
-      <c r="G133" s="48"/>
-      <c r="H133" s="38"/>
-      <c r="I133" s="38"/>
+      <c r="G133" s="46"/>
+      <c r="H133" s="36"/>
+      <c r="I133" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="21"/>
-      <c r="B134" s="38"/>
+      <c r="B134" s="36"/>
       <c r="C134" s="31"/>
       <c r="D134" s="32"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
-      <c r="G134" s="48"/>
-      <c r="H134" s="38"/>
-      <c r="I134" s="38"/>
+      <c r="G134" s="46"/>
+      <c r="H134" s="36"/>
+      <c r="I134" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
       <c r="A135" s="21"/>
-      <c r="B135" s="38"/>
+      <c r="B135" s="36"/>
       <c r="C135" s="31"/>
       <c r="D135" s="32"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
-      <c r="G135" s="48"/>
-      <c r="H135" s="38"/>
-      <c r="I135" s="38"/>
+      <c r="G135" s="46"/>
+      <c r="H135" s="36"/>
+      <c r="I135" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
       <c r="A136" s="21"/>
-      <c r="B136" s="38"/>
+      <c r="B136" s="36"/>
       <c r="C136" s="31"/>
       <c r="D136" s="32"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
-      <c r="G136" s="48"/>
-      <c r="H136" s="38"/>
-      <c r="I136" s="38"/>
+      <c r="G136" s="46"/>
+      <c r="H136" s="36"/>
+      <c r="I136" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
       <c r="A137" s="21"/>
-      <c r="B137" s="38"/>
+      <c r="B137" s="36"/>
       <c r="C137" s="31"/>
       <c r="D137" s="32"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
-      <c r="G137" s="48"/>
-      <c r="H137" s="38"/>
-      <c r="I137" s="38"/>
+      <c r="G137" s="46"/>
+      <c r="H137" s="36"/>
+      <c r="I137" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
       <c r="A138" s="21"/>
-      <c r="B138" s="38"/>
+      <c r="B138" s="36"/>
       <c r="C138" s="31"/>
       <c r="D138" s="32"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
-      <c r="G138" s="48"/>
-      <c r="H138" s="38"/>
-      <c r="I138" s="38"/>
+      <c r="G138" s="46"/>
+      <c r="H138" s="36"/>
+      <c r="I138" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
       <c r="A139" s="21"/>
-      <c r="B139" s="38"/>
+      <c r="B139" s="36"/>
       <c r="C139" s="31"/>
       <c r="D139" s="32"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
-      <c r="G139" s="48"/>
-      <c r="H139" s="38"/>
-      <c r="I139" s="38"/>
+      <c r="G139" s="46"/>
+      <c r="H139" s="36"/>
+      <c r="I139" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
       <c r="A140" s="21"/>
-      <c r="B140" s="38"/>
+      <c r="B140" s="36"/>
       <c r="C140" s="31"/>
       <c r="D140" s="32"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
-      <c r="G140" s="48"/>
-      <c r="H140" s="38"/>
-      <c r="I140" s="38"/>
+      <c r="G140" s="46"/>
+      <c r="H140" s="36"/>
+      <c r="I140" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
       <c r="A141" s="21"/>
-      <c r="B141" s="38"/>
+      <c r="B141" s="36"/>
       <c r="C141" s="31"/>
       <c r="D141" s="32"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
-      <c r="G141" s="48"/>
-      <c r="H141" s="38"/>
-      <c r="I141" s="38"/>
+      <c r="G141" s="46"/>
+      <c r="H141" s="36"/>
+      <c r="I141" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
       <c r="A142" s="21"/>
-      <c r="B142" s="38"/>
+      <c r="B142" s="36"/>
       <c r="C142" s="31"/>
       <c r="D142" s="32"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
-      <c r="G142" s="48"/>
-      <c r="H142" s="38"/>
-      <c r="I142" s="38"/>
+      <c r="G142" s="46"/>
+      <c r="H142" s="36"/>
+      <c r="I142" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
       <c r="A143" s="21"/>
-      <c r="B143" s="38"/>
+      <c r="B143" s="36"/>
       <c r="C143" s="31"/>
       <c r="D143" s="32"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
-      <c r="G143" s="48"/>
-      <c r="H143" s="38"/>
-      <c r="I143" s="38"/>
+      <c r="G143" s="46"/>
+      <c r="H143" s="36"/>
+      <c r="I143" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
       <c r="A144" s="21"/>
-      <c r="B144" s="38"/>
+      <c r="B144" s="36"/>
       <c r="C144" s="31"/>
       <c r="D144" s="32"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
-      <c r="G144" s="48"/>
-      <c r="H144" s="38"/>
-      <c r="I144" s="38"/>
+      <c r="G144" s="46"/>
+      <c r="H144" s="36"/>
+      <c r="I144" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
       <c r="A145" s="21"/>
-      <c r="B145" s="38"/>
+      <c r="B145" s="36"/>
       <c r="C145" s="31"/>
       <c r="D145" s="32"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
-      <c r="G145" s="48"/>
-      <c r="H145" s="38"/>
-      <c r="I145" s="38"/>
+      <c r="G145" s="46"/>
+      <c r="H145" s="36"/>
+      <c r="I145" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
       <c r="A146" s="21"/>
-      <c r="B146" s="38"/>
+      <c r="B146" s="36"/>
       <c r="C146" s="31"/>
       <c r="D146" s="32"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
-      <c r="G146" s="48"/>
-      <c r="H146" s="38"/>
-      <c r="I146" s="38"/>
+      <c r="G146" s="46"/>
+      <c r="H146" s="36"/>
+      <c r="I146" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
       <c r="A147" s="21"/>
-      <c r="B147" s="38"/>
+      <c r="B147" s="36"/>
       <c r="C147" s="31"/>
       <c r="D147" s="32"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
-      <c r="G147" s="48"/>
-      <c r="H147" s="38"/>
-      <c r="I147" s="38"/>
+      <c r="G147" s="46"/>
+      <c r="H147" s="36"/>
+      <c r="I147" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
       <c r="A148" s="21"/>
-      <c r="B148" s="38"/>
+      <c r="B148" s="36"/>
       <c r="C148" s="31"/>
       <c r="D148" s="32"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="48"/>
-      <c r="H148" s="38"/>
-      <c r="I148" s="38"/>
+      <c r="G148" s="46"/>
+      <c r="H148" s="36"/>
+      <c r="I148" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
       <c r="A149" s="21"/>
-      <c r="B149" s="38"/>
+      <c r="B149" s="36"/>
       <c r="C149" s="31"/>
       <c r="D149" s="32"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
-      <c r="G149" s="48"/>
-      <c r="H149" s="38"/>
-      <c r="I149" s="38"/>
+      <c r="G149" s="46"/>
+      <c r="H149" s="36"/>
+      <c r="I149" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
       <c r="A150" s="21"/>
-      <c r="B150" s="38"/>
+      <c r="B150" s="36"/>
       <c r="C150" s="31"/>
       <c r="D150" s="32"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
-      <c r="G150" s="48"/>
-      <c r="H150" s="38"/>
-      <c r="I150" s="38"/>
+      <c r="G150" s="46"/>
+      <c r="H150" s="36"/>
+      <c r="I150" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
       <c r="A151" s="21"/>
-      <c r="B151" s="38"/>
+      <c r="B151" s="36"/>
       <c r="C151" s="31"/>
       <c r="D151" s="32"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="48"/>
-      <c r="H151" s="38"/>
-      <c r="I151" s="38"/>
+      <c r="G151" s="46"/>
+      <c r="H151" s="36"/>
+      <c r="I151" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
       <c r="A152" s="21"/>
-      <c r="B152" s="38"/>
+      <c r="B152" s="36"/>
       <c r="C152" s="31"/>
       <c r="D152" s="32"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="48"/>
-      <c r="H152" s="38"/>
-      <c r="I152" s="38"/>
+      <c r="G152" s="46"/>
+      <c r="H152" s="36"/>
+      <c r="I152" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
       <c r="A153" s="21"/>
-      <c r="B153" s="38"/>
+      <c r="B153" s="36"/>
       <c r="C153" s="31"/>
       <c r="D153" s="32"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
-      <c r="G153" s="48"/>
-      <c r="H153" s="38"/>
-      <c r="I153" s="38"/>
+      <c r="G153" s="46"/>
+      <c r="H153" s="36"/>
+      <c r="I153" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="21"/>
-      <c r="B154" s="38"/>
+      <c r="B154" s="36"/>
       <c r="C154" s="31"/>
       <c r="D154" s="32"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
-      <c r="G154" s="48"/>
-      <c r="H154" s="38"/>
-      <c r="I154" s="38"/>
+      <c r="G154" s="46"/>
+      <c r="H154" s="36"/>
+      <c r="I154" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="21"/>
-      <c r="B155" s="38"/>
+      <c r="B155" s="36"/>
       <c r="C155" s="31"/>
       <c r="D155" s="32"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
-      <c r="G155" s="48"/>
-      <c r="H155" s="38"/>
-      <c r="I155" s="38"/>
+      <c r="G155" s="46"/>
+      <c r="H155" s="36"/>
+      <c r="I155" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="21"/>
-      <c r="B156" s="38"/>
+      <c r="B156" s="36"/>
       <c r="C156" s="31"/>
       <c r="D156" s="32"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
-      <c r="G156" s="48"/>
-      <c r="H156" s="38"/>
-      <c r="I156" s="38"/>
+      <c r="G156" s="46"/>
+      <c r="H156" s="36"/>
+      <c r="I156" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="21"/>
-      <c r="B157" s="38"/>
+      <c r="B157" s="36"/>
       <c r="C157" s="31"/>
       <c r="D157" s="32"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
-      <c r="G157" s="48"/>
-      <c r="H157" s="38"/>
-      <c r="I157" s="38"/>
+      <c r="G157" s="46"/>
+      <c r="H157" s="36"/>
+      <c r="I157" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="21"/>
-      <c r="B158" s="38"/>
+      <c r="B158" s="36"/>
       <c r="C158" s="31"/>
       <c r="D158" s="32"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
-      <c r="G158" s="48"/>
-      <c r="H158" s="38"/>
-      <c r="I158" s="38"/>
+      <c r="G158" s="46"/>
+      <c r="H158" s="36"/>
+      <c r="I158" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="21"/>
-      <c r="B159" s="38"/>
+      <c r="B159" s="36"/>
       <c r="C159" s="31"/>
       <c r="D159" s="32"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
-      <c r="G159" s="48"/>
-      <c r="H159" s="38"/>
-      <c r="I159" s="38"/>
+      <c r="G159" s="46"/>
+      <c r="H159" s="36"/>
+      <c r="I159" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="21"/>
-      <c r="B160" s="38"/>
+      <c r="B160" s="36"/>
       <c r="C160" s="31"/>
       <c r="D160" s="32"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
-      <c r="G160" s="48"/>
-      <c r="H160" s="38"/>
-      <c r="I160" s="38"/>
+      <c r="G160" s="46"/>
+      <c r="H160" s="36"/>
+      <c r="I160" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="21"/>
-      <c r="B161" s="38"/>
+      <c r="B161" s="36"/>
       <c r="C161" s="31"/>
       <c r="D161" s="32"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
-      <c r="G161" s="48"/>
-      <c r="H161" s="38"/>
-      <c r="I161" s="38"/>
+      <c r="G161" s="46"/>
+      <c r="H161" s="36"/>
+      <c r="I161" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="21"/>
-      <c r="B162" s="38"/>
+      <c r="B162" s="36"/>
       <c r="C162" s="31"/>
       <c r="D162" s="32"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="48"/>
-      <c r="H162" s="38"/>
-      <c r="I162" s="38"/>
+      <c r="G162" s="46"/>
+      <c r="H162" s="36"/>
+      <c r="I162" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="21"/>
-      <c r="B163" s="38"/>
+      <c r="B163" s="36"/>
       <c r="C163" s="31"/>
       <c r="D163" s="32"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
-      <c r="G163" s="48"/>
-      <c r="H163" s="38"/>
-      <c r="I163" s="38"/>
+      <c r="G163" s="46"/>
+      <c r="H163" s="36"/>
+      <c r="I163" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="21"/>
-      <c r="B164" s="38"/>
+      <c r="B164" s="36"/>
       <c r="C164" s="31"/>
       <c r="D164" s="32"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
-      <c r="G164" s="48"/>
-      <c r="H164" s="38"/>
-      <c r="I164" s="38"/>
+      <c r="G164" s="46"/>
+      <c r="H164" s="36"/>
+      <c r="I164" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="21"/>
-      <c r="B165" s="38"/>
+      <c r="B165" s="36"/>
       <c r="C165" s="31"/>
       <c r="D165" s="32"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
-      <c r="G165" s="48"/>
-      <c r="H165" s="38"/>
-      <c r="I165" s="38"/>
+      <c r="G165" s="46"/>
+      <c r="H165" s="36"/>
+      <c r="I165" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="21"/>
-      <c r="B166" s="38"/>
+      <c r="B166" s="36"/>
       <c r="C166" s="31"/>
       <c r="D166" s="32"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
-      <c r="G166" s="48"/>
-      <c r="H166" s="38"/>
-      <c r="I166" s="38"/>
+      <c r="G166" s="46"/>
+      <c r="H166" s="36"/>
+      <c r="I166" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="21"/>
-      <c r="B167" s="38"/>
+      <c r="B167" s="36"/>
       <c r="C167" s="31"/>
       <c r="D167" s="32"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
-      <c r="G167" s="48"/>
-      <c r="H167" s="38"/>
-      <c r="I167" s="38"/>
+      <c r="G167" s="46"/>
+      <c r="H167" s="36"/>
+      <c r="I167" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="21"/>
-      <c r="B168" s="38"/>
+      <c r="B168" s="36"/>
       <c r="C168" s="31"/>
       <c r="D168" s="32"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
-      <c r="G168" s="48"/>
-      <c r="H168" s="38"/>
-      <c r="I168" s="38"/>
+      <c r="G168" s="46"/>
+      <c r="H168" s="36"/>
+      <c r="I168" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
       <c r="A169" s="21"/>
-      <c r="B169" s="38"/>
+      <c r="B169" s="36"/>
       <c r="C169" s="31"/>
       <c r="D169" s="32"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
-      <c r="G169" s="48"/>
-      <c r="H169" s="38"/>
-      <c r="I169" s="38"/>
+      <c r="G169" s="46"/>
+      <c r="H169" s="36"/>
+      <c r="I169" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
       <c r="A170" s="21"/>
-      <c r="B170" s="38"/>
+      <c r="B170" s="36"/>
       <c r="C170" s="31"/>
       <c r="D170" s="32"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
-      <c r="G170" s="48"/>
-      <c r="H170" s="38"/>
-      <c r="I170" s="38"/>
+      <c r="G170" s="46"/>
+      <c r="H170" s="36"/>
+      <c r="I170" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
       <c r="A171" s="21"/>
-      <c r="B171" s="38"/>
+      <c r="B171" s="36"/>
       <c r="C171" s="31"/>
       <c r="D171" s="32"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
-      <c r="G171" s="48"/>
-      <c r="H171" s="38"/>
-      <c r="I171" s="38"/>
+      <c r="G171" s="46"/>
+      <c r="H171" s="36"/>
+      <c r="I171" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
       <c r="A172" s="21"/>
-      <c r="B172" s="38"/>
+      <c r="B172" s="36"/>
       <c r="C172" s="31"/>
       <c r="D172" s="32"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
-      <c r="G172" s="48"/>
-      <c r="H172" s="38"/>
-      <c r="I172" s="38"/>
+      <c r="G172" s="46"/>
+      <c r="H172" s="36"/>
+      <c r="I172" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
       <c r="A173" s="21"/>
-      <c r="B173" s="38"/>
+      <c r="B173" s="36"/>
       <c r="C173" s="31"/>
       <c r="D173" s="32"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
-      <c r="G173" s="48"/>
-      <c r="H173" s="38"/>
-      <c r="I173" s="38"/>
+      <c r="G173" s="46"/>
+      <c r="H173" s="36"/>
+      <c r="I173" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
       <c r="A174" s="21"/>
-      <c r="B174" s="38"/>
+      <c r="B174" s="36"/>
       <c r="C174" s="31"/>
       <c r="D174" s="32"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
-      <c r="G174" s="48"/>
-      <c r="H174" s="38"/>
-      <c r="I174" s="38"/>
+      <c r="G174" s="46"/>
+      <c r="H174" s="36"/>
+      <c r="I174" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
       <c r="A175" s="21"/>
-      <c r="B175" s="38"/>
+      <c r="B175" s="36"/>
       <c r="C175" s="31"/>
       <c r="D175" s="32"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
-      <c r="G175" s="48"/>
-      <c r="H175" s="38"/>
-      <c r="I175" s="38"/>
+      <c r="G175" s="46"/>
+      <c r="H175" s="36"/>
+      <c r="I175" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
       <c r="A176" s="21"/>
       <c r="B176" s="2"/>
-      <c r="C176" s="49"/>
+      <c r="C176" s="47"/>
       <c r="D176" s="32"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
-      <c r="G176" s="38"/>
-      <c r="H176" s="38"/>
-      <c r="I176" s="38"/>
+      <c r="G176" s="36"/>
+      <c r="H176" s="36"/>
+      <c r="I176" s="36"/>
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A177" s="44"/>
+      <c r="A177" s="42"/>
       <c r="B177" s="2"/>
-      <c r="C177" s="45"/>
-      <c r="D177" s="46"/>
+      <c r="C177" s="43"/>
+      <c r="D177" s="44"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
@@ -5488,10 +5476,10 @@
       <c r="I177" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A178" s="44"/>
+      <c r="A178" s="42"/>
       <c r="B178" s="2"/>
-      <c r="C178" s="45"/>
-      <c r="D178" s="46"/>
+      <c r="C178" s="43"/>
+      <c r="D178" s="44"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
@@ -5499,10 +5487,10 @@
       <c r="I178" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A179" s="44"/>
+      <c r="A179" s="42"/>
       <c r="B179" s="2"/>
-      <c r="C179" s="45"/>
-      <c r="D179" s="46"/>
+      <c r="C179" s="43"/>
+      <c r="D179" s="44"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
@@ -5510,10 +5498,10 @@
       <c r="I179" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A180" s="44"/>
+      <c r="A180" s="42"/>
       <c r="B180" s="2"/>
-      <c r="C180" s="45"/>
-      <c r="D180" s="46"/>
+      <c r="C180" s="43"/>
+      <c r="D180" s="44"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
@@ -5521,10 +5509,10 @@
       <c r="I180" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A181" s="44"/>
+      <c r="A181" s="42"/>
       <c r="B181" s="2"/>
-      <c r="C181" s="45"/>
-      <c r="D181" s="46"/>
+      <c r="C181" s="43"/>
+      <c r="D181" s="44"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
@@ -5532,10 +5520,10 @@
       <c r="I181" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A182" s="44"/>
+      <c r="A182" s="42"/>
       <c r="B182" s="2"/>
-      <c r="C182" s="45"/>
-      <c r="D182" s="46"/>
+      <c r="C182" s="43"/>
+      <c r="D182" s="44"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
@@ -5543,10 +5531,10 @@
       <c r="I182" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A183" s="44"/>
+      <c r="A183" s="42"/>
       <c r="B183" s="2"/>
-      <c r="C183" s="45"/>
-      <c r="D183" s="46"/>
+      <c r="C183" s="43"/>
+      <c r="D183" s="44"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
@@ -5554,10 +5542,10 @@
       <c r="I183" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A184" s="44"/>
+      <c r="A184" s="42"/>
       <c r="B184" s="2"/>
-      <c r="C184" s="45"/>
-      <c r="D184" s="46"/>
+      <c r="C184" s="43"/>
+      <c r="D184" s="44"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -5565,10 +5553,10 @@
       <c r="I184" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A185" s="44"/>
+      <c r="A185" s="42"/>
       <c r="B185" s="2"/>
-      <c r="C185" s="45"/>
-      <c r="D185" s="46"/>
+      <c r="C185" s="43"/>
+      <c r="D185" s="44"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
@@ -5576,10 +5564,10 @@
       <c r="I185" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A186" s="44"/>
+      <c r="A186" s="42"/>
       <c r="B186" s="2"/>
-      <c r="C186" s="45"/>
-      <c r="D186" s="46"/>
+      <c r="C186" s="43"/>
+      <c r="D186" s="44"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
@@ -5587,10 +5575,10 @@
       <c r="I186" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A187" s="44"/>
+      <c r="A187" s="42"/>
       <c r="B187" s="2"/>
-      <c r="C187" s="45"/>
-      <c r="D187" s="46"/>
+      <c r="C187" s="43"/>
+      <c r="D187" s="44"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
@@ -5598,10 +5586,10 @@
       <c r="I187" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A188" s="44"/>
+      <c r="A188" s="42"/>
       <c r="B188" s="2"/>
-      <c r="C188" s="45"/>
-      <c r="D188" s="46"/>
+      <c r="C188" s="43"/>
+      <c r="D188" s="44"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
@@ -5609,10 +5597,10 @@
       <c r="I188" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A189" s="44"/>
+      <c r="A189" s="42"/>
       <c r="B189" s="2"/>
-      <c r="C189" s="45"/>
-      <c r="D189" s="46"/>
+      <c r="C189" s="43"/>
+      <c r="D189" s="44"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
@@ -5620,10 +5608,10 @@
       <c r="I189" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A190" s="44"/>
+      <c r="A190" s="42"/>
       <c r="B190" s="2"/>
-      <c r="C190" s="45"/>
-      <c r="D190" s="46"/>
+      <c r="C190" s="43"/>
+      <c r="D190" s="44"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
@@ -5631,10 +5619,10 @@
       <c r="I190" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A191" s="44"/>
+      <c r="A191" s="42"/>
       <c r="B191" s="2"/>
-      <c r="C191" s="45"/>
-      <c r="D191" s="46"/>
+      <c r="C191" s="43"/>
+      <c r="D191" s="44"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
@@ -5642,10 +5630,10 @@
       <c r="I191" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A192" s="44"/>
+      <c r="A192" s="42"/>
       <c r="B192" s="2"/>
-      <c r="C192" s="45"/>
-      <c r="D192" s="46"/>
+      <c r="C192" s="43"/>
+      <c r="D192" s="44"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
@@ -5653,10 +5641,10 @@
       <c r="I192" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A193" s="44"/>
+      <c r="A193" s="42"/>
       <c r="B193" s="2"/>
-      <c r="C193" s="45"/>
-      <c r="D193" s="46"/>
+      <c r="C193" s="43"/>
+      <c r="D193" s="44"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
@@ -5664,10 +5652,10 @@
       <c r="I193" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A194" s="44"/>
+      <c r="A194" s="42"/>
       <c r="B194" s="2"/>
-      <c r="C194" s="45"/>
-      <c r="D194" s="46"/>
+      <c r="C194" s="43"/>
+      <c r="D194" s="44"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
@@ -5675,10 +5663,10 @@
       <c r="I194" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A195" s="44"/>
+      <c r="A195" s="42"/>
       <c r="B195" s="2"/>
-      <c r="C195" s="45"/>
-      <c r="D195" s="46"/>
+      <c r="C195" s="43"/>
+      <c r="D195" s="44"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
@@ -5686,10 +5674,10 @@
       <c r="I195" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A196" s="44"/>
+      <c r="A196" s="42"/>
       <c r="B196" s="2"/>
-      <c r="C196" s="45"/>
-      <c r="D196" s="46"/>
+      <c r="C196" s="43"/>
+      <c r="D196" s="44"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
@@ -5697,10 +5685,10 @@
       <c r="I196" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A197" s="44"/>
+      <c r="A197" s="42"/>
       <c r="B197" s="2"/>
-      <c r="C197" s="45"/>
-      <c r="D197" s="46"/>
+      <c r="C197" s="43"/>
+      <c r="D197" s="44"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
@@ -5708,10 +5696,10 @@
       <c r="I197" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A198" s="44"/>
+      <c r="A198" s="42"/>
       <c r="B198" s="2"/>
-      <c r="C198" s="45"/>
-      <c r="D198" s="46"/>
+      <c r="C198" s="43"/>
+      <c r="D198" s="44"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
@@ -5719,10 +5707,10 @@
       <c r="I198" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A199" s="44"/>
+      <c r="A199" s="42"/>
       <c r="B199" s="2"/>
-      <c r="C199" s="45"/>
-      <c r="D199" s="46"/>
+      <c r="C199" s="43"/>
+      <c r="D199" s="44"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
@@ -5730,10 +5718,10 @@
       <c r="I199" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A200" s="44"/>
+      <c r="A200" s="42"/>
       <c r="B200" s="2"/>
-      <c r="C200" s="45"/>
-      <c r="D200" s="46"/>
+      <c r="C200" s="43"/>
+      <c r="D200" s="44"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
@@ -5741,10 +5729,10 @@
       <c r="I200" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A201" s="44"/>
+      <c r="A201" s="42"/>
       <c r="B201" s="2"/>
-      <c r="C201" s="45"/>
-      <c r="D201" s="46"/>
+      <c r="C201" s="43"/>
+      <c r="D201" s="44"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
@@ -5752,10 +5740,10 @@
       <c r="I201" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A202" s="44"/>
+      <c r="A202" s="42"/>
       <c r="B202" s="2"/>
-      <c r="C202" s="45"/>
-      <c r="D202" s="46"/>
+      <c r="C202" s="43"/>
+      <c r="D202" s="44"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
@@ -5763,10 +5751,10 @@
       <c r="I202" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A203" s="44"/>
+      <c r="A203" s="42"/>
       <c r="B203" s="2"/>
-      <c r="C203" s="45"/>
-      <c r="D203" s="46"/>
+      <c r="C203" s="43"/>
+      <c r="D203" s="44"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
@@ -5794,11 +5782,11 @@
   <cols>
     <col min="1" max="1" style="23" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="43.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="35" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="36" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="34" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="35" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="24" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="37" width="16.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="23" width="16.433571428571426" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -6274,7 +6262,9 @@
       <c r="E22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="17"/>
+      <c r="F22" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G22" s="20"/>
       <c r="H22" s="2"/>
     </row>
@@ -6294,7 +6284,9 @@
       <c r="E23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="17"/>
+      <c r="F23" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G23" s="20"/>
       <c r="H23" s="2"/>
     </row>
@@ -6314,7 +6306,9 @@
       <c r="E24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="17"/>
+      <c r="F24" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G24" s="20"/>
       <c r="H24" s="2"/>
     </row>
@@ -6334,7 +6328,9 @@
       <c r="E25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="17"/>
+      <c r="F25" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G25" s="20">
         <v>1</v>
       </c>
@@ -6356,7 +6352,9 @@
       <c r="E26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="17"/>
+      <c r="F26" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G26" s="20">
         <v>2</v>
       </c>
@@ -7217,7 +7215,7 @@
       <c r="D69" s="32"/>
       <c r="E69" s="2"/>
       <c r="F69" s="22"/>
-      <c r="G69" s="33"/>
+      <c r="G69" s="21"/>
       <c r="H69" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="29" customFormat="1" s="1">
@@ -8797,7 +8795,7 @@
       <c r="B148" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="C148" s="34" t="s">
+      <c r="C148" s="33" t="s">
         <v>179</v>
       </c>
       <c r="D148" s="18">
@@ -8817,7 +8815,7 @@
       <c r="B149" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C149" s="34" t="s">
+      <c r="C149" s="33" t="s">
         <v>179</v>
       </c>
       <c r="D149" s="18">
@@ -8837,7 +8835,7 @@
       <c r="B150" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="C150" s="34" t="s">
+      <c r="C150" s="33" t="s">
         <v>179</v>
       </c>
       <c r="D150" s="18">
@@ -8857,7 +8855,7 @@
       <c r="B151" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="C151" s="34" t="s">
+      <c r="C151" s="33" t="s">
         <v>179</v>
       </c>
       <c r="D151" s="18">
@@ -8877,7 +8875,7 @@
       <c r="B152" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C152" s="34" t="s">
+      <c r="C152" s="33" t="s">
         <v>179</v>
       </c>
       <c r="D152" s="18">
@@ -8897,7 +8895,7 @@
       <c r="B153" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="C153" s="34" t="s">
+      <c r="C153" s="33" t="s">
         <v>179</v>
       </c>
       <c r="D153" s="18">
@@ -8917,7 +8915,7 @@
       <c r="D154" s="32"/>
       <c r="E154" s="2"/>
       <c r="F154" s="22"/>
-      <c r="G154" s="33"/>
+      <c r="G154" s="21"/>
       <c r="H154" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
@@ -8927,7 +8925,7 @@
       <c r="D155" s="32"/>
       <c r="E155" s="2"/>
       <c r="F155" s="22"/>
-      <c r="G155" s="33"/>
+      <c r="G155" s="21"/>
       <c r="H155" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
@@ -8937,7 +8935,7 @@
       <c r="D156" s="32"/>
       <c r="E156" s="2"/>
       <c r="F156" s="22"/>
-      <c r="G156" s="33"/>
+      <c r="G156" s="21"/>
       <c r="H156" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
@@ -8947,7 +8945,7 @@
       <c r="D157" s="32"/>
       <c r="E157" s="2"/>
       <c r="F157" s="22"/>
-      <c r="G157" s="33"/>
+      <c r="G157" s="21"/>
       <c r="H157" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
@@ -8957,7 +8955,7 @@
       <c r="D158" s="32"/>
       <c r="E158" s="2"/>
       <c r="F158" s="22"/>
-      <c r="G158" s="33"/>
+      <c r="G158" s="21"/>
       <c r="H158" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
@@ -8967,7 +8965,7 @@
       <c r="D159" s="32"/>
       <c r="E159" s="2"/>
       <c r="F159" s="22"/>
-      <c r="G159" s="33"/>
+      <c r="G159" s="21"/>
       <c r="H159" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
@@ -8977,7 +8975,7 @@
       <c r="D160" s="32"/>
       <c r="E160" s="2"/>
       <c r="F160" s="22"/>
-      <c r="G160" s="33"/>
+      <c r="G160" s="21"/>
       <c r="H160" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
@@ -8987,7 +8985,7 @@
       <c r="D161" s="32"/>
       <c r="E161" s="2"/>
       <c r="F161" s="22"/>
-      <c r="G161" s="33"/>
+      <c r="G161" s="21"/>
       <c r="H161" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
@@ -8997,7 +8995,7 @@
       <c r="D162" s="32"/>
       <c r="E162" s="2"/>
       <c r="F162" s="22"/>
-      <c r="G162" s="33"/>
+      <c r="G162" s="21"/>
       <c r="H162" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
@@ -9007,7 +9005,7 @@
       <c r="D163" s="32"/>
       <c r="E163" s="2"/>
       <c r="F163" s="22"/>
-      <c r="G163" s="33"/>
+      <c r="G163" s="21"/>
       <c r="H163" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
@@ -9017,7 +9015,7 @@
       <c r="D164" s="32"/>
       <c r="E164" s="2"/>
       <c r="F164" s="22"/>
-      <c r="G164" s="33"/>
+      <c r="G164" s="21"/>
       <c r="H164" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
@@ -9027,7 +9025,7 @@
       <c r="D165" s="32"/>
       <c r="E165" s="2"/>
       <c r="F165" s="22"/>
-      <c r="G165" s="33"/>
+      <c r="G165" s="21"/>
       <c r="H165" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
@@ -9037,7 +9035,7 @@
       <c r="D166" s="32"/>
       <c r="E166" s="2"/>
       <c r="F166" s="22"/>
-      <c r="G166" s="33"/>
+      <c r="G166" s="21"/>
       <c r="H166" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
@@ -9047,7 +9045,7 @@
       <c r="D167" s="32"/>
       <c r="E167" s="2"/>
       <c r="F167" s="22"/>
-      <c r="G167" s="33"/>
+      <c r="G167" s="21"/>
       <c r="H167" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
@@ -9057,7 +9055,7 @@
       <c r="D168" s="32"/>
       <c r="E168" s="2"/>
       <c r="F168" s="22"/>
-      <c r="G168" s="33"/>
+      <c r="G168" s="21"/>
       <c r="H168" s="2"/>
     </row>
   </sheetData>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="363">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -4045,7 +4045,7 @@
         <v>282</v>
       </c>
       <c r="C80" s="45">
-        <v>33.11769675925926</v>
+        <v>34.11758101851852</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -4068,7 +4068,7 @@
         <v>282</v>
       </c>
       <c r="C81" s="45">
-        <v>33.11769675925926</v>
+        <v>34.11758101851852</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -4091,7 +4091,7 @@
         <v>282</v>
       </c>
       <c r="C82" s="45">
-        <v>33.11769675925926</v>
+        <v>34.11758101851852</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -4114,7 +4114,7 @@
         <v>282</v>
       </c>
       <c r="C83" s="45">
-        <v>33.11769675925926</v>
+        <v>34.11758101851852</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
@@ -6376,7 +6376,9 @@
       <c r="E27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="17"/>
+      <c r="F27" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G27" s="20"/>
       <c r="H27" s="2"/>
     </row>
@@ -6396,7 +6398,9 @@
       <c r="E28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="17"/>
+      <c r="F28" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G28" s="20"/>
       <c r="H28" s="2"/>
     </row>
@@ -6416,7 +6420,9 @@
       <c r="E29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="17"/>
+      <c r="F29" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G29" s="20"/>
       <c r="H29" s="2"/>
     </row>
@@ -6436,7 +6442,9 @@
       <c r="E30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F30" s="17"/>
+      <c r="F30" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G30" s="20"/>
       <c r="H30" s="2"/>
     </row>
@@ -6456,7 +6464,9 @@
       <c r="E31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="17"/>
+      <c r="F31" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G31" s="20"/>
       <c r="H31" s="2"/>
     </row>
@@ -6476,11 +6486,13 @@
       <c r="E32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F32" s="17"/>
+      <c r="F32" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G32" s="20"/>
       <c r="H32" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="33.75">
       <c r="A33" s="15">
         <v>31</v>
       </c>
@@ -6496,11 +6508,13 @@
       <c r="E33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="17"/>
+      <c r="F33" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G33" s="20"/>
       <c r="H33" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="33.75">
       <c r="A34" s="15">
         <v>32</v>
       </c>
@@ -6516,11 +6530,13 @@
       <c r="E34" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F34" s="17"/>
+      <c r="F34" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G34" s="20"/>
       <c r="H34" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="33.75">
       <c r="A35" s="15">
         <v>33</v>
       </c>
@@ -6536,11 +6552,13 @@
       <c r="E35" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F35" s="17"/>
+      <c r="F35" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G35" s="20"/>
       <c r="H35" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="33.75">
       <c r="A36" s="15">
         <v>34</v>
       </c>
@@ -6556,11 +6574,13 @@
       <c r="E36" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="17"/>
+      <c r="F36" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G36" s="20"/>
       <c r="H36" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="33.75">
       <c r="A37" s="15">
         <v>35</v>
       </c>
@@ -6576,11 +6596,13 @@
       <c r="E37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="17"/>
+      <c r="F37" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G37" s="20"/>
       <c r="H37" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="33.75">
       <c r="A38" s="15">
         <v>36</v>
       </c>
@@ -6620,7 +6642,7 @@
       <c r="G39" s="20"/>
       <c r="H39" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="33.75">
       <c r="A40" s="15">
         <v>38</v>
       </c>
@@ -6640,7 +6662,7 @@
       <c r="G40" s="20"/>
       <c r="H40" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="33.75">
       <c r="A41" s="15">
         <v>39</v>
       </c>
@@ -6660,7 +6682,7 @@
       <c r="G41" s="20"/>
       <c r="H41" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="33.75">
       <c r="A42" s="15">
         <v>40</v>
       </c>
@@ -6680,7 +6702,7 @@
       <c r="G42" s="20"/>
       <c r="H42" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="33.75">
       <c r="A43" s="15">
         <v>41</v>
       </c>
@@ -6700,7 +6722,7 @@
       <c r="G43" s="20"/>
       <c r="H43" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="33.75">
       <c r="A44" s="15">
         <v>42</v>
       </c>
@@ -6722,7 +6744,7 @@
       </c>
       <c r="H44" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="33.75">
       <c r="A45" s="15">
         <v>43</v>
       </c>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="364">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -1068,7 +1068,7 @@
     <t>Azure Basics</t>
   </si>
   <si>
-    <t>Jenkins</t>
+    <t>CI/CD Jenkins</t>
   </si>
   <si>
     <t>CI/CD Pipelines</t>
@@ -1113,6 +1113,9 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=VYIDZ57mMy4</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -1226,7 +1229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1376,6 +1379,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1689,7 +1695,7 @@
     <col min="1" max="1" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="51" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="52" width="6.719285714285714" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="48" width="38.86214285714286" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="23" width="7.719285714285714" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="48" width="23.862142857142857" customWidth="1" bestFit="1"/>
@@ -2235,7 +2241,9 @@
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
       <c r="D30" s="49"/>
-      <c r="E30" s="36"/>
+      <c r="E30" s="51" t="s">
+        <v>363</v>
+      </c>
       <c r="F30" s="21"/>
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
@@ -4045,7 +4053,7 @@
         <v>282</v>
       </c>
       <c r="C80" s="45">
-        <v>34.11758101851852</v>
+        <v>35.117465277777775</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -4068,7 +4076,7 @@
         <v>282</v>
       </c>
       <c r="C81" s="45">
-        <v>34.11758101851852</v>
+        <v>35.117465277777775</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -4091,7 +4099,7 @@
         <v>282</v>
       </c>
       <c r="C82" s="45">
-        <v>34.11758101851852</v>
+        <v>35.117465277777775</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -4114,7 +4122,7 @@
         <v>282</v>
       </c>
       <c r="C83" s="45">
-        <v>34.11758101851852</v>
+        <v>35.117465277777775</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
@@ -6618,7 +6626,9 @@
       <c r="E38" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="17"/>
+      <c r="F38" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G38" s="20"/>
       <c r="H38" s="2"/>
     </row>
@@ -6638,7 +6648,9 @@
       <c r="E39" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="17"/>
+      <c r="F39" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G39" s="20"/>
       <c r="H39" s="2"/>
     </row>
@@ -6658,7 +6670,9 @@
       <c r="E40" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F40" s="17"/>
+      <c r="F40" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G40" s="20"/>
       <c r="H40" s="2"/>
     </row>
@@ -6678,7 +6692,9 @@
       <c r="E41" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="17"/>
+      <c r="F41" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G41" s="20"/>
       <c r="H41" s="2"/>
     </row>
@@ -6698,7 +6714,9 @@
       <c r="E42" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="17"/>
+      <c r="F42" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G42" s="20"/>
       <c r="H42" s="2"/>
     </row>
@@ -6718,7 +6736,9 @@
       <c r="E43" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="17"/>
+      <c r="F43" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G43" s="20"/>
       <c r="H43" s="2"/>
     </row>
@@ -6738,7 +6758,9 @@
       <c r="E44" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F44" s="17"/>
+      <c r="F44" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G44" s="20">
         <v>2</v>
       </c>
@@ -6760,7 +6782,9 @@
       <c r="E45" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F45" s="17"/>
+      <c r="F45" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G45" s="20">
         <v>3</v>
       </c>
@@ -6782,7 +6806,9 @@
       <c r="E46" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="17"/>
+      <c r="F46" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G46" s="20"/>
       <c r="H46" s="2"/>
     </row>
@@ -6802,7 +6828,9 @@
       <c r="E47" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F47" s="17"/>
+      <c r="F47" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G47" s="20"/>
       <c r="H47" s="2"/>
     </row>
@@ -6822,7 +6850,9 @@
       <c r="E48" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F48" s="17"/>
+      <c r="F48" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G48" s="20"/>
       <c r="H48" s="2"/>
     </row>
@@ -6842,7 +6872,9 @@
       <c r="E49" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F49" s="17"/>
+      <c r="F49" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G49" s="20"/>
       <c r="H49" s="2"/>
     </row>
@@ -6862,7 +6894,9 @@
       <c r="E50" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F50" s="17"/>
+      <c r="F50" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G50" s="20"/>
       <c r="H50" s="2"/>
     </row>
@@ -6882,7 +6916,9 @@
       <c r="E51" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F51" s="17"/>
+      <c r="F51" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G51" s="20"/>
       <c r="H51" s="2"/>
     </row>
@@ -6902,11 +6938,13 @@
       <c r="E52" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="17"/>
+      <c r="F52" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G52" s="20"/>
       <c r="H52" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="33.75">
       <c r="A53" s="15">
         <v>51</v>
       </c>
@@ -6922,11 +6960,13 @@
       <c r="E53" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F53" s="17"/>
+      <c r="F53" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G53" s="20"/>
       <c r="H53" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="33.75">
       <c r="A54" s="15">
         <v>52</v>
       </c>
@@ -6942,11 +6982,13 @@
       <c r="E54" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F54" s="17"/>
+      <c r="F54" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G54" s="20"/>
       <c r="H54" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="33.75">
       <c r="A55" s="15">
         <v>53</v>
       </c>
@@ -6962,11 +7004,13 @@
       <c r="E55" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F55" s="17"/>
+      <c r="F55" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G55" s="20"/>
       <c r="H55" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="33.75">
       <c r="A56" s="15">
         <v>54</v>
       </c>
@@ -6982,11 +7026,13 @@
       <c r="E56" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F56" s="17"/>
+      <c r="F56" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G56" s="20"/>
       <c r="H56" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="15">
         <v>55</v>
       </c>
@@ -7002,11 +7048,13 @@
       <c r="E57" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="17"/>
+      <c r="F57" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G57" s="20"/>
       <c r="H57" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="33.75">
       <c r="A58" s="15">
         <v>56</v>
       </c>
@@ -7022,11 +7070,13 @@
       <c r="E58" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F58" s="17"/>
+      <c r="F58" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G58" s="20"/>
       <c r="H58" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="33.75">
       <c r="A59" s="15">
         <v>57</v>
       </c>
@@ -7046,7 +7096,7 @@
       <c r="G59" s="20"/>
       <c r="H59" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="33.75">
       <c r="A60" s="15">
         <v>58</v>
       </c>
@@ -7066,7 +7116,7 @@
       <c r="G60" s="20"/>
       <c r="H60" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="33.75">
       <c r="A61" s="15">
         <v>59</v>
       </c>
@@ -7086,7 +7136,7 @@
       <c r="G61" s="20"/>
       <c r="H61" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="33.75">
       <c r="A62" s="15">
         <v>60</v>
       </c>
@@ -7106,7 +7156,7 @@
       <c r="G62" s="20"/>
       <c r="H62" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="33.75">
       <c r="A63" s="15">
         <v>61</v>
       </c>
@@ -7126,7 +7176,7 @@
       <c r="G63" s="20"/>
       <c r="H63" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="33.75">
       <c r="A64" s="15">
         <v>62</v>
       </c>
@@ -7146,7 +7196,7 @@
       <c r="G64" s="20"/>
       <c r="H64" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="33.75">
       <c r="A65" s="15">
         <v>63</v>
       </c>
@@ -7168,7 +7218,7 @@
       </c>
       <c r="H65" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="33.75">
       <c r="A66" s="15">
         <v>64</v>
       </c>
@@ -7190,7 +7240,7 @@
       </c>
       <c r="H66" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="33.75">
       <c r="A67" s="15">
         <v>65</v>
       </c>

--- a/001EffortTracker/KT Plan.xlsx
+++ b/001EffortTracker/KT Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="363">
   <si>
     <t>Playwright: Web Automation Testing From Zero to Hero - Artem Bondar</t>
   </si>
@@ -1113,9 +1113,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=VYIDZ57mMy4</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -1229,7 +1226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1379,9 +1376,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1695,7 +1689,7 @@
     <col min="1" max="1" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="52" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="51" width="6.719285714285714" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="48" width="38.86214285714286" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="23" width="7.719285714285714" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="48" width="23.862142857142857" customWidth="1" bestFit="1"/>
@@ -2241,9 +2235,7 @@
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
       <c r="D30" s="49"/>
-      <c r="E30" s="51" t="s">
-        <v>363</v>
-      </c>
+      <c r="E30" s="36"/>
       <c r="F30" s="21"/>
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
@@ -2329,7 +2321,7 @@
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="48" width="12.005" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="48" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="48" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="48" width="48.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -4053,7 +4045,7 @@
         <v>282</v>
       </c>
       <c r="C80" s="45">
-        <v>35.117465277777775</v>
+        <v>36.117349537037036</v>
       </c>
       <c r="D80" s="18">
         <v>45374</v>
@@ -4076,7 +4068,7 @@
         <v>282</v>
       </c>
       <c r="C81" s="45">
-        <v>35.117465277777775</v>
+        <v>36.117349537037036</v>
       </c>
       <c r="D81" s="18">
         <v>45375</v>
@@ -4099,7 +4091,7 @@
         <v>282</v>
       </c>
       <c r="C82" s="45">
-        <v>35.117465277777775</v>
+        <v>36.117349537037036</v>
       </c>
       <c r="D82" s="18">
         <v>45376</v>
@@ -4122,7 +4114,7 @@
         <v>282</v>
       </c>
       <c r="C83" s="45">
-        <v>35.117465277777775</v>
+        <v>36.117349537037036</v>
       </c>
       <c r="D83" s="18">
         <v>45377</v>
@@ -6790,7 +6782,7 @@
       </c>
       <c r="H45" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="33.75">
       <c r="A46" s="15">
         <v>44</v>
       </c>
@@ -6812,7 +6804,7 @@
       <c r="G46" s="20"/>
       <c r="H46" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="33.75">
       <c r="A47" s="15">
         <v>45</v>
       </c>
@@ -6834,7 +6826,7 @@
       <c r="G47" s="20"/>
       <c r="H47" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="33.75">
       <c r="A48" s="15">
         <v>46</v>
       </c>
@@ -6856,7 +6848,7 @@
       <c r="G48" s="20"/>
       <c r="H48" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="33.75">
       <c r="A49" s="15">
         <v>47</v>
       </c>
@@ -6878,7 +6870,7 @@
       <c r="G49" s="20"/>
       <c r="H49" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="33.75">
       <c r="A50" s="15">
         <v>48</v>
       </c>
@@ -6900,7 +6892,7 @@
       <c r="G50" s="20"/>
       <c r="H50" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="33.75">
       <c r="A51" s="15">
         <v>49</v>
       </c>
@@ -6922,7 +6914,7 @@
       <c r="G51" s="20"/>
       <c r="H51" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="33">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="33.75">
       <c r="A52" s="15">
         <v>50</v>
       </c>
@@ -7092,7 +7084,9 @@
       <c r="E59" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F59" s="17"/>
+      <c r="F59" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G59" s="20"/>
       <c r="H59" s="2"/>
     </row>
@@ -7112,7 +7106,9 @@
       <c r="E60" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F60" s="17"/>
+      <c r="F60" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G60" s="20"/>
       <c r="H60" s="2"/>
     </row>
@@ -7132,7 +7128,9 @@
       <c r="E61" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F61" s="17"/>
+      <c r="F61" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G61" s="20"/>
       <c r="H61" s="2"/>
     </row>
@@ -7152,7 +7150,9 @@
       <c r="E62" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F62" s="17"/>
+      <c r="F62" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G62" s="20"/>
       <c r="H62" s="2"/>
     </row>
@@ -7172,7 +7172,9 @@
       <c r="E63" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F63" s="17"/>
+      <c r="F63" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G63" s="20"/>
       <c r="H63" s="2"/>
     </row>
@@ -7192,7 +7194,9 @@
       <c r="E64" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="17"/>
+      <c r="F64" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G64" s="20"/>
       <c r="H64" s="2"/>
     </row>
@@ -7212,7 +7216,9 @@
       <c r="E65" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F65" s="17"/>
+      <c r="F65" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G65" s="20">
         <v>3</v>
       </c>
@@ -7234,7 +7240,9 @@
       <c r="E66" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F66" s="17"/>
+      <c r="F66" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G66" s="20">
         <v>4</v>
       </c>
@@ -7256,7 +7264,9 @@
       <c r="E67" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F67" s="17"/>
+      <c r="F67" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G67" s="20"/>
       <c r="H67" s="2"/>
     </row>
@@ -7276,7 +7286,9 @@
       <c r="E68" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F68" s="17"/>
+      <c r="F68" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="G68" s="20"/>
       <c r="H68" s="2"/>
     </row>
